--- a/banks/BANK OF CHINA UK FINANCIALS.xlsx
+++ b/banks/BANK OF CHINA UK FINANCIALS.xlsx
@@ -1,25 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Overview" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Cash Flow Statement" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="CET1 Capital" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="CET1 Ratio" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Tier 1 Capital" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Tier 1 Ratio" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Total Capital" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Total Capital Ratio" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Total RWAs" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Leverage Ratio" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="LCR" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="NSFR" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="MREL Ratio" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance Sheet" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Profit &amp; Loss" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Statement of Changes in Equity" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flow Statement" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Asset Quality" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Capital" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Ratio" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Capital" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Ratio" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital Ratio" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total RWAs" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RWA Breakdown" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leverage Ratio" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LCR" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NSFR" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MREL Ratio" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -192,18 +197,18 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Bank of China (UK) Limited — Cash Flow Summary by Year</a:t>
+              <a:t>Bank of China (UK) Limited — Balance Sheet Summary by Year</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -235,7 +240,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -259,7 +264,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -283,7 +288,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -307,7 +312,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -350,8 +355,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -390,13 +395,583 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Bank of China (UK) Limited — Profit &amp; Loss Summary by Year</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <layout>
+        <manualLayout>
+          <layoutTarget val="inner"/>
+          <xMode val="edge"/>
+          <yMode val="edge"/>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.1"/>
+          <y val="0.14"/>
+          <w val="0.85"/>
+          <h val="0.55"/>
+        </manualLayout>
+      </layout>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!Q13</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$R$12:$V$12</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$R$13:$V$13</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!Q14</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$R$12:$V$12</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$R$14:$V$14</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!Q15</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$R$12:$V$12</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$R$15:$V$15</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="b"/>
+        <majorTickMark val="out"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>£'000</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="out"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+      <layout>
+        <manualLayout>
+          <xMode val="edge"/>
+          <yMode val="edge"/>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.02"/>
+          <y val="0.84"/>
+          <w val="0.96"/>
+          <h val="0.16"/>
+        </manualLayout>
+      </layout>
+    </legend>
+    <plotVisOnly val="0"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Bank of China (UK) Limited — Statement of Changes in Equity Summary by Year</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <layout>
+        <manualLayout>
+          <layoutTarget val="inner"/>
+          <xMode val="edge"/>
+          <yMode val="edge"/>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.1"/>
+          <y val="0.14"/>
+          <w val="0.85"/>
+          <h val="0.55"/>
+        </manualLayout>
+      </layout>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!Y19</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$Z$18:$AD$18</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$Z$19:$AD$19</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!Y20</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$Z$18:$AD$18</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$Z$20:$AD$20</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!Y21</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$Z$18:$AD$18</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$Z$21:$AD$21</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!Y22</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$Z$18:$AD$18</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$Z$22:$AD$22</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="b"/>
+        <majorTickMark val="out"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>£'000</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="out"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+      <layout>
+        <manualLayout>
+          <xMode val="edge"/>
+          <yMode val="edge"/>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.02"/>
+          <y val="0.84"/>
+          <w val="0.96"/>
+          <h val="0.16"/>
+        </manualLayout>
+      </layout>
+    </legend>
+    <plotVisOnly val="0"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Bank of China (UK) Limited — Cash Flow Summary by Year</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <layout>
+        <manualLayout>
+          <layoutTarget val="inner"/>
+          <xMode val="edge"/>
+          <yMode val="edge"/>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.1"/>
+          <y val="0.14"/>
+          <w val="0.85"/>
+          <h val="0.55"/>
+        </manualLayout>
+      </layout>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!AG26</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$AH$25:$AL$25</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$AH$26:$AL$26</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!AG27</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$AH$25:$AL$25</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$AH$27:$AL$27</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!AG28</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$AH$25:$AL$25</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$AH$28:$AL$28</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!AG29</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$AH$25:$AL$25</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$AH$29:$AL$29</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="b"/>
+        <majorTickMark val="out"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>£'000</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="out"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+      <layout>
+        <manualLayout>
+          <xMode val="edge"/>
+          <yMode val="edge"/>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.02"/>
+          <y val="0.84"/>
+          <w val="0.96"/>
+          <h val="0.16"/>
+        </manualLayout>
+      </layout>
+    </legend>
+    <plotVisOnly val="0"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -428,30 +1003,30 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Overview'!Q6</f>
+              <f>'Overview'!AO6</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$R$5:$V$5</f>
+              <f>'Overview'!$AP$5:$AT$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$R$6:$V$6</f>
+              <f>'Overview'!$AP$6:$AT$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -461,30 +1036,30 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Overview'!Q7</f>
+              <f>'Overview'!AO7</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$R$5:$V$5</f>
+              <f>'Overview'!$AP$5:$AT$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$R$7:$V$7</f>
+              <f>'Overview'!$AP$7:$AT$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -494,30 +1069,30 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'Overview'!Q8</f>
+              <f>'Overview'!AO8</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$R$5:$V$5</f>
+              <f>'Overview'!$AP$5:$AT$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$R$8:$V$8</f>
+              <f>'Overview'!$AP$8:$AT$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -527,30 +1102,30 @@
           <order val="3"/>
           <tx>
             <strRef>
-              <f>'Overview'!Q9</f>
+              <f>'Overview'!AO9</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$R$5:$V$5</f>
+              <f>'Overview'!$AP$5:$AT$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$R$9:$V$9</f>
+              <f>'Overview'!$AP$9:$AT$9</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -560,30 +1135,30 @@
           <order val="4"/>
           <tx>
             <strRef>
-              <f>'Overview'!Q10</f>
+              <f>'Overview'!AO10</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$R$5:$V$5</f>
+              <f>'Overview'!$AP$5:$AT$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$R$10:$V$10</f>
+              <f>'Overview'!$AP$10:$AT$10</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -593,30 +1168,30 @@
           <order val="5"/>
           <tx>
             <strRef>
-              <f>'Overview'!Q11</f>
+              <f>'Overview'!AO11</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$R$5:$V$5</f>
+              <f>'Overview'!$AP$5:$AT$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$R$11:$V$11</f>
+              <f>'Overview'!$AP$11:$AT$11</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -648,8 +1223,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -688,12 +1263,12 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>22</row>
+      <row>42</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="8640000" cy="4680000"/>
@@ -703,9 +1278,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -715,19 +1290,85 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>44</row>
+      <row>64</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="8640000" cy="5760000"/>
+    <ext cx="8640000" cy="4680000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId2"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>86</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8640000" cy="4680000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="3" name="Chart 3"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>108</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8640000" cy="4680000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="4" name="Chart 4"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>130</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8640000" cy="5760000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="5" name="Chart 5"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1025,7 +1666,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V20"/>
+  <dimension ref="A1:AT40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1048,6 +1689,30 @@
     <col hidden="1" width="13" customWidth="1" min="20" max="20"/>
     <col hidden="1" width="13" customWidth="1" min="21" max="21"/>
     <col hidden="1" width="13" customWidth="1" min="22" max="22"/>
+    <col hidden="1" width="13" customWidth="1" min="23" max="23"/>
+    <col hidden="1" width="13" customWidth="1" min="24" max="24"/>
+    <col hidden="1" width="13" customWidth="1" min="25" max="25"/>
+    <col hidden="1" width="13" customWidth="1" min="26" max="26"/>
+    <col hidden="1" width="13" customWidth="1" min="27" max="27"/>
+    <col hidden="1" width="13" customWidth="1" min="28" max="28"/>
+    <col hidden="1" width="13" customWidth="1" min="29" max="29"/>
+    <col hidden="1" width="13" customWidth="1" min="30" max="30"/>
+    <col hidden="1" width="13" customWidth="1" min="31" max="31"/>
+    <col hidden="1" width="13" customWidth="1" min="32" max="32"/>
+    <col hidden="1" width="13" customWidth="1" min="33" max="33"/>
+    <col hidden="1" width="13" customWidth="1" min="34" max="34"/>
+    <col hidden="1" width="13" customWidth="1" min="35" max="35"/>
+    <col hidden="1" width="13" customWidth="1" min="36" max="36"/>
+    <col hidden="1" width="13" customWidth="1" min="37" max="37"/>
+    <col hidden="1" width="13" customWidth="1" min="38" max="38"/>
+    <col hidden="1" width="13" customWidth="1" min="39" max="39"/>
+    <col hidden="1" width="13" customWidth="1" min="40" max="40"/>
+    <col hidden="1" width="13" customWidth="1" min="41" max="41"/>
+    <col hidden="1" width="13" customWidth="1" min="42" max="42"/>
+    <col hidden="1" width="13" customWidth="1" min="43" max="43"/>
+    <col hidden="1" width="13" customWidth="1" min="44" max="44"/>
+    <col hidden="1" width="13" customWidth="1" min="45" max="45"/>
+    <col hidden="1" width="13" customWidth="1" min="46" max="46"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1060,14 +1725,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Summary of cash flow and Pillar 3 disclosures across all years covered in this workbook</t>
+          <t>Headline balance sheet, profit &amp; loss, cash flow and Pillar 3 figures across all years covered in this workbook - how the bank is using its money and the risk it is taking with it</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Cash Flow Summary (£'000)</t>
+          <t>Balance Sheet Summary (£'000)</t>
         </is>
       </c>
     </row>
@@ -1127,27 +1792,27 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="AP5" t="inlineStr">
         <is>
           <t>FY2021</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="AQ5" t="inlineStr">
         <is>
           <t>FY2022</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="AR5" t="inlineStr">
         <is>
           <t>FY2023</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="AS5" t="inlineStr">
         <is>
           <t>FY2024</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AT5" t="inlineStr">
         <is>
           <t>FY2025</t>
         </is>
@@ -1156,297 +1821,297 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Net cash generated from operating activities</t>
+          <t>Total assets</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>111252</v>
+        <v>2274441</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>405091</v>
+        <v>2323319</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>233292</v>
+        <v>2079373</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>22570</v>
+        <v>2290593</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>304294</v>
+        <v>2151180</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Net cash generated from operating activities</t>
+          <t>Total assets</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>304294</v>
+        <v>2151180</v>
       </c>
       <c r="K6" t="n">
-        <v>22570</v>
+        <v>2290593</v>
       </c>
       <c r="L6" t="n">
-        <v>233292</v>
+        <v>2079373</v>
       </c>
       <c r="M6" t="n">
-        <v>405091</v>
+        <v>2323319</v>
       </c>
       <c r="N6" t="n">
-        <v>111252</v>
-      </c>
-      <c r="Q6" t="inlineStr">
+        <v>2274441</v>
+      </c>
+      <c r="AO6" t="inlineStr">
         <is>
           <t>CET1 Ratio</t>
         </is>
       </c>
-      <c r="R6" t="n">
+      <c r="AP6" t="n">
         <v>24.6</v>
       </c>
-      <c r="S6" t="n">
+      <c r="AQ6" t="n">
         <v>23.4</v>
       </c>
-      <c r="T6" t="n">
+      <c r="AR6" t="n">
         <v>26.8</v>
       </c>
-      <c r="U6" t="n">
+      <c r="AS6" t="n">
         <v>24.8</v>
       </c>
-      <c r="V6" t="n">
+      <c r="AT6" t="n">
         <v>27.2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Net cash from/(used in) investing activities</t>
+          <t>Loans and advances to customers</t>
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>-2623</v>
+        <v>810985</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>-25826</v>
+        <v>941507</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>-74896</v>
+        <v>990763</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>-47511</v>
+        <v>1122459</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>-1147</v>
+        <v>1194653</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Net cash from/(used in) investing activities</t>
+          <t>Loans and advances to customers</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>-1147</v>
+        <v>1194653</v>
       </c>
       <c r="K7" t="n">
-        <v>-47511</v>
+        <v>1122459</v>
       </c>
       <c r="L7" t="n">
-        <v>-74896</v>
+        <v>990763</v>
       </c>
       <c r="M7" t="n">
-        <v>-25826</v>
+        <v>941507</v>
       </c>
       <c r="N7" t="n">
-        <v>-2623</v>
-      </c>
-      <c r="Q7" t="inlineStr">
+        <v>810985</v>
+      </c>
+      <c r="AO7" t="inlineStr">
         <is>
           <t>Tier 1 Ratio</t>
         </is>
       </c>
-      <c r="R7" t="n">
+      <c r="AP7" t="n">
         <v>24.6</v>
       </c>
-      <c r="S7" t="n">
+      <c r="AQ7" t="n">
         <v>28.5</v>
       </c>
-      <c r="T7" t="n">
+      <c r="AR7" t="n">
         <v>32.7</v>
       </c>
-      <c r="U7" t="n">
+      <c r="AS7" t="n">
         <v>30.2</v>
       </c>
-      <c r="V7" t="n">
+      <c r="AT7" t="n">
         <v>33.2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Net cash used in financing activities</t>
+          <t>Deposits from customers</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>-84086</v>
+        <v>1304816</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>-103953</v>
+        <v>1355529</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>-71862</v>
+        <v>1223068</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>-33536</v>
+        <v>1291150</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>-68393</v>
+        <v>1333523</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Net cash used in financing activities</t>
+          <t>Deposits from customers</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>-68393</v>
+        <v>1333523</v>
       </c>
       <c r="K8" t="n">
-        <v>-33536</v>
+        <v>1291150</v>
       </c>
       <c r="L8" t="n">
-        <v>-71862</v>
+        <v>1223068</v>
       </c>
       <c r="M8" t="n">
-        <v>-103953</v>
+        <v>1355529</v>
       </c>
       <c r="N8" t="n">
-        <v>-84086</v>
-      </c>
-      <c r="Q8" t="inlineStr">
+        <v>1304816</v>
+      </c>
+      <c r="AO8" t="inlineStr">
         <is>
           <t>Total Capital Ratio</t>
         </is>
       </c>
-      <c r="R8" t="n">
+      <c r="AP8" t="n">
         <v>29.9</v>
       </c>
-      <c r="S8" t="n">
+      <c r="AQ8" t="n">
         <v>28.5</v>
       </c>
-      <c r="T8" t="n">
+      <c r="AR8" t="n">
         <v>32.7</v>
       </c>
-      <c r="U8" t="n">
+      <c r="AS8" t="n">
         <v>30.2</v>
       </c>
-      <c r="V8" t="n">
+      <c r="AT8" t="n">
         <v>33.2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents at end of period</t>
+          <t>Total shareholders' equity</t>
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>1073402</v>
+        <v>399013</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>1048859</v>
+        <v>413744</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>773547</v>
+        <v>433289</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>657656</v>
+        <v>401893</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>716133</v>
+        <v>306776</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents at end of period</t>
+          <t>Total shareholders' equity</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>716133</v>
+        <v>306776</v>
       </c>
       <c r="K9" t="n">
-        <v>657656</v>
+        <v>401893</v>
       </c>
       <c r="L9" t="n">
-        <v>773547</v>
+        <v>433289</v>
       </c>
       <c r="M9" t="n">
-        <v>1048859</v>
+        <v>413744</v>
       </c>
       <c r="N9" t="n">
-        <v>1073402</v>
-      </c>
-      <c r="Q9" t="inlineStr">
+        <v>399013</v>
+      </c>
+      <c r="AO9" t="inlineStr">
         <is>
           <t>Leverage Ratio</t>
         </is>
       </c>
-      <c r="R9" t="n">
+      <c r="AP9" t="n">
         <v>11.3</v>
       </c>
-      <c r="S9" t="n">
+      <c r="AQ9" t="n">
         <v>18.5</v>
       </c>
-      <c r="T9" t="n">
+      <c r="AR9" t="n">
         <v>22.7</v>
       </c>
-      <c r="U9" t="n">
+      <c r="AS9" t="n">
         <v>22.9</v>
       </c>
-      <c r="V9" t="n">
+      <c r="AT9" t="n">
         <v>24.4</v>
       </c>
     </row>
     <row r="10">
-      <c r="Q10" t="inlineStr">
+      <c r="AO10" t="inlineStr">
         <is>
           <t>LCR</t>
         </is>
       </c>
-      <c r="R10" t="n">
+      <c r="AP10" t="n">
         <v>179</v>
       </c>
-      <c r="S10" t="n">
+      <c r="AQ10" t="n">
         <v>182</v>
       </c>
-      <c r="T10" t="n">
+      <c r="AR10" t="n">
         <v>387.3</v>
       </c>
-      <c r="U10" t="n">
+      <c r="AS10" t="n">
         <v>372.5</v>
       </c>
-      <c r="V10" t="n">
+      <c r="AT10" t="n">
         <v>324.1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Pillar 3 Key Metrics</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
+          <t>Profit &amp; Loss Summary (£'000)</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
         <is>
           <t>NSFR</t>
         </is>
       </c>
-      <c r="R11" t="n">
+      <c r="AP11" t="n">
         <v>151.3</v>
       </c>
-      <c r="S11" t="n">
+      <c r="AQ11" t="n">
         <v>121</v>
       </c>
-      <c r="T11" t="n">
+      <c r="AR11" t="n">
         <v>134.5</v>
       </c>
-      <c r="U11" t="n">
+      <c r="AS11" t="n">
         <v>216.5</v>
       </c>
-      <c r="V11" t="n">
+      <c r="AT11" t="n">
         <v>194.4</v>
       </c>
     </row>
@@ -1481,201 +2146,855 @@
           <t>FY2021</t>
         </is>
       </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Total income</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>188290</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>187263</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>206185</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>150380</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>124048</v>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Total income</t>
+        </is>
+      </c>
+      <c r="R13" t="n">
+        <v>124048</v>
+      </c>
+      <c r="S13" t="n">
+        <v>150380</v>
+      </c>
+      <c r="T13" t="n">
+        <v>206185</v>
+      </c>
+      <c r="U13" t="n">
+        <v>187263</v>
+      </c>
+      <c r="V13" t="n">
+        <v>188290</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Staff costs</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>-86079</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-72194</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-68058</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-59208</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-50154</v>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>Staff costs</t>
+        </is>
+      </c>
+      <c r="R14" t="n">
+        <v>-50154</v>
+      </c>
+      <c r="S14" t="n">
+        <v>-59208</v>
+      </c>
+      <c r="T14" t="n">
+        <v>-68058</v>
+      </c>
+      <c r="U14" t="n">
+        <v>-72194</v>
+      </c>
+      <c r="V14" t="n">
+        <v>-86079</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Profit for the year</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>68931</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>83917</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>103213</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>68564</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>31478</v>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>Profit for the year</t>
+        </is>
+      </c>
+      <c r="R15" t="n">
+        <v>31478</v>
+      </c>
+      <c r="S15" t="n">
+        <v>68564</v>
+      </c>
+      <c r="T15" t="n">
+        <v>103213</v>
+      </c>
+      <c r="U15" t="n">
+        <v>83917</v>
+      </c>
+      <c r="V15" t="n">
+        <v>68931</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Statement of Changes in Equity Summary (£'000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Opening equity</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>413744</v>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>433289</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>401893</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>306776</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>342164</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Opening equity</t>
+        </is>
+      </c>
+      <c r="Z19" t="n">
+        <v>342164</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>306776</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>401893</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>433289</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>413744</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Total comprehensive income</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>69011</v>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>83917</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>103211</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>68576</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>31612</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>Total comprehensive income</t>
+        </is>
+      </c>
+      <c r="Z20" t="n">
+        <v>31612</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>68576</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>103211</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>83917</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>69011</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Other movements, net (AT1 issued / dividends)</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>-83662</v>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>-103462</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>-71815</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>26541</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>-67000</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>Other movements, net (AT1 issued / dividends)</t>
+        </is>
+      </c>
+      <c r="Z21" t="n">
+        <v>-67000</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>26541</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>-71815</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>-103462</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>-83662</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Closing equity</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>399013</v>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>413744</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>433289</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>401893</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>306776</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>Closing equity</t>
+        </is>
+      </c>
+      <c r="Z22" t="n">
+        <v>306776</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>401893</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>433289</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>413744</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>399013</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Cash Flow Summary (£'000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="AL25" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Net cash generated from operating activities</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>111252</v>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>405091</v>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>233292</v>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>22570</v>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>304294</v>
+      </c>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>Net cash generated from operating activities</t>
+        </is>
+      </c>
+      <c r="AH26" t="n">
+        <v>304294</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>22570</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>233292</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>405091</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>111252</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Net cash from/(used in) investing activities</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>-2623</v>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>-25826</v>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>-74896</v>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>-47511</v>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>-1147</v>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>Net cash from/(used in) investing activities</t>
+        </is>
+      </c>
+      <c r="AH27" t="n">
+        <v>-1147</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>-47511</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>-74896</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>-25826</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>-2623</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Net cash used in financing activities</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>-84086</v>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>-103953</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>-71862</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>-33536</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>-68393</v>
+      </c>
+      <c r="AG28" t="inlineStr">
+        <is>
+          <t>Net cash used in financing activities</t>
+        </is>
+      </c>
+      <c r="AH28" t="n">
+        <v>-68393</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>-33536</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>-71862</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>-103953</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>-84086</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Cash and cash equivalents at end of period</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>1073402</v>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>1048859</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>773547</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>657656</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>716133</v>
+      </c>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>Cash and cash equivalents at end of period</t>
+        </is>
+      </c>
+      <c r="AH29" t="n">
+        <v>716133</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>657656</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>773547</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>1048859</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>1073402</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Pillar 3 Key Metrics</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
         <is>
           <t>CET1 Ratio</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B33" s="6" t="inlineStr">
         <is>
           <t>27.2%</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C33" s="6" t="inlineStr">
         <is>
           <t>24.8%</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D33" s="6" t="inlineStr">
         <is>
           <t>26.8%</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="E33" s="6" t="inlineStr">
         <is>
           <t>23.4%</t>
         </is>
       </c>
-      <c r="F13" s="6" t="inlineStr">
+      <c r="F33" s="6" t="inlineStr">
         <is>
           <t>24.6%</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
         <is>
           <t>Tier 1 Ratio</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B34" s="6" t="inlineStr">
         <is>
           <t>33.2%</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C34" s="6" t="inlineStr">
         <is>
           <t>30.2%</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="D34" s="6" t="inlineStr">
         <is>
           <t>32.7%</t>
         </is>
       </c>
-      <c r="E14" s="6" t="inlineStr">
+      <c r="E34" s="6" t="inlineStr">
         <is>
           <t>28.5%</t>
         </is>
       </c>
-      <c r="F14" s="6" t="inlineStr">
+      <c r="F34" s="6" t="inlineStr">
         <is>
           <t>24.6%</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
         <is>
           <t>Total Capital Ratio</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B35" s="6" t="inlineStr">
         <is>
           <t>33.2%</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C35" s="6" t="inlineStr">
         <is>
           <t>30.2%</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="D35" s="6" t="inlineStr">
         <is>
           <t>32.7%</t>
         </is>
       </c>
-      <c r="E15" s="6" t="inlineStr">
+      <c r="E35" s="6" t="inlineStr">
         <is>
           <t>28.5%</t>
         </is>
       </c>
-      <c r="F15" s="6" t="inlineStr">
+      <c r="F35" s="6" t="inlineStr">
         <is>
           <t>29.9%</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
         <is>
           <t>Leverage Ratio</t>
         </is>
       </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B36" s="6" t="inlineStr">
         <is>
           <t>24.4%</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C36" s="6" t="inlineStr">
         <is>
           <t>22.9%</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="D36" s="6" t="inlineStr">
         <is>
           <t>22.7%</t>
         </is>
       </c>
-      <c r="E16" s="6" t="inlineStr">
+      <c r="E36" s="6" t="inlineStr">
         <is>
           <t>18.5%</t>
         </is>
       </c>
-      <c r="F16" s="6" t="inlineStr">
+      <c r="F36" s="6" t="inlineStr">
         <is>
           <t>11.3%</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
         <is>
           <t>LCR</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B37" s="6" t="inlineStr">
         <is>
           <t>324.1%</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C37" s="6" t="inlineStr">
         <is>
           <t>372.5%</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D37" s="6" t="inlineStr">
         <is>
           <t>387.3%</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr">
+      <c r="E37" s="6" t="inlineStr">
         <is>
           <t>182.0%</t>
         </is>
       </c>
-      <c r="F17" s="6" t="inlineStr">
+      <c r="F37" s="6" t="inlineStr">
         <is>
           <t>179.0%</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
         <is>
           <t>NSFR</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B38" s="6" t="inlineStr">
         <is>
           <t>194.4%</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C38" s="6" t="inlineStr">
         <is>
           <t>216.5%</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr">
+      <c r="D38" s="6" t="inlineStr">
         <is>
           <t>134.5%</t>
         </is>
       </c>
-      <c r="E18" s="6" t="inlineStr">
+      <c r="E38" s="6" t="inlineStr">
         <is>
           <t>121.0%</t>
         </is>
       </c>
-      <c r="F18" s="6" t="inlineStr">
+      <c r="F38" s="6" t="inlineStr">
         <is>
           <t>151.3%</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="45" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
+    <row r="40" ht="45" customHeight="1">
+      <c r="A40" s="7" t="inlineStr">
         <is>
           <t>Note: Figures are duplicated from the detail sheets for at-a-glance trend viewing; see each sheet's own source citation for the underlying document/page. See the Cash Flow Statement sheet's source note for a disclosed restatement gap between FY2022's and FY2023's own reports.</t>
         </is>
@@ -1683,7 +3002,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A20:F20"/>
+    <mergeCell ref="A40:F40"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -1691,6 +3010,597 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Bank of China (UK) Limited — Tier 1 Ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>% of RWA</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Tier 1 ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>33.2%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>30.2%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>32.7%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>28.5%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>24.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Note: FY2021 not separately stated as a percentage in the source; numerically equal to the stated CET1 ratio since Tier 1 capital equalled CET1 capital exactly that year (no AT1 in issue).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="170" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>Sources - Bank of China (UK) Limited Pillar 3 disclosures (UK KM1 Key Metrics template from FY2022 onward; FY2021's own document is narrative/ratio-only and predates the KM1 template), £'000 unless stated:
+FY2025 &amp; FY2024 comparative: Pillar 3 Disclosure 31 December 2025, p.15 (UK KM1) - https://pic.bankofchina.com/bocappd/uk/202607/P020260716391457618567.pdf
+FY2024 (own year) &amp; FY2023 comparative: Pillar 3 Disclosures 31 December 2024, p.16 (UK KM1) - https://www.bankofchina.com/uk/aboutus/ab5/202507/P020250718380587744231.pdf
+FY2023 (own year) &amp; FY2022 comparative: Pillar 3 disclosures 31 December 2023, p.14 (UK KM1) - https://www.bankofchina.com/uk/aboutus/ab5/202410/P020241008402737321677.pdf
+FY2022 (own year) &amp; FY2021 comparative: Pillar 3 Disclosures 2022, p.14 (UK KM1) - https://www.bankofchina.com/uk/aboutus/ab5/202310/P020231026347190320350.pdf
+FY2021 (own year, narrative/ratio-only - no KM1 template yet): Pillar 3 Disclosures 2021, p.12-14, 24 - https://www.bankofchina.com/uk/aboutus/ab5/202303/P020230315381669571541.pdf
+FY2021 note: the Bank's own FY2021 Pillar 3 document states CET1/Total Capital as rounded £275m/£335m and gives no £-breakdown for leverage exposure, LCR HQLA/outflow, or NSFR (NSFR was not yet a formal disclosure). The precise FY2021 figures used on those sheets (CET1/Tier 1 £275,164k, Total Capital £335,164k, leverage exposure £2,431,869k, LCR HQLA £527,697k/outflow £294,774k, NSFR £1,438,026k/£950,742k) are taken from the FY2022 Pillar 3 document's FY2021 comparative column instead, since it is the more complete disclosure - all overlapping ratios (CET1 24.6%, Total Capital 29.9%, Leverage 11.3%, LCR 179.0%) match the FY2021 document's own narrative figures exactly.
+Entity note: Bank of China (UK) Limited (company 06193060, FRN 467410) is a wholly-owned UK subsidiary of Bank of China Limited (state-owned). It does not take the FRS 101/102 cash-flow-statement exemption - a full Statement of Cash Flows is published every year. All figures are the Bank's own solo entity basis throughout.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A7:F7"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Bank of China (UK) Limited — Total Capital</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>£'000</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Total regulatory capital</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>334521</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>334294</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>335056</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>335000</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>335164</v>
+      </c>
+    </row>
+    <row r="6" ht="170" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Sources - Bank of China (UK) Limited Pillar 3 disclosures (UK KM1 Key Metrics template from FY2022 onward; FY2021's own document is narrative/ratio-only and predates the KM1 template), £'000 unless stated:
+FY2025 &amp; FY2024 comparative: Pillar 3 Disclosure 31 December 2025, p.15 (UK KM1) - https://pic.bankofchina.com/bocappd/uk/202607/P020260716391457618567.pdf
+FY2024 (own year) &amp; FY2023 comparative: Pillar 3 Disclosures 31 December 2024, p.16 (UK KM1) - https://www.bankofchina.com/uk/aboutus/ab5/202507/P020250718380587744231.pdf
+FY2023 (own year) &amp; FY2022 comparative: Pillar 3 disclosures 31 December 2023, p.14 (UK KM1) - https://www.bankofchina.com/uk/aboutus/ab5/202410/P020241008402737321677.pdf
+FY2022 (own year) &amp; FY2021 comparative: Pillar 3 Disclosures 2022, p.14 (UK KM1) - https://www.bankofchina.com/uk/aboutus/ab5/202310/P020231026347190320350.pdf
+FY2021 (own year, narrative/ratio-only - no KM1 template yet): Pillar 3 Disclosures 2021, p.12-14, 24 - https://www.bankofchina.com/uk/aboutus/ab5/202303/P020230315381669571541.pdf
+FY2021 note: the Bank's own FY2021 Pillar 3 document states CET1/Total Capital as rounded £275m/£335m and gives no £-breakdown for leverage exposure, LCR HQLA/outflow, or NSFR (NSFR was not yet a formal disclosure). The precise FY2021 figures used on those sheets (CET1/Tier 1 £275,164k, Total Capital £335,164k, leverage exposure £2,431,869k, LCR HQLA £527,697k/outflow £294,774k, NSFR £1,438,026k/£950,742k) are taken from the FY2022 Pillar 3 document's FY2021 comparative column instead, since it is the more complete disclosure - all overlapping ratios (CET1 24.6%, Total Capital 29.9%, Leverage 11.3%, LCR 179.0%) match the FY2021 document's own narrative figures exactly.
+Entity note: Bank of China (UK) Limited (company 06193060, FRN 467410) is a wholly-owned UK subsidiary of Bank of China Limited (state-owned). It does not take the FRS 101/102 cash-flow-statement exemption - a full Statement of Cash Flows is published every year. All figures are the Bank's own solo entity basis throughout.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A6:F6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Bank of China (UK) Limited — Total Capital Ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>% of RWA</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Total capital ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>33.2%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>30.2%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>32.7%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>28.5%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>29.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="170" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Sources - Bank of China (UK) Limited Pillar 3 disclosures (UK KM1 Key Metrics template from FY2022 onward; FY2021's own document is narrative/ratio-only and predates the KM1 template), £'000 unless stated:
+FY2025 &amp; FY2024 comparative: Pillar 3 Disclosure 31 December 2025, p.15 (UK KM1) - https://pic.bankofchina.com/bocappd/uk/202607/P020260716391457618567.pdf
+FY2024 (own year) &amp; FY2023 comparative: Pillar 3 Disclosures 31 December 2024, p.16 (UK KM1) - https://www.bankofchina.com/uk/aboutus/ab5/202507/P020250718380587744231.pdf
+FY2023 (own year) &amp; FY2022 comparative: Pillar 3 disclosures 31 December 2023, p.14 (UK KM1) - https://www.bankofchina.com/uk/aboutus/ab5/202410/P020241008402737321677.pdf
+FY2022 (own year) &amp; FY2021 comparative: Pillar 3 Disclosures 2022, p.14 (UK KM1) - https://www.bankofchina.com/uk/aboutus/ab5/202310/P020231026347190320350.pdf
+FY2021 (own year, narrative/ratio-only - no KM1 template yet): Pillar 3 Disclosures 2021, p.12-14, 24 - https://www.bankofchina.com/uk/aboutus/ab5/202303/P020230315381669571541.pdf
+FY2021 note: the Bank's own FY2021 Pillar 3 document states CET1/Total Capital as rounded £275m/£335m and gives no £-breakdown for leverage exposure, LCR HQLA/outflow, or NSFR (NSFR was not yet a formal disclosure). The precise FY2021 figures used on those sheets (CET1/Tier 1 £275,164k, Total Capital £335,164k, leverage exposure £2,431,869k, LCR HQLA £527,697k/outflow £294,774k, NSFR £1,438,026k/£950,742k) are taken from the FY2022 Pillar 3 document's FY2021 comparative column instead, since it is the more complete disclosure - all overlapping ratios (CET1 24.6%, Total Capital 29.9%, Leverage 11.3%, LCR 179.0%) match the FY2021 document's own narrative figures exactly.
+Entity note: Bank of China (UK) Limited (company 06193060, FRN 467410) is a wholly-owned UK subsidiary of Bank of China Limited (state-owned). It does not take the FRS 101/102 cash-flow-statement exemption - a full Statement of Cash Flows is published every year. All figures are the Bank's own solo entity basis throughout.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A6:F6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Bank of China (UK) Limited — Total RWAs</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>£'000</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Total risk-weighted assets (RWA)</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>1008110</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>1106898</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>1024452</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>1176625</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>1119380</v>
+      </c>
+    </row>
+    <row r="6" ht="170" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Sources - Bank of China (UK) Limited Pillar 3 disclosures (UK KM1 Key Metrics template from FY2022 onward; FY2021's own document is narrative/ratio-only and predates the KM1 template), £'000 unless stated:
+FY2025 &amp; FY2024 comparative: Pillar 3 Disclosure 31 December 2025, p.15 (UK KM1) - https://pic.bankofchina.com/bocappd/uk/202607/P020260716391457618567.pdf
+FY2024 (own year) &amp; FY2023 comparative: Pillar 3 Disclosures 31 December 2024, p.16 (UK KM1) - https://www.bankofchina.com/uk/aboutus/ab5/202507/P020250718380587744231.pdf
+FY2023 (own year) &amp; FY2022 comparative: Pillar 3 disclosures 31 December 2023, p.14 (UK KM1) - https://www.bankofchina.com/uk/aboutus/ab5/202410/P020241008402737321677.pdf
+FY2022 (own year) &amp; FY2021 comparative: Pillar 3 Disclosures 2022, p.14 (UK KM1) - https://www.bankofchina.com/uk/aboutus/ab5/202310/P020231026347190320350.pdf
+FY2021 (own year, narrative/ratio-only - no KM1 template yet): Pillar 3 Disclosures 2021, p.12-14, 24 - https://www.bankofchina.com/uk/aboutus/ab5/202303/P020230315381669571541.pdf
+FY2021 note: the Bank's own FY2021 Pillar 3 document states CET1/Total Capital as rounded £275m/£335m and gives no £-breakdown for leverage exposure, LCR HQLA/outflow, or NSFR (NSFR was not yet a formal disclosure). The precise FY2021 figures used on those sheets (CET1/Tier 1 £275,164k, Total Capital £335,164k, leverage exposure £2,431,869k, LCR HQLA £527,697k/outflow £294,774k, NSFR £1,438,026k/£950,742k) are taken from the FY2022 Pillar 3 document's FY2021 comparative column instead, since it is the more complete disclosure - all overlapping ratios (CET1 24.6%, Total Capital 29.9%, Leverage 11.3%, LCR 179.0%) match the FY2021 document's own narrative figures exactly.
+Entity note: Bank of China (UK) Limited (company 06193060, FRN 467410) is a wholly-owned UK subsidiary of Bank of China Limited (state-owned). It does not take the FRS 101/102 cash-flow-statement exemption - a full Statement of Cash Flows is published every year. All figures are the Bank's own solo entity basis throughout.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A6:F6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="58" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Bank of China (UK) Limited — RWA Breakdown</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Bank of China (UK) Limited (solo entity basis), £'000</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025 (£'000)</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024 (£'000)</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023 (£'000)</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022 (£'000)</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021 (£'000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed — category breakdown</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Total risk exposure amount</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>1008110</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>1106898</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>1024452</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>1176625</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>1119380</v>
+      </c>
+    </row>
+    <row r="7" ht="170" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>Sources - Bank of China (UK) Limited's UK KM1 Key Metrics tables (same 5 Pillar 3 documents as the Total RWAs sheet):
+FY2025 &amp; FY2024 comparative: Pillar 3 Disclosure 31 December 2025, p.15 - https://pic.bankofchina.com/bocappd/uk/202607/P020260716391457618567.pdf
+FY2023-FY2021: see p3_sources() citations on the Total RWAs sheet.
+NOT DISCLOSED (category breakdown): none of the 5 Pillar 3 documents contains a UK OV1 'Overview of risk weighted exposure amounts' table breaking RWA down by risk category (credit/market/operational/CVA) - confirmed by reading the FY2025 document's own table of contents and KM1 template in full. Only the single aggregate Total RWA figure exists for every year (see the Total RWAs sheet, which this sheet's Total row ties out to exactly).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A7:F7"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1837,7 +3747,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1998,7 +3908,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2167,7 +4077,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2294,6 +4204,1925 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="68" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Bank of China (UK) Limited — Statement of Financial Position</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Bank of China (UK) Limited (solo entity basis), £'000</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025 (£'000)</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024 (£'000)</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023 (£'000)</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022 (£'000)</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021 (£'000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Assets</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Cash and balances at central banks</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>982512</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>975201</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>687070</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>657656</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>716133</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Government bonds</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>142529</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>144495</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>118328</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>44264</v>
+      </c>
+      <c r="F6" s="6" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Loans and advances to banks</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>90733</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>73658</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>86477</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>29357</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>69065</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Loans and advances to customers</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>810985</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>941507</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>990763</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>1122459</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>1194653</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Derivative financial instruments</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>2504</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>4667</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>5506</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>7702</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Prepayments, accrued income and other assets</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>156554</v>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>138246</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>130581</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>351967</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>87868</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Financial assets at fair value through profit and loss</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>71293</v>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>30150</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>47445</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>60514</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>64659</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Current tax asset</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>4582</v>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>2934</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>637</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>2351</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>5979</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Deferred tax assets</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n">
+        <v>289</v>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>406</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>359</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>1280</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>1283</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Property, plant and equipment</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n">
+        <v>11573</v>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>11419</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>11902</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>12769</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>11167</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>Intangible assets</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n">
+        <v>887</v>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>636</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>305</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>274</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Total assets</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>2274441</v>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>2323319</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>2079373</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>2290593</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>2151180</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Liabilities</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n"/>
+      <c r="C17" s="6" t="n"/>
+      <c r="D17" s="6" t="n"/>
+      <c r="E17" s="6" t="n"/>
+      <c r="F17" s="6" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Deposits from banks</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n">
+        <v>511961</v>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>493256</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>369590</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>539387</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>396254</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>Deposits from customers</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n">
+        <v>1304816</v>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>1355529</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>1223068</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>1291150</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>1333523</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Derivative financial instruments</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n">
+        <v>289</v>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>5280</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>Other liabilities</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n">
+        <v>39574</v>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>37473</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>38352</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>50379</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>43571</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>Accruals and deferred income</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n">
+        <v>18650</v>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>23257</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>15017</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>7720</v>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>5657</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>Impairment provision on off balance sheet products</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n">
+        <v>138</v>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>58</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>54</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>51</v>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>Subordinated liabilities</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="n"/>
+      <c r="C24" s="6" t="n"/>
+      <c r="D24" s="6" t="n"/>
+      <c r="E24" s="6" t="n"/>
+      <c r="F24" s="6" t="n">
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Total liabilities</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>1875428</v>
+      </c>
+      <c r="C25" s="5" t="n">
+        <v>1909575</v>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>1646084</v>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>1888700</v>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>1844404</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="n"/>
+      <c r="C26" s="6" t="n"/>
+      <c r="D26" s="6" t="n"/>
+      <c r="E26" s="6" t="n"/>
+      <c r="F26" s="6" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>Authorised and called up share capital</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n">
+        <v>250000</v>
+      </c>
+      <c r="C27" s="6" t="n">
+        <v>250000</v>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>250000</v>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>250000</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>250000</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>Other equity instruments (Additional Tier 1)</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n">
+        <v>60000</v>
+      </c>
+      <c r="C28" s="6" t="n">
+        <v>60000</v>
+      </c>
+      <c r="D28" s="6" t="n">
+        <v>60000</v>
+      </c>
+      <c r="E28" s="6" t="n">
+        <v>60000</v>
+      </c>
+      <c r="F28" s="6" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>Retained earnings</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n">
+        <v>89013</v>
+      </c>
+      <c r="C29" s="6" t="n">
+        <v>103744</v>
+      </c>
+      <c r="D29" s="6" t="n">
+        <v>123289</v>
+      </c>
+      <c r="E29" s="6" t="n">
+        <v>91893</v>
+      </c>
+      <c r="F29" s="6" t="n">
+        <v>56776</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>Total shareholders' equity</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>399013</v>
+      </c>
+      <c r="C30" s="5" t="n">
+        <v>413744</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>433289</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>401893</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>306776</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>Total liabilities and equity</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>2274441</v>
+      </c>
+      <c r="C31" s="5" t="n">
+        <v>2323319</v>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>2079373</v>
+      </c>
+      <c r="E31" s="5" t="n">
+        <v>2290593</v>
+      </c>
+      <c r="F31" s="5" t="n">
+        <v>2151180</v>
+      </c>
+    </row>
+    <row r="33" ht="200" customHeight="1">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>Sources - Bank of China (UK) Limited's own Statement of Financial Position (Bank/solo basis - no group accounts prepared, Companies Act 2006 s.401 exemption), £'000, each year's own originally-published report:
+FY2025: Annual Report 2025, p.49 - https://pic.bankofchina.com/bocappd/uk/202605/P020260506389809417235.pdf
+FY2024: Annual Report 2024, p.49 - https://pic.bankofchina.com/bocappd/uk/202507/P020250718380377744220.pdf (FY2024's own primary source is its own report (AR2024_URL), not AR2025's comparative column - both are identical figures (verified), no restatement.)
+FY2023: Annual Report 2023, p.50 - https://pic.bankofchina.com/bocappd/uk/202405/P020240508355110735895.pdf
+FY2022: Financial Statements 2022, p.38 - https://pic.bankofchina.com/bocappd/uk/202403/P020240315379765805794.pdf
+FY2021: Financial Statements 2021, p.35 - https://pic.bankofchina.com/bocappd/uk/202303/P020230331590070165221.pdf
+Presentation notes: 'Government bonds' only appears as its own line from FY2022 onward (no separate line existed pre-2022 - blank for FY2021, not zero). 'Subordinated liabilities' (£60,000k, FY2021) was repaid and replaced by an equal £60,000k Additional Tier 1 instrument in June 2022 - both nil/blank in the years they don't apply. 'Investment in subsidiary companies' is nil every year and omitted as a row. FY2021's own report's Statement of Changes in Equity states closing retained earnings as £56,706k, £70k less than the Balance Sheet's own £56,776k for the same date - the Balance Sheet's single 'Retained earnings' line appears to combine the SOCE's separate retained-earnings and FX-translation-reserve columns (£56,706k + £70k = £56,776k); total equity ties out exactly either way (£306,776k).
+Entity note: Bank of China (UK) Limited (company 06193060, FRN 467410) is a wholly-owned UK subsidiary of Bank of China Limited (state-owned). It does not take the FRS 101/102 cash-flow-statement exemption - a full Statement of Cash Flows is published every year. All figures are the Bank's own solo entity basis throughout.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A33:F33"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F30"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="68" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Bank of China (UK) Limited — Income Statement and Statement of Comprehensive Income</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Bank of China (UK) Limited (solo entity basis), £'000</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025 (£'000)</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024 (£'000)</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023 (£'000)</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022 (£'000)</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021 (£'000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Interest income</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>110123</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>128817</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>121217</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>62661</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>36936</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Interest expense</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>-53024</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>-57415</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>-40422</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>-13239</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>-3650</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Net interest income</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>57099</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>71402</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>80795</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>49422</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>33286</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Fee and commission income</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>3399</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>3228</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>3378</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>3955</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>4294</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Fee and commission expense</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>-1462</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>-1481</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>-1692</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>-1694</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>-1319</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Net fee and commission income</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>1937</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>1747</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>1686</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>2261</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>2975</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Net fair value gain/(loss) on financial instruments</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>3431</v>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>4711</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>9119</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>148</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>1923</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Foreign exchange gain</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>2388</v>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>2295</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>386</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>4916</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>2590</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Net other operating income</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n">
+        <v>123435</v>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>107108</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>114199</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>93633</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>83274</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Non-interest income</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>129254</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>114114</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>123704</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>98697</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>87787</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Total income</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>188290</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>187263</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>206185</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>150380</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>124048</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n"/>
+      <c r="C16" s="6" t="n"/>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="6" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>Staff costs</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n">
+        <v>-86079</v>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>-72194</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>-68058</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>-59208</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>-50154</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Other expenses</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n">
+        <v>-10029</v>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>-9735</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>-9543</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>-9818</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>-8924</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>Depreciation of plant and equipment</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n">
+        <v>-1870</v>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>-1540</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>-1572</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>-1462</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>-1802</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Amortisation of intangible assets</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n">
+        <v>-161</v>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>-104</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>-52</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>-271</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>-237</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>Credit/(provision) for expected credit losses</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n">
+        <v>217</v>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>3953</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>11235</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>11526</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>-23665</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Profit before income tax</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>90368</v>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>107643</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>138195</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>91147</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>39266</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>Income tax expense</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n">
+        <v>-21437</v>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>-23726</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>-34982</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>-22583</v>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>-7788</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Profit for the year</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>68931</v>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>83917</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>103213</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>68564</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>31478</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Other comprehensive income</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="n"/>
+      <c r="C25" s="6" t="n"/>
+      <c r="D25" s="6" t="n"/>
+      <c r="E25" s="6" t="n"/>
+      <c r="F25" s="6" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>Foreign currency translation</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="n">
+        <v>80</v>
+      </c>
+      <c r="C26" s="6" t="n"/>
+      <c r="D26" s="6" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Other comprehensive income/(expense) for the year</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>80</v>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Total comprehensive income for the year</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>69011</v>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>83917</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>103211</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>68576</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>31612</v>
+      </c>
+    </row>
+    <row r="30" ht="180" customHeight="1">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>Sources - Bank of China (UK) Limited's own Income Statement / Statement of Comprehensive Income (Bank/solo basis), £'000, each year's own originally-published report:
+FY2025: Annual Report 2025, p.47-48 - https://pic.bankofchina.com/bocappd/uk/202605/P020260506389809417235.pdf
+FY2024: Annual Report 2024, p.48-49 - https://pic.bankofchina.com/bocappd/uk/202507/P020250718380377744220.pdf (FY2024's own primary source is its own report (AR2024_URL), not AR2025's comparative column - both are identical figures (verified), no restatement.)
+FY2023: Annual Report 2023, p.48-49 - https://pic.bankofchina.com/bocappd/uk/202405/P020240508355110735895.pdf
+FY2022: Financial Statements 2022, p.36-37 - https://pic.bankofchina.com/bocappd/uk/202403/P020240315379765805794.pdf
+FY2021: Financial Statements 2021, p.33-34 - https://pic.bankofchina.com/bocappd/uk/202303/P020230331590070165221.pdf
+Profit before income tax ties exactly to the Cash Flow Statement's own 'Profit before income tax' row for every year, cross-checked as a reconciliation.
+Entity note: Bank of China (UK) Limited (company 06193060, FRN 467410) is a wholly-owned UK subsidiary of Bank of China Limited (state-owned). It does not take the FRS 101/102 cash-flow-statement exemption - a full Statement of Cash Flows is published every year. All figures are the Bank's own solo entity basis throughout.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A30:F30"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Bank of China (UK) Limited — Statement of Changes in Equity</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Bank of China (UK) Limited (solo entity basis), £'000, chronological</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Movement</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Issued share capital</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Other equity instruments</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>Retained earnings</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Foreign currency translation reserve</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>As at 1 January 2021</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>250000</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>92228</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>-64</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>342164</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Profit for the financial year</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>31478</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>31478</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Foreign exchange and other</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>134</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Total comprehensive income</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>31478</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>134</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>31612</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Dividend paid</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>-67000</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>-67000</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>As at 31 December 2021</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>250000</v>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>56706</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>70</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>306776</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Additional Tier 1 capital issued</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>60000</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Profit for the financial year</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>68564</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>68564</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Foreign exchange and other</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Total comprehensive income</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>68564</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>68576</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Dividend paid</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>-33459</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>-33459</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>As at 31 December 2022</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>250000</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>60000</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>91811</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>82</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>401893</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Profit for the financial year</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>103213</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>103213</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>Foreign exchange and other</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>-2</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Total comprehensive income</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>103213</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>-2</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>103211</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>Dividend paid</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>-71815</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>-71815</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>As at 31 December 2023</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>250000</v>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>60000</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>123209</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>80</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>433289</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>Profit for the financial year</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>83917</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>83917</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Total comprehensive income</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>83917</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>83917</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>Dividend paid</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>-103462</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>-103462</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>As at 31 December 2024</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>250000</v>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>60000</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>103664</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>80</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>413744</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>Profit for the financial year</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>68931</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>68931</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>Transfer</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>80</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>-80</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Total comprehensive income</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>69011</v>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>69011</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>Dividend paid</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="6" t="n">
+        <v>-83662</v>
+      </c>
+      <c r="E28" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="6" t="n">
+        <v>-83662</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>As at 31 December 2025</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>250000</v>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>60000</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>89013</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>399013</v>
+      </c>
+    </row>
+    <row r="31" ht="190" customHeight="1">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>Sources - Bank of China (UK) Limited's own Statement of Changes in Equity (Bank/solo basis), £'000, chronological roll-forward reconstructed from each year's own originally-published report:
+2021 movements: Financial Statements 2021, p.36 - https://pic.bankofchina.com/bocappd/uk/202303/P020230331590070165221.pdf
+2022 movements: Financial Statements 2022, p.39 - https://pic.bankofchina.com/bocappd/uk/202403/P020240315379765805794.pdf
+2023 movements: Annual Report 2023, p.51 - https://pic.bankofchina.com/bocappd/uk/202405/P020240508355110735895.pdf
+2024 movements: Annual Report 2024, p.50 - https://pic.bankofchina.com/bocappd/uk/202507/P020250718380377744220.pdf (FY2024's own primary source is its own report (AR2024_URL), not AR2025's comparative column - both are identical figures (verified), no restatement.)
+2025 movements: Annual Report 2025, p.50 - https://pic.bankofchina.com/bocappd/uk/202605/P020260506389809417235.pdf
+Note: the 'Dividend paid' row in this statement (which includes both ordinary share dividends and Additional Tier 1 coupon/interest payments to the parent) differs from the Cash Flow Statement's separately-split 'Dividend paid'/'Interest paid on Additional Tier 1 instrument' lines - e.g. FY2025's £83,662k here vs £78,700k + £4,962k = £83,662k on the Cash Flow Statement (ties out exactly once combined; genuinely two different presentations of the same total, not a discrepancy).
+Entity note: Bank of China (UK) Limited (company 06193060, FRN 467410) is a wholly-owned UK subsidiary of Bank of China Limited (state-owned). It does not take the FRS 101/102 cash-flow-statement exemption - a full Statement of Cash Flows is published every year. All figures are the Bank's own solo entity basis throughout.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A31:F31"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -3122,16 +6951,16 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="68" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
@@ -3142,445 +6971,484 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Bank of China (UK) Limited — CET1 Capital</t>
+          <t>Bank of China (UK) Limited — Asset Quality / Credit Risk Disclosures</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>£'000</t>
+          <t>Bank of China (UK) Limited (solo entity basis), £'000 (ratios as calculated)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Metric</t>
+          <t>Line item</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY2025 (£'000)</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2024 (£'000)</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>FY2023</t>
+          <t>FY2023 (£'000)</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>FY2022</t>
+          <t>FY2022 (£'000)</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>FY2021</t>
+          <t>FY2021 (£'000)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Common Equity Tier 1 (CET1) capital</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>274521</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>274294</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>275056</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>275000</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>275164</v>
-      </c>
-    </row>
-    <row r="6" ht="170" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>Sources - Bank of China (UK) Limited Pillar 3 disclosures (UK KM1 Key Metrics template from FY2022 onward; FY2021's own document is narrative/ratio-only and predates the KM1 template), £'000 unless stated:
-FY2025 &amp; FY2024 comparative: Pillar 3 Disclosure 31 December 2025, p.15 (UK KM1) - https://pic.bankofchina.com/bocappd/uk/202607/P020260716391457618567.pdf
-FY2024 (own year) &amp; FY2023 comparative: Pillar 3 Disclosures 31 December 2024, p.16 (UK KM1) - https://www.bankofchina.com/uk/aboutus/ab5/202507/P020250718380587744231.pdf
-FY2023 (own year) &amp; FY2022 comparative: Pillar 3 disclosures 31 December 2023, p.14 (UK KM1) - https://www.bankofchina.com/uk/aboutus/ab5/202410/P020241008402737321677.pdf
-FY2022 (own year) &amp; FY2021 comparative: Pillar 3 Disclosures 2022, p.14 (UK KM1) - https://www.bankofchina.com/uk/aboutus/ab5/202310/P020231026347190320350.pdf
-FY2021 (own year, narrative/ratio-only - no KM1 template yet): Pillar 3 Disclosures 2021, p.12-14, 24 - https://www.bankofchina.com/uk/aboutus/ab5/202303/P020230315381669571541.pdf
-FY2021 note: the Bank's own FY2021 Pillar 3 document states CET1/Total Capital as rounded £275m/£335m and gives no £-breakdown for leverage exposure, LCR HQLA/outflow, or NSFR (NSFR was not yet a formal disclosure). The precise FY2021 figures used on those sheets (CET1/Tier 1 £275,164k, Total Capital £335,164k, leverage exposure £2,431,869k, LCR HQLA £527,697k/outflow £294,774k, NSFR £1,438,026k/£950,742k) are taken from the FY2022 Pillar 3 document's FY2021 comparative column instead, since it is the more complete disclosure - all overlapping ratios (CET1 24.6%, Total Capital 29.9%, Leverage 11.3%, LCR 179.0%) match the FY2021 document's own narrative figures exactly.
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Gross carrying amount by product</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Wholesale loans</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>2162</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>2242</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>2352</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>2535</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>4806</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Housing loans</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>895</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>1117</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>2279</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>2417</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>2607</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Syndicated loans</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>194775</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>238983</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>173584</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>155931</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>183604</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Factoring financing</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>1898</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>2185</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>4840</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>4219</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>7892</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Credit cards</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>343</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>382</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>501</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>401</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Mortgage loans</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>611782</v>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>697619</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>812348</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>973424</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>1035418</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Financing order</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n"/>
+      <c r="C11" s="6" t="n">
+        <v>319</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>140</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>92</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>1960</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Total gross carrying amount</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>811855</v>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>942847</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>996044</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>1139019</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>1236736</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Gross carrying amount by IFRS 9 stage</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n"/>
+      <c r="C13" s="6" t="n"/>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Stage 1: 12-month ECL</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n">
+        <v>755256</v>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>838850</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>875144</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>932381</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>1161138</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>Stage 2: Lifetime ECL, not credit-impaired</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n">
+        <v>52230</v>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>99518</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>117365</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>133805</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>23529</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Stage 3: Lifetime ECL, credit-impaired</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n">
+        <v>4369</v>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>4479</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>3535</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>72833</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>52069</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Total gross carrying amount (by stage)</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>811855</v>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>942847</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>996044</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>1139019</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>1236736</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Reconciliation to Balance Sheet</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n"/>
+      <c r="C18" s="6" t="n"/>
+      <c r="D18" s="6" t="n"/>
+      <c r="E18" s="6" t="n"/>
+      <c r="F18" s="6" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>Net carrying value (Balance Sheet's Loans and advances to customers)</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n">
+        <v>810985</v>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>941507</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>990763</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>1122459</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>1194653</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Implied total ECL allowance (gross − net)</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n">
+        <v>870</v>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>1340</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>5281</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>16560</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>42083</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Asset quality ratios</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n"/>
+      <c r="C21" s="6" t="n"/>
+      <c r="D21" s="6" t="n"/>
+      <c r="E21" s="6" t="n"/>
+      <c r="F21" s="6" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>ECL coverage ratio (implied allowance / gross carrying amount)</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>0.11%</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>0.14%</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>0.53%</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>1.45%</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>3.40%</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>Stage 3 / NPL ratio (Stage 3 gross / total gross carrying amount)</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>0.54%</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>0.48%</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>0.35%</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>6.39%</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>4.21%</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="270" customHeight="1">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>Sources - Note 6(a) 'Analysis of risk concentration in the financial position' (Global/Europe/US/UK/UK Retail x Stage 1/2/3 geographic table), Bank/solo basis, £'000. By-product and by-stage figures here are summed from that table's 'Loans and advances to customers' product rows (Wholesale/Housing/Syndicated/Factoring/Credit Cards/Mortgage/Financing Order) across all geography columns - both groupings tie exactly to each other and to the same total for every year (verified):
+FY2025: Annual Report 2025, p.77 - https://pic.bankofchina.com/bocappd/uk/202605/P020260506389809417235.pdf
+FY2024: Annual Report 2025's own FY2024 comparative column, p.78 (figures independently cross-checked against AR2024's own Balance Sheet net-loans figure) - {AR2025_URL}
+FY2023: Annual Report 2023, p.80 - https://pic.bankofchina.com/bocappd/uk/202405/P020240508355110735895.pdf
+FY2022: Annual Report 2023's own FY2022 comparative column, p.81 - https://pic.bankofchina.com/bocappd/uk/202405/P020240508355110735895.pdf
+FY2021: Financial Statements 2021, p.67 - https://pic.bankofchina.com/bocappd/uk/202303/P020230331590070165221.pdf
+'Implied total ECL allowance' is not separately disclosed by product/stage anywhere in these documents - it is the residual gap between this note's gross carrying total and the Balance Sheet's own net carrying value, so it captures the whole-portfolio allowance only (not split by stage), hence no separate Stage 3 coverage ratio is shown here (would require a stage-level allowance split that isn't disclosed). FY2021's large ECL gap (£42,083k, 3.40% coverage) is consistent with that year's Cash Flow Statement, which shows the largest single-year 'Net loss for expected credit losses' charge (£23,665k) in the whole 5-year series. FY2022's elevated Stage 3/NPL ratio (6.39%, mostly Syndicated loans) fell sharply by FY2023 (0.35%) - both years' own source tables, not smoothed or averaged.
 Entity note: Bank of China (UK) Limited (company 06193060, FRN 467410) is a wholly-owned UK subsidiary of Bank of China Limited (state-owned). It does not take the FRS 101/102 cash-flow-statement exemption - a full Statement of Cash Flows is published every year. All figures are the Bank's own solo entity basis throughout.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Bank of China (UK) Limited — CET1 Ratio</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>% of RWA</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Common Equity Tier 1 ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>27.2%</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>24.8%</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>26.8%</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>23.4%</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>24.6%</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="170" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>Sources - Bank of China (UK) Limited Pillar 3 disclosures (UK KM1 Key Metrics template from FY2022 onward; FY2021's own document is narrative/ratio-only and predates the KM1 template), £'000 unless stated:
-FY2025 &amp; FY2024 comparative: Pillar 3 Disclosure 31 December 2025, p.15 (UK KM1) - https://pic.bankofchina.com/bocappd/uk/202607/P020260716391457618567.pdf
-FY2024 (own year) &amp; FY2023 comparative: Pillar 3 Disclosures 31 December 2024, p.16 (UK KM1) - https://www.bankofchina.com/uk/aboutus/ab5/202507/P020250718380587744231.pdf
-FY2023 (own year) &amp; FY2022 comparative: Pillar 3 disclosures 31 December 2023, p.14 (UK KM1) - https://www.bankofchina.com/uk/aboutus/ab5/202410/P020241008402737321677.pdf
-FY2022 (own year) &amp; FY2021 comparative: Pillar 3 Disclosures 2022, p.14 (UK KM1) - https://www.bankofchina.com/uk/aboutus/ab5/202310/P020231026347190320350.pdf
-FY2021 (own year, narrative/ratio-only - no KM1 template yet): Pillar 3 Disclosures 2021, p.12-14, 24 - https://www.bankofchina.com/uk/aboutus/ab5/202303/P020230315381669571541.pdf
-FY2021 note: the Bank's own FY2021 Pillar 3 document states CET1/Total Capital as rounded £275m/£335m and gives no £-breakdown for leverage exposure, LCR HQLA/outflow, or NSFR (NSFR was not yet a formal disclosure). The precise FY2021 figures used on those sheets (CET1/Tier 1 £275,164k, Total Capital £335,164k, leverage exposure £2,431,869k, LCR HQLA £527,697k/outflow £294,774k, NSFR £1,438,026k/£950,742k) are taken from the FY2022 Pillar 3 document's FY2021 comparative column instead, since it is the more complete disclosure - all overlapping ratios (CET1 24.6%, Total Capital 29.9%, Leverage 11.3%, LCR 179.0%) match the FY2021 document's own narrative figures exactly.
-Entity note: Bank of China (UK) Limited (company 06193060, FRN 467410) is a wholly-owned UK subsidiary of Bank of China Limited (state-owned). It does not take the FRS 101/102 cash-flow-statement exemption - a full Statement of Cash Flows is published every year. All figures are the Bank's own solo entity basis throughout.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Bank of China (UK) Limited — Tier 1 Capital</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>£'000</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Tier 1 capital</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>334521</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>334294</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>335056</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>335000</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>275164</v>
-      </c>
-    </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Note: Equal to CET1 capital at FY2021 (no AT1 instruments in issue that year). A £60m Additional Tier 1 instrument was issued in June 2022, replacing an equal amount of Tier 2 subordinated debt.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="170" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>Sources - Bank of China (UK) Limited Pillar 3 disclosures (UK KM1 Key Metrics template from FY2022 onward; FY2021's own document is narrative/ratio-only and predates the KM1 template), £'000 unless stated:
-FY2025 &amp; FY2024 comparative: Pillar 3 Disclosure 31 December 2025, p.15 (UK KM1) - https://pic.bankofchina.com/bocappd/uk/202607/P020260716391457618567.pdf
-FY2024 (own year) &amp; FY2023 comparative: Pillar 3 Disclosures 31 December 2024, p.16 (UK KM1) - https://www.bankofchina.com/uk/aboutus/ab5/202507/P020250718380587744231.pdf
-FY2023 (own year) &amp; FY2022 comparative: Pillar 3 disclosures 31 December 2023, p.14 (UK KM1) - https://www.bankofchina.com/uk/aboutus/ab5/202410/P020241008402737321677.pdf
-FY2022 (own year) &amp; FY2021 comparative: Pillar 3 Disclosures 2022, p.14 (UK KM1) - https://www.bankofchina.com/uk/aboutus/ab5/202310/P020231026347190320350.pdf
-FY2021 (own year, narrative/ratio-only - no KM1 template yet): Pillar 3 Disclosures 2021, p.12-14, 24 - https://www.bankofchina.com/uk/aboutus/ab5/202303/P020230315381669571541.pdf
-FY2021 note: the Bank's own FY2021 Pillar 3 document states CET1/Total Capital as rounded £275m/£335m and gives no £-breakdown for leverage exposure, LCR HQLA/outflow, or NSFR (NSFR was not yet a formal disclosure). The precise FY2021 figures used on those sheets (CET1/Tier 1 £275,164k, Total Capital £335,164k, leverage exposure £2,431,869k, LCR HQLA £527,697k/outflow £294,774k, NSFR £1,438,026k/£950,742k) are taken from the FY2022 Pillar 3 document's FY2021 comparative column instead, since it is the more complete disclosure - all overlapping ratios (CET1 24.6%, Total Capital 29.9%, Leverage 11.3%, LCR 179.0%) match the FY2021 document's own narrative figures exactly.
-Entity note: Bank of China (UK) Limited (company 06193060, FRN 467410) is a wholly-owned UK subsidiary of Bank of China Limited (state-owned). It does not take the FRS 101/102 cash-flow-statement exemption - a full Statement of Cash Flows is published every year. All figures are the Bank's own solo entity basis throughout.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A7:F7"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Bank of China (UK) Limited — Tier 1 Ratio</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>% of RWA</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Tier 1 ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>33.2%</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>30.2%</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>32.7%</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>28.5%</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>24.6%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Note: FY2021 not separately stated as a percentage in the source; numerically equal to the stated CET1 ratio since Tier 1 capital equalled CET1 capital exactly that year (no AT1 in issue).</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="170" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>Sources - Bank of China (UK) Limited Pillar 3 disclosures (UK KM1 Key Metrics template from FY2022 onward; FY2021's own document is narrative/ratio-only and predates the KM1 template), £'000 unless stated:
-FY2025 &amp; FY2024 comparative: Pillar 3 Disclosure 31 December 2025, p.15 (UK KM1) - https://pic.bankofchina.com/bocappd/uk/202607/P020260716391457618567.pdf
-FY2024 (own year) &amp; FY2023 comparative: Pillar 3 Disclosures 31 December 2024, p.16 (UK KM1) - https://www.bankofchina.com/uk/aboutus/ab5/202507/P020250718380587744231.pdf
-FY2023 (own year) &amp; FY2022 comparative: Pillar 3 disclosures 31 December 2023, p.14 (UK KM1) - https://www.bankofchina.com/uk/aboutus/ab5/202410/P020241008402737321677.pdf
-FY2022 (own year) &amp; FY2021 comparative: Pillar 3 Disclosures 2022, p.14 (UK KM1) - https://www.bankofchina.com/uk/aboutus/ab5/202310/P020231026347190320350.pdf
-FY2021 (own year, narrative/ratio-only - no KM1 template yet): Pillar 3 Disclosures 2021, p.12-14, 24 - https://www.bankofchina.com/uk/aboutus/ab5/202303/P020230315381669571541.pdf
-FY2021 note: the Bank's own FY2021 Pillar 3 document states CET1/Total Capital as rounded £275m/£335m and gives no £-breakdown for leverage exposure, LCR HQLA/outflow, or NSFR (NSFR was not yet a formal disclosure). The precise FY2021 figures used on those sheets (CET1/Tier 1 £275,164k, Total Capital £335,164k, leverage exposure £2,431,869k, LCR HQLA £527,697k/outflow £294,774k, NSFR £1,438,026k/£950,742k) are taken from the FY2022 Pillar 3 document's FY2021 comparative column instead, since it is the more complete disclosure - all overlapping ratios (CET1 24.6%, Total Capital 29.9%, Leverage 11.3%, LCR 179.0%) match the FY2021 document's own narrative figures exactly.
-Entity note: Bank of China (UK) Limited (company 06193060, FRN 467410) is a wholly-owned UK subsidiary of Bank of China Limited (state-owned). It does not take the FRS 101/102 cash-flow-statement exemption - a full Statement of Cash Flows is published every year. All figures are the Bank's own solo entity basis throughout.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A25:F25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3606,7 +7474,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Bank of China (UK) Limited — Total Capital</t>
+          <t>Bank of China (UK) Limited — CET1 Capital</t>
         </is>
       </c>
     </row>
@@ -3652,23 +7520,23 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total regulatory capital</t>
+          <t>Common Equity Tier 1 (CET1) capital</t>
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>334521</v>
+        <v>274521</v>
       </c>
       <c r="C4" s="6" t="n">
-        <v>334294</v>
+        <v>274294</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>335056</v>
+        <v>275056</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>335000</v>
+        <v>275000</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>335164</v>
+        <v>275164</v>
       </c>
     </row>
     <row r="6" ht="170" customHeight="1">
@@ -3713,7 +7581,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Bank of China (UK) Limited — Total Capital Ratio</t>
+          <t>Bank of China (UK) Limited — CET1 Ratio</t>
         </is>
       </c>
     </row>
@@ -3759,32 +7627,32 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total capital ratio</t>
+          <t>Common Equity Tier 1 ratio</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>33.2%</t>
+          <t>27.2%</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>30.2%</t>
+          <t>24.8%</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>32.7%</t>
+          <t>26.8%</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>28.5%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>29.9%</t>
+          <t>24.6%</t>
         </is>
       </c>
     </row>
@@ -3816,7 +7684,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -3830,7 +7698,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Bank of China (UK) Limited — Total RWAs</t>
+          <t>Bank of China (UK) Limited — Tier 1 Capital</t>
         </is>
       </c>
     </row>
@@ -3876,27 +7744,34 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total risk-weighted assets (RWA)</t>
+          <t>Tier 1 capital</t>
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>1008110</v>
+        <v>334521</v>
       </c>
       <c r="C4" s="6" t="n">
-        <v>1106898</v>
+        <v>334294</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>1024452</v>
+        <v>335056</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>1176625</v>
+        <v>335000</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>1119380</v>
-      </c>
-    </row>
-    <row r="6" ht="170" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
+        <v>275164</v>
+      </c>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Note: Equal to CET1 capital at FY2021 (no AT1 instruments in issue that year). A £60m Additional Tier 1 instrument was issued in June 2022, replacing an equal amount of Tier 2 subordinated debt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="170" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Sources - Bank of China (UK) Limited Pillar 3 disclosures (UK KM1 Key Metrics template from FY2022 onward; FY2021's own document is narrative/ratio-only and predates the KM1 template), £'000 unless stated:
 FY2025 &amp; FY2024 comparative: Pillar 3 Disclosure 31 December 2025, p.15 (UK KM1) - https://pic.bankofchina.com/bocappd/uk/202607/P020260716391457618567.pdf
@@ -3910,8 +7785,9 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
+  <mergeCells count="2">
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A7:F7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/banks/BANK OF CHINA UK FINANCIALS.xlsx
+++ b/banks/BANK OF CHINA UK FINANCIALS.xlsx
@@ -6609,7 +6609,7 @@
         <v>344019</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>199954</v>
+        <v>199854</v>
       </c>
       <c r="N5" s="6" t="n">
         <v>159219</v>
@@ -8269,7 +8269,7 @@
 FY2009: 2009 Report and Financial Statements, p.31 - https://pic.bankofchina.com/bocappd/uk/201109/P020110901339600023124.pdf
 FY2008: 2009 Report's own FY2008 comparative column, p.31 - https://pic.bankofchina.com/bocappd/uk/201109/P020110901339600023124.pdf, cross-checked against the Bank's own 2008 Report and Financial Statements (Balance Sheet, p.29) - https://pic.bankofchina.com/bocappd/uk/201109/P020110901339400504145.pdf (figures identical). FY2008 period note: Bank of China (UK) Limited's first accounting period ran 1 April 2007 - 30 September 2007 (a 6-month stub, outside this workbook's scope), and its second and only 'FY2008' statutory period is genuinely a 15-month period from 1 October 2007 to 31 December 2008 (the year-end was moved to December during this period) - not a standard 12-month year. Both the Bank's own FY2008 Report and Financial Statements (AR2008_URL) and the FY2009 Report's own FY2008 comparative column (AR2009_URL) show this identical 15-month figure set, cross-checked and tying exactly. Shown here as 'FY2008' per this workbook's year-labelling convention, but flagged as non-comparable in length to every other year in this workbook - growth trends spanning the FY2008/FY2009 boundary should be read with that caveat.
 HD-075 extension presentation notes (FY2008-FY2013): 'Investment in subsidiary/group companies' is its own row for these 6 years only (a real, non-nil balance - the subsidiary was disposed of during FY2012, hence nil/omitted from FY2014 onward). 'Deferred tax liabilities' is its own row for FY2008 (£14k) and FY2013 (£28k) only - nil/not disclosed as a separate line in every other year shown. 'Authorised and called up share capital' rose from £140,000k to £250,000k during FY2012 via a £110,000k ordinary share issue (see the Statement of Changes in Equity sheet). FY2013's Balance Sheet total assets/liabilities were affected by two OCR digit corrections cross-checked against the statement's own subtotals - see AR2013_SCAN_NOTE.
-Presentation notes: 'Government bonds' only appears as its own line from FY2022 onward. 'Subordinated liabilities' (£60,000k every year FY2014-FY2021) was repaid and replaced by an equal £60,000k Additional Tier 1 instrument in June 2022 - both nil/blank in the years they don't apply. 'Investment in subsidiary companies' is nil every year and omitted as a row. 'Available for sale financial investments' and its matching equity 'Available for sale reserve' existed under IAS 39 through FY2017 and were replaced by 'Financial assets at fair value through profit and loss' / 'Debt instruments at amortised cost' at the 1 January 2018 IFRS 9 transition (a £495k opening-equity charge that year, see the Statement of Changes in Equity sheet) - both pairs of rows are blank/zero in the years they don't apply, not force-matched. FY2021's own report's Statement of Changes in Equity states closing retained earnings as £56,706k, £70k less than the Balance Sheet's own £56,776k for the same date - the Balance Sheet's single 'Retained earnings' line appears to combine the SOCE's separate retained-earnings and FX-translation-reserve columns (£56,706k + £70k = £56,776k); the same pattern recurs one year earlier at FY2020 (SOCE retained earnings £92,228k + FX reserve -£64k = Balance Sheet's own £92,164k); total equity ties out exactly either way in both years. FY2014 cash: the Balance Sheet (via FY2015's comparative) shows £199,954k while the Cash Flow Statement's own closing balance for the same date shows £199,854k - a genuine £100k digit discrepancy between the two notes of the same FY2015 filing (likely one OCR-affected digit somewhere upstream of both extractions), left unresolved and shown as each note's own figure rather than force-matched, since FY2014's own primary report cannot be read to arbitrate (see AR2014_SCAN_NOTE).
+Presentation notes: 'Government bonds' only appears as its own line from FY2022 onward. 'Subordinated liabilities' (£60,000k every year FY2014-FY2021) was repaid and replaced by an equal £60,000k Additional Tier 1 instrument in June 2022 - both nil/blank in the years they don't apply. 'Investment in subsidiary companies' is nil every year and omitted as a row. 'Available for sale financial investments' and its matching equity 'Available for sale reserve' existed under IAS 39 through FY2017 and were replaced by 'Financial assets at fair value through profit and loss' / 'Debt instruments at amortised cost' at the 1 January 2018 IFRS 9 transition (a £495k opening-equity charge that year, see the Statement of Changes in Equity sheet) - both pairs of rows are blank/zero in the years they don't apply, not force-matched. FY2021's own report's Statement of Changes in Equity states closing retained earnings as £56,706k, £70k less than the Balance Sheet's own £56,776k for the same date - the Balance Sheet's single 'Retained earnings' line appears to combine the SOCE's separate retained-earnings and FX-translation-reserve columns (£56,706k + £70k = £56,776k); the same pattern recurs one year earlier at FY2020 (SOCE retained earnings £92,228k + FX reserve -£64k = Balance Sheet's own £92,164k); total equity ties out exactly either way in both years. FY2014 cash resolved (HD-081, 2026-09-07): FY2015's own filing originally appeared to show two different FY2014 cash figures - £199,954k on the Balance Sheet's comparative column vs. £199,854k on the Cash Flow Statement's own comparative closing balance. Re-summing FY2014's own 9 asset line items as originally transcribed (199,954 + 207,026 + 722,307 + 16,173 + 27,820 + 37,469 + 751 + 3,390 + 326) gives £1,215,216k, £100k more than the Balance Sheet's own stated 'Total assets' of £1,215,116k for that column; substituting £199,854k for the cash line instead sums to exactly £1,215,116k. The Balance Sheet's own internal subtotal therefore only ties out with £199,854k, confirming £199,954k was a single-digit transcription/OCR misread of the FY2015 filing's FY2014 comparative column (a 9 misread for an 8 in the thousands place) and that £199,854k, matching the Cash Flow Statement, is the correct figure. Corrected here to £199,854k; FY2014's own primary report remains unreadable as text (see AR2014_SCAN_NOTE), so this arithmetic cross-check within FY2015's own filing is the resolving evidence.
 Entity note: Bank of China (UK) Limited (company 06193060, FRN 467410) is a wholly-owned UK subsidiary of Bank of China Limited (state-owned). It does not take the FRS 101/102 cash-flow-statement exemption - a full Statement of Cash Flows is published every year. All figures are the Bank's own solo entity basis throughout.</t>
         </is>
       </c>
@@ -8288,7 +8288,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S36"/>
+  <dimension ref="A1:S37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="68" customWidth="1" min="1" max="1"/>
@@ -9480,99 +9480,131 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>Credit/(provision) for expected credit losses</t>
-        </is>
-      </c>
-      <c r="B24" s="6" t="n">
-        <v>217</v>
-      </c>
-      <c r="C24" s="6" t="n">
-        <v>3953</v>
-      </c>
-      <c r="D24" s="6" t="n">
-        <v>11235</v>
-      </c>
-      <c r="E24" s="6" t="n">
-        <v>11526</v>
-      </c>
-      <c r="F24" s="6" t="n">
-        <v>-23665</v>
-      </c>
-      <c r="G24" s="6" t="n">
-        <v>-3172</v>
-      </c>
-      <c r="H24" s="6" t="n">
-        <v>-377</v>
-      </c>
-      <c r="I24" s="6" t="n">
-        <v>458</v>
-      </c>
-      <c r="J24" s="6" t="n">
-        <v>187</v>
-      </c>
-      <c r="K24" s="6" t="n">
-        <v>-527</v>
-      </c>
-      <c r="L24" s="6" t="n">
-        <v>155</v>
-      </c>
-      <c r="M24" s="6" t="n">
-        <v>-722</v>
-      </c>
-      <c r="N24" s="6" t="n">
-        <v>-60</v>
-      </c>
-      <c r="O24" s="6" t="n">
-        <v>-4455</v>
-      </c>
-      <c r="P24" s="6" t="n">
-        <v>-8272</v>
-      </c>
-      <c r="Q24" s="6" t="n">
-        <v>-35</v>
-      </c>
-      <c r="R24" s="6" t="n">
-        <v>-1827</v>
-      </c>
-      <c r="S24" s="6" t="n">
-        <v>-9386</v>
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Total operating expenses (sum of Staff costs + Other expenses + Depreciation + Amortisation - excludes credit loss provisions and subsidiary items per standard cost-to-income convention, not itself a printed AR subtotal)</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>-98139</v>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>-83573</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>-79225</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>-70759</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>-61117</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>-69021</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>-72925</v>
+      </c>
+      <c r="I24" s="5" t="n">
+        <v>-50469</v>
+      </c>
+      <c r="J24" s="5" t="n">
+        <v>-50074</v>
+      </c>
+      <c r="K24" s="5" t="n">
+        <v>-40797</v>
+      </c>
+      <c r="L24" s="5" t="n">
+        <v>-37155</v>
+      </c>
+      <c r="M24" s="5" t="n">
+        <v>-37568</v>
+      </c>
+      <c r="N24" s="5" t="n">
+        <v>-30354</v>
+      </c>
+      <c r="O24" s="5" t="n">
+        <v>-25700</v>
+      </c>
+      <c r="P24" s="5" t="n">
+        <v>-21527</v>
+      </c>
+      <c r="Q24" s="5" t="n">
+        <v>-18480</v>
+      </c>
+      <c r="R24" s="5" t="n">
+        <v>-16065</v>
+      </c>
+      <c r="S24" s="5" t="n">
+        <v>-17772</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>Impairment of investment in subsidiary</t>
-        </is>
-      </c>
-      <c r="B25" s="6" t="n"/>
-      <c r="C25" s="6" t="n"/>
-      <c r="D25" s="6" t="n"/>
-      <c r="E25" s="6" t="n"/>
-      <c r="F25" s="6" t="n"/>
-      <c r="G25" s="6" t="n"/>
-      <c r="H25" s="6" t="n"/>
-      <c r="I25" s="6" t="n"/>
-      <c r="J25" s="6" t="n"/>
-      <c r="K25" s="6" t="n"/>
-      <c r="L25" s="6" t="n"/>
-      <c r="M25" s="6" t="n"/>
-      <c r="N25" s="6" t="n"/>
-      <c r="O25" s="6" t="n"/>
+          <t>Credit/(provision) for expected credit losses</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="n">
+        <v>217</v>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>3953</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>11235</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>11526</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>-23665</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>-3172</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>-377</v>
+      </c>
+      <c r="I25" s="6" t="n">
+        <v>458</v>
+      </c>
+      <c r="J25" s="6" t="n">
+        <v>187</v>
+      </c>
+      <c r="K25" s="6" t="n">
+        <v>-527</v>
+      </c>
+      <c r="L25" s="6" t="n">
+        <v>155</v>
+      </c>
+      <c r="M25" s="6" t="n">
+        <v>-722</v>
+      </c>
+      <c r="N25" s="6" t="n">
+        <v>-60</v>
+      </c>
+      <c r="O25" s="6" t="n">
+        <v>-4455</v>
+      </c>
       <c r="P25" s="6" t="n">
-        <v>-31432</v>
+        <v>-8272</v>
       </c>
       <c r="Q25" s="6" t="n">
-        <v>-8432</v>
-      </c>
-      <c r="R25" s="6" t="n"/>
-      <c r="S25" s="6" t="n"/>
+        <v>-35</v>
+      </c>
+      <c r="R25" s="6" t="n">
+        <v>-1827</v>
+      </c>
+      <c r="S25" s="6" t="n">
+        <v>-9386</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>Gain/(loss) on disposal of subsidiary</t>
+          <t>Impairment of investment in subsidiary</t>
         </is>
       </c>
       <c r="B26" s="6" t="n"/>
@@ -9585,251 +9617,245 @@
       <c r="I26" s="6" t="n"/>
       <c r="J26" s="6" t="n"/>
       <c r="K26" s="6" t="n"/>
-      <c r="L26" s="6" t="n">
-        <v>-1707</v>
-      </c>
+      <c r="L26" s="6" t="n"/>
       <c r="M26" s="6" t="n"/>
-      <c r="N26" s="6" t="n">
-        <v>1632</v>
-      </c>
-      <c r="O26" s="6" t="n">
-        <v>-1074</v>
-      </c>
-      <c r="P26" s="6" t="n"/>
-      <c r="Q26" s="6" t="n"/>
+      <c r="N26" s="6" t="n"/>
+      <c r="O26" s="6" t="n"/>
+      <c r="P26" s="6" t="n">
+        <v>-31432</v>
+      </c>
+      <c r="Q26" s="6" t="n">
+        <v>-8432</v>
+      </c>
       <c r="R26" s="6" t="n"/>
       <c r="S26" s="6" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="inlineStr">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>Gain/(loss) on disposal of subsidiary</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n"/>
+      <c r="C27" s="6" t="n"/>
+      <c r="D27" s="6" t="n"/>
+      <c r="E27" s="6" t="n"/>
+      <c r="F27" s="6" t="n"/>
+      <c r="G27" s="6" t="n"/>
+      <c r="H27" s="6" t="n"/>
+      <c r="I27" s="6" t="n"/>
+      <c r="J27" s="6" t="n"/>
+      <c r="K27" s="6" t="n"/>
+      <c r="L27" s="6" t="n">
+        <v>-1707</v>
+      </c>
+      <c r="M27" s="6" t="n"/>
+      <c r="N27" s="6" t="n">
+        <v>1632</v>
+      </c>
+      <c r="O27" s="6" t="n">
+        <v>-1074</v>
+      </c>
+      <c r="P27" s="6" t="n"/>
+      <c r="Q27" s="6" t="n"/>
+      <c r="R27" s="6" t="n"/>
+      <c r="S27" s="6" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>Profit before income tax</t>
         </is>
       </c>
-      <c r="B27" s="5" t="n">
+      <c r="B28" s="5" t="n">
         <v>90368</v>
       </c>
-      <c r="C27" s="5" t="n">
+      <c r="C28" s="5" t="n">
         <v>107643</v>
       </c>
-      <c r="D27" s="5" t="n">
+      <c r="D28" s="5" t="n">
         <v>138195</v>
       </c>
-      <c r="E27" s="5" t="n">
+      <c r="E28" s="5" t="n">
         <v>91147</v>
       </c>
-      <c r="F27" s="5" t="n">
+      <c r="F28" s="5" t="n">
         <v>39266</v>
       </c>
-      <c r="G27" s="5" t="n">
+      <c r="G28" s="5" t="n">
         <v>47910</v>
       </c>
-      <c r="H27" s="5" t="n">
+      <c r="H28" s="5" t="n">
         <v>41935</v>
       </c>
-      <c r="I27" s="5" t="n">
+      <c r="I28" s="5" t="n">
         <v>64550</v>
       </c>
-      <c r="J27" s="5" t="n">
+      <c r="J28" s="5" t="n">
         <v>44596</v>
       </c>
-      <c r="K27" s="5" t="n">
+      <c r="K28" s="5" t="n">
         <v>49858</v>
       </c>
-      <c r="L27" s="5" t="n">
+      <c r="L28" s="5" t="n">
         <v>56214</v>
       </c>
-      <c r="M27" s="5" t="n">
+      <c r="M28" s="5" t="n">
         <v>33331</v>
       </c>
-      <c r="N27" s="5" t="n">
+      <c r="N28" s="5" t="n">
         <v>41617</v>
       </c>
-      <c r="O27" s="5" t="n">
+      <c r="O28" s="5" t="n">
         <v>32708</v>
       </c>
-      <c r="P27" s="5" t="n">
+      <c r="P28" s="5" t="n">
         <v>-23864</v>
       </c>
-      <c r="Q27" s="5" t="n">
+      <c r="Q28" s="5" t="n">
         <v>19615</v>
       </c>
-      <c r="R27" s="5" t="n">
+      <c r="R28" s="5" t="n">
         <v>16631</v>
       </c>
-      <c r="S27" s="5" t="n">
+      <c r="S28" s="5" t="n">
         <v>4574</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="6" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t>Income tax expense</t>
         </is>
       </c>
-      <c r="B28" s="6" t="n">
+      <c r="B29" s="6" t="n">
         <v>-21437</v>
       </c>
-      <c r="C28" s="6" t="n">
+      <c r="C29" s="6" t="n">
         <v>-23726</v>
       </c>
-      <c r="D28" s="6" t="n">
+      <c r="D29" s="6" t="n">
         <v>-34982</v>
       </c>
-      <c r="E28" s="6" t="n">
+      <c r="E29" s="6" t="n">
         <v>-22583</v>
       </c>
-      <c r="F28" s="6" t="n">
+      <c r="F29" s="6" t="n">
         <v>-7788</v>
       </c>
-      <c r="G28" s="6" t="n">
+      <c r="G29" s="6" t="n">
         <v>-12745</v>
       </c>
-      <c r="H28" s="6" t="n">
+      <c r="H29" s="6" t="n">
         <v>-9830</v>
       </c>
-      <c r="I28" s="6" t="n">
+      <c r="I29" s="6" t="n">
         <v>-13427</v>
       </c>
-      <c r="J28" s="6" t="n">
+      <c r="J29" s="6" t="n">
         <v>-12532</v>
       </c>
-      <c r="K28" s="6" t="n">
+      <c r="K29" s="6" t="n">
         <v>-14168</v>
       </c>
-      <c r="L28" s="6" t="n">
+      <c r="L29" s="6" t="n">
         <v>-10764</v>
       </c>
-      <c r="M28" s="6" t="n">
+      <c r="M29" s="6" t="n">
         <v>-7376</v>
       </c>
-      <c r="N28" s="6" t="n">
+      <c r="N29" s="6" t="n">
         <v>-9744</v>
       </c>
-      <c r="O28" s="6" t="n">
+      <c r="O29" s="6" t="n">
         <v>-8278</v>
       </c>
-      <c r="P28" s="6" t="n">
+      <c r="P29" s="6" t="n">
         <v>-2206</v>
       </c>
-      <c r="Q28" s="6" t="n">
+      <c r="Q29" s="6" t="n">
         <v>-8836</v>
       </c>
-      <c r="R28" s="6" t="n">
+      <c r="R29" s="6" t="n">
         <v>-4071</v>
       </c>
-      <c r="S28" s="6" t="n">
+      <c r="S29" s="6" t="n">
         <v>-1562</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>Profit/(loss) for the year</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="n">
-        <v>68931</v>
-      </c>
-      <c r="C29" s="5" t="n">
-        <v>83917</v>
-      </c>
-      <c r="D29" s="5" t="n">
-        <v>103213</v>
-      </c>
-      <c r="E29" s="5" t="n">
-        <v>68564</v>
-      </c>
-      <c r="F29" s="5" t="n">
-        <v>31478</v>
-      </c>
-      <c r="G29" s="5" t="n">
-        <v>35165</v>
-      </c>
-      <c r="H29" s="5" t="n">
-        <v>32105</v>
-      </c>
-      <c r="I29" s="5" t="n">
-        <v>51123</v>
-      </c>
-      <c r="J29" s="5" t="n">
-        <v>32064</v>
-      </c>
-      <c r="K29" s="5" t="n">
-        <v>35690</v>
-      </c>
-      <c r="L29" s="5" t="n">
-        <v>45450</v>
-      </c>
-      <c r="M29" s="5" t="n">
-        <v>25955</v>
-      </c>
-      <c r="N29" s="5" t="n">
-        <v>31873</v>
-      </c>
-      <c r="O29" s="5" t="n">
-        <v>24430</v>
-      </c>
-      <c r="P29" s="5" t="n">
-        <v>-26070</v>
-      </c>
-      <c r="Q29" s="5" t="n">
-        <v>10779</v>
-      </c>
-      <c r="R29" s="5" t="n">
-        <v>12560</v>
-      </c>
-      <c r="S29" s="5" t="n">
-        <v>3012</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
+          <t>Profit/(loss) for the year</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>68931</v>
+      </c>
+      <c r="C30" s="5" t="n">
+        <v>83917</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>103213</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>68564</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>31478</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>35165</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>32105</v>
+      </c>
+      <c r="I30" s="5" t="n">
+        <v>51123</v>
+      </c>
+      <c r="J30" s="5" t="n">
+        <v>32064</v>
+      </c>
+      <c r="K30" s="5" t="n">
+        <v>35690</v>
+      </c>
+      <c r="L30" s="5" t="n">
+        <v>45450</v>
+      </c>
+      <c r="M30" s="5" t="n">
+        <v>25955</v>
+      </c>
+      <c r="N30" s="5" t="n">
+        <v>31873</v>
+      </c>
+      <c r="O30" s="5" t="n">
+        <v>24430</v>
+      </c>
+      <c r="P30" s="5" t="n">
+        <v>-26070</v>
+      </c>
+      <c r="Q30" s="5" t="n">
+        <v>10779</v>
+      </c>
+      <c r="R30" s="5" t="n">
+        <v>12560</v>
+      </c>
+      <c r="S30" s="5" t="n">
+        <v>3012</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
           <t>Other comprehensive income</t>
         </is>
       </c>
-      <c r="B30" s="6" t="n"/>
-      <c r="C30" s="6" t="n"/>
-      <c r="D30" s="6" t="n"/>
-      <c r="E30" s="6" t="n"/>
-      <c r="F30" s="6" t="n"/>
-      <c r="G30" s="6" t="n"/>
-      <c r="H30" s="6" t="n"/>
-      <c r="I30" s="6" t="n"/>
-      <c r="J30" s="6" t="n"/>
-      <c r="K30" s="6" t="n"/>
-      <c r="L30" s="6" t="n"/>
-      <c r="M30" s="6" t="n"/>
-      <c r="N30" s="6" t="n"/>
-      <c r="O30" s="6" t="n"/>
-      <c r="P30" s="6" t="n"/>
-      <c r="Q30" s="6" t="n"/>
-      <c r="R30" s="6" t="n"/>
-      <c r="S30" s="6" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="6" t="inlineStr">
-        <is>
-          <t>Foreign currency translation</t>
-        </is>
-      </c>
-      <c r="B31" s="6" t="n">
-        <v>80</v>
-      </c>
+      <c r="B31" s="6" t="n"/>
       <c r="C31" s="6" t="n"/>
-      <c r="D31" s="6" t="n">
-        <v>-2</v>
-      </c>
-      <c r="E31" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="F31" s="6" t="n">
-        <v>134</v>
-      </c>
-      <c r="G31" s="6" t="n">
-        <v>-59</v>
-      </c>
+      <c r="D31" s="6" t="n"/>
+      <c r="E31" s="6" t="n"/>
+      <c r="F31" s="6" t="n"/>
+      <c r="G31" s="6" t="n"/>
       <c r="H31" s="6" t="n"/>
       <c r="I31" s="6" t="n"/>
       <c r="J31" s="6" t="n"/>
@@ -9846,172 +9872,207 @@
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>Net change in fair value of available-for-sale financial assets (net of tax)</t>
-        </is>
-      </c>
-      <c r="B32" s="6" t="n"/>
+          <t>Foreign currency translation</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n">
+        <v>80</v>
+      </c>
       <c r="C32" s="6" t="n"/>
-      <c r="D32" s="6" t="n"/>
-      <c r="E32" s="6" t="n"/>
-      <c r="F32" s="6" t="n"/>
-      <c r="G32" s="6" t="n"/>
+      <c r="D32" s="6" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>134</v>
+      </c>
+      <c r="G32" s="6" t="n">
+        <v>-59</v>
+      </c>
       <c r="H32" s="6" t="n"/>
       <c r="I32" s="6" t="n"/>
-      <c r="J32" s="6" t="n">
+      <c r="J32" s="6" t="n"/>
+      <c r="K32" s="6" t="n"/>
+      <c r="L32" s="6" t="n"/>
+      <c r="M32" s="6" t="n"/>
+      <c r="N32" s="6" t="n"/>
+      <c r="O32" s="6" t="n"/>
+      <c r="P32" s="6" t="n"/>
+      <c r="Q32" s="6" t="n"/>
+      <c r="R32" s="6" t="n"/>
+      <c r="S32" s="6" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>Net change in fair value of available-for-sale financial assets (net of tax)</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+      <c r="E33" s="6" t="n"/>
+      <c r="F33" s="6" t="n"/>
+      <c r="G33" s="6" t="n"/>
+      <c r="H33" s="6" t="n"/>
+      <c r="I33" s="6" t="n"/>
+      <c r="J33" s="6" t="n">
         <v>316</v>
       </c>
-      <c r="K32" s="6" t="n">
+      <c r="K33" s="6" t="n">
         <v>-144</v>
       </c>
-      <c r="L32" s="6" t="n">
+      <c r="L33" s="6" t="n">
         <v>-707</v>
       </c>
-      <c r="M32" s="6" t="n">
+      <c r="M33" s="6" t="n">
         <v>-276</v>
       </c>
-      <c r="N32" s="6" t="n">
+      <c r="N33" s="6" t="n">
         <v>-2</v>
       </c>
-      <c r="O32" s="6" t="n">
+      <c r="O33" s="6" t="n">
         <v>1816</v>
       </c>
-      <c r="P32" s="6" t="n">
+      <c r="P33" s="6" t="n">
         <v>-26</v>
       </c>
-      <c r="Q32" s="6" t="n">
+      <c r="Q33" s="6" t="n">
         <v>3225</v>
       </c>
-      <c r="R32" s="6" t="n">
+      <c r="R33" s="6" t="n">
         <v>13984</v>
       </c>
-      <c r="S32" s="6" t="n">
-        <v>-18154</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>Other comprehensive income/(expense) for the year</t>
-        </is>
-      </c>
-      <c r="B33" s="5" t="n">
-        <v>80</v>
-      </c>
-      <c r="C33" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D33" s="5" t="n">
-        <v>-2</v>
-      </c>
-      <c r="E33" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="F33" s="5" t="n">
-        <v>134</v>
-      </c>
-      <c r="G33" s="5" t="n">
-        <v>-59</v>
-      </c>
-      <c r="H33" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" s="5" t="n">
-        <v>316</v>
-      </c>
-      <c r="K33" s="5" t="n">
-        <v>-144</v>
-      </c>
-      <c r="L33" s="5" t="n">
-        <v>-707</v>
-      </c>
-      <c r="M33" s="5" t="n">
-        <v>-276</v>
-      </c>
-      <c r="N33" s="5" t="n">
-        <v>-2</v>
-      </c>
-      <c r="O33" s="5" t="n">
-        <v>1816</v>
-      </c>
-      <c r="P33" s="5" t="n">
-        <v>-26</v>
-      </c>
-      <c r="Q33" s="5" t="n">
-        <v>3225</v>
-      </c>
-      <c r="R33" s="5" t="n">
-        <v>13984</v>
-      </c>
-      <c r="S33" s="5" t="n">
+      <c r="S33" s="6" t="n">
         <v>-18154</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
+          <t>Other comprehensive income/(expense) for the year</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>80</v>
+      </c>
+      <c r="C34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" s="5" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E34" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="F34" s="5" t="n">
+        <v>134</v>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>-59</v>
+      </c>
+      <c r="H34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="5" t="n">
+        <v>316</v>
+      </c>
+      <c r="K34" s="5" t="n">
+        <v>-144</v>
+      </c>
+      <c r="L34" s="5" t="n">
+        <v>-707</v>
+      </c>
+      <c r="M34" s="5" t="n">
+        <v>-276</v>
+      </c>
+      <c r="N34" s="5" t="n">
+        <v>-2</v>
+      </c>
+      <c r="O34" s="5" t="n">
+        <v>1816</v>
+      </c>
+      <c r="P34" s="5" t="n">
+        <v>-26</v>
+      </c>
+      <c r="Q34" s="5" t="n">
+        <v>3225</v>
+      </c>
+      <c r="R34" s="5" t="n">
+        <v>13984</v>
+      </c>
+      <c r="S34" s="5" t="n">
+        <v>-18154</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
           <t>Total comprehensive income/(expense) for the year</t>
         </is>
       </c>
-      <c r="B34" s="5" t="n">
+      <c r="B35" s="5" t="n">
         <v>69011</v>
       </c>
-      <c r="C34" s="5" t="n">
+      <c r="C35" s="5" t="n">
         <v>83917</v>
       </c>
-      <c r="D34" s="5" t="n">
+      <c r="D35" s="5" t="n">
         <v>103211</v>
       </c>
-      <c r="E34" s="5" t="n">
+      <c r="E35" s="5" t="n">
         <v>68576</v>
       </c>
-      <c r="F34" s="5" t="n">
+      <c r="F35" s="5" t="n">
         <v>31612</v>
       </c>
-      <c r="G34" s="5" t="n">
+      <c r="G35" s="5" t="n">
         <v>35106</v>
       </c>
-      <c r="H34" s="5" t="n">
+      <c r="H35" s="5" t="n">
         <v>32105</v>
       </c>
-      <c r="I34" s="5" t="n">
+      <c r="I35" s="5" t="n">
         <v>51123</v>
       </c>
-      <c r="J34" s="5" t="n">
+      <c r="J35" s="5" t="n">
         <v>32380</v>
       </c>
-      <c r="K34" s="5" t="n">
+      <c r="K35" s="5" t="n">
         <v>35546</v>
       </c>
-      <c r="L34" s="5" t="n">
+      <c r="L35" s="5" t="n">
         <v>44743</v>
       </c>
-      <c r="M34" s="5" t="n">
+      <c r="M35" s="5" t="n">
         <v>25679</v>
       </c>
-      <c r="N34" s="5" t="n">
+      <c r="N35" s="5" t="n">
         <v>31871</v>
       </c>
-      <c r="O34" s="5" t="n">
+      <c r="O35" s="5" t="n">
         <v>26246</v>
       </c>
-      <c r="P34" s="5" t="n">
+      <c r="P35" s="5" t="n">
         <v>-26096</v>
       </c>
-      <c r="Q34" s="5" t="n">
+      <c r="Q35" s="5" t="n">
         <v>14004</v>
       </c>
-      <c r="R34" s="5" t="n">
+      <c r="R35" s="5" t="n">
         <v>26544</v>
       </c>
-      <c r="S34" s="5" t="n">
+      <c r="S35" s="5" t="n">
         <v>-15142</v>
       </c>
     </row>
-    <row r="36" ht="180" customHeight="1">
-      <c r="A36" s="8" t="inlineStr">
+    <row r="37" ht="180" customHeight="1">
+      <c r="A37" s="8" t="inlineStr">
         <is>
           <t>Sources - Bank of China (UK) Limited's own Income Statement / Statement of Comprehensive Income (Bank/solo basis), £'000, each year's own originally-published report:
 FY2025: Annual Report 2025, p.47-48 - https://pic.bankofchina.com/bocappd/uk/202605/P020260506389809417235.pdf
@@ -10040,7 +10101,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A36:S36"/>
+    <mergeCell ref="A37:S37"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -14977,7 +15038,7 @@
 FY2010: Annual Report 2011's own FY2010 comparative column, p.26 - https://pic.bankofchina.com/bocappd/uk/201301/P020130110394685934112.pdf (AR2010_URL note: the Bank's own FY2010 Annual Report PDF is a scanned/photocopied document (Canon iR-ADV C5045 scanner output, the same scanner/pattern as FY2014's own PDF) with no extractable text layer. FY2010 figures on every sheet are therefore taken from the FY2011 Annual Report's own FY2010 comparative column instead (a real, live, text-searchable document), the same each-year's-own-report-one-year-removed methodology used for FY2014 via AR2015.)
 FY2009: 2009 Report and Financial Statements, p.33 - https://pic.bankofchina.com/bocappd/uk/201109/P020110901339600023124.pdf
 FY2008: 2009 Report's own FY2008 comparative column, p.33 - https://pic.bankofchina.com/bocappd/uk/201109/P020110901339600023124.pdf, cross-checked against the Bank's own 2008 Report and Financial Statements (Statement of Cash Flows, p.31) - https://pic.bankofchina.com/bocappd/uk/201109/P020110901339400504145.pdf (figures identical). FY2008 period note: Bank of China (UK) Limited's first accounting period ran 1 April 2007 - 30 September 2007 (a 6-month stub, outside this workbook's scope), and its second and only 'FY2008' statutory period is genuinely a 15-month period from 1 October 2007 to 31 December 2008 (the year-end was moved to December during this period) - not a standard 12-month year. Both the Bank's own FY2008 Report and Financial Statements (AR2008_URL) and the FY2009 Report's own FY2008 comparative column (AR2009_URL) show this identical 15-month figure set, cross-checked and tying exactly. Shown here as 'FY2008' per this workbook's year-labelling convention, but flagged as non-comparable in length to every other year in this workbook - growth trends spanning the FY2008/FY2009 boundary should be read with that caveat.
-FY2008-FY2020 presentation note: through FY2020's own report, 'Dividend paid' and 'Interest paid' sit inside the operating-activities 'Adjustment for cash items' subsection (own rows here, labelled '...FY2008-FY2020 presentation' to distinguish them from the FY2021-onward financing-section rows of the same name, which are left blank for FY2008-FY2020 rather than merged into a single row spanning two different statement sections); 'Cash flows from financing activities' is genuinely nil every year FY2008-FY2019 and, in FY2020's own report, contains only the new lease-liability repayment line. FY2014's cash flow reconciles a genuine £100k discrepancy against the Balance Sheet (see the Balance Sheet sheet's own source note); every other year's cash-flow closing balance ties exactly to that year's own Balance Sheet cash figure. Individual reconciling items were independently verified by summing each year's disclosed components back to that year's own reported 'Net cash generated from operating activities' total (all matched exactly), used as a correction check against several PDFs' garbled OCR text (e.g. FY2014's 'Acquisition of intangible assets' printed without its minus sign was resolved to -£426k this way).
+FY2008-FY2020 presentation note: through FY2020's own report, 'Dividend paid' and 'Interest paid' sit inside the operating-activities 'Adjustment for cash items' subsection (own rows here, labelled '...FY2008-FY2020 presentation' to distinguish them from the FY2021-onward financing-section rows of the same name, which are left blank for FY2008-FY2020 rather than merged into a single row spanning two different statement sections); 'Cash flows from financing activities' is genuinely nil every year FY2008-FY2019 and, in FY2020's own report, contains only the new lease-liability repayment line. FY2014's cash flow figure (£199,854k) was confirmed against the Balance Sheet's own internal subtotal arithmetic (see the Balance Sheet sheet's own source note, HD-081 2026-09-07) - the Balance Sheet's originally-transcribed £199,954k was a single-digit misread that broke its own 'Total assets' subtotal by £100k; every year's cash-flow closing balance ties exactly to that year's own Balance Sheet cash figure. Individual reconciling items were independently verified by summing each year's disclosed components back to that year's own reported 'Net cash generated from operating activities' total (all matched exactly), used as a correction check against several PDFs' garbled OCR text (e.g. FY2014's 'Acquisition of intangible assets' printed without its minus sign was resolved to -£426k this way).
 HD-075 extension presentation notes (FY2008-FY2013): FY2008-FY2009's own statements separately disclose 'Change in derivative assets/liabilities held for risk management' (folded into the FY2014+ 'Change in derivative financial instruments assets/liabilities' rows here); FY2010-FY2012 combine both into a single 'Change in derivatives held for risk management' line instead (its own row, not force-split). FY2012's own statement presents 'Proceeds from the issue of ordinary shares' (£110,000k, the same capital raise recorded on the Statement of Changes in Equity sheet) and 'Investment in subsidiaries' (£62,210k, the same-year subsidiary disposal) both under investing activities rather than financing (own rows, noting this year's presentation); FY2013's own restated FY2012 comparative instead splits the ordinary-share proceeds into financing activities - this workbook uses each year's own originally-published presentation throughout, per project convention, so FY2012's own figures stay under investing here. FY2013's own statement has no corresponding 'Loss/(gain) on disposal of subsidiary' cash-flow addback despite the Income Statement's one-off £1,632k gain that year - confirmed absent by full-text reading of the OCR'd document and by the fact that FY2013's own operating/investing/financing subtotals already tie exactly to its own disclosed opening/closing cash balances without one (see AR2013_SCAN_NOTE). FY2009's own statement includes a standalone 'Effects of exchange-rate changes on cash and cash equivalents' line (-£2,477k) between the net movement and closing balance, not present in any other year (own row). Every FY2008-FY2013 year's cash-flow closing balance ties exactly to that year's own Balance Sheet cash figure, and every operating/investing/financing subtotal for these 6 years was independently verified by full-component summation against each year's own disclosed net-movement and opening/closing balances (all matched exactly, including through the FY2013 OCR reconstruction).
 Restatement note: FY2023's own report marks its FY2022 comparative column 'Restated' and shows different figures (e.g. operating activities -£17,138k, closing cash £687,013k) to FY2022's own originally-published report (operating activities +£22,570k, closing cash £657,656k). This workbook uses each year's own originally-published figures as the primary column (project convention), which creates a genuine, disclosed £29,357k gap between FY2022's own closing balance and FY2023's own opening balance - flagged here rather than silently blended or force-reconciled. The underlying cause of the restatement is not explained in either source.
 Presentation notes: FY2021-FY2023 include small 'Exchange rate movements on plant and equipment/on equity' lines not present in FY2024/FY2025's statements. FY2022 alone shows a one-off Tier 2-to-AT1 capital replacement (subordinated debt of £60,000k repaid, an equal Additional Tier 1 instrument issued, both under financing activities). FY2025's own report split 'Change in financial assets at amortised cost/fair value' into two lines (the government-bond component shown separately) and separated lease-liability cash flows into principal and interest portions for the first time - both are FY2025-only presentational changes with no net impact on any section total. FY2025's own supplementary 'cash and cash equivalents comprise' note totals £1,073,245k (£157k less than the statement's own £1,073,402k closing balance), a gap matching the same page's separately-shown expected-credit-loss allowance of £157k - the statement's own total is used as the primary closing-balance figure here. FY2022's own report does not break out a separate 'Interest paid on Additional Tier 1 instrument' line (the AT1 instrument was only issued in June 2022); FY2023's restated FY2022 comparative does show one (£1,759k), consistent with the broader FY2022 restatement noted above - not included here since it wasn't part of FY2022's own originally-published statement.

--- a/banks/BANK OF CHINA UK FINANCIALS.xlsx
+++ b/banks/BANK OF CHINA UK FINANCIALS.xlsx
@@ -5100,7 +5100,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:M12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -5205,31 +5205,11 @@
           <t>Not publicly disclosed — category breakdown</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="6" t="n"/>
       <c r="G4" s="6" t="n"/>
       <c r="H4" s="6" t="n"/>
       <c r="I4" s="6" t="inlineStr">
@@ -5264,11 +5244,21 @@
           <t>Credit risk (excluding counterparty credit risk, standardised approach)</t>
         </is>
       </c>
-      <c r="B5" s="6" t="n"/>
-      <c r="C5" s="6" t="n"/>
-      <c r="D5" s="6" t="n"/>
-      <c r="E5" s="6" t="n"/>
-      <c r="F5" s="6" t="n"/>
+      <c r="B5" s="6" t="n">
+        <v>606687</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>662567</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>641596</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>730027</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>793055</v>
+      </c>
       <c r="G5" s="6" t="n">
         <v>822496</v>
       </c>
@@ -5284,20 +5274,24 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Credit valuation adjustment (CVA)</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="n"/>
-      <c r="C6" s="6" t="n"/>
-      <c r="D6" s="6" t="n"/>
-      <c r="E6" s="6" t="n"/>
+          <t>Counterparty credit risk (CCR, standardised approach)</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>5053</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>8763</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>6946</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>19086</v>
+      </c>
       <c r="F6" s="6" t="n"/>
-      <c r="G6" s="6" t="n">
-        <v>114722</v>
-      </c>
-      <c r="H6" s="6" t="n">
-        <v>12598</v>
-      </c>
+      <c r="G6" s="6" t="n"/>
+      <c r="H6" s="6" t="n"/>
       <c r="I6" s="6" t="n"/>
       <c r="J6" s="6" t="n"/>
       <c r="K6" s="6" t="n"/>
@@ -5307,19 +5301,29 @@
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>Market risk (standardised approach)</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="n"/>
-      <c r="C7" s="6" t="n"/>
-      <c r="D7" s="6" t="n"/>
-      <c r="E7" s="6" t="n"/>
-      <c r="F7" s="6" t="n"/>
+          <t>Credit valuation adjustment (CVA)</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>31552</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>94533</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>74760</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>198501</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>93581</v>
+      </c>
       <c r="G7" s="6" t="n">
-        <v>11621</v>
+        <v>114722</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>5448</v>
+        <v>12598</v>
       </c>
       <c r="I7" s="6" t="n"/>
       <c r="J7" s="6" t="n"/>
@@ -5330,19 +5334,29 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Operational risk</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="n"/>
-      <c r="C8" s="6" t="n"/>
-      <c r="D8" s="6" t="n"/>
-      <c r="E8" s="6" t="n"/>
-      <c r="F8" s="6" t="n"/>
+          <t>Market risk (standardised approach)</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>1231</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>1143</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>766</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>4394</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>14056</v>
+      </c>
       <c r="G8" s="6" t="n">
-        <v>202676</v>
+        <v>11621</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>187641</v>
+        <v>5448</v>
       </c>
       <c r="I8" s="6" t="n"/>
       <c r="J8" s="6" t="n"/>
@@ -5351,62 +5365,99 @@
       <c r="M8" s="6" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Operational risk</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>363586</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>339893</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>300383</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>224618</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>218688</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>202676</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>187641</v>
+      </c>
+      <c r="I9" s="6" t="n"/>
+      <c r="J9" s="6" t="n"/>
+      <c r="K9" s="6" t="n"/>
+      <c r="L9" s="6" t="n"/>
+      <c r="M9" s="6" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>Total risk exposure amount</t>
         </is>
       </c>
-      <c r="B9" s="5" t="n">
+      <c r="B10" s="5" t="n">
         <v>1008110</v>
       </c>
-      <c r="C9" s="5" t="n">
+      <c r="C10" s="5" t="n">
         <v>1106898</v>
       </c>
-      <c r="D9" s="5" t="n">
+      <c r="D10" s="5" t="n">
         <v>1024452</v>
       </c>
-      <c r="E9" s="5" t="n">
+      <c r="E10" s="5" t="n">
         <v>1176625</v>
       </c>
-      <c r="F9" s="5" t="n">
+      <c r="F10" s="5" t="n">
         <v>1119380</v>
       </c>
-      <c r="G9" s="5" t="n">
+      <c r="G10" s="5" t="n">
         <v>1151516</v>
       </c>
-      <c r="H9" s="5" t="n">
+      <c r="H10" s="5" t="n">
         <v>988901</v>
       </c>
-      <c r="I9" s="5" t="n">
+      <c r="I10" s="5" t="n">
         <v>941052</v>
       </c>
-      <c r="J9" s="5" t="n">
+      <c r="J10" s="5" t="n">
         <v>931206</v>
       </c>
-      <c r="K9" s="5" t="n">
+      <c r="K10" s="5" t="n">
         <v>1003913</v>
       </c>
-      <c r="L9" s="5" t="n">
+      <c r="L10" s="5" t="n">
         <v>895473</v>
       </c>
-      <c r="M9" s="5" t="n">
+      <c r="M10" s="5" t="n">
         <v>800993</v>
       </c>
     </row>
-    <row r="11" ht="220" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>Sources - Bank of China (UK) Limited's UK KM1 Key Metrics tables (same 5 Pillar 3 documents as the Total RWAs sheet):
-FY2025 &amp; FY2024 comparative: Pillar 3 Disclosure 31 December 2025, p.15 - https://pic.bankofchina.com/bocappd/uk/202607/P020260716391457618567.pdf
-FY2023-FY2021: see p3_sources() citations on the Total RWAs sheet.
-NOT DISCLOSED (category breakdown) for FY2014-FY2018 and FY2021-FY2025: none of those Pillar 3 documents contains a UK OV1/'Overview of risk weighted assets' table breaking RWA down by risk category - confirmed by reading the FY2025 document's own table of contents and KM1 template in full, and each of the FY2014-FY2018 documents' own Table 1 in full. Only the single aggregate Total RWA figure exists for those 10 years (see the Total RWAs sheet, which this sheet's Total row ties out to exactly).
-FY2020 (own year) &amp; FY2019 comparative: the FY2020 Pillar 3 document's own Table 9 'Overview of risk weighted assets' (UK OV1 template), p.20-22 - {P3_2020_URL}. The only year in this bank's whole 12-year history where a category breakdown was found - it splits Credit risk (standardised approach only), Credit valuation adjustment (CVA), Market risk (standardised approach only) and Operational risk, each tying exactly to the Total RWAs sheet's own aggregate figure for both years.</t>
+    <row r="12" ht="280" customHeight="1">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>Sources - Bank of China (UK) Limited's own UK OV1/EU OV1 'Overview of risk weighted exposure amounts' tables (same 5 Pillar 3 documents as the Total RWAs sheet), each year's own originally-published figures used as primary (not a later restated comparative), per project convention:
+FY2025: Pillar 3 Disclosure 2025, Table 'UK OV1' - https://pic.bankofchina.com/bocappd/uk/202607/P020260716391457618567.pdf
+FY2024: Pillar 3 Disclosure 2024, Table 'UK OV1' - https://www.bankofchina.com/uk/aboutus/ab5/202507/P020250718380587744231.pdf
+FY2023: Pillar 3 Disclosure 2023, Table 'UK OV1', p.15 - https://www.bankofchina.com/uk/aboutus/ab5/202410/P020241008402737321677.pdf
+FY2022: Pillar 3 Disclosure 2022, Table 'UK OV1', p.16 - https://www.bankofchina.com/uk/aboutus/ab5/202310/P020231026347190320350.pdf
+FY2021: Pillar 3 Disclosure 2021, Table 1 'Template EU OV1', p.14 - https://www.bankofchina.com/uk/aboutus/ab5/202303/P020230315381669571541.pdf
+FY2020 (own year) &amp; FY2019 comparative: the FY2020 Pillar 3 document's own Table 9 'Overview of risk weighted assets' (UK OV1 template), p.20-22 - https://pic.bankofchina.com/bocappd/uk/202110/P020211027537761891740.pdf
+CORRECTION (fresh re-verification, 2026-09-12): the prior version of this sheet claimed FY2021-FY2025 (and FY2014-FY2018) had no category-level breakdown disclosed. That was wrong for FY2021-FY2025 - every one of those 5 Pillar 3 documents was re-read directly and each contains a full OV1/EU OV1 table, with every year's Total tying exactly to the Total RWAs sheet's own figure. FY2014-FY2018 were not re-checked in this pass (out of scope - this re-verification targeted the last-5-years gap) and remain as previously documented pending a future check.
+TEMPLATE FORMAT CHANGE: FY2021's own document does not carry a separate 'Counterparty credit risk (CCR)' line (only Credit risk, CVA, Market risk, Operational risk) - the following year's own document's FY2021 comparative column DOES split out a CCR figure (£16,535k) with a correspondingly smaller credit-risk figure (£776,521k vs £793,055k as FY2021's own document states it, a difference of £16,534k), confirming the CCR amount was folded into the 'credit risk' line in FY2021's own original publication rather than omitted entirely. FY2021's own originally-published split is used here per project convention, with the later restatement noted rather than silently substituted. FY2022 onward carries CCR as its own explicit line every year.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A11:M11"/>
+    <mergeCell ref="A12:M12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/banks/BANK OF CHINA UK FINANCIALS.xlsx
+++ b/banks/BANK OF CHINA UK FINANCIALS.xlsx
@@ -13,18 +13,19 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Statement of Changes in Equity" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flow Statement" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Asset Quality" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Capital" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Ratio" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Capital" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Ratio" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital Ratio" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total RWAs" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RWA Breakdown" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leverage Ratio" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LCR" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NSFR" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MREL Ratio" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KM1 Key Metrics" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Capital" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Ratio" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Capital" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Ratio" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital Ratio" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total RWAs" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RWA Breakdown" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leverage Ratio" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LCR" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NSFR" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MREL Ratio" sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4345,14 +4346,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Bank of China (UK) Limited — Tier 1 Ratio</t>
+          <t>Bank of China (UK) Limited — Tier 1 Capital</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>% of RWA</t>
+          <t>£'000</t>
         </is>
       </c>
     </row>
@@ -4426,74 +4427,50 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Tier 1 ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>33.2%</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>30.2%</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>32.7%</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>28.5%</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>24.6%</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>26.7%</t>
-        </is>
-      </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>27.8%</t>
-        </is>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>29.2%</t>
-        </is>
-      </c>
-      <c r="J4" s="6" t="inlineStr">
-        <is>
-          <t>30%</t>
-        </is>
-      </c>
-      <c r="K4" s="6" t="inlineStr">
-        <is>
-          <t>27%</t>
-        </is>
-      </c>
-      <c r="L4" s="6" t="inlineStr">
-        <is>
-          <t>31%</t>
-        </is>
-      </c>
-      <c r="M4" s="6" t="inlineStr">
-        <is>
-          <t>34%</t>
-        </is>
+          <t>Tier 1 capital</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>334521</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>334294</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>335056</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>335000</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>275164</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>307058</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>274958</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>274958</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>274958</v>
+      </c>
+      <c r="K4" s="6" t="n">
+        <v>274958</v>
+      </c>
+      <c r="L4" s="6" t="n">
+        <v>274958</v>
+      </c>
+      <c r="M4" s="6" t="n">
+        <v>274958</v>
       </c>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Note: Numerically equal to the CET1 ratio every year FY2014-FY2021 since Tier 1 capital equalled CET1 capital exactly (no AT1 in issue until June 2022); each year's own Table 1/KM1 document states this explicitly as its own 'Tier 1 capital ratio' line, not just inferred.</t>
+          <t>Note: Equal to CET1 capital every year FY2014-FY2021 (no AT1 instruments in issue until June 2022). A £60m Additional Tier 1 instrument was issued in June 2022, replacing an equal amount of Tier 2 subordinated debt.</t>
         </is>
       </c>
     </row>
@@ -4534,7 +4511,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -4555,14 +4532,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Bank of China (UK) Limited — Total Capital</t>
+          <t>Bank of China (UK) Limited — Tier 1 Ratio</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>£'000</t>
+          <t>% of RWA</t>
         </is>
       </c>
     </row>
@@ -4636,48 +4613,79 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total regulatory capital</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>334521</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>334294</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>335056</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>335000</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>335164</v>
-      </c>
-      <c r="G4" s="6" t="n">
-        <v>367058</v>
-      </c>
-      <c r="H4" s="6" t="n">
-        <v>334958</v>
-      </c>
-      <c r="I4" s="6" t="n">
-        <v>334958</v>
-      </c>
-      <c r="J4" s="6" t="n">
-        <v>334958</v>
-      </c>
-      <c r="K4" s="6" t="n">
-        <v>334958</v>
-      </c>
-      <c r="L4" s="6" t="n">
-        <v>334958</v>
-      </c>
-      <c r="M4" s="6" t="n">
-        <v>334958</v>
-      </c>
-    </row>
-    <row r="6" ht="170" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
+          <t>Tier 1 ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>33.2%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>30.2%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>32.7%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>28.5%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>24.6%</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>26.7%</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>27.8%</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>29.2%</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="K4" s="6" t="inlineStr">
+        <is>
+          <t>27%</t>
+        </is>
+      </c>
+      <c r="L4" s="6" t="inlineStr">
+        <is>
+          <t>31%</t>
+        </is>
+      </c>
+      <c r="M4" s="6" t="inlineStr">
+        <is>
+          <t>34%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Note: Numerically equal to the CET1 ratio every year FY2014-FY2021 since Tier 1 capital equalled CET1 capital exactly (no AT1 in issue until June 2022); each year's own Table 1/KM1 document states this explicitly as its own 'Tier 1 capital ratio' line, not just inferred.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="170" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Sources - Bank of China (UK) Limited Pillar 3 disclosures (UK KM1 Key Metrics template from FY2022 onward; FY2021's own document is narrative/ratio-only and predates the KM1 template; FY2014-FY2020 use the pre-KM1 CRD IV 'Table 1: Total capital resources and risk asset ratios' / 'Table 2: Leverage ratio' narrative-table format), £'000 unless stated:
 FY2025 &amp; FY2024 comparative: Pillar 3 Disclosure 31 December 2025, p.15 (UK KM1) - https://pic.bankofchina.com/bocappd/uk/202607/P020260716391457618567.pdf
@@ -4699,8 +4707,9 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A6:M6"/>
+  <mergeCells count="2">
+    <mergeCell ref="A5:M5"/>
+    <mergeCell ref="A7:M7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4733,14 +4742,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Bank of China (UK) Limited — Total Capital Ratio</t>
+          <t>Bank of China (UK) Limited — Total Capital</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>% of RWA</t>
+          <t>£'000</t>
         </is>
       </c>
     </row>
@@ -4814,68 +4823,44 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total capital ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>33.2%</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>30.2%</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>32.7%</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>28.5%</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>29.9%</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>31.9%</t>
-        </is>
-      </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>33.9%</t>
-        </is>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>35.6%</t>
-        </is>
-      </c>
-      <c r="J4" s="6" t="inlineStr">
-        <is>
-          <t>36%</t>
-        </is>
-      </c>
-      <c r="K4" s="6" t="inlineStr">
-        <is>
-          <t>33%</t>
-        </is>
-      </c>
-      <c r="L4" s="6" t="inlineStr">
-        <is>
-          <t>37%</t>
-        </is>
-      </c>
-      <c r="M4" s="6" t="inlineStr">
-        <is>
-          <t>42%</t>
-        </is>
+          <t>Total regulatory capital</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>334521</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>334294</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>335056</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>335000</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>335164</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>367058</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>334958</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>334958</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>334958</v>
+      </c>
+      <c r="K4" s="6" t="n">
+        <v>334958</v>
+      </c>
+      <c r="L4" s="6" t="n">
+        <v>334958</v>
+      </c>
+      <c r="M4" s="6" t="n">
+        <v>334958</v>
       </c>
     </row>
     <row r="6" ht="170" customHeight="1">
@@ -4909,6 +4894,208 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Bank of China (UK) Limited — Total Capital Ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>% of RWA</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>FY2017</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>FY2016</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>FY2015</t>
+        </is>
+      </c>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>FY2014</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Total capital ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>33.2%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>30.2%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>32.7%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>28.5%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>29.9%</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>31.9%</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>33.9%</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>35.6%</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>36%</t>
+        </is>
+      </c>
+      <c r="K4" s="6" t="inlineStr">
+        <is>
+          <t>33%</t>
+        </is>
+      </c>
+      <c r="L4" s="6" t="inlineStr">
+        <is>
+          <t>37%</t>
+        </is>
+      </c>
+      <c r="M4" s="6" t="inlineStr">
+        <is>
+          <t>42%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="170" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Sources - Bank of China (UK) Limited Pillar 3 disclosures (UK KM1 Key Metrics template from FY2022 onward; FY2021's own document is narrative/ratio-only and predates the KM1 template; FY2014-FY2020 use the pre-KM1 CRD IV 'Table 1: Total capital resources and risk asset ratios' / 'Table 2: Leverage ratio' narrative-table format), £'000 unless stated:
+FY2025 &amp; FY2024 comparative: Pillar 3 Disclosure 31 December 2025, p.15 (UK KM1) - https://pic.bankofchina.com/bocappd/uk/202607/P020260716391457618567.pdf
+FY2024 (own year) &amp; FY2023 comparative: Pillar 3 Disclosures 31 December 2024, p.16 (UK KM1) - https://www.bankofchina.com/uk/aboutus/ab5/202507/P020250718380587744231.pdf
+FY2023 (own year) &amp; FY2022 comparative: Pillar 3 disclosures 31 December 2023, p.14 (UK KM1) - https://www.bankofchina.com/uk/aboutus/ab5/202410/P020241008402737321677.pdf
+FY2022 (own year) &amp; FY2021 comparative: Pillar 3 Disclosures 2022, p.14 (UK KM1) - https://www.bankofchina.com/uk/aboutus/ab5/202310/P020231026347190320350.pdf
+FY2021 (own year, narrative/ratio-only - no KM1 template yet): Pillar 3 Disclosures 2021, p.12-14, 24 - https://www.bankofchina.com/uk/aboutus/ab5/202303/P020230315381669571541.pdf
+FY2021 note: the Bank's own FY2021 Pillar 3 document states CET1/Total Capital as rounded £275m/£335m and gives no £-breakdown for leverage exposure, LCR HQLA/outflow, or NSFR (NSFR was not yet a formal disclosure). The precise FY2021 figures used on those sheets (CET1/Tier 1 £275,164k, Total Capital £335,164k, leverage exposure £2,431,869k, LCR HQLA £527,697k/outflow £294,774k, NSFR £1,438,026k/£950,742k) are taken from the FY2022 Pillar 3 document's FY2021 comparative column instead, since it is the more complete disclosure - all overlapping ratios (CET1 24.6%, Total Capital 29.9%, Leverage 11.3%, LCR 179.0%) match the FY2021 document's own narrative figures exactly.
+FY2020 (own year) &amp; FY2019 comparative: Pillar 3 Disclosures 31 December 2020, Table 9 'Overview of risk weighted assets', p.20-22, Table 31 'Liquidity coverage ratio' - https://pic.bankofchina.com/bocappd/uk/202110/P020211027537761891740.pdf
+FY2019 (own year) &amp; FY2018 comparative: Pillar 3 Disclosures 31 December 2019, p.16-19, 33 - https://pic.bankofchina.com/bocappd/uk/202009/P020200909535865685853.pdf
+FY2018 (own year) &amp; FY2017 comparative: Pillar 3 Disclosures 31 December 2018, p.15-18, 31 - https://pic.bankofchina.com/bocappd/uk/201904/P020190410408108385209.pdf
+FY2017 (own year) &amp; FY2016 comparative: Pillar 3 Disclosures 2017, Table 1/Table 2, p.9-10 - https://pic.bankofchina.com/bocappd/uk/201803/P020180328577372288229.pdf
+FY2016 (own year) &amp; FY2015 comparative: Pillar 3 Disclosures 2016, Table 1/Table 2, p.10-11 - https://pic.bankofchina.com/bocappd/uk/201706/P020170627381103226068.pdf
+FY2015 (own year) &amp; FY2014 comparative: Pillar III Disclosures 2015, Table 1/Table 2, p.9-10 - https://pic.bankofchina.com/bocappd/uk/201606/P020160620504436264971.pdf
+FY2014 (own year) &amp; FY2013 comparative: Pillar III Disclosure 2014, Table 1/Table 2, p.8-9 - https://pic.bankofchina.com/bocappd/uk/201509/P020150910375228515274.pdf
+FY2014-FY2017 note: 'Tier 1 capital' equals 'CET1 capital' every year (£274,958k throughout - the Bank issued no AT1 instruments until far later) and 'Total capital' equals CET1 capital plus the £60,000k Tier 2 subordinated debt facility, both stated directly in each year's own Table 1. LCR and NSFR are genuinely undisclosed for FY2014-FY2016 (no LCR/HQLA/NSFR concept appears anywhere in those 3 documents, confirmed by reading each in full); FY2017's LCR ratio (167%) is not in FY2017's own document at all (confirmed absent) but appears as the FY2018 Pillar 3 document's own FY2017 comparative column, the earliest point any LCR figure for this bank exists - shown here with no £-breakdown since none is given for that comparative year. RWA breakdown by risk category (credit/market/operational/CVA) is genuinely undisclosed for FY2014-FY2018 (only the single aggregate RWA figure appears in each Table 1); the FY2020 Pillar 3 document introduces a full 'Table 9: Overview of risk weighted assets' (its own year plus its own FY2019 comparative column), the first and only such breakdown found across all 12 years covered.
+Entity note: Bank of China (UK) Limited (company 06193060, FRN 467410) is a wholly-owned UK subsidiary of Bank of China Limited (state-owned). It does not take the FRS 101/102 cash-flow-statement exemption - a full Statement of Cash Flows is published every year. All figures are the Bank's own solo entity basis throughout.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A6:M6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5094,7 +5281,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5463,7 +5650,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5711,274 +5898,6 @@
   <mergeCells count="2">
     <mergeCell ref="A8:M8"/>
     <mergeCell ref="A6:M6"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:M9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="15" customWidth="1" min="12" max="12"/>
-    <col width="15" customWidth="1" min="13" max="13"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Bank of China (UK) Limited — LCR</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>£'000 / %</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>FY2020</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>FY2019</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>FY2018</t>
-        </is>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>FY2017</t>
-        </is>
-      </c>
-      <c r="K3" s="4" t="inlineStr">
-        <is>
-          <t>FY2016</t>
-        </is>
-      </c>
-      <c r="L3" s="4" t="inlineStr">
-        <is>
-          <t>FY2015</t>
-        </is>
-      </c>
-      <c r="M3" s="4" t="inlineStr">
-        <is>
-          <t>FY2014</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Total high-quality liquid assets (HQLA)</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>1007375</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>1014087</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>677646</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>545654</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>527697</v>
-      </c>
-      <c r="G4" s="6" t="n">
-        <v>360820</v>
-      </c>
-      <c r="H4" s="6" t="n">
-        <v>302154</v>
-      </c>
-      <c r="I4" s="6" t="n">
-        <v>381928</v>
-      </c>
-      <c r="J4" s="6" t="n"/>
-      <c r="K4" s="6" t="n"/>
-      <c r="L4" s="6" t="n"/>
-      <c r="M4" s="6" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>Total net cash outflow</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="n">
-        <v>310866</v>
-      </c>
-      <c r="C5" s="6" t="n">
-        <v>272240</v>
-      </c>
-      <c r="D5" s="6" t="n">
-        <v>174967</v>
-      </c>
-      <c r="E5" s="6" t="n">
-        <v>299877</v>
-      </c>
-      <c r="F5" s="6" t="n">
-        <v>294774</v>
-      </c>
-      <c r="G5" s="6" t="n">
-        <v>148715</v>
-      </c>
-      <c r="H5" s="6" t="n">
-        <v>139559</v>
-      </c>
-      <c r="I5" s="6" t="n">
-        <v>164459</v>
-      </c>
-      <c r="J5" s="6" t="n"/>
-      <c r="K5" s="6" t="n"/>
-      <c r="L5" s="6" t="n"/>
-      <c r="M5" s="6" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>LCR ratio (%)</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>324.1%</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>372.5%</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>387.3%</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>182.0%</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>179.0%</t>
-        </is>
-      </c>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>243%</t>
-        </is>
-      </c>
-      <c r="H6" s="6" t="inlineStr">
-        <is>
-          <t>217%</t>
-        </is>
-      </c>
-      <c r="I6" s="6" t="inlineStr">
-        <is>
-          <t>232%</t>
-        </is>
-      </c>
-      <c r="J6" s="6" t="inlineStr">
-        <is>
-          <t>167%</t>
-        </is>
-      </c>
-      <c r="K6" s="6" t="n"/>
-      <c r="L6" s="6" t="n"/>
-      <c r="M6" s="6" t="n"/>
-    </row>
-    <row r="7" ht="60" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>Note: FY2017's 167% ratio is the only FY2017 LCR figure available anywhere (from the FY2018 Pillar 3 document's own FY2017 comparative column - FY2017's own document predates LCR disclosure entirely) and has no accompanying HQLA/outflow £-breakdown, hence the blank cells on those two rows. LCR is genuinely undisclosed for FY2014-FY2016 (confirmed absent from all three years' own Pillar 3 documents, read in full).</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="170" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>Sources - Bank of China (UK) Limited Pillar 3 disclosures (UK KM1 Key Metrics template from FY2022 onward; FY2021's own document is narrative/ratio-only and predates the KM1 template; FY2014-FY2020 use the pre-KM1 CRD IV 'Table 1: Total capital resources and risk asset ratios' / 'Table 2: Leverage ratio' narrative-table format), £'000 unless stated:
-FY2025 &amp; FY2024 comparative: Pillar 3 Disclosure 31 December 2025, p.15 (UK KM1) - https://pic.bankofchina.com/bocappd/uk/202607/P020260716391457618567.pdf
-FY2024 (own year) &amp; FY2023 comparative: Pillar 3 Disclosures 31 December 2024, p.16 (UK KM1) - https://www.bankofchina.com/uk/aboutus/ab5/202507/P020250718380587744231.pdf
-FY2023 (own year) &amp; FY2022 comparative: Pillar 3 disclosures 31 December 2023, p.14 (UK KM1) - https://www.bankofchina.com/uk/aboutus/ab5/202410/P020241008402737321677.pdf
-FY2022 (own year) &amp; FY2021 comparative: Pillar 3 Disclosures 2022, p.14 (UK KM1) - https://www.bankofchina.com/uk/aboutus/ab5/202310/P020231026347190320350.pdf
-FY2021 (own year, narrative/ratio-only - no KM1 template yet): Pillar 3 Disclosures 2021, p.12-14, 24 - https://www.bankofchina.com/uk/aboutus/ab5/202303/P020230315381669571541.pdf
-FY2021 note: the Bank's own FY2021 Pillar 3 document states CET1/Total Capital as rounded £275m/£335m and gives no £-breakdown for leverage exposure, LCR HQLA/outflow, or NSFR (NSFR was not yet a formal disclosure). The precise FY2021 figures used on those sheets (CET1/Tier 1 £275,164k, Total Capital £335,164k, leverage exposure £2,431,869k, LCR HQLA £527,697k/outflow £294,774k, NSFR £1,438,026k/£950,742k) are taken from the FY2022 Pillar 3 document's FY2021 comparative column instead, since it is the more complete disclosure - all overlapping ratios (CET1 24.6%, Total Capital 29.9%, Leverage 11.3%, LCR 179.0%) match the FY2021 document's own narrative figures exactly.
-FY2020 (own year) &amp; FY2019 comparative: Pillar 3 Disclosures 31 December 2020, Table 9 'Overview of risk weighted assets', p.20-22, Table 31 'Liquidity coverage ratio' - https://pic.bankofchina.com/bocappd/uk/202110/P020211027537761891740.pdf
-FY2019 (own year) &amp; FY2018 comparative: Pillar 3 Disclosures 31 December 2019, p.16-19, 33 - https://pic.bankofchina.com/bocappd/uk/202009/P020200909535865685853.pdf
-FY2018 (own year) &amp; FY2017 comparative: Pillar 3 Disclosures 31 December 2018, p.15-18, 31 - https://pic.bankofchina.com/bocappd/uk/201904/P020190410408108385209.pdf
-FY2017 (own year) &amp; FY2016 comparative: Pillar 3 Disclosures 2017, Table 1/Table 2, p.9-10 - https://pic.bankofchina.com/bocappd/uk/201803/P020180328577372288229.pdf
-FY2016 (own year) &amp; FY2015 comparative: Pillar 3 Disclosures 2016, Table 1/Table 2, p.10-11 - https://pic.bankofchina.com/bocappd/uk/201706/P020170627381103226068.pdf
-FY2015 (own year) &amp; FY2014 comparative: Pillar III Disclosures 2015, Table 1/Table 2, p.9-10 - https://pic.bankofchina.com/bocappd/uk/201606/P020160620504436264971.pdf
-FY2014 (own year) &amp; FY2013 comparative: Pillar III Disclosure 2014, Table 1/Table 2, p.8-9 - https://pic.bankofchina.com/bocappd/uk/201509/P020150910375228515274.pdf
-FY2014-FY2017 note: 'Tier 1 capital' equals 'CET1 capital' every year (£274,958k throughout - the Bank issued no AT1 instruments until far later) and 'Total capital' equals CET1 capital plus the £60,000k Tier 2 subordinated debt facility, both stated directly in each year's own Table 1. LCR and NSFR are genuinely undisclosed for FY2014-FY2016 (no LCR/HQLA/NSFR concept appears anywhere in those 3 documents, confirmed by reading each in full); FY2017's LCR ratio (167%) is not in FY2017's own document at all (confirmed absent) but appears as the FY2018 Pillar 3 document's own FY2017 comparative column, the earliest point any LCR figure for this bank exists - shown here with no £-breakdown since none is given for that comparative year. RWA breakdown by risk category (credit/market/operational/CVA) is genuinely undisclosed for FY2014-FY2018 (only the single aggregate RWA figure appears in each Table 1); the FY2020 Pillar 3 document introduces a full 'Table 9: Overview of risk weighted assets' (its own year plus its own FY2019 comparative column), the first and only such breakdown found across all 12 years covered.
-Entity note: Bank of China (UK) Limited (company 06193060, FRN 467410) is a wholly-owned UK subsidiary of Bank of China Limited (state-owned). It does not take the FRS 101/102 cash-flow-statement exemption - a full Statement of Cash Flows is published every year. All figures are the Bank's own solo entity basis throughout.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A9:M9"/>
-    <mergeCell ref="A7:M7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6011,7 +5930,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Bank of China (UK) Limited — NSFR</t>
+          <t>Bank of China (UK) Limited — LCR</t>
         </is>
       </c>
     </row>
@@ -6092,32 +6011,32 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total available stable funding</t>
+          <t>Total high-quality liquid assets (HQLA)</t>
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>1389486</v>
+        <v>1007375</v>
       </c>
       <c r="C4" s="6" t="n">
-        <v>1630136</v>
+        <v>1014087</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>1289845</v>
+        <v>677646</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>1463448</v>
+        <v>545654</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>1438026</v>
+        <v>527697</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>1429700</v>
+        <v>360820</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>1263428</v>
+        <v>302154</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>1219968</v>
+        <v>381928</v>
       </c>
       <c r="J4" s="6" t="n"/>
       <c r="K4" s="6" t="n"/>
@@ -6127,32 +6046,32 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Total required stable funding</t>
+          <t>Total net cash outflow</t>
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>714820</v>
+        <v>310866</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>752941</v>
+        <v>272240</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>959234</v>
+        <v>174967</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>1209361</v>
+        <v>299877</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>950742</v>
+        <v>294774</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>884460</v>
+        <v>148715</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>797680</v>
+        <v>139559</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>843948</v>
+        <v>164459</v>
       </c>
       <c r="J5" s="6" t="n"/>
       <c r="K5" s="6" t="n"/>
@@ -6162,50 +6081,54 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>NSFR ratio (%)</t>
+          <t>LCR ratio (%)</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>194.4%</t>
+          <t>324.1%</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>216.5%</t>
+          <t>372.5%</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>134.5%</t>
+          <t>387.3%</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>121.0%</t>
+          <t>182.0%</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>151.3%</t>
+          <t>179.0%</t>
         </is>
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>162%</t>
+          <t>243%</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>158%</t>
+          <t>217%</t>
         </is>
       </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
-          <t>145%</t>
-        </is>
-      </c>
-      <c r="J6" s="6" t="n"/>
+          <t>232%</t>
+        </is>
+      </c>
+      <c r="J6" s="6" t="inlineStr">
+        <is>
+          <t>167%</t>
+        </is>
+      </c>
       <c r="K6" s="6" t="n"/>
       <c r="L6" s="6" t="n"/>
       <c r="M6" s="6" t="n"/>
@@ -6213,7 +6136,7 @@
     <row r="7" ht="60" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>Note: FY2021's own Pillar 3 document does not disclose an NSFR figure at all (the UK NSFR regime's formal KM1 disclosure only started from FY2022) - the FY2021 figures here are taken from the FY2022 Pillar 3 document's FY2021 comparative column instead, the only source where they appear. NSFR is genuinely undisclosed for FY2014-FY2017 (confirmed absent from all four years' own Pillar 3 documents, read in full) - FY2018 is the earliest year any NSFR figure exists for this bank.</t>
+          <t>Note: FY2017's 167% ratio is the only FY2017 LCR figure available anywhere (from the FY2018 Pillar 3 document's own FY2017 comparative column - FY2017's own document predates LCR disclosure entirely) and has no accompanying HQLA/outflow £-breakdown, hence the blank cells on those two rows. LCR is genuinely undisclosed for FY2014-FY2016 (confirmed absent from all three years' own Pillar 3 documents, read in full).</t>
         </is>
       </c>
     </row>
@@ -6249,6 +6172,270 @@
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Bank of China (UK) Limited — NSFR</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>£'000 / %</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>FY2017</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>FY2016</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>FY2015</t>
+        </is>
+      </c>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>FY2014</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Total available stable funding</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>1389486</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>1630136</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>1289845</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>1463448</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>1438026</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>1429700</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>1263428</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>1219968</v>
+      </c>
+      <c r="J4" s="6" t="n"/>
+      <c r="K4" s="6" t="n"/>
+      <c r="L4" s="6" t="n"/>
+      <c r="M4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Total required stable funding</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>714820</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>752941</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>959234</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>1209361</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>950742</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>884460</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>797680</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>843948</v>
+      </c>
+      <c r="J5" s="6" t="n"/>
+      <c r="K5" s="6" t="n"/>
+      <c r="L5" s="6" t="n"/>
+      <c r="M5" s="6" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>NSFR ratio (%)</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>194.4%</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>216.5%</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>134.5%</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>121.0%</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>151.3%</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>162%</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>158%</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>145%</t>
+        </is>
+      </c>
+      <c r="J6" s="6" t="n"/>
+      <c r="K6" s="6" t="n"/>
+      <c r="L6" s="6" t="n"/>
+      <c r="M6" s="6" t="n"/>
+    </row>
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Note: FY2021's own Pillar 3 document does not disclose an NSFR figure at all (the UK NSFR regime's formal KM1 disclosure only started from FY2022) - the FY2021 figures here are taken from the FY2022 Pillar 3 document's FY2021 comparative column instead, the only source where they appear. NSFR is genuinely undisclosed for FY2014-FY2017 (confirmed absent from all four years' own Pillar 3 documents, read in full) - FY2018 is the earliest year any NSFR figure exists for this bank.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="170" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>Sources - Bank of China (UK) Limited Pillar 3 disclosures (UK KM1 Key Metrics template from FY2022 onward; FY2021's own document is narrative/ratio-only and predates the KM1 template; FY2014-FY2020 use the pre-KM1 CRD IV 'Table 1: Total capital resources and risk asset ratios' / 'Table 2: Leverage ratio' narrative-table format), £'000 unless stated:
+FY2025 &amp; FY2024 comparative: Pillar 3 Disclosure 31 December 2025, p.15 (UK KM1) - https://pic.bankofchina.com/bocappd/uk/202607/P020260716391457618567.pdf
+FY2024 (own year) &amp; FY2023 comparative: Pillar 3 Disclosures 31 December 2024, p.16 (UK KM1) - https://www.bankofchina.com/uk/aboutus/ab5/202507/P020250718380587744231.pdf
+FY2023 (own year) &amp; FY2022 comparative: Pillar 3 disclosures 31 December 2023, p.14 (UK KM1) - https://www.bankofchina.com/uk/aboutus/ab5/202410/P020241008402737321677.pdf
+FY2022 (own year) &amp; FY2021 comparative: Pillar 3 Disclosures 2022, p.14 (UK KM1) - https://www.bankofchina.com/uk/aboutus/ab5/202310/P020231026347190320350.pdf
+FY2021 (own year, narrative/ratio-only - no KM1 template yet): Pillar 3 Disclosures 2021, p.12-14, 24 - https://www.bankofchina.com/uk/aboutus/ab5/202303/P020230315381669571541.pdf
+FY2021 note: the Bank's own FY2021 Pillar 3 document states CET1/Total Capital as rounded £275m/£335m and gives no £-breakdown for leverage exposure, LCR HQLA/outflow, or NSFR (NSFR was not yet a formal disclosure). The precise FY2021 figures used on those sheets (CET1/Tier 1 £275,164k, Total Capital £335,164k, leverage exposure £2,431,869k, LCR HQLA £527,697k/outflow £294,774k, NSFR £1,438,026k/£950,742k) are taken from the FY2022 Pillar 3 document's FY2021 comparative column instead, since it is the more complete disclosure - all overlapping ratios (CET1 24.6%, Total Capital 29.9%, Leverage 11.3%, LCR 179.0%) match the FY2021 document's own narrative figures exactly.
+FY2020 (own year) &amp; FY2019 comparative: Pillar 3 Disclosures 31 December 2020, Table 9 'Overview of risk weighted assets', p.20-22, Table 31 'Liquidity coverage ratio' - https://pic.bankofchina.com/bocappd/uk/202110/P020211027537761891740.pdf
+FY2019 (own year) &amp; FY2018 comparative: Pillar 3 Disclosures 31 December 2019, p.16-19, 33 - https://pic.bankofchina.com/bocappd/uk/202009/P020200909535865685853.pdf
+FY2018 (own year) &amp; FY2017 comparative: Pillar 3 Disclosures 31 December 2018, p.15-18, 31 - https://pic.bankofchina.com/bocappd/uk/201904/P020190410408108385209.pdf
+FY2017 (own year) &amp; FY2016 comparative: Pillar 3 Disclosures 2017, Table 1/Table 2, p.9-10 - https://pic.bankofchina.com/bocappd/uk/201803/P020180328577372288229.pdf
+FY2016 (own year) &amp; FY2015 comparative: Pillar 3 Disclosures 2016, Table 1/Table 2, p.10-11 - https://pic.bankofchina.com/bocappd/uk/201706/P020170627381103226068.pdf
+FY2015 (own year) &amp; FY2014 comparative: Pillar III Disclosures 2015, Table 1/Table 2, p.9-10 - https://pic.bankofchina.com/bocappd/uk/201606/P020160620504436264971.pdf
+FY2014 (own year) &amp; FY2013 comparative: Pillar III Disclosure 2014, Table 1/Table 2, p.8-9 - https://pic.bankofchina.com/bocappd/uk/201509/P020150910375228515274.pdf
+FY2014-FY2017 note: 'Tier 1 capital' equals 'CET1 capital' every year (£274,958k throughout - the Bank issued no AT1 instruments until far later) and 'Total capital' equals CET1 capital plus the £60,000k Tier 2 subordinated debt facility, both stated directly in each year's own Table 1. LCR and NSFR are genuinely undisclosed for FY2014-FY2016 (no LCR/HQLA/NSFR concept appears anywhere in those 3 documents, confirmed by reading each in full); FY2017's LCR ratio (167%) is not in FY2017's own document at all (confirmed absent) but appears as the FY2018 Pillar 3 document's own FY2017 comparative column, the earliest point any LCR figure for this bank exists - shown here with no £-breakdown since none is given for that comparative year. RWA breakdown by risk category (credit/market/operational/CVA) is genuinely undisclosed for FY2014-FY2018 (only the single aggregate RWA figure appears in each Table 1); the FY2020 Pillar 3 document introduces a full 'Table 9: Overview of risk weighted assets' (its own year plus its own FY2019 comparative column), the first and only such breakdown found across all 12 years covered.
+Entity note: Bank of China (UK) Limited (company 06193060, FRN 467410) is a wholly-owned UK subsidiary of Bank of China Limited (state-owned). It does not take the FRS 101/102 cash-flow-statement exemption - a full Statement of Cash Flows is published every year. All figures are the Bank's own solo entity basis throughout.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A9:M9"/>
+    <mergeCell ref="A7:M7"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -16345,10 +16532,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="72" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
@@ -16366,21 +16553,21 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Bank of China (UK) Limited — CET1 Capital</t>
+          <t>Bank of China (UK) Limited — KM1 Key Metrics</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>£'000</t>
+          <t>The Bank's own published table, headed 'UK KM1 - Key Metrics', reproduced in its row order with its own row numbers, captions and precision — including the Basel III buffer/leverage row set it uses in place of the PRA template's, and its own mis-numbering of row 16 as '6'. Amounts in £'000, ratios as printed. FY2020 and earlier predate the template and are intentionally blank.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Metric</t>
+          <t>Line item</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
@@ -16445,50 +16632,830 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Common Equity Tier 1 (CET1) capital</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Available capital (£'000)</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="6" t="n"/>
+      <c r="G4" s="6" t="n"/>
+      <c r="H4" s="6" t="n"/>
+      <c r="I4" s="6" t="n"/>
+      <c r="J4" s="6" t="n"/>
+      <c r="K4" s="6" t="n"/>
+      <c r="L4" s="6" t="n"/>
+      <c r="M4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>1    Common equity tier 1 capital (CET1)</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
         <v>274521</v>
       </c>
-      <c r="C4" s="6" t="n">
+      <c r="C5" s="6" t="n">
         <v>274294</v>
       </c>
-      <c r="D4" s="6" t="n">
+      <c r="D5" s="6" t="n">
         <v>275056</v>
       </c>
-      <c r="E4" s="6" t="n">
+      <c r="E5" s="6" t="n">
         <v>275000</v>
       </c>
-      <c r="F4" s="6" t="n">
+      <c r="F5" s="6" t="n">
         <v>275164</v>
       </c>
-      <c r="G4" s="6" t="n">
-        <v>307058</v>
-      </c>
-      <c r="H4" s="6" t="n">
-        <v>274958</v>
-      </c>
-      <c r="I4" s="6" t="n">
-        <v>274958</v>
-      </c>
-      <c r="J4" s="6" t="n">
-        <v>274958</v>
-      </c>
-      <c r="K4" s="6" t="n">
-        <v>274958</v>
-      </c>
-      <c r="L4" s="6" t="n">
-        <v>274958</v>
-      </c>
-      <c r="M4" s="6" t="n">
-        <v>274958</v>
-      </c>
-    </row>
-    <row r="6" ht="170" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="G5" s="6" t="n"/>
+      <c r="H5" s="6" t="n"/>
+      <c r="I5" s="6" t="n"/>
+      <c r="J5" s="6" t="n"/>
+      <c r="K5" s="6" t="n"/>
+      <c r="L5" s="6" t="n"/>
+      <c r="M5" s="6" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>2    Tier 1 capital</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>334521</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>334294</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>335056</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>335000</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>275164</v>
+      </c>
+      <c r="G6" s="6" t="n"/>
+      <c r="H6" s="6" t="n"/>
+      <c r="I6" s="6" t="n"/>
+      <c r="J6" s="6" t="n"/>
+      <c r="K6" s="6" t="n"/>
+      <c r="L6" s="6" t="n"/>
+      <c r="M6" s="6" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>3    Total regulatory capital</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>334521</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>334294</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>335056</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>335000</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>335164</v>
+      </c>
+      <c r="G7" s="6" t="n"/>
+      <c r="H7" s="6" t="n"/>
+      <c r="I7" s="6" t="n"/>
+      <c r="J7" s="6" t="n"/>
+      <c r="K7" s="6" t="n"/>
+      <c r="L7" s="6" t="n"/>
+      <c r="M7" s="6" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Risk-weighted assets ('RWAs') (£'000)</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n"/>
+      <c r="C8" s="6" t="n"/>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="6" t="n"/>
+      <c r="G8" s="6" t="n"/>
+      <c r="H8" s="6" t="n"/>
+      <c r="I8" s="6" t="n"/>
+      <c r="J8" s="6" t="n"/>
+      <c r="K8" s="6" t="n"/>
+      <c r="L8" s="6" t="n"/>
+      <c r="M8" s="6" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>4    Total risk-weighted assets (RWA)</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>1008110</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>1106898</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>1024452</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>1176625</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>1119380</v>
+      </c>
+      <c r="G9" s="6" t="n"/>
+      <c r="H9" s="6" t="n"/>
+      <c r="I9" s="6" t="n"/>
+      <c r="J9" s="6" t="n"/>
+      <c r="K9" s="6" t="n"/>
+      <c r="L9" s="6" t="n"/>
+      <c r="M9" s="6" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Risk-based capital ratios as a percentage of RWA (%)</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n"/>
+      <c r="C10" s="6" t="n"/>
+      <c r="D10" s="6" t="n"/>
+      <c r="E10" s="6" t="n"/>
+      <c r="F10" s="6" t="n"/>
+      <c r="G10" s="6" t="n"/>
+      <c r="H10" s="6" t="n"/>
+      <c r="I10" s="6" t="n"/>
+      <c r="J10" s="6" t="n"/>
+      <c r="K10" s="6" t="n"/>
+      <c r="L10" s="6" t="n"/>
+      <c r="M10" s="6" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>5    Common Equity Tier 1 ratio (%)</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>27.2%</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>24.8%</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>26.8%</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>23.4%</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>24.6%</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="n"/>
+      <c r="H11" s="6" t="n"/>
+      <c r="I11" s="6" t="n"/>
+      <c r="J11" s="6" t="n"/>
+      <c r="K11" s="6" t="n"/>
+      <c r="L11" s="6" t="n"/>
+      <c r="M11" s="6" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>6    Tier 1 ratio (%)</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>33.2%</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>30.2%</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>32.7%</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>28.5%</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>24.6%</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="n"/>
+      <c r="H12" s="6" t="n"/>
+      <c r="I12" s="6" t="n"/>
+      <c r="J12" s="6" t="n"/>
+      <c r="K12" s="6" t="n"/>
+      <c r="L12" s="6" t="n"/>
+      <c r="M12" s="6" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>7    Total capital ratio (%)</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>33.2%</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>30.2%</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>32.7%</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>28.5%</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>29.9%</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="n"/>
+      <c r="H13" s="6" t="n"/>
+      <c r="I13" s="6" t="n"/>
+      <c r="J13" s="6" t="n"/>
+      <c r="K13" s="6" t="n"/>
+      <c r="L13" s="6" t="n"/>
+      <c r="M13" s="6" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Additional CET1 buffer requirements as a percentage of RWA (%)</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="6" t="n"/>
+      <c r="G14" s="6" t="n"/>
+      <c r="H14" s="6" t="n"/>
+      <c r="I14" s="6" t="n"/>
+      <c r="J14" s="6" t="n"/>
+      <c r="K14" s="6" t="n"/>
+      <c r="L14" s="6" t="n"/>
+      <c r="M14" s="6" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>8    Capital conservation buffer requirement (%)</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="n"/>
+      <c r="H15" s="6" t="n"/>
+      <c r="I15" s="6" t="n"/>
+      <c r="J15" s="6" t="n"/>
+      <c r="K15" s="6" t="n"/>
+      <c r="L15" s="6" t="n"/>
+      <c r="M15" s="6" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>9    Countercyclical buffer requirement (%)</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="n"/>
+      <c r="H16" s="6" t="n"/>
+      <c r="I16" s="6" t="n"/>
+      <c r="J16" s="6" t="n"/>
+      <c r="K16" s="6" t="n"/>
+      <c r="L16" s="6" t="n"/>
+      <c r="M16" s="6" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>10    Bank G-SIB and/or D-SIB additional requirements (%)</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="n"/>
+      <c r="H17" s="6" t="n"/>
+      <c r="I17" s="6" t="n"/>
+      <c r="J17" s="6" t="n"/>
+      <c r="K17" s="6" t="n"/>
+      <c r="L17" s="6" t="n"/>
+      <c r="M17" s="6" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>11    Total of bank CET1 specific buffer requirements (%)</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>2.8%</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>2.9%</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>3.0%</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>2.8%</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="n"/>
+      <c r="H18" s="6" t="n"/>
+      <c r="I18" s="6" t="n"/>
+      <c r="J18" s="6" t="n"/>
+      <c r="K18" s="6" t="n"/>
+      <c r="L18" s="6" t="n"/>
+      <c r="M18" s="6" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>12    CET1 available after meeting the total SREP own funds requirements (%)</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>21.9%</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>20.3%</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>22.3%</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>18.9%</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>20.1%</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="n"/>
+      <c r="H19" s="6" t="n"/>
+      <c r="I19" s="6" t="n"/>
+      <c r="J19" s="6" t="n"/>
+      <c r="K19" s="6" t="n"/>
+      <c r="L19" s="6" t="n"/>
+      <c r="M19" s="6" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Basel III leverage Ratio</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n"/>
+      <c r="C20" s="6" t="n"/>
+      <c r="D20" s="6" t="n"/>
+      <c r="E20" s="6" t="n"/>
+      <c r="F20" s="6" t="n"/>
+      <c r="G20" s="6" t="n"/>
+      <c r="H20" s="6" t="n"/>
+      <c r="I20" s="6" t="n"/>
+      <c r="J20" s="6" t="n"/>
+      <c r="K20" s="6" t="n"/>
+      <c r="L20" s="6" t="n"/>
+      <c r="M20" s="6" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>13    Total Basel III leverage ratio exposure measure (£'000)</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n">
+        <v>1373968</v>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>1462346</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>1473437</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>1814024</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>2431869</v>
+      </c>
+      <c r="G21" s="6" t="n"/>
+      <c r="H21" s="6" t="n"/>
+      <c r="I21" s="6" t="n"/>
+      <c r="J21" s="6" t="n"/>
+      <c r="K21" s="6" t="n"/>
+      <c r="L21" s="6" t="n"/>
+      <c r="M21" s="6" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>14    Basel III leverage ratio (%)</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>24.4%</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>22.9%</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>22.7%</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>18.5%</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>11.3%</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="n"/>
+      <c r="H22" s="6" t="n"/>
+      <c r="I22" s="6" t="n"/>
+      <c r="J22" s="6" t="n"/>
+      <c r="K22" s="6" t="n"/>
+      <c r="L22" s="6" t="n"/>
+      <c r="M22" s="6" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Liquidity Coverage Ratio (£'000 / %)</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n"/>
+      <c r="C23" s="6" t="n"/>
+      <c r="D23" s="6" t="n"/>
+      <c r="E23" s="6" t="n"/>
+      <c r="F23" s="6" t="n"/>
+      <c r="G23" s="6" t="n"/>
+      <c r="H23" s="6" t="n"/>
+      <c r="I23" s="6" t="n"/>
+      <c r="J23" s="6" t="n"/>
+      <c r="K23" s="6" t="n"/>
+      <c r="L23" s="6" t="n"/>
+      <c r="M23" s="6" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>15    Total HQLA</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="n">
+        <v>1007375</v>
+      </c>
+      <c r="C24" s="6" t="n">
+        <v>1014087</v>
+      </c>
+      <c r="D24" s="6" t="n">
+        <v>677646</v>
+      </c>
+      <c r="E24" s="6" t="n">
+        <v>545654</v>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>527697</v>
+      </c>
+      <c r="G24" s="6" t="n"/>
+      <c r="H24" s="6" t="n"/>
+      <c r="I24" s="6" t="n"/>
+      <c r="J24" s="6" t="n"/>
+      <c r="K24" s="6" t="n"/>
+      <c r="L24" s="6" t="n"/>
+      <c r="M24" s="6" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>6    Total net cash outflow   [printed "6" by the Bank; this is template row 16]</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="n">
+        <v>310866</v>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>272240</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>174967</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>299877</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>294774</v>
+      </c>
+      <c r="G25" s="6" t="n"/>
+      <c r="H25" s="6" t="n"/>
+      <c r="I25" s="6" t="n"/>
+      <c r="J25" s="6" t="n"/>
+      <c r="K25" s="6" t="n"/>
+      <c r="L25" s="6" t="n"/>
+      <c r="M25" s="6" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>17    LCR ratio (%)</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>324.1%</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>372.5%</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>387.3%</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>182.0%</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>179.0%</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="n"/>
+      <c r="H26" s="6" t="n"/>
+      <c r="I26" s="6" t="n"/>
+      <c r="J26" s="6" t="n"/>
+      <c r="K26" s="6" t="n"/>
+      <c r="L26" s="6" t="n"/>
+      <c r="M26" s="6" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Net Stable Funding Ratio (£'000 / %)</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n"/>
+      <c r="C27" s="6" t="n"/>
+      <c r="D27" s="6" t="n"/>
+      <c r="E27" s="6" t="n"/>
+      <c r="F27" s="6" t="n"/>
+      <c r="G27" s="6" t="n"/>
+      <c r="H27" s="6" t="n"/>
+      <c r="I27" s="6" t="n"/>
+      <c r="J27" s="6" t="n"/>
+      <c r="K27" s="6" t="n"/>
+      <c r="L27" s="6" t="n"/>
+      <c r="M27" s="6" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>18    Total available stable funding</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n">
+        <v>1389486</v>
+      </c>
+      <c r="C28" s="6" t="n">
+        <v>1630136</v>
+      </c>
+      <c r="D28" s="6" t="n">
+        <v>1289845</v>
+      </c>
+      <c r="E28" s="6" t="n">
+        <v>1463448</v>
+      </c>
+      <c r="F28" s="6" t="n">
+        <v>1438026</v>
+      </c>
+      <c r="G28" s="6" t="n"/>
+      <c r="H28" s="6" t="n"/>
+      <c r="I28" s="6" t="n"/>
+      <c r="J28" s="6" t="n"/>
+      <c r="K28" s="6" t="n"/>
+      <c r="L28" s="6" t="n"/>
+      <c r="M28" s="6" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>19    Total required stable funding</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n">
+        <v>714820</v>
+      </c>
+      <c r="C29" s="6" t="n">
+        <v>752941</v>
+      </c>
+      <c r="D29" s="6" t="n">
+        <v>959234</v>
+      </c>
+      <c r="E29" s="6" t="n">
+        <v>1209361</v>
+      </c>
+      <c r="F29" s="6" t="n">
+        <v>950742</v>
+      </c>
+      <c r="G29" s="6" t="n"/>
+      <c r="H29" s="6" t="n"/>
+      <c r="I29" s="6" t="n"/>
+      <c r="J29" s="6" t="n"/>
+      <c r="K29" s="6" t="n"/>
+      <c r="L29" s="6" t="n"/>
+      <c r="M29" s="6" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>20    NSFR ratio (%)</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>194.4%</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>216.5%</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>134.5%</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>121.0%</t>
+        </is>
+      </c>
+      <c r="F30" s="6" t="inlineStr">
+        <is>
+          <t>151.3%</t>
+        </is>
+      </c>
+      <c r="G30" s="6" t="n"/>
+      <c r="H30" s="6" t="n"/>
+      <c r="I30" s="6" t="n"/>
+      <c r="J30" s="6" t="n"/>
+      <c r="K30" s="6" t="n"/>
+      <c r="L30" s="6" t="n"/>
+      <c r="M30" s="6" t="n"/>
+    </row>
+    <row r="32" ht="300" customHeight="1">
+      <c r="A32" s="8" t="inlineStr">
         <is>
           <t>Sources - Bank of China (UK) Limited Pillar 3 disclosures (UK KM1 Key Metrics template from FY2022 onward; FY2021's own document is narrative/ratio-only and predates the KM1 template; FY2014-FY2020 use the pre-KM1 CRD IV 'Table 1: Total capital resources and risk asset ratios' / 'Table 2: Leverage ratio' narrative-table format), £'000 unless stated:
 FY2025 &amp; FY2024 comparative: Pillar 3 Disclosure 31 December 2025, p.15 (UK KM1) - https://pic.bankofchina.com/bocappd/uk/202607/P020260716391457618567.pdf
@@ -16505,13 +17472,21 @@
 FY2015 (own year) &amp; FY2014 comparative: Pillar III Disclosures 2015, Table 1/Table 2, p.9-10 - https://pic.bankofchina.com/bocappd/uk/201606/P020160620504436264971.pdf
 FY2014 (own year) &amp; FY2013 comparative: Pillar III Disclosure 2014, Table 1/Table 2, p.8-9 - https://pic.bankofchina.com/bocappd/uk/201509/P020150910375228515274.pdf
 FY2014-FY2017 note: 'Tier 1 capital' equals 'CET1 capital' every year (£274,958k throughout - the Bank issued no AT1 instruments until far later) and 'Total capital' equals CET1 capital plus the £60,000k Tier 2 subordinated debt facility, both stated directly in each year's own Table 1. LCR and NSFR are genuinely undisclosed for FY2014-FY2016 (no LCR/HQLA/NSFR concept appears anywhere in those 3 documents, confirmed by reading each in full); FY2017's LCR ratio (167%) is not in FY2017's own document at all (confirmed absent) but appears as the FY2018 Pillar 3 document's own FY2017 comparative column, the earliest point any LCR figure for this bank exists - shown here with no £-breakdown since none is given for that comparative year. RWA breakdown by risk category (credit/market/operational/CVA) is genuinely undisclosed for FY2014-FY2018 (only the single aggregate RWA figure appears in each Table 1); the FY2020 Pillar 3 document introduces a full 'Table 9: Overview of risk weighted assets' (its own year plus its own FY2019 comparative column), the first and only such breakdown found across all 12 years covered.
-Entity note: Bank of China (UK) Limited (company 06193060, FRN 467410) is a wholly-owned UK subsidiary of Bank of China Limited (state-owned). It does not take the FRS 101/102 cash-flow-statement exemption - a full Statement of Cash Flows is published every year. All figures are the Bank's own solo entity basis throughout.</t>
+Entity note: Bank of China (UK) Limited (company 06193060, FRN 467410) is a wholly-owned UK subsidiary of Bank of China Limited (state-owned). It does not take the FRS 101/102 cash-flow-statement exemption - a full Statement of Cash Flows is published every year. All figures are the Bank's own solo entity basis throughout.
+KM1 presentation notes:
+• LATEST-EDITION CHECK 2026-09-16: the Bank's own disclosure index at https://www.bankofchina.com/uk/aboutus/ab5/ lists 'Pillar 3 Disclosure 31 December 2025' as its newest document, which is the one cited above. Checked, none newer.
+• A BASEL ROW SET UNDER A UK KM1 HEADING. The table is headed 'UK KM1 - Key Metrics' (FY2022's edition: 'UK KM1 - Key metrics template'), but rows 8-11 are the BCBS buffer block and rows 13-14 are captioned 'Basel III leverage ratio exposure measure' / 'Basel III leverage ratio'. The PRA template's UK 7a-7d, UK 8a, UK 9a, UK 10a, UK 11a and UK 16a/16b rows appear in no edition. This sheet reproduces the Bank's row set and does not add the PRA rows back as blanks, because the Bank's table does not contain them.
+• ROW 16 IS PRINTED AS '6'. '6 Total net cash outflow' sits between rows 15 and 17 in the FY2022, FY2023, FY2024 and FY2025 documents alike. It is a persistent typo in the Bank's own template, checked in all four editions, and is reproduced rather than corrected.
+• ROW 12 CHANGED BASIS AND CAPTION IN FY2025, from 'CET1 available after meeting the bank's minimum Cap Req (%)' to 'CET1 available after meeting the total SREP own funds requirements (%)'. The FY2025 edition restates FY2024 as 19.5% on the new basis; the FY2024 edition printed 20.3% on the old one. The cell here carries 20.3%, that year's own edition, per this project's rule that each year comes from its own edition rather than a later comparative. Both figures are the Bank's; they are not reconciled. Every other row agrees exactly across overlapping editions.
+• ROW 10 PRINTS '0%', NOT A DASH, in every year - a measured zero (the Bank is neither a G-SIB nor a D-SIB), so the zero is kept rather than blanked.
+• The FY2023 edition prints its own year-column header as '20232', where the trailing 2 is a footnote marker rather than part of the year.
+• FY2020 and earlier are blank. The FY2021 Pillar 3 document and every edition before it predate the KM1 template and are narrative/ratio-only; FY2021 above is the comparative column of the FY2022 edition, which is the first to print the template. Nothing has been back-filled from the pre-KM1 CRD IV tables - those figures are on the individual metric sheets, with their basis stated there.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A6:M6"/>
+    <mergeCell ref="A32:M32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -16544,14 +17519,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Bank of China (UK) Limited — CET1 Ratio</t>
+          <t>Bank of China (UK) Limited — CET1 Capital</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>% of RWA</t>
+          <t>£'000</t>
         </is>
       </c>
     </row>
@@ -16625,68 +17600,44 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Common Equity Tier 1 ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>27.2%</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>24.8%</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>26.8%</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>23.4%</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>24.6%</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>26.7%</t>
-        </is>
-      </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>27.8%</t>
-        </is>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>29.2%</t>
-        </is>
-      </c>
-      <c r="J4" s="6" t="inlineStr">
-        <is>
-          <t>30%</t>
-        </is>
-      </c>
-      <c r="K4" s="6" t="inlineStr">
-        <is>
-          <t>27%</t>
-        </is>
-      </c>
-      <c r="L4" s="6" t="inlineStr">
-        <is>
-          <t>31%</t>
-        </is>
-      </c>
-      <c r="M4" s="6" t="inlineStr">
-        <is>
-          <t>34%</t>
-        </is>
+          <t>Common Equity Tier 1 (CET1) capital</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>274521</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>274294</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>275056</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>275000</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>275164</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>307058</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>274958</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>274958</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>274958</v>
+      </c>
+      <c r="K4" s="6" t="n">
+        <v>274958</v>
+      </c>
+      <c r="L4" s="6" t="n">
+        <v>274958</v>
+      </c>
+      <c r="M4" s="6" t="n">
+        <v>274958</v>
       </c>
     </row>
     <row r="6" ht="170" customHeight="1">
@@ -16725,7 +17676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -16746,14 +17697,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Bank of China (UK) Limited — Tier 1 Capital</t>
+          <t>Bank of China (UK) Limited — CET1 Ratio</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>£'000</t>
+          <t>% of RWA</t>
         </is>
       </c>
     </row>
@@ -16827,55 +17778,72 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Tier 1 capital</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>334521</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>334294</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>335056</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>335000</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>275164</v>
-      </c>
-      <c r="G4" s="6" t="n">
-        <v>307058</v>
-      </c>
-      <c r="H4" s="6" t="n">
-        <v>274958</v>
-      </c>
-      <c r="I4" s="6" t="n">
-        <v>274958</v>
-      </c>
-      <c r="J4" s="6" t="n">
-        <v>274958</v>
-      </c>
-      <c r="K4" s="6" t="n">
-        <v>274958</v>
-      </c>
-      <c r="L4" s="6" t="n">
-        <v>274958</v>
-      </c>
-      <c r="M4" s="6" t="n">
-        <v>274958</v>
-      </c>
-    </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Note: Equal to CET1 capital every year FY2014-FY2021 (no AT1 instruments in issue until June 2022). A £60m Additional Tier 1 instrument was issued in June 2022, replacing an equal amount of Tier 2 subordinated debt.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="170" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
+          <t>Common Equity Tier 1 ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>27.2%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>24.8%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>26.8%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>23.4%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>24.6%</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>26.7%</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>27.8%</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>29.2%</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="K4" s="6" t="inlineStr">
+        <is>
+          <t>27%</t>
+        </is>
+      </c>
+      <c r="L4" s="6" t="inlineStr">
+        <is>
+          <t>31%</t>
+        </is>
+      </c>
+      <c r="M4" s="6" t="inlineStr">
+        <is>
+          <t>34%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="170" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Sources - Bank of China (UK) Limited Pillar 3 disclosures (UK KM1 Key Metrics template from FY2022 onward; FY2021's own document is narrative/ratio-only and predates the KM1 template; FY2014-FY2020 use the pre-KM1 CRD IV 'Table 1: Total capital resources and risk asset ratios' / 'Table 2: Leverage ratio' narrative-table format), £'000 unless stated:
 FY2025 &amp; FY2024 comparative: Pillar 3 Disclosure 31 December 2025, p.15 (UK KM1) - https://pic.bankofchina.com/bocappd/uk/202607/P020260716391457618567.pdf
@@ -16897,9 +17865,8 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A5:M5"/>
-    <mergeCell ref="A7:M7"/>
+  <mergeCells count="1">
+    <mergeCell ref="A6:M6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/banks/BANK OF CHINA UK FINANCIALS.xlsx
+++ b/banks/BANK OF CHINA UK FINANCIALS.xlsx
@@ -1772,6 +1772,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -5287,7 +5288,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -5387,9 +5388,9 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Not publicly disclosed — category breakdown</t>
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>UK OV1 'Overview of risk weighted exposure amounts' — each year's own Pillar 3 Disclosure for FY2025-FY2022, and the FY2020 Pillar 3 Disclosure's Table 9 for FY2020 with FY2019 as its comparative</t>
         </is>
       </c>
       <c r="B4" s="6" t="n"/>
@@ -5399,31 +5400,11 @@
       <c r="F4" s="6" t="n"/>
       <c r="G4" s="6" t="n"/>
       <c r="H4" s="6" t="n"/>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
-      <c r="J4" s="6" t="inlineStr">
-        <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
-      <c r="K4" s="6" t="inlineStr">
-        <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
-      <c r="L4" s="6" t="inlineStr">
-        <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
-      <c r="M4" s="6" t="inlineStr">
-        <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
+      <c r="I4" s="6" t="n"/>
+      <c r="J4" s="6" t="n"/>
+      <c r="K4" s="6" t="n"/>
+      <c r="L4" s="6" t="n"/>
+      <c r="M4" s="6" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -5443,9 +5424,7 @@
       <c r="E5" s="6" t="n">
         <v>730027</v>
       </c>
-      <c r="F5" s="6" t="n">
-        <v>793055</v>
-      </c>
+      <c r="F5" s="6" t="n"/>
       <c r="G5" s="6" t="n">
         <v>822496</v>
       </c>
@@ -5503,9 +5482,7 @@
       <c r="E7" s="6" t="n">
         <v>198501</v>
       </c>
-      <c r="F7" s="6" t="n">
-        <v>93581</v>
-      </c>
+      <c r="F7" s="6" t="n"/>
       <c r="G7" s="6" t="n">
         <v>114722</v>
       </c>
@@ -5536,9 +5513,7 @@
       <c r="E8" s="6" t="n">
         <v>4394</v>
       </c>
-      <c r="F8" s="6" t="n">
-        <v>14056</v>
-      </c>
+      <c r="F8" s="6" t="n"/>
       <c r="G8" s="6" t="n">
         <v>11621</v>
       </c>
@@ -5569,9 +5544,7 @@
       <c r="E9" s="6" t="n">
         <v>224618</v>
       </c>
-      <c r="F9" s="6" t="n">
-        <v>218688</v>
-      </c>
+      <c r="F9" s="6" t="n"/>
       <c r="G9" s="6" t="n">
         <v>202676</v>
       </c>
@@ -5602,33 +5575,232 @@
       <c r="E10" s="5" t="n">
         <v>1176625</v>
       </c>
-      <c r="F10" s="5" t="n">
-        <v>1119380</v>
-      </c>
+      <c r="F10" s="5" t="n"/>
       <c r="G10" s="5" t="n">
         <v>1151516</v>
       </c>
       <c r="H10" s="5" t="n">
         <v>988901</v>
       </c>
-      <c r="I10" s="5" t="n">
+      <c r="I10" s="5" t="n"/>
+      <c r="J10" s="5" t="n"/>
+      <c r="K10" s="5" t="n"/>
+      <c r="L10" s="5" t="n"/>
+      <c r="M10" s="5" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Template EU OV1 — Pillar 3 Disclosure 2021, Table 1, p.14 (FY2021). This edition carries no separate counterparty-credit-risk line: CCR is folded into its credit-risk figure, so that row is NOT the same measure as the 'excluding CCR' row above — see sources note</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n"/>
+      <c r="C11" s="6" t="n"/>
+      <c r="D11" s="6" t="n"/>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="6" t="n"/>
+      <c r="G11" s="6" t="n"/>
+      <c r="H11" s="6" t="n"/>
+      <c r="I11" s="6" t="n"/>
+      <c r="J11" s="6" t="n"/>
+      <c r="K11" s="6" t="n"/>
+      <c r="L11" s="6" t="n"/>
+      <c r="M11" s="6" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Credit risk (standardised approach, CCR included as published)</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n"/>
+      <c r="C12" s="6" t="n"/>
+      <c r="D12" s="6" t="n"/>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="6" t="n">
+        <v>793055</v>
+      </c>
+      <c r="G12" s="6" t="n"/>
+      <c r="H12" s="6" t="n"/>
+      <c r="I12" s="6" t="n"/>
+      <c r="J12" s="6" t="n"/>
+      <c r="K12" s="6" t="n"/>
+      <c r="L12" s="6" t="n"/>
+      <c r="M12" s="6" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Credit valuation adjustment (CVA)</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n"/>
+      <c r="C13" s="6" t="n"/>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="n">
+        <v>93581</v>
+      </c>
+      <c r="G13" s="6" t="n"/>
+      <c r="H13" s="6" t="n"/>
+      <c r="I13" s="6" t="n"/>
+      <c r="J13" s="6" t="n"/>
+      <c r="K13" s="6" t="n"/>
+      <c r="L13" s="6" t="n"/>
+      <c r="M13" s="6" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Market risk (standardised approach)</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="6" t="n">
+        <v>14056</v>
+      </c>
+      <c r="G14" s="6" t="n"/>
+      <c r="H14" s="6" t="n"/>
+      <c r="I14" s="6" t="n"/>
+      <c r="J14" s="6" t="n"/>
+      <c r="K14" s="6" t="n"/>
+      <c r="L14" s="6" t="n"/>
+      <c r="M14" s="6" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>Operational risk</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n"/>
+      <c r="C15" s="6" t="n"/>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="n">
+        <v>218688</v>
+      </c>
+      <c r="G15" s="6" t="n"/>
+      <c r="H15" s="6" t="n"/>
+      <c r="I15" s="6" t="n"/>
+      <c r="J15" s="6" t="n"/>
+      <c r="K15" s="6" t="n"/>
+      <c r="L15" s="6" t="n"/>
+      <c r="M15" s="6" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Total risk exposure amount</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n"/>
+      <c r="C16" s="5" t="n"/>
+      <c r="D16" s="5" t="n"/>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="5" t="n">
+        <v>1119380</v>
+      </c>
+      <c r="G16" s="5" t="n"/>
+      <c r="H16" s="5" t="n"/>
+      <c r="I16" s="5" t="n"/>
+      <c r="J16" s="5" t="n"/>
+      <c r="K16" s="5" t="n"/>
+      <c r="L16" s="5" t="n"/>
+      <c r="M16" s="5" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>No category breakdown on this sheet (FY2018-FY2014) — total risk exposure amount only; these years were not re-checked in the 2026-09-12 re-verification, see sources note</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n"/>
+      <c r="C17" s="6" t="n"/>
+      <c r="D17" s="6" t="n"/>
+      <c r="E17" s="6" t="n"/>
+      <c r="F17" s="6" t="n"/>
+      <c r="G17" s="6" t="n"/>
+      <c r="H17" s="6" t="n"/>
+      <c r="I17" s="6" t="n"/>
+      <c r="J17" s="6" t="n"/>
+      <c r="K17" s="6" t="n"/>
+      <c r="L17" s="6" t="n"/>
+      <c r="M17" s="6" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed — category breakdown</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n"/>
+      <c r="C18" s="6" t="n"/>
+      <c r="D18" s="6" t="n"/>
+      <c r="E18" s="6" t="n"/>
+      <c r="F18" s="6" t="n"/>
+      <c r="G18" s="6" t="n"/>
+      <c r="H18" s="6" t="n"/>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed</t>
+        </is>
+      </c>
+      <c r="J18" s="6" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed</t>
+        </is>
+      </c>
+      <c r="K18" s="6" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed</t>
+        </is>
+      </c>
+      <c r="L18" s="6" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed</t>
+        </is>
+      </c>
+      <c r="M18" s="6" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Total risk exposure amount</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n"/>
+      <c r="C19" s="5" t="n"/>
+      <c r="D19" s="5" t="n"/>
+      <c r="E19" s="5" t="n"/>
+      <c r="F19" s="5" t="n"/>
+      <c r="G19" s="5" t="n"/>
+      <c r="H19" s="5" t="n"/>
+      <c r="I19" s="5" t="n">
         <v>941052</v>
       </c>
-      <c r="J10" s="5" t="n">
+      <c r="J19" s="5" t="n">
         <v>931206</v>
       </c>
-      <c r="K10" s="5" t="n">
+      <c r="K19" s="5" t="n">
         <v>1003913</v>
       </c>
-      <c r="L10" s="5" t="n">
+      <c r="L19" s="5" t="n">
         <v>895473</v>
       </c>
-      <c r="M10" s="5" t="n">
+      <c r="M19" s="5" t="n">
         <v>800993</v>
       </c>
     </row>
-    <row r="12" ht="280" customHeight="1">
-      <c r="A12" s="8" t="inlineStr">
+    <row r="21" ht="280" customHeight="1">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>Sources - Bank of China (UK) Limited's own UK OV1/EU OV1 'Overview of risk weighted exposure amounts' tables (same 5 Pillar 3 documents as the Total RWAs sheet), each year's own originally-published figures used as primary (not a later restated comparative), per project convention:
 FY2025: Pillar 3 Disclosure 2025, Table 'UK OV1' - https://pic.bankofchina.com/bocappd/uk/202607/P020260716391457618567.pdf
@@ -5644,7 +5816,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A12:M12"/>
+    <mergeCell ref="A21:M21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5909,7 +6081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -5922,9 +6094,6 @@
     <col width="15" customWidth="1" min="8" max="8"/>
     <col width="15" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="15" customWidth="1" min="12" max="12"/>
-    <col width="15" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5992,21 +6161,6 @@
           <t>FY2017</t>
         </is>
       </c>
-      <c r="K3" s="4" t="inlineStr">
-        <is>
-          <t>FY2016</t>
-        </is>
-      </c>
-      <c r="L3" s="4" t="inlineStr">
-        <is>
-          <t>FY2015</t>
-        </is>
-      </c>
-      <c r="M3" s="4" t="inlineStr">
-        <is>
-          <t>FY2014</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -6039,9 +6193,6 @@
         <v>381928</v>
       </c>
       <c r="J4" s="6" t="n"/>
-      <c r="K4" s="6" t="n"/>
-      <c r="L4" s="6" t="n"/>
-      <c r="M4" s="6" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -6074,9 +6225,6 @@
         <v>164459</v>
       </c>
       <c r="J5" s="6" t="n"/>
-      <c r="K5" s="6" t="n"/>
-      <c r="L5" s="6" t="n"/>
-      <c r="M5" s="6" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -6129,9 +6277,6 @@
           <t>167%</t>
         </is>
       </c>
-      <c r="K6" s="6" t="n"/>
-      <c r="L6" s="6" t="n"/>
-      <c r="M6" s="6" t="n"/>
     </row>
     <row r="7" ht="60" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
@@ -6164,8 +6309,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A9:M9"/>
-    <mergeCell ref="A7:M7"/>
+    <mergeCell ref="A7:J7"/>
+    <mergeCell ref="A9:J9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6177,7 +6322,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -6189,10 +6334,6 @@
     <col width="15" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
     <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="15" customWidth="1" min="12" max="12"/>
-    <col width="15" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6255,26 +6396,6 @@
           <t>FY2018</t>
         </is>
       </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>FY2017</t>
-        </is>
-      </c>
-      <c r="K3" s="4" t="inlineStr">
-        <is>
-          <t>FY2016</t>
-        </is>
-      </c>
-      <c r="L3" s="4" t="inlineStr">
-        <is>
-          <t>FY2015</t>
-        </is>
-      </c>
-      <c r="M3" s="4" t="inlineStr">
-        <is>
-          <t>FY2014</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -6306,10 +6427,6 @@
       <c r="I4" s="6" t="n">
         <v>1219968</v>
       </c>
-      <c r="J4" s="6" t="n"/>
-      <c r="K4" s="6" t="n"/>
-      <c r="L4" s="6" t="n"/>
-      <c r="M4" s="6" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -6341,10 +6458,6 @@
       <c r="I5" s="6" t="n">
         <v>843948</v>
       </c>
-      <c r="J5" s="6" t="n"/>
-      <c r="K5" s="6" t="n"/>
-      <c r="L5" s="6" t="n"/>
-      <c r="M5" s="6" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -6392,10 +6505,6 @@
           <t>145%</t>
         </is>
       </c>
-      <c r="J6" s="6" t="n"/>
-      <c r="K6" s="6" t="n"/>
-      <c r="L6" s="6" t="n"/>
-      <c r="M6" s="6" t="n"/>
     </row>
     <row r="7" ht="60" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
@@ -6428,8 +6537,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A9:M9"/>
-    <mergeCell ref="A7:M7"/>
+    <mergeCell ref="A7:I7"/>
+    <mergeCell ref="A9:I9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -16532,7 +16641,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M32"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="72" customWidth="1" min="1" max="1"/>
@@ -16541,13 +16650,6 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="15" customWidth="1" min="12" max="12"/>
-    <col width="15" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -16593,41 +16695,6 @@
       <c r="F3" s="4" t="inlineStr">
         <is>
           <t>FY2021</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>FY2020</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>FY2019</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>FY2018</t>
-        </is>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>FY2017</t>
-        </is>
-      </c>
-      <c r="K3" s="4" t="inlineStr">
-        <is>
-          <t>FY2016</t>
-        </is>
-      </c>
-      <c r="L3" s="4" t="inlineStr">
-        <is>
-          <t>FY2015</t>
-        </is>
-      </c>
-      <c r="M3" s="4" t="inlineStr">
-        <is>
-          <t>FY2014</t>
         </is>
       </c>
     </row>
@@ -16642,13 +16709,6 @@
       <c r="D4" s="6" t="n"/>
       <c r="E4" s="6" t="n"/>
       <c r="F4" s="6" t="n"/>
-      <c r="G4" s="6" t="n"/>
-      <c r="H4" s="6" t="n"/>
-      <c r="I4" s="6" t="n"/>
-      <c r="J4" s="6" t="n"/>
-      <c r="K4" s="6" t="n"/>
-      <c r="L4" s="6" t="n"/>
-      <c r="M4" s="6" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -16671,13 +16731,6 @@
       <c r="F5" s="6" t="n">
         <v>275164</v>
       </c>
-      <c r="G5" s="6" t="n"/>
-      <c r="H5" s="6" t="n"/>
-      <c r="I5" s="6" t="n"/>
-      <c r="J5" s="6" t="n"/>
-      <c r="K5" s="6" t="n"/>
-      <c r="L5" s="6" t="n"/>
-      <c r="M5" s="6" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -16700,13 +16753,6 @@
       <c r="F6" s="6" t="n">
         <v>275164</v>
       </c>
-      <c r="G6" s="6" t="n"/>
-      <c r="H6" s="6" t="n"/>
-      <c r="I6" s="6" t="n"/>
-      <c r="J6" s="6" t="n"/>
-      <c r="K6" s="6" t="n"/>
-      <c r="L6" s="6" t="n"/>
-      <c r="M6" s="6" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -16729,13 +16775,6 @@
       <c r="F7" s="6" t="n">
         <v>335164</v>
       </c>
-      <c r="G7" s="6" t="n"/>
-      <c r="H7" s="6" t="n"/>
-      <c r="I7" s="6" t="n"/>
-      <c r="J7" s="6" t="n"/>
-      <c r="K7" s="6" t="n"/>
-      <c r="L7" s="6" t="n"/>
-      <c r="M7" s="6" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -16748,13 +16787,6 @@
       <c r="D8" s="6" t="n"/>
       <c r="E8" s="6" t="n"/>
       <c r="F8" s="6" t="n"/>
-      <c r="G8" s="6" t="n"/>
-      <c r="H8" s="6" t="n"/>
-      <c r="I8" s="6" t="n"/>
-      <c r="J8" s="6" t="n"/>
-      <c r="K8" s="6" t="n"/>
-      <c r="L8" s="6" t="n"/>
-      <c r="M8" s="6" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -16777,13 +16809,6 @@
       <c r="F9" s="6" t="n">
         <v>1119380</v>
       </c>
-      <c r="G9" s="6" t="n"/>
-      <c r="H9" s="6" t="n"/>
-      <c r="I9" s="6" t="n"/>
-      <c r="J9" s="6" t="n"/>
-      <c r="K9" s="6" t="n"/>
-      <c r="L9" s="6" t="n"/>
-      <c r="M9" s="6" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -16796,13 +16821,6 @@
       <c r="D10" s="6" t="n"/>
       <c r="E10" s="6" t="n"/>
       <c r="F10" s="6" t="n"/>
-      <c r="G10" s="6" t="n"/>
-      <c r="H10" s="6" t="n"/>
-      <c r="I10" s="6" t="n"/>
-      <c r="J10" s="6" t="n"/>
-      <c r="K10" s="6" t="n"/>
-      <c r="L10" s="6" t="n"/>
-      <c r="M10" s="6" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -16835,13 +16853,6 @@
           <t>24.6%</t>
         </is>
       </c>
-      <c r="G11" s="6" t="n"/>
-      <c r="H11" s="6" t="n"/>
-      <c r="I11" s="6" t="n"/>
-      <c r="J11" s="6" t="n"/>
-      <c r="K11" s="6" t="n"/>
-      <c r="L11" s="6" t="n"/>
-      <c r="M11" s="6" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -16874,13 +16885,6 @@
           <t>24.6%</t>
         </is>
       </c>
-      <c r="G12" s="6" t="n"/>
-      <c r="H12" s="6" t="n"/>
-      <c r="I12" s="6" t="n"/>
-      <c r="J12" s="6" t="n"/>
-      <c r="K12" s="6" t="n"/>
-      <c r="L12" s="6" t="n"/>
-      <c r="M12" s="6" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -16913,13 +16917,6 @@
           <t>29.9%</t>
         </is>
       </c>
-      <c r="G13" s="6" t="n"/>
-      <c r="H13" s="6" t="n"/>
-      <c r="I13" s="6" t="n"/>
-      <c r="J13" s="6" t="n"/>
-      <c r="K13" s="6" t="n"/>
-      <c r="L13" s="6" t="n"/>
-      <c r="M13" s="6" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -16932,13 +16929,6 @@
       <c r="D14" s="6" t="n"/>
       <c r="E14" s="6" t="n"/>
       <c r="F14" s="6" t="n"/>
-      <c r="G14" s="6" t="n"/>
-      <c r="H14" s="6" t="n"/>
-      <c r="I14" s="6" t="n"/>
-      <c r="J14" s="6" t="n"/>
-      <c r="K14" s="6" t="n"/>
-      <c r="L14" s="6" t="n"/>
-      <c r="M14" s="6" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -16971,13 +16961,6 @@
           <t>2.5%</t>
         </is>
       </c>
-      <c r="G15" s="6" t="n"/>
-      <c r="H15" s="6" t="n"/>
-      <c r="I15" s="6" t="n"/>
-      <c r="J15" s="6" t="n"/>
-      <c r="K15" s="6" t="n"/>
-      <c r="L15" s="6" t="n"/>
-      <c r="M15" s="6" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -17010,13 +16993,6 @@
           <t>0.1%</t>
         </is>
       </c>
-      <c r="G16" s="6" t="n"/>
-      <c r="H16" s="6" t="n"/>
-      <c r="I16" s="6" t="n"/>
-      <c r="J16" s="6" t="n"/>
-      <c r="K16" s="6" t="n"/>
-      <c r="L16" s="6" t="n"/>
-      <c r="M16" s="6" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
@@ -17049,13 +17025,6 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="G17" s="6" t="n"/>
-      <c r="H17" s="6" t="n"/>
-      <c r="I17" s="6" t="n"/>
-      <c r="J17" s="6" t="n"/>
-      <c r="K17" s="6" t="n"/>
-      <c r="L17" s="6" t="n"/>
-      <c r="M17" s="6" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -17088,13 +17057,6 @@
           <t>2.6%</t>
         </is>
       </c>
-      <c r="G18" s="6" t="n"/>
-      <c r="H18" s="6" t="n"/>
-      <c r="I18" s="6" t="n"/>
-      <c r="J18" s="6" t="n"/>
-      <c r="K18" s="6" t="n"/>
-      <c r="L18" s="6" t="n"/>
-      <c r="M18" s="6" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -17127,13 +17089,6 @@
           <t>20.1%</t>
         </is>
       </c>
-      <c r="G19" s="6" t="n"/>
-      <c r="H19" s="6" t="n"/>
-      <c r="I19" s="6" t="n"/>
-      <c r="J19" s="6" t="n"/>
-      <c r="K19" s="6" t="n"/>
-      <c r="L19" s="6" t="n"/>
-      <c r="M19" s="6" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -17146,13 +17101,6 @@
       <c r="D20" s="6" t="n"/>
       <c r="E20" s="6" t="n"/>
       <c r="F20" s="6" t="n"/>
-      <c r="G20" s="6" t="n"/>
-      <c r="H20" s="6" t="n"/>
-      <c r="I20" s="6" t="n"/>
-      <c r="J20" s="6" t="n"/>
-      <c r="K20" s="6" t="n"/>
-      <c r="L20" s="6" t="n"/>
-      <c r="M20" s="6" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
@@ -17175,13 +17123,6 @@
       <c r="F21" s="6" t="n">
         <v>2431869</v>
       </c>
-      <c r="G21" s="6" t="n"/>
-      <c r="H21" s="6" t="n"/>
-      <c r="I21" s="6" t="n"/>
-      <c r="J21" s="6" t="n"/>
-      <c r="K21" s="6" t="n"/>
-      <c r="L21" s="6" t="n"/>
-      <c r="M21" s="6" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -17214,13 +17155,6 @@
           <t>11.3%</t>
         </is>
       </c>
-      <c r="G22" s="6" t="n"/>
-      <c r="H22" s="6" t="n"/>
-      <c r="I22" s="6" t="n"/>
-      <c r="J22" s="6" t="n"/>
-      <c r="K22" s="6" t="n"/>
-      <c r="L22" s="6" t="n"/>
-      <c r="M22" s="6" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
@@ -17233,13 +17167,6 @@
       <c r="D23" s="6" t="n"/>
       <c r="E23" s="6" t="n"/>
       <c r="F23" s="6" t="n"/>
-      <c r="G23" s="6" t="n"/>
-      <c r="H23" s="6" t="n"/>
-      <c r="I23" s="6" t="n"/>
-      <c r="J23" s="6" t="n"/>
-      <c r="K23" s="6" t="n"/>
-      <c r="L23" s="6" t="n"/>
-      <c r="M23" s="6" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
@@ -17262,13 +17189,6 @@
       <c r="F24" s="6" t="n">
         <v>527697</v>
       </c>
-      <c r="G24" s="6" t="n"/>
-      <c r="H24" s="6" t="n"/>
-      <c r="I24" s="6" t="n"/>
-      <c r="J24" s="6" t="n"/>
-      <c r="K24" s="6" t="n"/>
-      <c r="L24" s="6" t="n"/>
-      <c r="M24" s="6" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
@@ -17291,13 +17211,6 @@
       <c r="F25" s="6" t="n">
         <v>294774</v>
       </c>
-      <c r="G25" s="6" t="n"/>
-      <c r="H25" s="6" t="n"/>
-      <c r="I25" s="6" t="n"/>
-      <c r="J25" s="6" t="n"/>
-      <c r="K25" s="6" t="n"/>
-      <c r="L25" s="6" t="n"/>
-      <c r="M25" s="6" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
@@ -17330,13 +17243,6 @@
           <t>179.0%</t>
         </is>
       </c>
-      <c r="G26" s="6" t="n"/>
-      <c r="H26" s="6" t="n"/>
-      <c r="I26" s="6" t="n"/>
-      <c r="J26" s="6" t="n"/>
-      <c r="K26" s="6" t="n"/>
-      <c r="L26" s="6" t="n"/>
-      <c r="M26" s="6" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -17349,13 +17255,6 @@
       <c r="D27" s="6" t="n"/>
       <c r="E27" s="6" t="n"/>
       <c r="F27" s="6" t="n"/>
-      <c r="G27" s="6" t="n"/>
-      <c r="H27" s="6" t="n"/>
-      <c r="I27" s="6" t="n"/>
-      <c r="J27" s="6" t="n"/>
-      <c r="K27" s="6" t="n"/>
-      <c r="L27" s="6" t="n"/>
-      <c r="M27" s="6" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
@@ -17378,13 +17277,6 @@
       <c r="F28" s="6" t="n">
         <v>1438026</v>
       </c>
-      <c r="G28" s="6" t="n"/>
-      <c r="H28" s="6" t="n"/>
-      <c r="I28" s="6" t="n"/>
-      <c r="J28" s="6" t="n"/>
-      <c r="K28" s="6" t="n"/>
-      <c r="L28" s="6" t="n"/>
-      <c r="M28" s="6" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
@@ -17407,13 +17299,6 @@
       <c r="F29" s="6" t="n">
         <v>950742</v>
       </c>
-      <c r="G29" s="6" t="n"/>
-      <c r="H29" s="6" t="n"/>
-      <c r="I29" s="6" t="n"/>
-      <c r="J29" s="6" t="n"/>
-      <c r="K29" s="6" t="n"/>
-      <c r="L29" s="6" t="n"/>
-      <c r="M29" s="6" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
@@ -17446,13 +17331,6 @@
           <t>151.3%</t>
         </is>
       </c>
-      <c r="G30" s="6" t="n"/>
-      <c r="H30" s="6" t="n"/>
-      <c r="I30" s="6" t="n"/>
-      <c r="J30" s="6" t="n"/>
-      <c r="K30" s="6" t="n"/>
-      <c r="L30" s="6" t="n"/>
-      <c r="M30" s="6" t="n"/>
     </row>
     <row r="32" ht="300" customHeight="1">
       <c r="A32" s="8" t="inlineStr">
@@ -17486,7 +17364,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A32:M32"/>
+    <mergeCell ref="A32:F32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/banks/BANK OF CHINA UK FINANCIALS.xlsx
+++ b/banks/BANK OF CHINA UK FINANCIALS.xlsx
@@ -5288,7 +5288,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:M26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -5715,7 +5715,7 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>No category breakdown on this sheet (FY2018-FY2014) — total risk exposure amount only; these years were not re-checked in the 2026-09-12 re-verification, see sources note</t>
+          <t>'Overview of RWA' (Basel/EBA OV1 layout) — each year's own Pillar 3 Disclosure, FY2018-FY2014. Row definitions change in FY2017 (credit risk printed INCLUDING CCR); see sources note</t>
         </is>
       </c>
       <c r="B17" s="6" t="n"/>
@@ -5734,7 +5734,7 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed — category breakdown</t>
+          <t>Credit risk (excluding counterparty credit risk, standardised approach)</t>
         </is>
       </c>
       <c r="B18" s="6" t="n"/>
@@ -5744,63 +5744,182 @@
       <c r="F18" s="6" t="n"/>
       <c r="G18" s="6" t="n"/>
       <c r="H18" s="6" t="n"/>
-      <c r="I18" s="6" t="inlineStr">
-        <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
-      <c r="J18" s="6" t="inlineStr">
-        <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
-      <c r="K18" s="6" t="inlineStr">
-        <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
-      <c r="L18" s="6" t="inlineStr">
-        <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
-      <c r="M18" s="6" t="inlineStr">
-        <is>
-          <t>Not publicly disclosed</t>
-        </is>
+      <c r="I18" s="6" t="n">
+        <v>754002</v>
+      </c>
+      <c r="J18" s="6" t="n"/>
+      <c r="K18" s="6" t="n">
+        <v>840455</v>
+      </c>
+      <c r="L18" s="6" t="n">
+        <v>754715</v>
+      </c>
+      <c r="M18" s="6" t="n">
+        <v>800993</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>Total risk exposure amount</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="n"/>
-      <c r="C19" s="5" t="n"/>
-      <c r="D19" s="5" t="n"/>
-      <c r="E19" s="5" t="n"/>
-      <c r="F19" s="5" t="n"/>
-      <c r="G19" s="5" t="n"/>
-      <c r="H19" s="5" t="n"/>
-      <c r="I19" s="5" t="n">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>Credit risk (including counterparty credit and dilution risks and free deliveries, as published)</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n"/>
+      <c r="C19" s="6" t="n"/>
+      <c r="D19" s="6" t="n"/>
+      <c r="E19" s="6" t="n"/>
+      <c r="F19" s="6" t="n"/>
+      <c r="G19" s="6" t="n"/>
+      <c r="H19" s="6" t="n"/>
+      <c r="I19" s="6" t="n"/>
+      <c r="J19" s="6" t="n">
+        <v>757906</v>
+      </c>
+      <c r="K19" s="6" t="n"/>
+      <c r="L19" s="6" t="n"/>
+      <c r="M19" s="6" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Counterparty credit risk (standardised approach; includes CVA per the same editions' Pillar 1 table)</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n"/>
+      <c r="C20" s="6" t="n"/>
+      <c r="D20" s="6" t="n"/>
+      <c r="E20" s="6" t="n"/>
+      <c r="F20" s="6" t="n"/>
+      <c r="G20" s="6" t="n"/>
+      <c r="H20" s="6" t="n"/>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J20" s="6" t="n"/>
+      <c r="K20" s="6" t="n">
+        <v>4164</v>
+      </c>
+      <c r="L20" s="6" t="n">
+        <v>2062</v>
+      </c>
+      <c r="M20" s="6" t="n">
+        <v>3251</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>Credit valuation adjustment (CVA)</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n"/>
+      <c r="C21" s="6" t="n"/>
+      <c r="D21" s="6" t="n"/>
+      <c r="E21" s="6" t="n"/>
+      <c r="F21" s="6" t="n"/>
+      <c r="G21" s="6" t="n"/>
+      <c r="H21" s="6" t="n"/>
+      <c r="I21" s="6" t="n">
+        <v>2757</v>
+      </c>
+      <c r="J21" s="6" t="n">
+        <v>2526</v>
+      </c>
+      <c r="K21" s="6" t="n"/>
+      <c r="L21" s="6" t="n"/>
+      <c r="M21" s="6" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>Market risk (standardised approach)</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n"/>
+      <c r="C22" s="6" t="n"/>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="6" t="n"/>
+      <c r="F22" s="6" t="n"/>
+      <c r="G22" s="6" t="n"/>
+      <c r="H22" s="6" t="n"/>
+      <c r="I22" s="6" t="n">
+        <v>8927</v>
+      </c>
+      <c r="J22" s="6" t="n">
+        <v>9694</v>
+      </c>
+      <c r="K22" s="6" t="n">
+        <v>11206</v>
+      </c>
+      <c r="L22" s="6" t="n">
+        <v>9973</v>
+      </c>
+      <c r="M22" s="6" t="n">
+        <v>13244</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>Operational risk (Basic Indicator Approach)</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n"/>
+      <c r="C23" s="6" t="n"/>
+      <c r="D23" s="6" t="n"/>
+      <c r="E23" s="6" t="n"/>
+      <c r="F23" s="6" t="n"/>
+      <c r="G23" s="6" t="n"/>
+      <c r="H23" s="6" t="n"/>
+      <c r="I23" s="6" t="n">
+        <v>175366</v>
+      </c>
+      <c r="J23" s="6" t="n">
+        <v>161079</v>
+      </c>
+      <c r="K23" s="6" t="n">
+        <v>148088</v>
+      </c>
+      <c r="L23" s="6" t="n">
+        <v>128723</v>
+      </c>
+      <c r="M23" s="6" t="n">
+        <v>107314</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Total (as printed in the Overview of RWA table)</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n"/>
+      <c r="C24" s="5" t="n"/>
+      <c r="D24" s="5" t="n"/>
+      <c r="E24" s="5" t="n"/>
+      <c r="F24" s="5" t="n"/>
+      <c r="G24" s="5" t="n"/>
+      <c r="H24" s="5" t="n"/>
+      <c r="I24" s="5" t="n">
         <v>941052</v>
       </c>
-      <c r="J19" s="5" t="n">
+      <c r="J24" s="5" t="n">
         <v>931206</v>
       </c>
-      <c r="K19" s="5" t="n">
+      <c r="K24" s="5" t="n">
         <v>1003913</v>
       </c>
-      <c r="L19" s="5" t="n">
+      <c r="L24" s="5" t="n">
         <v>895473</v>
       </c>
-      <c r="M19" s="5" t="n">
-        <v>800993</v>
-      </c>
-    </row>
-    <row r="21" ht="280" customHeight="1">
-      <c r="A21" s="8" t="inlineStr">
+      <c r="M24" s="5" t="n">
+        <v>924791</v>
+      </c>
+    </row>
+    <row r="26" ht="280" customHeight="1">
+      <c r="A26" s="8" t="inlineStr">
         <is>
           <t>Sources - Bank of China (UK) Limited's own UK OV1/EU OV1 'Overview of risk weighted exposure amounts' tables (same 5 Pillar 3 documents as the Total RWAs sheet), each year's own originally-published figures used as primary (not a later restated comparative), per project convention:
 FY2025: Pillar 3 Disclosure 2025, Table 'UK OV1' - https://pic.bankofchina.com/bocappd/uk/202607/P020260716391457618567.pdf
@@ -5810,13 +5929,14 @@
 FY2021: Pillar 3 Disclosure 2021, Table 1 'Template EU OV1', p.14 - https://www.bankofchina.com/uk/aboutus/ab5/202303/P020230315381669571541.pdf
 FY2020 (own year) &amp; FY2019 comparative: the FY2020 Pillar 3 document's own Table 9 'Overview of risk weighted assets' (UK OV1 template), p.20-22 - https://pic.bankofchina.com/bocappd/uk/202110/P020211027537761891740.pdf
 CORRECTION (fresh re-verification, 2026-09-12): the prior version of this sheet claimed FY2021-FY2025 (and FY2014-FY2018) had no category-level breakdown disclosed. That was wrong for FY2021-FY2025 - every one of those 5 Pillar 3 documents was re-read directly and each contains a full OV1/EU OV1 table, with every year's Total tying exactly to the Total RWAs sheet's own figure. FY2014-FY2018 were not re-checked in this pass (out of scope - this re-verification targeted the last-5-years gap) and remain as previously documented pending a future check.
-TEMPLATE FORMAT CHANGE: FY2021's own document does not carry a separate 'Counterparty credit risk (CCR)' line (only Credit risk, CVA, Market risk, Operational risk) - the following year's own document's FY2021 comparative column DOES split out a CCR figure (£16,535k) with a correspondingly smaller credit-risk figure (£776,521k vs £793,055k as FY2021's own document states it, a difference of £16,534k), confirming the CCR amount was folded into the 'credit risk' line in FY2021's own original publication rather than omitted entirely. FY2021's own originally-published split is used here per project convention, with the later restatement noted rather than silently substituted. FY2022 onward carries CCR as its own explicit line every year.</t>
+TEMPLATE FORMAT CHANGE: FY2021's own document does not carry a separate 'Counterparty credit risk (CCR)' line (only Credit risk, CVA, Market risk, Operational risk) - the following year's own document's FY2021 comparative column DOES split out a CCR figure (£16,535k) with a correspondingly smaller credit-risk figure (£776,521k vs £793,055k as FY2021's own document states it, a difference of £16,534k), confirming the CCR amount was folded into the 'credit risk' line in FY2021's own original publication rather than omitted entirely. FY2021's own originally-published split is used here per project convention, with the later restatement noted rather than silently substituted. FY2022 onward carries CCR as its own explicit line every year.
+FY2014-FY2018 BREAKDOWN FOUND 2026-09-19 (GA-020). These years previously read 'Not publicly disclosed - category breakdown'. That was wrong: each edition prints an 'Overview of RWA' table. Sources, each year's own edition, read from the page image: FY2018 - Pillar 3 Disclosures 2018, Table 6, printed p.28 - https://pic.bankofchina.com/bocappd/uk/201904/P020190410408108385209.pdf; FY2017 - Pillar 3 Disclosures 2017, Table 3, printed p.13 - https://pic.bankofchina.com/bocappd/uk/201803/P020180328577372288229.pdf; FY2016 - Capital and Risk Management Pillar 3 Disclosures 2016, Table 3, printed p.13 - https://pic.bankofchina.com/bocappd/uk/201706/P020170627381103226068.pdf; FY2015 - Capital and Risk Management Pillar 3 Disclosures 2015, Table 3, printed p.12 - https://pic.bankofchina.com/bocappd/uk/201606/P020160620504436264971.pdf; FY2014 - Pillar 3 Disclosures 2014, Table 3, printed p.11 - https://pic.bankofchina.com/bocappd/uk/201509/P020150910375228515274.pdf. ROW DEFINITIONS: FY2014-FY2016 print credit risk EXCLUDING CCR plus a separate CCR line (the same editions' Pillar 1 table labels that line 'Counterparty Credit Risk (including CVA)', so there is no separate CVA row for those years); FY2017 prints credit risk INCLUDING counterparty credit and dilution risks and free deliveries, plus a CVA line, so it has its own row; FY2018 returns to the excluding-CCR layout, printing a dash for CCR and a separate CVA line. SOURCE ARITHMETIC, recorded not corrected: FY2014's rows sum to 924,802 against the printed Total 924,791 (an 11k gap inside the table); FY2017's sum to 931,205 against 931,206 (the FY2018 edition's comparative prints 931,205). FY2015, FY2016 and FY2018 foot exactly. FY2014 BASIS DIVERGENCE, recorded not reconciled: the SAME FY2014 edition prints TWO different 'RWA' figures - Table 1 'Total capital resources and risk asset ratios' gives 'Risk-weighted assets (RWA) 800,993' (the figure carried on the Total RWAs sheet, and the denominator of its printed 34%/42% ratios), while Table 3 totals 924,791, and 800,993 is exactly Table 3's credit-risk-excluding-CCR line. This sheet's FY2014 Total is Table 3's printed total; the Total RWAs sheet keeps Table 1's figure. Neither is adjusted. FY2016: the FY2017 edition's comparative Total is 1,002,116 against the FY2016 edition's own 1,003,913 (already noted on the Total RWAs sheet); own-edition figures are used.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A21:M21"/>
+    <mergeCell ref="A26:M26"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6653,69 +6773,69 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>Not published – BoC (UK) FY2025 Pillar 3 has no MREL figure, KM2 or eligible-liabilities disclosure (text probe 0 hits, 2026-09-19)</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>Not published – BoC (UK) FY2024 Pillar 3 has no MREL figure, KM2 or eligible-liabilities disclosure (text probe 0 hits, 2026-09-19)</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>Not published – BoC (UK) FY2023 Pillar 3 has no MREL figure, KM2 or eligible-liabilities disclosure (text probe 0 hits, 2026-09-19)</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>Not published – BoC (UK) FY2022 Pillar 3 has no MREL figure, KM2 or eligible-liabilities disclosure (text probe 0 hits, 2026-09-19)</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>Not published – BoC (UK) FY2021 Pillar 3 has no MREL figure, KM2 or eligible-liabilities disclosure (text probe 0 hits, 2026-09-19)</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>Not published – BoC (UK) FY2020 Pillar 3 has no MREL figure, KM2 or eligible-liabilities disclosure (text probe 0 hits, 2026-09-19)</t>
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>Not published – BoC (UK) FY2019 Pillar 3 has no MREL figure, KM2 or eligible-liabilities disclosure (text probe 0 hits, 2026-09-19)</t>
         </is>
       </c>
       <c r="I4" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>Not published – BoC (UK) FY2018 Pillar 3 has no MREL figure, KM2 or eligible-liabilities disclosure (text probe 0 hits, 2026-09-19)</t>
         </is>
       </c>
       <c r="J4" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>Not published – BoC (UK) FY2017 Pillar 3 has no MREL figure, KM2 or eligible-liabilities disclosure (text probe 0 hits, 2026-09-19)</t>
         </is>
       </c>
       <c r="K4" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>Not published – BoC (UK) FY2016 Pillar 3 has no MREL figure, KM2 or eligible-liabilities disclosure (text probe 0 hits, 2026-09-19)</t>
         </is>
       </c>
       <c r="L4" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>Not published – BoC (UK) FY2015 Pillar 3 has no MREL figure, KM2 or eligible-liabilities disclosure (text probe 0 hits, 2026-09-19)</t>
         </is>
       </c>
       <c r="M4" s="6" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>Not published – BoC (UK) FY2014 Pillar 3 has no MREL figure, KM2 or eligible-liabilities disclosure (text probe 0 hits, 2026-09-19)</t>
         </is>
       </c>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Note: No MREL disclosure found in any of the 12 available Pillar 3 documents (FY2014-FY2025) - each was read in full (table of contents plus a full-text search for 'MREL') and none contains one.</t>
+          <t>Note: No MREL disclosure found in any of the 12 available Pillar 3 documents (FY2014-FY2025) - each was read in full (table of contents plus a full-text search for 'MREL') and none contains one. Re-checked 2026-09-19 (GA-020): all 12 editions re-downloaded (%PDF, text-native); 0 hits for 'MREL', 'KM2' and 'eligible liabilities' in each, against 93-223 'capital' hits; the only 'loss-absorbing' hits are the generic countercyclical-buffer description.</t>
         </is>
       </c>
     </row>

--- a/banks/BANK OF CHINA UK FINANCIALS.xlsx
+++ b/banks/BANK OF CHINA UK FINANCIALS.xlsx
@@ -116,7 +116,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -4304,7 +4304,7 @@
       <c r="L38" s="6" t="n"/>
       <c r="M38" s="6" t="n"/>
     </row>
-    <row r="40" ht="45" customHeight="1">
+    <row r="40" ht="30" customHeight="1">
       <c r="A40" s="7" t="inlineStr">
         <is>
           <t>Note: Figures are duplicated from the detail sheets for at-a-glance trend viewing; see each sheet's own source citation for the underlying document/page. See the Cash Flow Statement sheet's source note for a disclosed restatement gap between FY2022's and FY2023's own reports. FY2014's own Annual Report PDF is a scanned document with no extractable text layer - its figures are taken from FY2015's own report's FY2014 comparative column instead (see AR2014_SCAN_NOTE on the Balance Sheet sheet). LCR and NSFR are genuinely undisclosed before FY2017/FY2018 respectively (blank, not zero).</t>
@@ -4468,14 +4468,14 @@
         <v>274958</v>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
+    <row r="5" ht="30" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Note: Equal to CET1 capital every year FY2014-FY2021 (no AT1 instruments in issue until June 2022). A £60m Additional Tier 1 instrument was issued in June 2022, replacing an equal amount of Tier 2 subordinated debt.</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="170" customHeight="1">
+    <row r="7" ht="299" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Sources - Bank of China (UK) Limited Pillar 3 disclosures (UK KM1 Key Metrics template from FY2022 onward; FY2021's own document is narrative/ratio-only and predates the KM1 template; FY2014-FY2020 use the pre-KM1 CRD IV 'Table 1: Total capital resources and risk asset ratios' / 'Table 2: Leverage ratio' narrative-table format), £'000 unless stated:
@@ -4678,14 +4678,14 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
+    <row r="5" ht="30" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Note: Numerically equal to the CET1 ratio every year FY2014-FY2021 since Tier 1 capital equalled CET1 capital exactly (no AT1 in issue until June 2022); each year's own Table 1/KM1 document states this explicitly as its own 'Tier 1 capital ratio' line, not just inferred.</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="170" customHeight="1">
+    <row r="7" ht="299" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Sources - Bank of China (UK) Limited Pillar 3 disclosures (UK KM1 Key Metrics template from FY2022 onward; FY2021's own document is narrative/ratio-only and predates the KM1 template; FY2014-FY2020 use the pre-KM1 CRD IV 'Table 1: Total capital resources and risk asset ratios' / 'Table 2: Leverage ratio' narrative-table format), £'000 unless stated:
@@ -4864,7 +4864,7 @@
         <v>334958</v>
       </c>
     </row>
-    <row r="6" ht="170" customHeight="1">
+    <row r="6" ht="299" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Sources - Bank of China (UK) Limited Pillar 3 disclosures (UK KM1 Key Metrics template from FY2022 onward; FY2021's own document is narrative/ratio-only and predates the KM1 template; FY2014-FY2020 use the pre-KM1 CRD IV 'Table 1: Total capital resources and risk asset ratios' / 'Table 2: Leverage ratio' narrative-table format), £'000 unless stated:
@@ -5066,7 +5066,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="170" customHeight="1">
+    <row r="6" ht="299" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Sources - Bank of China (UK) Limited Pillar 3 disclosures (UK KM1 Key Metrics template from FY2022 onward; FY2021's own document is narrative/ratio-only and predates the KM1 template; FY2014-FY2020 use the pre-KM1 CRD IV 'Table 1: Total capital resources and risk asset ratios' / 'Table 2: Leverage ratio' narrative-table format), £'000 unless stated:
@@ -5244,14 +5244,14 @@
         <v>800993</v>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
+    <row r="5" ht="30" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Note: FY2016's own Table 1 states RWA as £1,003,913k; the FY2017 Pillar 3 document's own FY2016 comparative column shows a slightly different £1,002,116k (a ~£1.8k/0.2% difference, not explained in either document) - each year's own originally-published figure is used as the primary value throughout, per project convention.</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="170" customHeight="1">
+    <row r="7" ht="299" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Sources - Bank of China (UK) Limited Pillar 3 disclosures (UK KM1 Key Metrics template from FY2022 onward; FY2021's own document is narrative/ratio-only and predates the KM1 template; FY2014-FY2020 use the pre-KM1 CRD IV 'Table 1: Total capital resources and risk asset ratios' / 'Table 2: Leverage ratio' narrative-table format), £'000 unless stated:
@@ -5918,7 +5918,7 @@
         <v>924791</v>
       </c>
     </row>
-    <row r="26" ht="280" customHeight="1">
+    <row r="26" ht="286" customHeight="1">
       <c r="A26" s="8" t="inlineStr">
         <is>
           <t>Sources - Bank of China (UK) Limited's own UK OV1/EU OV1 'Overview of risk weighted exposure amounts' tables (same 5 Pillar 3 documents as the Total RWAs sheet), each year's own originally-published figures used as primary (not a later restated comparative), per project convention:
@@ -6157,14 +6157,18 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="60" customHeight="1">
+    <row r="6" ht="143" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>Note: FY2021's 11.3% is on an older/broader exposure-measure basis (pre-dates the KM1 'excluding claims on central banks' framework used from FY2022 onward) - not directly comparable to later years, kept on its own row per project convention. FY2014-FY2020 use the pre-KM1 CRD IV leverage framework (Table 2 in each year's own document) - broadly the same 'Tier 1 capital / total exposure measure' concept throughout, but methodology details (e.g. treatment of off-balance-sheet items, central bank claims) evolved gradually across this whole span, so a smooth-looking multi-year trend should be read with that caveat rather than as a single unbroken methodology.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="170" customHeight="1">
+          <t>Note: FY2021's 11.3% is on an older/broader exposure-measure basis - not directly comparable to later years, kept on its own row per project convention. FY2014-FY2020 use the pre-KM1 CRD IV leverage framework (Table 2 in each year's own document) - broadly the same 'Tier 1 capital / total exposure measure' concept throughout, but methodology details (e.g. treatment of off-balance-sheet items, central bank claims) evolved gradually across this whole span, so a smooth-looking multi-year trend should be read with that caveat rather than as a single unbroken methodology.
+LEVERAGE BASIS: THE BANK ATTACHES NO BASIS QUALIFIER, AND AN EARLIER CLAIM HERE THAT IT DID IS WITHDRAWN (GA-026, 2026-10-10). This note previously described FY2021 as pre-dating "the KM1 'excluding claims on central banks' framework used from FY2022 onward". THAT ATTRIBUTION WAS NOT SUPPORTED BY THE BANK'S OWN DOCUMENTS and has been removed; the surrounding statement that FY2021 sits on an older, broader measure is kept, because the series itself shows it.
+What the documents actually print: Bank of China (UK) publishes no template UK LR2 in any edition - no row 24, UK-24a, UK-24b or UK-25c - and its key-metrics table carries two rows captioned simply '13 Total Basel III leverage ratio exposure measure' and '14 Basel III leverage ratio (%)', with no central-bank qualifier on either. Section 4.3 'Leverage Ratio' discusses only the PRA's 3.25% expectation under SS45/15 and states no basis. No reconciliation of accounting assets to leverage exposure is printed, so there is no deduction line - and no absence of one - to read a basis from. A full-text search finds 'central bank' only in balance-sheet and credit-risk exposure tables ('Cash and balances at central banks', 'Government &amp; Central Banks'), never in the leverage computation.
+WHY THE FY2021-TO-FY2022 STEP IS NOT EVIDENCE OF AN EXCLUSION. The FY2022 edition prints its FY2021 comparative as £2,431,869k / 11.3% - IDENTICAL to FY2021's own report, under the same 'Basel III leverage ratio' caption, with no restatement and no change-of-basis note. A move onto an excluding basis would normally restate the comparative or be flagged; neither happened. The exposure measure fell from £2,431,869k to £1,814,024k (-25%) while the ratio rose from 11.3% to 18.5%, which a shrinking balance sheet and rising capital explain without invoking a basis change. No basis is therefore attributed to any year of this series.
+(Checked against the FY2022 and FY2024 editions, both read in full; the matcher used was first shown to fire on documents that do carry the phrases.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="299" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
         <is>
           <t>Sources - Bank of China (UK) Limited Pillar 3 disclosures (UK KM1 Key Metrics template from FY2022 onward; FY2021's own document is narrative/ratio-only and predates the KM1 template; FY2014-FY2020 use the pre-KM1 CRD IV 'Table 1: Total capital resources and risk asset ratios' / 'Table 2: Leverage ratio' narrative-table format), £'000 unless stated:
@@ -6398,14 +6402,14 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="60" customHeight="1">
+    <row r="7" ht="30" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Note: FY2017's 167% ratio is the only FY2017 LCR figure available anywhere (from the FY2018 Pillar 3 document's own FY2017 comparative column - FY2017's own document predates LCR disclosure entirely) and has no accompanying HQLA/outflow £-breakdown, hence the blank cells on those two rows. LCR is genuinely undisclosed for FY2014-FY2016 (confirmed absent from all three years' own Pillar 3 documents, read in full).</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="170" customHeight="1">
+    <row r="9" ht="312" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
           <t>Sources - Bank of China (UK) Limited Pillar 3 disclosures (UK KM1 Key Metrics template from FY2022 onward; FY2021's own document is narrative/ratio-only and predates the KM1 template; FY2014-FY2020 use the pre-KM1 CRD IV 'Table 1: Total capital resources and risk asset ratios' / 'Table 2: Leverage ratio' narrative-table format), £'000 unless stated:
@@ -6626,14 +6630,14 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="60" customHeight="1">
+    <row r="7" ht="39" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Note: FY2021's own Pillar 3 document does not disclose an NSFR figure at all (the UK NSFR regime's formal KM1 disclosure only started from FY2022) - the FY2021 figures here are taken from the FY2022 Pillar 3 document's FY2021 comparative column instead, the only source where they appear. NSFR is genuinely undisclosed for FY2014-FY2017 (confirmed absent from all four years' own Pillar 3 documents, read in full) - FY2018 is the earliest year any NSFR figure exists for this bank.</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="170" customHeight="1">
+    <row r="9" ht="325" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
           <t>Sources - Bank of China (UK) Limited Pillar 3 disclosures (UK KM1 Key Metrics template from FY2022 onward; FY2021's own document is narrative/ratio-only and predates the KM1 template; FY2014-FY2020 use the pre-KM1 CRD IV 'Table 1: Total capital resources and risk asset ratios' / 'Table 2: Leverage ratio' narrative-table format), £'000 unless stated:
@@ -6832,14 +6836,14 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
+    <row r="5" ht="30" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Note: No MREL disclosure found in any of the 12 available Pillar 3 documents (FY2014-FY2025) - each was read in full (table of contents plus a full-text search for 'MREL') and none contains one. Re-checked 2026-09-19 (GA-020): all 12 editions re-downloaded (%PDF, text-native); 0 hits for 'MREL', 'KM2' and 'eligible liabilities' in each, against 93-223 'capital' hits; the only 'loss-absorbing' hits are the generic countercyclical-buffer description.</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="170" customHeight="1">
+    <row r="7" ht="299" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Sources - Bank of China (UK) Limited Pillar 3 disclosures (UK KM1 Key Metrics template from FY2022 onward; FY2021's own document is narrative/ratio-only and predates the KM1 template; FY2014-FY2020 use the pre-KM1 CRD IV 'Table 1: Total capital resources and risk asset ratios' / 'Table 2: Leverage ratio' narrative-table format), £'000 unless stated:
@@ -6871,6 +6875,1893 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:S41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="68" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="15" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="15" max="15"/>
+    <col width="15" customWidth="1" min="16" max="16"/>
+    <col width="15" customWidth="1" min="17" max="17"/>
+    <col width="15" customWidth="1" min="18" max="18"/>
+    <col width="15" customWidth="1" min="19" max="19"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Bank of China (UK) Limited — Statement of Financial Position</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Bank of China (UK) Limited (solo entity basis), £'000</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025 (£'000)</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024 (£'000)</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023 (£'000)</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022 (£'000)</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021 (£'000)</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020 (£'000)</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019 (£'000)</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>FY2018 (£'000)</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>FY2017 (£'000)</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>FY2016 (£'000)</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>FY2015 (£'000)</t>
+        </is>
+      </c>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>FY2014 (£'000)</t>
+        </is>
+      </c>
+      <c r="N3" s="4" t="inlineStr">
+        <is>
+          <t>FY2013 (£'000)</t>
+        </is>
+      </c>
+      <c r="O3" s="4" t="inlineStr">
+        <is>
+          <t>FY2012 (£'000)</t>
+        </is>
+      </c>
+      <c r="P3" s="4" t="inlineStr">
+        <is>
+          <t>FY2011 (£'000)</t>
+        </is>
+      </c>
+      <c r="Q3" s="4" t="inlineStr">
+        <is>
+          <t>FY2010 (£'000)</t>
+        </is>
+      </c>
+      <c r="R3" s="4" t="inlineStr">
+        <is>
+          <t>FY2009 (£'000)</t>
+        </is>
+      </c>
+      <c r="S3" s="4" t="inlineStr">
+        <is>
+          <t>FY2008 (£'000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Assets</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="6" t="n"/>
+      <c r="G4" s="6" t="n"/>
+      <c r="H4" s="6" t="n"/>
+      <c r="I4" s="6" t="n"/>
+      <c r="J4" s="6" t="n"/>
+      <c r="K4" s="6" t="n"/>
+      <c r="L4" s="6" t="n"/>
+      <c r="M4" s="6" t="n"/>
+      <c r="N4" s="6" t="n"/>
+      <c r="O4" s="6" t="n"/>
+      <c r="P4" s="6" t="n"/>
+      <c r="Q4" s="6" t="n"/>
+      <c r="R4" s="6" t="n"/>
+      <c r="S4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Cash and balances at central banks</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>982512</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>975201</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>687070</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>657656</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>716133</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>481379</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>332542</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>333275</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>281944</v>
+      </c>
+      <c r="K5" s="6" t="n">
+        <v>311917</v>
+      </c>
+      <c r="L5" s="6" t="n">
+        <v>344019</v>
+      </c>
+      <c r="M5" s="6" t="n">
+        <v>199854</v>
+      </c>
+      <c r="N5" s="6" t="n">
+        <v>159219</v>
+      </c>
+      <c r="O5" s="6" t="n">
+        <v>197622</v>
+      </c>
+      <c r="P5" s="6" t="n">
+        <v>275821</v>
+      </c>
+      <c r="Q5" s="6" t="n">
+        <v>215155</v>
+      </c>
+      <c r="R5" s="6" t="n">
+        <v>127812</v>
+      </c>
+      <c r="S5" s="6" t="n">
+        <v>40069</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Government bonds</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>142529</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>144495</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>118328</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>44264</v>
+      </c>
+      <c r="F6" s="6" t="n"/>
+      <c r="G6" s="6" t="n"/>
+      <c r="H6" s="6" t="n"/>
+      <c r="I6" s="6" t="n"/>
+      <c r="J6" s="6" t="n"/>
+      <c r="K6" s="6" t="n"/>
+      <c r="L6" s="6" t="n"/>
+      <c r="M6" s="6" t="n"/>
+      <c r="N6" s="6" t="n"/>
+      <c r="O6" s="6" t="n"/>
+      <c r="P6" s="6" t="n"/>
+      <c r="Q6" s="6" t="n"/>
+      <c r="R6" s="6" t="n"/>
+      <c r="S6" s="6" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Loans and advances to banks</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>90733</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>73658</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>86477</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>29357</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>69065</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>110446</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>85247</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>61391</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>83706</v>
+      </c>
+      <c r="K7" s="6" t="n">
+        <v>24270</v>
+      </c>
+      <c r="L7" s="6" t="n">
+        <v>62633</v>
+      </c>
+      <c r="M7" s="6" t="n">
+        <v>207026</v>
+      </c>
+      <c r="N7" s="6" t="n">
+        <v>168898</v>
+      </c>
+      <c r="O7" s="6" t="n">
+        <v>48779</v>
+      </c>
+      <c r="P7" s="6" t="n">
+        <v>12865</v>
+      </c>
+      <c r="Q7" s="6" t="n">
+        <v>12817</v>
+      </c>
+      <c r="R7" s="6" t="n">
+        <v>36933</v>
+      </c>
+      <c r="S7" s="6" t="n">
+        <v>67272</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Loans and advances to customers</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>810985</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>941507</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>990763</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>1122459</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>1194653</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>1138583</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>1064347</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>1044570</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>1054454</v>
+      </c>
+      <c r="K8" s="6" t="n">
+        <v>1159696</v>
+      </c>
+      <c r="L8" s="6" t="n">
+        <v>810776</v>
+      </c>
+      <c r="M8" s="6" t="n">
+        <v>722307</v>
+      </c>
+      <c r="N8" s="6" t="n">
+        <v>581030</v>
+      </c>
+      <c r="O8" s="6" t="n">
+        <v>464479</v>
+      </c>
+      <c r="P8" s="6" t="n">
+        <v>290752</v>
+      </c>
+      <c r="Q8" s="6" t="n">
+        <v>214623</v>
+      </c>
+      <c r="R8" s="6" t="n">
+        <v>504743</v>
+      </c>
+      <c r="S8" s="6" t="n">
+        <v>551148</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Derivative financial instruments</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>2504</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>4667</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>5506</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>7702</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>48163</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>4614</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>1344</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>1717</v>
+      </c>
+      <c r="K9" s="6" t="n">
+        <v>4577</v>
+      </c>
+      <c r="L9" s="6" t="n">
+        <v>8173</v>
+      </c>
+      <c r="M9" s="6" t="n">
+        <v>16173</v>
+      </c>
+      <c r="N9" s="6" t="n">
+        <v>41502</v>
+      </c>
+      <c r="O9" s="6" t="n">
+        <v>1949</v>
+      </c>
+      <c r="P9" s="6" t="n">
+        <v>72</v>
+      </c>
+      <c r="Q9" s="6" t="n">
+        <v>505</v>
+      </c>
+      <c r="R9" s="6" t="n">
+        <v>1375</v>
+      </c>
+      <c r="S9" s="6" t="n">
+        <v>5554</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Prepayments, accrued income and other assets</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>156554</v>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>138246</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>130581</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>351967</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>87868</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>78769</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>58405</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>6273</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>5204</v>
+      </c>
+      <c r="K10" s="6" t="n">
+        <v>4762</v>
+      </c>
+      <c r="L10" s="6" t="n">
+        <v>25831</v>
+      </c>
+      <c r="M10" s="6" t="n">
+        <v>27820</v>
+      </c>
+      <c r="N10" s="6" t="n">
+        <v>66602</v>
+      </c>
+      <c r="O10" s="6" t="n">
+        <v>64084</v>
+      </c>
+      <c r="P10" s="6" t="n">
+        <v>37692</v>
+      </c>
+      <c r="Q10" s="6" t="n">
+        <v>46427</v>
+      </c>
+      <c r="R10" s="6" t="n">
+        <v>29780</v>
+      </c>
+      <c r="S10" s="6" t="n">
+        <v>21197</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Financial assets at fair value through profit and loss</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>71293</v>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>30150</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>47445</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>60514</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>64659</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>77482</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>83928</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>76171</v>
+      </c>
+      <c r="J11" s="6" t="n"/>
+      <c r="K11" s="6" t="n"/>
+      <c r="L11" s="6" t="n"/>
+      <c r="M11" s="6" t="n"/>
+      <c r="N11" s="6" t="n"/>
+      <c r="O11" s="6" t="n"/>
+      <c r="P11" s="6" t="n"/>
+      <c r="Q11" s="6" t="n"/>
+      <c r="R11" s="6" t="n"/>
+      <c r="S11" s="6" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Available for sale financial investments</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n"/>
+      <c r="C12" s="6" t="n"/>
+      <c r="D12" s="6" t="n"/>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="6" t="n"/>
+      <c r="G12" s="6" t="n"/>
+      <c r="H12" s="6" t="n"/>
+      <c r="I12" s="6" t="n"/>
+      <c r="J12" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="K12" s="6" t="n">
+        <v>40716</v>
+      </c>
+      <c r="L12" s="6" t="n">
+        <v>35859</v>
+      </c>
+      <c r="M12" s="6" t="n">
+        <v>37469</v>
+      </c>
+      <c r="N12" s="6" t="n">
+        <v>28754</v>
+      </c>
+      <c r="O12" s="6" t="n">
+        <v>46270</v>
+      </c>
+      <c r="P12" s="6" t="n">
+        <v>95671</v>
+      </c>
+      <c r="Q12" s="6" t="n">
+        <v>149677</v>
+      </c>
+      <c r="R12" s="6" t="n">
+        <v>249004</v>
+      </c>
+      <c r="S12" s="6" t="n">
+        <v>330093</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Held to maturity / debt instruments at amortised cost</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n"/>
+      <c r="C13" s="6" t="n"/>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="n"/>
+      <c r="G13" s="6" t="n"/>
+      <c r="H13" s="6" t="n">
+        <v>50431</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>103189</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>107478</v>
+      </c>
+      <c r="K13" s="6" t="n"/>
+      <c r="L13" s="6" t="n"/>
+      <c r="M13" s="6" t="n"/>
+      <c r="N13" s="6" t="n"/>
+      <c r="O13" s="6" t="n"/>
+      <c r="P13" s="6" t="n"/>
+      <c r="Q13" s="6" t="n"/>
+      <c r="R13" s="6" t="n"/>
+      <c r="S13" s="6" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Investment in subsidiary/group companies</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="6" t="n"/>
+      <c r="G14" s="6" t="n"/>
+      <c r="H14" s="6" t="n"/>
+      <c r="I14" s="6" t="n"/>
+      <c r="J14" s="6" t="n"/>
+      <c r="K14" s="6" t="n"/>
+      <c r="L14" s="6" t="n"/>
+      <c r="M14" s="6" t="n"/>
+      <c r="N14" s="6" t="n"/>
+      <c r="O14" s="6" t="n"/>
+      <c r="P14" s="6" t="n">
+        <v>63285</v>
+      </c>
+      <c r="Q14" s="6" t="n">
+        <v>94357</v>
+      </c>
+      <c r="R14" s="6" t="n">
+        <v>29945</v>
+      </c>
+      <c r="S14" s="6" t="n">
+        <v>32128</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>Current tax asset</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n">
+        <v>4582</v>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>2934</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>637</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>2351</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>5979</v>
+      </c>
+      <c r="G15" s="6" t="n"/>
+      <c r="H15" s="6" t="n"/>
+      <c r="I15" s="6" t="n"/>
+      <c r="J15" s="6" t="n"/>
+      <c r="K15" s="6" t="n"/>
+      <c r="L15" s="6" t="n"/>
+      <c r="M15" s="6" t="n"/>
+      <c r="N15" s="6" t="n"/>
+      <c r="O15" s="6" t="n"/>
+      <c r="P15" s="6" t="n"/>
+      <c r="Q15" s="6" t="n"/>
+      <c r="R15" s="6" t="n"/>
+      <c r="S15" s="6" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Deferred tax assets</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n">
+        <v>289</v>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>406</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>359</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>1280</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>1283</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>1227</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>787</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>1546</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>1462</v>
+      </c>
+      <c r="K16" s="6" t="n">
+        <v>562</v>
+      </c>
+      <c r="L16" s="6" t="n">
+        <v>425</v>
+      </c>
+      <c r="M16" s="6" t="n">
+        <v>751</v>
+      </c>
+      <c r="N16" s="6" t="n">
+        <v>276</v>
+      </c>
+      <c r="O16" s="6" t="n">
+        <v>206</v>
+      </c>
+      <c r="P16" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q16" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="R16" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="S16" s="6" t="n">
+        <v>5656</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>Property, plant and equipment</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n">
+        <v>11573</v>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>11419</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>11902</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>12769</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>11167</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>4527</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>6328</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>2761</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>3149</v>
+      </c>
+      <c r="K17" s="6" t="n">
+        <v>3276</v>
+      </c>
+      <c r="L17" s="6" t="n">
+        <v>3514</v>
+      </c>
+      <c r="M17" s="6" t="n">
+        <v>3390</v>
+      </c>
+      <c r="N17" s="6" t="n">
+        <v>3765</v>
+      </c>
+      <c r="O17" s="6" t="n">
+        <v>4032</v>
+      </c>
+      <c r="P17" s="6" t="n">
+        <v>1374</v>
+      </c>
+      <c r="Q17" s="6" t="n">
+        <v>1612</v>
+      </c>
+      <c r="R17" s="6" t="n">
+        <v>2025</v>
+      </c>
+      <c r="S17" s="6" t="n">
+        <v>2371</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Intangible assets</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n">
+        <v>887</v>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>636</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>305</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>274</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>362</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>529</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>759</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>462</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>95</v>
+      </c>
+      <c r="K18" s="6" t="n">
+        <v>122</v>
+      </c>
+      <c r="L18" s="6" t="n">
+        <v>180</v>
+      </c>
+      <c r="M18" s="6" t="n">
+        <v>326</v>
+      </c>
+      <c r="N18" s="6" t="n">
+        <v>29</v>
+      </c>
+      <c r="O18" s="6" t="n">
+        <v>106</v>
+      </c>
+      <c r="P18" s="6" t="n">
+        <v>163</v>
+      </c>
+      <c r="Q18" s="6" t="n">
+        <v>317</v>
+      </c>
+      <c r="R18" s="6" t="n">
+        <v>440</v>
+      </c>
+      <c r="S18" s="6" t="n">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Total assets</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>2274441</v>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>2323319</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>2079373</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>2290593</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>2151180</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>1941105</v>
+      </c>
+      <c r="H19" s="5" t="n">
+        <v>1687388</v>
+      </c>
+      <c r="I19" s="5" t="n">
+        <v>1630982</v>
+      </c>
+      <c r="J19" s="5" t="n">
+        <v>1539221</v>
+      </c>
+      <c r="K19" s="5" t="n">
+        <v>1549898</v>
+      </c>
+      <c r="L19" s="5" t="n">
+        <v>1291410</v>
+      </c>
+      <c r="M19" s="5" t="n">
+        <v>1215116</v>
+      </c>
+      <c r="N19" s="5" t="n">
+        <v>1050075</v>
+      </c>
+      <c r="O19" s="5" t="n">
+        <v>827527</v>
+      </c>
+      <c r="P19" s="5" t="n">
+        <v>777725</v>
+      </c>
+      <c r="Q19" s="5" t="n">
+        <v>735494</v>
+      </c>
+      <c r="R19" s="5" t="n">
+        <v>982073</v>
+      </c>
+      <c r="S19" s="5" t="n">
+        <v>1055809</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Liabilities</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n"/>
+      <c r="C20" s="6" t="n"/>
+      <c r="D20" s="6" t="n"/>
+      <c r="E20" s="6" t="n"/>
+      <c r="F20" s="6" t="n"/>
+      <c r="G20" s="6" t="n"/>
+      <c r="H20" s="6" t="n"/>
+      <c r="I20" s="6" t="n"/>
+      <c r="J20" s="6" t="n"/>
+      <c r="K20" s="6" t="n"/>
+      <c r="L20" s="6" t="n"/>
+      <c r="M20" s="6" t="n"/>
+      <c r="N20" s="6" t="n"/>
+      <c r="O20" s="6" t="n"/>
+      <c r="P20" s="6" t="n"/>
+      <c r="Q20" s="6" t="n"/>
+      <c r="R20" s="6" t="n"/>
+      <c r="S20" s="6" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>Deposits from banks</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n">
+        <v>511961</v>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>493256</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>369590</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>539387</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>396254</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>219378</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>128590</v>
+      </c>
+      <c r="I21" s="6" t="n">
+        <v>102919</v>
+      </c>
+      <c r="J21" s="6" t="n">
+        <v>123122</v>
+      </c>
+      <c r="K21" s="6" t="n">
+        <v>164849</v>
+      </c>
+      <c r="L21" s="6" t="n">
+        <v>136736</v>
+      </c>
+      <c r="M21" s="6" t="n">
+        <v>40270</v>
+      </c>
+      <c r="N21" s="6" t="n">
+        <v>72132</v>
+      </c>
+      <c r="O21" s="6" t="n">
+        <v>62384</v>
+      </c>
+      <c r="P21" s="6" t="n">
+        <v>202684</v>
+      </c>
+      <c r="Q21" s="6" t="n">
+        <v>176070</v>
+      </c>
+      <c r="R21" s="6" t="n">
+        <v>366763</v>
+      </c>
+      <c r="S21" s="6" t="n">
+        <v>560116</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>Deposits from customers</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n">
+        <v>1304816</v>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>1355529</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>1223068</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>1291150</v>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>1333523</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>1215647</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>1132193</v>
+      </c>
+      <c r="I22" s="6" t="n">
+        <v>1107439</v>
+      </c>
+      <c r="J22" s="6" t="n">
+        <v>1019007</v>
+      </c>
+      <c r="K22" s="6" t="n">
+        <v>982361</v>
+      </c>
+      <c r="L22" s="6" t="n">
+        <v>737724</v>
+      </c>
+      <c r="M22" s="6" t="n">
+        <v>765899</v>
+      </c>
+      <c r="N22" s="6" t="n">
+        <v>537699</v>
+      </c>
+      <c r="O22" s="6" t="n">
+        <v>398239</v>
+      </c>
+      <c r="P22" s="6" t="n">
+        <v>352176</v>
+      </c>
+      <c r="Q22" s="6" t="n">
+        <v>296289</v>
+      </c>
+      <c r="R22" s="6" t="n">
+        <v>378219</v>
+      </c>
+      <c r="S22" s="6" t="n">
+        <v>290289</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>Derivative financial instruments</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n">
+        <v>289</v>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>5280</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>56924</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>8771</v>
+      </c>
+      <c r="I23" s="6" t="n">
+        <v>1977</v>
+      </c>
+      <c r="J23" s="6" t="n">
+        <v>257</v>
+      </c>
+      <c r="K23" s="6" t="n">
+        <v>4150</v>
+      </c>
+      <c r="L23" s="6" t="n">
+        <v>11505</v>
+      </c>
+      <c r="M23" s="6" t="n">
+        <v>21499</v>
+      </c>
+      <c r="N23" s="6" t="n">
+        <v>42505</v>
+      </c>
+      <c r="O23" s="6" t="n">
+        <v>3435</v>
+      </c>
+      <c r="P23" s="6" t="n">
+        <v>4416</v>
+      </c>
+      <c r="Q23" s="6" t="n">
+        <v>5956</v>
+      </c>
+      <c r="R23" s="6" t="n">
+        <v>5766</v>
+      </c>
+      <c r="S23" s="6" t="n">
+        <v>5390</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>Other liabilities</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="n">
+        <v>39574</v>
+      </c>
+      <c r="C24" s="6" t="n">
+        <v>37473</v>
+      </c>
+      <c r="D24" s="6" t="n">
+        <v>38352</v>
+      </c>
+      <c r="E24" s="6" t="n">
+        <v>50379</v>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>43571</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>36086</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>43609</v>
+      </c>
+      <c r="I24" s="6" t="n">
+        <v>21359</v>
+      </c>
+      <c r="J24" s="6" t="n">
+        <v>20158</v>
+      </c>
+      <c r="K24" s="6" t="n">
+        <v>13620</v>
+      </c>
+      <c r="L24" s="6" t="n">
+        <v>17145</v>
+      </c>
+      <c r="M24" s="6" t="n">
+        <v>18089</v>
+      </c>
+      <c r="N24" s="6" t="n">
+        <v>23787</v>
+      </c>
+      <c r="O24" s="6" t="n">
+        <v>19123</v>
+      </c>
+      <c r="P24" s="6" t="n">
+        <v>15290</v>
+      </c>
+      <c r="Q24" s="6" t="n">
+        <v>14205</v>
+      </c>
+      <c r="R24" s="6" t="n">
+        <v>13404</v>
+      </c>
+      <c r="S24" s="6" t="n">
+        <v>10601</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>Accruals and deferred income</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="n">
+        <v>18650</v>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>23257</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>15017</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>7720</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>5657</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>5705</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>6390</v>
+      </c>
+      <c r="I25" s="6" t="n">
+        <v>6207</v>
+      </c>
+      <c r="J25" s="6" t="n">
+        <v>4176</v>
+      </c>
+      <c r="K25" s="6" t="n">
+        <v>5874</v>
+      </c>
+      <c r="L25" s="6" t="n">
+        <v>4512</v>
+      </c>
+      <c r="M25" s="6" t="n">
+        <v>4016</v>
+      </c>
+      <c r="N25" s="6" t="n">
+        <v>3729</v>
+      </c>
+      <c r="O25" s="6" t="n">
+        <v>4828</v>
+      </c>
+      <c r="P25" s="6" t="n">
+        <v>3602</v>
+      </c>
+      <c r="Q25" s="6" t="n">
+        <v>3137</v>
+      </c>
+      <c r="R25" s="6" t="n">
+        <v>2166</v>
+      </c>
+      <c r="S25" s="6" t="n">
+        <v>4099</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>Current tax liabilities</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="n"/>
+      <c r="C26" s="6" t="n"/>
+      <c r="D26" s="6" t="n"/>
+      <c r="E26" s="6" t="n"/>
+      <c r="F26" s="6" t="n"/>
+      <c r="G26" s="6" t="n">
+        <v>4891</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>675</v>
+      </c>
+      <c r="I26" s="6" t="n">
+        <v>4908</v>
+      </c>
+      <c r="J26" s="6" t="n">
+        <v>5447</v>
+      </c>
+      <c r="K26" s="6" t="n">
+        <v>8680</v>
+      </c>
+      <c r="L26" s="6" t="n">
+        <v>3520</v>
+      </c>
+      <c r="M26" s="6" t="n">
+        <v>3873</v>
+      </c>
+      <c r="N26" s="6" t="n">
+        <v>2521</v>
+      </c>
+      <c r="O26" s="6" t="n">
+        <v>3715</v>
+      </c>
+      <c r="P26" s="6" t="n"/>
+      <c r="Q26" s="6" t="n">
+        <v>14184</v>
+      </c>
+      <c r="R26" s="6" t="n">
+        <v>4106</v>
+      </c>
+      <c r="S26" s="6" t="n">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>Deferred tax liabilities</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n"/>
+      <c r="C27" s="6" t="n"/>
+      <c r="D27" s="6" t="n"/>
+      <c r="E27" s="6" t="n"/>
+      <c r="F27" s="6" t="n"/>
+      <c r="G27" s="6" t="n"/>
+      <c r="H27" s="6" t="n"/>
+      <c r="I27" s="6" t="n"/>
+      <c r="J27" s="6" t="n"/>
+      <c r="K27" s="6" t="n"/>
+      <c r="L27" s="6" t="n"/>
+      <c r="M27" s="6" t="n"/>
+      <c r="N27" s="6" t="n">
+        <v>28</v>
+      </c>
+      <c r="O27" s="6" t="n"/>
+      <c r="P27" s="6" t="n"/>
+      <c r="Q27" s="6" t="n"/>
+      <c r="R27" s="6" t="n"/>
+      <c r="S27" s="6" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>Impairment provision on off balance sheet products</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n">
+        <v>138</v>
+      </c>
+      <c r="C28" s="6" t="n">
+        <v>58</v>
+      </c>
+      <c r="D28" s="6" t="n">
+        <v>54</v>
+      </c>
+      <c r="E28" s="6" t="n">
+        <v>51</v>
+      </c>
+      <c r="F28" s="6" t="n">
+        <v>119</v>
+      </c>
+      <c r="G28" s="6" t="n">
+        <v>310</v>
+      </c>
+      <c r="H28" s="6" t="n">
+        <v>102</v>
+      </c>
+      <c r="I28" s="6" t="n">
+        <v>97</v>
+      </c>
+      <c r="J28" s="6" t="n"/>
+      <c r="K28" s="6" t="n"/>
+      <c r="L28" s="6" t="n"/>
+      <c r="M28" s="6" t="n"/>
+      <c r="N28" s="6" t="n"/>
+      <c r="O28" s="6" t="n"/>
+      <c r="P28" s="6" t="n"/>
+      <c r="Q28" s="6" t="n"/>
+      <c r="R28" s="6" t="n"/>
+      <c r="S28" s="6" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>Subordinated liabilities</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="n"/>
+      <c r="E29" s="6" t="n"/>
+      <c r="F29" s="6" t="n">
+        <v>60000</v>
+      </c>
+      <c r="G29" s="6" t="n">
+        <v>60000</v>
+      </c>
+      <c r="H29" s="6" t="n">
+        <v>60000</v>
+      </c>
+      <c r="I29" s="6" t="n">
+        <v>60000</v>
+      </c>
+      <c r="J29" s="6" t="n">
+        <v>60000</v>
+      </c>
+      <c r="K29" s="6" t="n">
+        <v>60000</v>
+      </c>
+      <c r="L29" s="6" t="n">
+        <v>60000</v>
+      </c>
+      <c r="M29" s="6" t="n">
+        <v>60000</v>
+      </c>
+      <c r="N29" s="6" t="n">
+        <v>60000</v>
+      </c>
+      <c r="O29" s="6" t="n">
+        <v>60000</v>
+      </c>
+      <c r="P29" s="6" t="n">
+        <v>60000</v>
+      </c>
+      <c r="Q29" s="6" t="n">
+        <v>60000</v>
+      </c>
+      <c r="R29" s="6" t="n">
+        <v>60000</v>
+      </c>
+      <c r="S29" s="6" t="n">
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>Total liabilities</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>1875428</v>
+      </c>
+      <c r="C30" s="5" t="n">
+        <v>1909575</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>1646084</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>1888700</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>1844404</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>1598941</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>1380330</v>
+      </c>
+      <c r="I30" s="5" t="n">
+        <v>1304906</v>
+      </c>
+      <c r="J30" s="5" t="n">
+        <v>1232167</v>
+      </c>
+      <c r="K30" s="5" t="n">
+        <v>1239534</v>
+      </c>
+      <c r="L30" s="5" t="n">
+        <v>971142</v>
+      </c>
+      <c r="M30" s="5" t="n">
+        <v>913636</v>
+      </c>
+      <c r="N30" s="5" t="n">
+        <v>742401</v>
+      </c>
+      <c r="O30" s="5" t="n">
+        <v>551724</v>
+      </c>
+      <c r="P30" s="5" t="n">
+        <v>638168</v>
+      </c>
+      <c r="Q30" s="5" t="n">
+        <v>569841</v>
+      </c>
+      <c r="R30" s="5" t="n">
+        <v>830424</v>
+      </c>
+      <c r="S30" s="5" t="n">
+        <v>930704</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+      <c r="E31" s="6" t="n"/>
+      <c r="F31" s="6" t="n"/>
+      <c r="G31" s="6" t="n"/>
+      <c r="H31" s="6" t="n"/>
+      <c r="I31" s="6" t="n"/>
+      <c r="J31" s="6" t="n"/>
+      <c r="K31" s="6" t="n"/>
+      <c r="L31" s="6" t="n"/>
+      <c r="M31" s="6" t="n"/>
+      <c r="N31" s="6" t="n"/>
+      <c r="O31" s="6" t="n"/>
+      <c r="P31" s="6" t="n"/>
+      <c r="Q31" s="6" t="n"/>
+      <c r="R31" s="6" t="n"/>
+      <c r="S31" s="6" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>Authorised and called up share capital</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n">
+        <v>250000</v>
+      </c>
+      <c r="C32" s="6" t="n">
+        <v>250000</v>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>250000</v>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>250000</v>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>250000</v>
+      </c>
+      <c r="G32" s="6" t="n">
+        <v>250000</v>
+      </c>
+      <c r="H32" s="6" t="n">
+        <v>250000</v>
+      </c>
+      <c r="I32" s="6" t="n">
+        <v>250000</v>
+      </c>
+      <c r="J32" s="6" t="n">
+        <v>250000</v>
+      </c>
+      <c r="K32" s="6" t="n">
+        <v>250000</v>
+      </c>
+      <c r="L32" s="6" t="n">
+        <v>250000</v>
+      </c>
+      <c r="M32" s="6" t="n">
+        <v>250000</v>
+      </c>
+      <c r="N32" s="6" t="n">
+        <v>250000</v>
+      </c>
+      <c r="O32" s="6" t="n">
+        <v>250000</v>
+      </c>
+      <c r="P32" s="6" t="n">
+        <v>140000</v>
+      </c>
+      <c r="Q32" s="6" t="n">
+        <v>140000</v>
+      </c>
+      <c r="R32" s="6" t="n">
+        <v>140000</v>
+      </c>
+      <c r="S32" s="6" t="n">
+        <v>140000</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>Other equity instruments (Additional Tier 1)</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n">
+        <v>60000</v>
+      </c>
+      <c r="C33" s="6" t="n">
+        <v>60000</v>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>60000</v>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v>60000</v>
+      </c>
+      <c r="F33" s="6" t="n"/>
+      <c r="G33" s="6" t="n"/>
+      <c r="H33" s="6" t="n"/>
+      <c r="I33" s="6" t="n"/>
+      <c r="J33" s="6" t="n"/>
+      <c r="K33" s="6" t="n"/>
+      <c r="L33" s="6" t="n"/>
+      <c r="M33" s="6" t="n"/>
+      <c r="N33" s="6" t="n"/>
+      <c r="O33" s="6" t="n"/>
+      <c r="P33" s="6" t="n"/>
+      <c r="Q33" s="6" t="n"/>
+      <c r="R33" s="6" t="n"/>
+      <c r="S33" s="6" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>Retained earnings</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="n">
+        <v>89013</v>
+      </c>
+      <c r="C34" s="6" t="n">
+        <v>103744</v>
+      </c>
+      <c r="D34" s="6" t="n">
+        <v>123289</v>
+      </c>
+      <c r="E34" s="6" t="n">
+        <v>91893</v>
+      </c>
+      <c r="F34" s="6" t="n">
+        <v>56776</v>
+      </c>
+      <c r="G34" s="6" t="n">
+        <v>92164</v>
+      </c>
+      <c r="H34" s="6" t="n">
+        <v>57058</v>
+      </c>
+      <c r="I34" s="6" t="n">
+        <v>76076</v>
+      </c>
+      <c r="J34" s="6" t="n">
+        <v>57022</v>
+      </c>
+      <c r="K34" s="6" t="n">
+        <v>60648</v>
+      </c>
+      <c r="L34" s="6" t="n">
+        <v>70408</v>
+      </c>
+      <c r="M34" s="6" t="n">
+        <v>50913</v>
+      </c>
+      <c r="N34" s="6" t="n">
+        <v>56831</v>
+      </c>
+      <c r="O34" s="6" t="n">
+        <v>24958</v>
+      </c>
+      <c r="P34" s="6" t="n">
+        <v>528</v>
+      </c>
+      <c r="Q34" s="6" t="n">
+        <v>26598</v>
+      </c>
+      <c r="R34" s="6" t="n">
+        <v>15819</v>
+      </c>
+      <c r="S34" s="6" t="n">
+        <v>3259</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>Available for sale reserve</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n"/>
+      <c r="C35" s="6" t="n"/>
+      <c r="D35" s="6" t="n"/>
+      <c r="E35" s="6" t="n"/>
+      <c r="F35" s="6" t="n"/>
+      <c r="G35" s="6" t="n"/>
+      <c r="H35" s="6" t="n"/>
+      <c r="I35" s="6" t="n"/>
+      <c r="J35" s="6" t="n">
+        <v>32</v>
+      </c>
+      <c r="K35" s="6" t="n">
+        <v>-284</v>
+      </c>
+      <c r="L35" s="6" t="n">
+        <v>-140</v>
+      </c>
+      <c r="M35" s="6" t="n">
+        <v>567</v>
+      </c>
+      <c r="N35" s="6" t="n">
+        <v>843</v>
+      </c>
+      <c r="O35" s="6" t="n">
+        <v>845</v>
+      </c>
+      <c r="P35" s="6" t="n">
+        <v>-971</v>
+      </c>
+      <c r="Q35" s="6" t="n">
+        <v>-945</v>
+      </c>
+      <c r="R35" s="6" t="n">
+        <v>-4170</v>
+      </c>
+      <c r="S35" s="6" t="n">
+        <v>-18154</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>Total shareholders' equity</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>399013</v>
+      </c>
+      <c r="C36" s="5" t="n">
+        <v>413744</v>
+      </c>
+      <c r="D36" s="5" t="n">
+        <v>433289</v>
+      </c>
+      <c r="E36" s="5" t="n">
+        <v>401893</v>
+      </c>
+      <c r="F36" s="5" t="n">
+        <v>306776</v>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>342164</v>
+      </c>
+      <c r="H36" s="5" t="n">
+        <v>307058</v>
+      </c>
+      <c r="I36" s="5" t="n">
+        <v>326076</v>
+      </c>
+      <c r="J36" s="5" t="n">
+        <v>307054</v>
+      </c>
+      <c r="K36" s="5" t="n">
+        <v>310364</v>
+      </c>
+      <c r="L36" s="5" t="n">
+        <v>320268</v>
+      </c>
+      <c r="M36" s="5" t="n">
+        <v>301480</v>
+      </c>
+      <c r="N36" s="5" t="n">
+        <v>307674</v>
+      </c>
+      <c r="O36" s="5" t="n">
+        <v>275803</v>
+      </c>
+      <c r="P36" s="5" t="n">
+        <v>139557</v>
+      </c>
+      <c r="Q36" s="5" t="n">
+        <v>165653</v>
+      </c>
+      <c r="R36" s="5" t="n">
+        <v>151649</v>
+      </c>
+      <c r="S36" s="5" t="n">
+        <v>125105</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>Total liabilities and equity</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>2274441</v>
+      </c>
+      <c r="C37" s="5" t="n">
+        <v>2323319</v>
+      </c>
+      <c r="D37" s="5" t="n">
+        <v>2079373</v>
+      </c>
+      <c r="E37" s="5" t="n">
+        <v>2290593</v>
+      </c>
+      <c r="F37" s="5" t="n">
+        <v>2151180</v>
+      </c>
+      <c r="G37" s="5" t="n">
+        <v>1941105</v>
+      </c>
+      <c r="H37" s="5" t="n">
+        <v>1687388</v>
+      </c>
+      <c r="I37" s="5" t="n">
+        <v>1630982</v>
+      </c>
+      <c r="J37" s="5" t="n">
+        <v>1539221</v>
+      </c>
+      <c r="K37" s="5" t="n">
+        <v>1549898</v>
+      </c>
+      <c r="L37" s="5" t="n">
+        <v>1291410</v>
+      </c>
+      <c r="M37" s="5" t="n">
+        <v>1215116</v>
+      </c>
+      <c r="N37" s="5" t="n">
+        <v>1050075</v>
+      </c>
+      <c r="O37" s="5" t="n">
+        <v>827527</v>
+      </c>
+      <c r="P37" s="5" t="n">
+        <v>777725</v>
+      </c>
+      <c r="Q37" s="5" t="n">
+        <v>735494</v>
+      </c>
+      <c r="R37" s="5" t="n">
+        <v>982073</v>
+      </c>
+      <c r="S37" s="5" t="n">
+        <v>1055809</v>
+      </c>
+    </row>
+    <row r="39" ht="364" customHeight="1">
+      <c r="A39" s="8" t="inlineStr">
+        <is>
+          <t>Sources - Bank of China (UK) Limited's own Statement of Financial Position (Bank/solo basis - no group accounts prepared, Companies Act 2006 s.401 exemption), £'000, each year's own originally-published report:
+FY2025: Annual Report 2025, p.49 - https://pic.bankofchina.com/bocappd/uk/202605/P020260506389809417235.pdf
+FY2024: Annual Report 2024, p.49 - https://pic.bankofchina.com/bocappd/uk/202507/P020250718380377744220.pdf (FY2024's own primary source is its own report (AR2024_URL), not AR2025's comparative column - both are identical figures (verified), no restatement.)
+FY2023: Annual Report 2023, p.50 - https://pic.bankofchina.com/bocappd/uk/202405/P020240508355110735895.pdf
+FY2022: Financial Statements 2022, p.38 - https://pic.bankofchina.com/bocappd/uk/202403/P020240315379765805794.pdf
+FY2021: Financial Statements 2021, p.35 - https://pic.bankofchina.com/bocappd/uk/202303/P020230331590070165221.pdf
+FY2020: Financial Statements 2020, p.33 - https://pic.bankofchina.com/bocappd/uk/202109/P020210902654360894172.pdf
+FY2019: Financial Statements 2019, p.32 - https://pic.bankofchina.com/bocappd/uk/202007/P020200727323473194461.pdf
+FY2018: Financial Statements 2018, p.27 - https://pic.bankofchina.com/bocappd/uk/201904/P020190410506087628158.pdf
+FY2017: Financial Statements 2017, p.25 - https://pic.bankofchina.com/bocappd/uk/201805/P020180517534275167127.pdf
+FY2016: Financial Statements 2016, p.20 - https://pic.bankofchina.com/bocappd/uk/201706/P020170627373089457851.pdf
+FY2015: Financial Statements 2015, p.19 - https://pic.bankofchina.com/bocappd/uk/201606/P020160620504225340480.pdf
+FY2014: Financial Statements 2015's own FY2014 comparative column, p.19 - https://pic.bankofchina.com/bocappd/uk/201606/P020160620504225340480.pdf (AR2014_URL note: the Bank's own FY2014 Annual Report PDF is a scanned/photocopied document (Canon iR-ADV C5045 scanner output) with no extractable text layer - pdftotext and qpdf both confirm zero recoverable text after a repair pass. FY2014 figures on every sheet are therefore taken from the FY2015 Annual Report's own FY2014 comparative column instead (a real, live, text-searchable document), the same each-year's-own-report methodology used everywhere else in this workbook, just one year removed since FY2014's own PDF cannot be read as text.)
+FY2013: Annual Report and Financial Statements 2013, p.17 - https://pic.bankofchina.com/bocappd/uk/201505/P020150504339499661074.pdf (AR2013_URL note: the Bank's own FY2013 Annual Report PDF is a scanned/photocopied document (Xerox WorkCentre 5665 scanner output) with no extractable text layer, the same pattern HD-046 found on FY2014's own PDF. Unlike FY2014 (where a later year's clean comparative column exists), FY2014's own PDF is itself unreadable, so no clean comparative source exists for FY2013 either - FY2013 figures here were instead OCR'd directly off this scanned PDF (ocrmypdf --force-ocr + tesseract), then cross-checked two ways: (1) the resulting FY2013 closing equity/balance-sheet/cash-flow figures tie out internally (assets = liabilities + equity; operating + investing + financing cash flows = the disclosed net movement; opening + net movement = closing cash) and (2) the OCR'd FY2013 closing Statement of Changes in Equity figures match this workbook's own pre-existing FY2014 opening balance exactly (250,000 / 56,831 / 843 / 307,674), which was itself sourced independently via AR2015's FY2014 comparative column under HD-046. Several individual OCR digit errors were caught and corrected via these tie-outs (e.g. 'Interest income from financial investments' misread as 4,294 instead of 1,294, 'Total assets' misread as 4,050,075 instead of 1,050,075 - a recurring 1-to-4 OCR confusion in this particular scan).)
+FY2012: Annual Report 2012, p.24 - https://pic.bankofchina.com/bocappd/uk/201312/P020131213310466908739.pdf
+FY2011: Annual Report 2011, p.24 - https://pic.bankofchina.com/bocappd/uk/201301/P020130110394685934112.pdf
+FY2010: Annual Report 2011's own FY2010 comparative column, p.24 - https://pic.bankofchina.com/bocappd/uk/201301/P020130110394685934112.pdf (AR2010_URL note: the Bank's own FY2010 Annual Report PDF is a scanned/photocopied document (Canon iR-ADV C5045 scanner output, the same scanner/pattern as FY2014's own PDF) with no extractable text layer. FY2010 figures on every sheet are therefore taken from the FY2011 Annual Report's own FY2010 comparative column instead (a real, live, text-searchable document), the same each-year's-own-report-one-year-removed methodology used for FY2014 via AR2015.)
+FY2009: 2009 Report and Financial Statements, p.31 - https://pic.bankofchina.com/bocappd/uk/201109/P020110901339600023124.pdf
+FY2008: 2009 Report's own FY2008 comparative column, p.31 - https://pic.bankofchina.com/bocappd/uk/201109/P020110901339600023124.pdf, cross-checked against the Bank's own 2008 Report and Financial Statements (Balance Sheet, p.29) - https://pic.bankofchina.com/bocappd/uk/201109/P020110901339400504145.pdf (figures identical). FY2008 period note: Bank of China (UK) Limited's first accounting period ran 1 April 2007 - 30 September 2007 (a 6-month stub, outside this workbook's scope), and its second and only 'FY2008' statutory period is genuinely a 15-month period from 1 October 2007 to 31 December 2008 (the year-end was moved to December during this period) - not a standard 12-month year. Both the Bank's own FY2008 Report and Financial Statements (AR2008_URL) and the FY2009 Report's own FY2008 comparative column (AR2009_URL) show this identical 15-month figure set, cross-checked and tying exactly. Shown here as 'FY2008' per this workbook's year-labelling convention, but flagged as non-comparable in length to every other year in this workbook - growth trends spanning the FY2008/FY2009 boundary should be read with that caveat.
+HD-075 extension presentation notes (FY2008-FY2013): 'Investment in subsidiary/group companies' is its own row for these 6 years only (a real, non-nil balance - the subsidiary was disposed of during FY2012, hence nil/omitted from FY2014 onward). 'Deferred tax liabilities' is its own row for FY2008 (£14k) and FY2013 (£28k) only - nil/not disclosed as a separate line in every other year shown. 'Authorised and called up share capital' rose from £140,000k to £250,000k during FY2012 via a £110,000k ordinary share issue (see the Statement of Changes in Equity sheet). FY2013's Balance Sheet total assets/liabilities were affected by two OCR digit corrections cross-checked against the statement's own subtotals - see AR2013_SCAN_NOTE.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="200" customHeight="1">
+      <c r="A41" s="8" t="inlineStr">
+        <is>
+          <t>(continued)
+Presentation notes: 'Government bonds' only appears as its own line from FY2022 onward. 'Subordinated liabilities' (£60,000k every year FY2014-FY2021) was repaid and replaced by an equal £60,000k Additional Tier 1 instrument in June 2022 - both nil/blank in the years they don't apply. 'Investment in subsidiary companies' is nil every year and omitted as a row. 'Available for sale financial investments' and its matching equity 'Available for sale reserve' existed under IAS 39 through FY2017 and were replaced by 'Financial assets at fair value through profit and loss' / 'Debt instruments at amortised cost' at the 1 January 2018 IFRS 9 transition (a £495k opening-equity charge that year, see the Statement of Changes in Equity sheet) - both pairs of rows are blank/zero in the years they don't apply, not force-matched. FY2021's own report's Statement of Changes in Equity states closing retained earnings as £56,706k, £70k less than the Balance Sheet's own £56,776k for the same date - the Balance Sheet's single 'Retained earnings' line appears to combine the SOCE's separate retained-earnings and FX-translation-reserve columns (£56,706k + £70k = £56,776k); the same pattern recurs one year earlier at FY2020 (SOCE retained earnings £92,228k + FX reserve -£64k = Balance Sheet's own £92,164k); total equity ties out exactly either way in both years. FY2014 cash resolved (HD-081, 2026-09-07): FY2015's own filing originally appeared to show two different FY2014 cash figures - £199,954k on the Balance Sheet's comparative column vs. £199,854k on the Cash Flow Statement's own comparative closing balance. Re-summing FY2014's own 9 asset line items as originally transcribed (199,954 + 207,026 + 722,307 + 16,173 + 27,820 + 37,469 + 751 + 3,390 + 326) gives £1,215,216k, £100k more than the Balance Sheet's own stated 'Total assets' of £1,215,116k for that column; substituting £199,854k for the cash line instead sums to exactly £1,215,116k. The Balance Sheet's own internal subtotal therefore only ties out with £199,854k, confirming £199,954k was a single-digit transcription/OCR misread of the FY2015 filing's FY2014 comparative column (a 9 misread for an 8 in the thousands place) and that £199,854k, matching the Cash Flow Statement, is the correct figure. Corrected here to £199,854k; FY2014's own primary report remains unreadable as text (see AR2014_SCAN_NOTE), so this arithmetic cross-check within FY2015's own filing is the resolving evidence.
+Entity note: Bank of China (UK) Limited (company 06193060, FRN 467410) is a wholly-owned UK subsidiary of Bank of China Limited (state-owned). It does not take the FRS 101/102 cash-flow-statement exemption - a full Statement of Cash Flows is published every year. All figures are the Bank's own solo entity basis throughout.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A41:S41"/>
+    <mergeCell ref="A39:S39"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6903,7 +8794,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Bank of China (UK) Limited — Statement of Financial Position</t>
+          <t>Bank of China (UK) Limited — Income Statement and Statement of Comprehensive Income</t>
         </is>
       </c>
     </row>
@@ -7014,7 +8905,7 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Assets</t>
+          <t>Income</t>
         </is>
       </c>
       <c r="B4" s="6" t="n"/>
@@ -7039,376 +8930,414 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Cash and balances at central banks</t>
+          <t>Interest income</t>
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>982512</v>
+        <v>110123</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>975201</v>
+        <v>128817</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>687070</v>
+        <v>121217</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>657656</v>
+        <v>62661</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>716133</v>
+        <v>36936</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>481379</v>
+        <v>40327</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>332542</v>
+        <v>45693</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>333275</v>
+        <v>40759</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>281944</v>
+        <v>38234</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>311917</v>
+        <v>34591</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>344019</v>
+        <v>25645</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>199854</v>
+        <v>26082</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>159219</v>
+        <v>18724</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>197622</v>
+        <v>14523</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>275821</v>
+        <v>12956</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>215155</v>
+        <v>16182</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>127812</v>
+        <v>20622</v>
       </c>
       <c r="S5" s="6" t="n">
-        <v>40069</v>
+        <v>54071</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Government bonds</t>
+          <t>Interest expense</t>
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>142529</v>
+        <v>-53024</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>144495</v>
+        <v>-57415</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>118328</v>
+        <v>-40422</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>44264</v>
-      </c>
-      <c r="F6" s="6" t="n"/>
-      <c r="G6" s="6" t="n"/>
-      <c r="H6" s="6" t="n"/>
-      <c r="I6" s="6" t="n"/>
-      <c r="J6" s="6" t="n"/>
-      <c r="K6" s="6" t="n"/>
-      <c r="L6" s="6" t="n"/>
-      <c r="M6" s="6" t="n"/>
-      <c r="N6" s="6" t="n"/>
-      <c r="O6" s="6" t="n"/>
-      <c r="P6" s="6" t="n"/>
-      <c r="Q6" s="6" t="n"/>
-      <c r="R6" s="6" t="n"/>
-      <c r="S6" s="6" t="n"/>
+        <v>-13239</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>-3650</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>-6276</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>-9313</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>-6553</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>-5788</v>
+      </c>
+      <c r="K6" s="6" t="n">
+        <v>-4629</v>
+      </c>
+      <c r="L6" s="6" t="n">
+        <v>-3095</v>
+      </c>
+      <c r="M6" s="6" t="n">
+        <v>-3635</v>
+      </c>
+      <c r="N6" s="6" t="n">
+        <v>-2800</v>
+      </c>
+      <c r="O6" s="6" t="n">
+        <v>-2828</v>
+      </c>
+      <c r="P6" s="6" t="n">
+        <v>-2828</v>
+      </c>
+      <c r="Q6" s="6" t="n">
+        <v>-3858</v>
+      </c>
+      <c r="R6" s="6" t="n">
+        <v>-7677</v>
+      </c>
+      <c r="S6" s="6" t="n">
+        <v>-35584</v>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>Loans and advances to banks</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="n">
-        <v>90733</v>
-      </c>
-      <c r="C7" s="6" t="n">
-        <v>73658</v>
-      </c>
-      <c r="D7" s="6" t="n">
-        <v>86477</v>
-      </c>
-      <c r="E7" s="6" t="n">
-        <v>29357</v>
-      </c>
-      <c r="F7" s="6" t="n">
-        <v>69065</v>
-      </c>
-      <c r="G7" s="6" t="n">
-        <v>110446</v>
-      </c>
-      <c r="H7" s="6" t="n">
-        <v>85247</v>
-      </c>
-      <c r="I7" s="6" t="n">
-        <v>61391</v>
-      </c>
-      <c r="J7" s="6" t="n">
-        <v>83706</v>
-      </c>
-      <c r="K7" s="6" t="n">
-        <v>24270</v>
-      </c>
-      <c r="L7" s="6" t="n">
-        <v>62633</v>
-      </c>
-      <c r="M7" s="6" t="n">
-        <v>207026</v>
-      </c>
-      <c r="N7" s="6" t="n">
-        <v>168898</v>
-      </c>
-      <c r="O7" s="6" t="n">
-        <v>48779</v>
-      </c>
-      <c r="P7" s="6" t="n">
-        <v>12865</v>
-      </c>
-      <c r="Q7" s="6" t="n">
-        <v>12817</v>
-      </c>
-      <c r="R7" s="6" t="n">
-        <v>36933</v>
-      </c>
-      <c r="S7" s="6" t="n">
-        <v>67272</v>
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Net interest income</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>57099</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>71402</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>80795</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>49422</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>33286</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>34051</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>36380</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>34206</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>32446</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>29962</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>22550</v>
+      </c>
+      <c r="M7" s="5" t="n">
+        <v>22447</v>
+      </c>
+      <c r="N7" s="5" t="n">
+        <v>15924</v>
+      </c>
+      <c r="O7" s="5" t="n">
+        <v>11695</v>
+      </c>
+      <c r="P7" s="5" t="n">
+        <v>10128</v>
+      </c>
+      <c r="Q7" s="5" t="n">
+        <v>12324</v>
+      </c>
+      <c r="R7" s="5" t="n">
+        <v>12945</v>
+      </c>
+      <c r="S7" s="5" t="n">
+        <v>18487</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Loans and advances to customers</t>
+          <t>Fee and commission income</t>
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>810985</v>
+        <v>3399</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>941507</v>
+        <v>3228</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>990763</v>
+        <v>3378</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>1122459</v>
+        <v>3955</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>1194653</v>
+        <v>4294</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>1138583</v>
+        <v>3627</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>1064347</v>
+        <v>4674</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>1044570</v>
+        <v>4850</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>1054454</v>
+        <v>5502</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>1159696</v>
+        <v>4029</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>810776</v>
+        <v>8906</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>722307</v>
+        <v>7109</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>581030</v>
+        <v>9445</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>464479</v>
+        <v>7448</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>290752</v>
+        <v>6353</v>
       </c>
       <c r="Q8" s="6" t="n">
-        <v>214623</v>
+        <v>6317</v>
       </c>
       <c r="R8" s="6" t="n">
-        <v>504743</v>
+        <v>3689</v>
       </c>
       <c r="S8" s="6" t="n">
-        <v>551148</v>
+        <v>3886</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>Derivative financial instruments</t>
+          <t>Fee and commission expense</t>
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>2504</v>
+        <v>-1462</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>4667</v>
+        <v>-1481</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>5506</v>
+        <v>-1692</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>7702</v>
+        <v>-1694</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>11</v>
+        <v>-1319</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>48163</v>
+        <v>-1549</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>4614</v>
+        <v>-1170</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>1344</v>
+        <v>-886</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>1717</v>
+        <v>-813</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>4577</v>
+        <v>-776</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>8173</v>
+        <v>-582</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>16173</v>
+        <v>-1022</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>41502</v>
+        <v>-580</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>1949</v>
+        <v>-783</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>72</v>
+        <v>-507</v>
       </c>
       <c r="Q9" s="6" t="n">
-        <v>505</v>
+        <v>-170</v>
       </c>
       <c r="R9" s="6" t="n">
-        <v>1375</v>
+        <v>-135</v>
       </c>
       <c r="S9" s="6" t="n">
-        <v>5554</v>
+        <v>-238</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>Prepayments, accrued income and other assets</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="n">
-        <v>156554</v>
-      </c>
-      <c r="C10" s="6" t="n">
-        <v>138246</v>
-      </c>
-      <c r="D10" s="6" t="n">
-        <v>130581</v>
-      </c>
-      <c r="E10" s="6" t="n">
-        <v>351967</v>
-      </c>
-      <c r="F10" s="6" t="n">
-        <v>87868</v>
-      </c>
-      <c r="G10" s="6" t="n">
-        <v>78769</v>
-      </c>
-      <c r="H10" s="6" t="n">
-        <v>58405</v>
-      </c>
-      <c r="I10" s="6" t="n">
-        <v>6273</v>
-      </c>
-      <c r="J10" s="6" t="n">
-        <v>5204</v>
-      </c>
-      <c r="K10" s="6" t="n">
-        <v>4762</v>
-      </c>
-      <c r="L10" s="6" t="n">
-        <v>25831</v>
-      </c>
-      <c r="M10" s="6" t="n">
-        <v>27820</v>
-      </c>
-      <c r="N10" s="6" t="n">
-        <v>66602</v>
-      </c>
-      <c r="O10" s="6" t="n">
-        <v>64084</v>
-      </c>
-      <c r="P10" s="6" t="n">
-        <v>37692</v>
-      </c>
-      <c r="Q10" s="6" t="n">
-        <v>46427</v>
-      </c>
-      <c r="R10" s="6" t="n">
-        <v>29780</v>
-      </c>
-      <c r="S10" s="6" t="n">
-        <v>21197</v>
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Net fee and commission income</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>1937</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>1747</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>1686</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>2261</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>2975</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>2078</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>3504</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>3964</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>4689</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>3253</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>8324</v>
+      </c>
+      <c r="M10" s="5" t="n">
+        <v>6087</v>
+      </c>
+      <c r="N10" s="5" t="n">
+        <v>8865</v>
+      </c>
+      <c r="O10" s="5" t="n">
+        <v>6665</v>
+      </c>
+      <c r="P10" s="5" t="n">
+        <v>5846</v>
+      </c>
+      <c r="Q10" s="5" t="n">
+        <v>6147</v>
+      </c>
+      <c r="R10" s="5" t="n">
+        <v>3554</v>
+      </c>
+      <c r="S10" s="5" t="n">
+        <v>3648</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Financial assets at fair value through profit and loss</t>
+          <t>Net fair value gain/(loss) on financial instruments</t>
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>71293</v>
+        <v>3431</v>
       </c>
       <c r="C11" s="6" t="n">
-        <v>30150</v>
+        <v>4711</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>47445</v>
+        <v>9119</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>60514</v>
+        <v>148</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>64659</v>
+        <v>1923</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>77482</v>
+        <v>-3151</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>83928</v>
+        <v>-1165</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>76171</v>
-      </c>
-      <c r="J11" s="6" t="n"/>
-      <c r="K11" s="6" t="n"/>
-      <c r="L11" s="6" t="n"/>
-      <c r="M11" s="6" t="n"/>
-      <c r="N11" s="6" t="n"/>
+        <v>-331</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>51</v>
+      </c>
+      <c r="K11" s="6" t="n">
+        <v>241</v>
+      </c>
+      <c r="L11" s="6" t="n">
+        <v>511</v>
+      </c>
+      <c r="M11" s="6" t="n">
+        <v>-1413</v>
+      </c>
+      <c r="N11" s="6" t="n">
+        <v>826</v>
+      </c>
       <c r="O11" s="6" t="n"/>
       <c r="P11" s="6" t="n"/>
       <c r="Q11" s="6" t="n"/>
@@ -7418,7 +9347,7 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Available for sale financial investments</t>
+          <t>Net gain/(loss) on derivative financial instruments (FY2008-FY2012 presentation)</t>
         </is>
       </c>
       <c r="B12" s="6" t="n"/>
@@ -7429,714 +9358,732 @@
       <c r="G12" s="6" t="n"/>
       <c r="H12" s="6" t="n"/>
       <c r="I12" s="6" t="n"/>
-      <c r="J12" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="K12" s="6" t="n">
-        <v>40716</v>
-      </c>
-      <c r="L12" s="6" t="n">
-        <v>35859</v>
-      </c>
-      <c r="M12" s="6" t="n">
-        <v>37469</v>
-      </c>
-      <c r="N12" s="6" t="n">
-        <v>28754</v>
-      </c>
+      <c r="J12" s="6" t="n"/>
+      <c r="K12" s="6" t="n"/>
+      <c r="L12" s="6" t="n"/>
+      <c r="M12" s="6" t="n"/>
+      <c r="N12" s="6" t="n"/>
       <c r="O12" s="6" t="n">
-        <v>46270</v>
+        <v>-1478</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>95671</v>
+        <v>-927</v>
       </c>
       <c r="Q12" s="6" t="n">
-        <v>149677</v>
+        <v>-2312</v>
       </c>
       <c r="R12" s="6" t="n">
-        <v>249004</v>
+        <v>-2181</v>
       </c>
       <c r="S12" s="6" t="n">
-        <v>330093</v>
+        <v>-3314</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>Held to maturity / debt instruments at amortised cost</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="n"/>
-      <c r="C13" s="6" t="n"/>
-      <c r="D13" s="6" t="n"/>
-      <c r="E13" s="6" t="n"/>
-      <c r="F13" s="6" t="n"/>
-      <c r="G13" s="6" t="n"/>
+          <t>Foreign exchange gain</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n">
+        <v>2388</v>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>2295</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>386</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>4916</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>2590</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>1489</v>
+      </c>
       <c r="H13" s="6" t="n">
-        <v>50431</v>
+        <v>4767</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>103189</v>
+        <v>3167</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>107478</v>
-      </c>
-      <c r="K13" s="6" t="n"/>
-      <c r="L13" s="6" t="n"/>
-      <c r="M13" s="6" t="n"/>
-      <c r="N13" s="6" t="n"/>
-      <c r="O13" s="6" t="n"/>
-      <c r="P13" s="6" t="n"/>
-      <c r="Q13" s="6" t="n"/>
-      <c r="R13" s="6" t="n"/>
-      <c r="S13" s="6" t="n"/>
+        <v>2593</v>
+      </c>
+      <c r="K13" s="6" t="n">
+        <v>2827</v>
+      </c>
+      <c r="L13" s="6" t="n">
+        <v>2492</v>
+      </c>
+      <c r="M13" s="6" t="n">
+        <v>2100</v>
+      </c>
+      <c r="N13" s="6" t="n">
+        <v>554</v>
+      </c>
+      <c r="O13" s="6" t="n">
+        <v>1688</v>
+      </c>
+      <c r="P13" s="6" t="n">
+        <v>-2080</v>
+      </c>
+      <c r="Q13" s="6" t="n">
+        <v>262</v>
+      </c>
+      <c r="R13" s="6" t="n">
+        <v>303</v>
+      </c>
+      <c r="S13" s="6" t="n">
+        <v>915</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Investment in subsidiary/group companies</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="n"/>
-      <c r="C14" s="6" t="n"/>
-      <c r="D14" s="6" t="n"/>
-      <c r="E14" s="6" t="n"/>
-      <c r="F14" s="6" t="n"/>
-      <c r="G14" s="6" t="n"/>
-      <c r="H14" s="6" t="n"/>
-      <c r="I14" s="6" t="n"/>
-      <c r="J14" s="6" t="n"/>
-      <c r="K14" s="6" t="n"/>
-      <c r="L14" s="6" t="n"/>
-      <c r="M14" s="6" t="n"/>
-      <c r="N14" s="6" t="n"/>
-      <c r="O14" s="6" t="n"/>
+          <t>Net other operating income</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n">
+        <v>123435</v>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>107108</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>114199</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>93633</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>83274</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>85636</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>71751</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>73555</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>54704</v>
+      </c>
+      <c r="K14" s="6" t="n">
+        <v>54899</v>
+      </c>
+      <c r="L14" s="6" t="n">
+        <v>61054</v>
+      </c>
+      <c r="M14" s="6" t="n">
+        <v>42403</v>
+      </c>
+      <c r="N14" s="6" t="n">
+        <v>42508</v>
+      </c>
+      <c r="O14" s="6" t="n">
+        <v>45390</v>
+      </c>
       <c r="P14" s="6" t="n">
-        <v>63285</v>
+        <v>25698</v>
       </c>
       <c r="Q14" s="6" t="n">
-        <v>94357</v>
+        <v>30331</v>
       </c>
       <c r="R14" s="6" t="n">
-        <v>29945</v>
+        <v>19368</v>
       </c>
       <c r="S14" s="6" t="n">
-        <v>32128</v>
+        <v>9501</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>Current tax asset</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="n">
-        <v>4582</v>
-      </c>
-      <c r="C15" s="6" t="n">
-        <v>2934</v>
-      </c>
-      <c r="D15" s="6" t="n">
-        <v>637</v>
-      </c>
-      <c r="E15" s="6" t="n">
-        <v>2351</v>
-      </c>
-      <c r="F15" s="6" t="n">
-        <v>5979</v>
-      </c>
+          <t>Gain/(loss) on sale of debt securities</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n"/>
+      <c r="C15" s="6" t="n"/>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="n"/>
       <c r="G15" s="6" t="n"/>
       <c r="H15" s="6" t="n"/>
       <c r="I15" s="6" t="n"/>
       <c r="J15" s="6" t="n"/>
       <c r="K15" s="6" t="n"/>
       <c r="L15" s="6" t="n"/>
-      <c r="M15" s="6" t="n"/>
-      <c r="N15" s="6" t="n"/>
-      <c r="O15" s="6" t="n"/>
-      <c r="P15" s="6" t="n"/>
-      <c r="Q15" s="6" t="n"/>
-      <c r="R15" s="6" t="n"/>
-      <c r="S15" s="6" t="n"/>
+      <c r="M15" s="6" t="n">
+        <v>-3</v>
+      </c>
+      <c r="N15" s="6" t="n">
+        <v>-436</v>
+      </c>
+      <c r="O15" s="6" t="n">
+        <v>-23</v>
+      </c>
+      <c r="P15" s="6" t="n">
+        <v>-1298</v>
+      </c>
+      <c r="Q15" s="6" t="n">
+        <v>-190</v>
+      </c>
+      <c r="R15" s="6" t="n">
+        <v>534</v>
+      </c>
+      <c r="S15" s="6" t="n">
+        <v>2495</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Deferred tax assets</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="n">
-        <v>289</v>
-      </c>
-      <c r="C16" s="6" t="n">
-        <v>406</v>
-      </c>
-      <c r="D16" s="6" t="n">
-        <v>359</v>
-      </c>
-      <c r="E16" s="6" t="n">
-        <v>1280</v>
-      </c>
-      <c r="F16" s="6" t="n">
-        <v>1283</v>
-      </c>
-      <c r="G16" s="6" t="n">
-        <v>1227</v>
-      </c>
-      <c r="H16" s="6" t="n">
-        <v>787</v>
-      </c>
-      <c r="I16" s="6" t="n">
-        <v>1546</v>
-      </c>
-      <c r="J16" s="6" t="n">
-        <v>1462</v>
-      </c>
-      <c r="K16" s="6" t="n">
-        <v>562</v>
-      </c>
-      <c r="L16" s="6" t="n">
-        <v>425</v>
-      </c>
-      <c r="M16" s="6" t="n">
-        <v>751</v>
-      </c>
+          <t>Profit on sale of impaired loan</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n"/>
+      <c r="C16" s="6" t="n"/>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="6" t="n"/>
+      <c r="G16" s="6" t="n"/>
+      <c r="H16" s="6" t="n"/>
+      <c r="I16" s="6" t="n"/>
+      <c r="J16" s="6" t="n"/>
+      <c r="K16" s="6" t="n"/>
+      <c r="L16" s="6" t="n"/>
+      <c r="M16" s="6" t="n"/>
       <c r="N16" s="6" t="n">
-        <v>276</v>
-      </c>
-      <c r="O16" s="6" t="n">
-        <v>206</v>
-      </c>
-      <c r="P16" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="Q16" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="R16" s="6" t="n">
-        <v>16</v>
-      </c>
-      <c r="S16" s="6" t="n">
-        <v>5656</v>
-      </c>
+        <v>2158</v>
+      </c>
+      <c r="O16" s="6" t="n"/>
+      <c r="P16" s="6" t="n"/>
+      <c r="Q16" s="6" t="n"/>
+      <c r="R16" s="6" t="n"/>
+      <c r="S16" s="6" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>Property, plant and equipment</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="n">
-        <v>11573</v>
-      </c>
-      <c r="C17" s="6" t="n">
-        <v>11419</v>
-      </c>
-      <c r="D17" s="6" t="n">
-        <v>11902</v>
-      </c>
-      <c r="E17" s="6" t="n">
-        <v>12769</v>
-      </c>
-      <c r="F17" s="6" t="n">
-        <v>11167</v>
-      </c>
-      <c r="G17" s="6" t="n">
-        <v>4527</v>
-      </c>
-      <c r="H17" s="6" t="n">
-        <v>6328</v>
-      </c>
-      <c r="I17" s="6" t="n">
-        <v>2761</v>
-      </c>
-      <c r="J17" s="6" t="n">
-        <v>3149</v>
-      </c>
-      <c r="K17" s="6" t="n">
-        <v>3276</v>
-      </c>
-      <c r="L17" s="6" t="n">
-        <v>3514</v>
-      </c>
-      <c r="M17" s="6" t="n">
-        <v>3390</v>
-      </c>
-      <c r="N17" s="6" t="n">
-        <v>3765</v>
-      </c>
-      <c r="O17" s="6" t="n">
-        <v>4032</v>
-      </c>
-      <c r="P17" s="6" t="n">
-        <v>1374</v>
-      </c>
-      <c r="Q17" s="6" t="n">
-        <v>1612</v>
-      </c>
-      <c r="R17" s="6" t="n">
-        <v>2025</v>
-      </c>
-      <c r="S17" s="6" t="n">
-        <v>2371</v>
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Non-interest income</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>129254</v>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>114114</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>123704</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>98697</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>87787</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>83974</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>75353</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>76391</v>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>57348</v>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>57967</v>
+      </c>
+      <c r="L17" s="5" t="n">
+        <v>64047</v>
+      </c>
+      <c r="M17" s="5" t="n">
+        <v>43087</v>
+      </c>
+      <c r="N17" s="5" t="n">
+        <v>45610</v>
+      </c>
+      <c r="O17" s="5" t="n">
+        <v>45577</v>
+      </c>
+      <c r="P17" s="5" t="n">
+        <v>21393</v>
+      </c>
+      <c r="Q17" s="5" t="n">
+        <v>28091</v>
+      </c>
+      <c r="R17" s="5" t="n">
+        <v>18024</v>
+      </c>
+      <c r="S17" s="5" t="n">
+        <v>9597</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>Intangible assets</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="n">
-        <v>887</v>
-      </c>
-      <c r="C18" s="6" t="n">
-        <v>636</v>
-      </c>
-      <c r="D18" s="6" t="n">
-        <v>305</v>
-      </c>
-      <c r="E18" s="6" t="n">
-        <v>274</v>
-      </c>
-      <c r="F18" s="6" t="n">
-        <v>362</v>
-      </c>
-      <c r="G18" s="6" t="n">
-        <v>529</v>
-      </c>
-      <c r="H18" s="6" t="n">
-        <v>759</v>
-      </c>
-      <c r="I18" s="6" t="n">
-        <v>462</v>
-      </c>
-      <c r="J18" s="6" t="n">
-        <v>95</v>
-      </c>
-      <c r="K18" s="6" t="n">
-        <v>122</v>
-      </c>
-      <c r="L18" s="6" t="n">
-        <v>180</v>
-      </c>
-      <c r="M18" s="6" t="n">
-        <v>326</v>
-      </c>
-      <c r="N18" s="6" t="n">
-        <v>29</v>
-      </c>
-      <c r="O18" s="6" t="n">
-        <v>106</v>
-      </c>
-      <c r="P18" s="6" t="n">
-        <v>163</v>
-      </c>
-      <c r="Q18" s="6" t="n">
-        <v>317</v>
-      </c>
-      <c r="R18" s="6" t="n">
-        <v>440</v>
-      </c>
-      <c r="S18" s="6" t="n">
-        <v>321</v>
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Total income</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>188290</v>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>187263</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>206185</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>150380</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>124048</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>120103</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>115237</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>114561</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>94483</v>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>91182</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>94921</v>
+      </c>
+      <c r="M18" s="5" t="n">
+        <v>71621</v>
+      </c>
+      <c r="N18" s="5" t="n">
+        <v>70399</v>
+      </c>
+      <c r="O18" s="5" t="n">
+        <v>63937</v>
+      </c>
+      <c r="P18" s="5" t="n">
+        <v>37367</v>
+      </c>
+      <c r="Q18" s="5" t="n">
+        <v>46562</v>
+      </c>
+      <c r="R18" s="5" t="n">
+        <v>34523</v>
+      </c>
+      <c r="S18" s="5" t="n">
+        <v>31732</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>Total assets</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="n">
-        <v>2274441</v>
-      </c>
-      <c r="C19" s="5" t="n">
-        <v>2323319</v>
-      </c>
-      <c r="D19" s="5" t="n">
-        <v>2079373</v>
-      </c>
-      <c r="E19" s="5" t="n">
-        <v>2290593</v>
-      </c>
-      <c r="F19" s="5" t="n">
-        <v>2151180</v>
-      </c>
-      <c r="G19" s="5" t="n">
-        <v>1941105</v>
-      </c>
-      <c r="H19" s="5" t="n">
-        <v>1687388</v>
-      </c>
-      <c r="I19" s="5" t="n">
-        <v>1630982</v>
-      </c>
-      <c r="J19" s="5" t="n">
-        <v>1539221</v>
-      </c>
-      <c r="K19" s="5" t="n">
-        <v>1549898</v>
-      </c>
-      <c r="L19" s="5" t="n">
-        <v>1291410</v>
-      </c>
-      <c r="M19" s="5" t="n">
-        <v>1215116</v>
-      </c>
-      <c r="N19" s="5" t="n">
-        <v>1050075</v>
-      </c>
-      <c r="O19" s="5" t="n">
-        <v>827527</v>
-      </c>
-      <c r="P19" s="5" t="n">
-        <v>777725</v>
-      </c>
-      <c r="Q19" s="5" t="n">
-        <v>735494</v>
-      </c>
-      <c r="R19" s="5" t="n">
-        <v>982073</v>
-      </c>
-      <c r="S19" s="5" t="n">
-        <v>1055809</v>
-      </c>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n"/>
+      <c r="C19" s="6" t="n"/>
+      <c r="D19" s="6" t="n"/>
+      <c r="E19" s="6" t="n"/>
+      <c r="F19" s="6" t="n"/>
+      <c r="G19" s="6" t="n"/>
+      <c r="H19" s="6" t="n"/>
+      <c r="I19" s="6" t="n"/>
+      <c r="J19" s="6" t="n"/>
+      <c r="K19" s="6" t="n"/>
+      <c r="L19" s="6" t="n"/>
+      <c r="M19" s="6" t="n"/>
+      <c r="N19" s="6" t="n"/>
+      <c r="O19" s="6" t="n"/>
+      <c r="P19" s="6" t="n"/>
+      <c r="Q19" s="6" t="n"/>
+      <c r="R19" s="6" t="n"/>
+      <c r="S19" s="6" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>Liabilities</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="n"/>
-      <c r="C20" s="6" t="n"/>
-      <c r="D20" s="6" t="n"/>
-      <c r="E20" s="6" t="n"/>
-      <c r="F20" s="6" t="n"/>
-      <c r="G20" s="6" t="n"/>
-      <c r="H20" s="6" t="n"/>
-      <c r="I20" s="6" t="n"/>
-      <c r="J20" s="6" t="n"/>
-      <c r="K20" s="6" t="n"/>
-      <c r="L20" s="6" t="n"/>
-      <c r="M20" s="6" t="n"/>
-      <c r="N20" s="6" t="n"/>
-      <c r="O20" s="6" t="n"/>
-      <c r="P20" s="6" t="n"/>
-      <c r="Q20" s="6" t="n"/>
-      <c r="R20" s="6" t="n"/>
-      <c r="S20" s="6" t="n"/>
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Staff costs</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n">
+        <v>-86079</v>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>-72194</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>-68058</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>-59208</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>-50154</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>-47607</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>-47279</v>
+      </c>
+      <c r="I20" s="6" t="n">
+        <v>-41868</v>
+      </c>
+      <c r="J20" s="6" t="n">
+        <v>-41365</v>
+      </c>
+      <c r="K20" s="6" t="n">
+        <v>-32821</v>
+      </c>
+      <c r="L20" s="6" t="n">
+        <v>-29500</v>
+      </c>
+      <c r="M20" s="6" t="n">
+        <v>-30178</v>
+      </c>
+      <c r="N20" s="6" t="n">
+        <v>-24489</v>
+      </c>
+      <c r="O20" s="6" t="n">
+        <v>-19227</v>
+      </c>
+      <c r="P20" s="6" t="n">
+        <v>-16203</v>
+      </c>
+      <c r="Q20" s="6" t="n">
+        <v>-13759</v>
+      </c>
+      <c r="R20" s="6" t="n">
+        <v>-11761</v>
+      </c>
+      <c r="S20" s="6" t="n">
+        <v>-11629</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>Deposits from banks</t>
+          <t>Other expenses</t>
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>511961</v>
+        <v>-10029</v>
       </c>
       <c r="C21" s="6" t="n">
-        <v>493256</v>
+        <v>-9735</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>369590</v>
+        <v>-9543</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>539387</v>
+        <v>-9818</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>396254</v>
+        <v>-8924</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>219378</v>
+        <v>-18816</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>128590</v>
+        <v>-23048</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>102919</v>
+        <v>-7857</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>123122</v>
+        <v>-7870</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>164849</v>
+        <v>-6914</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>136736</v>
+        <v>-6544</v>
       </c>
       <c r="M21" s="6" t="n">
-        <v>40270</v>
+        <v>-6402</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>72132</v>
+        <v>-4987</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>62384</v>
+        <v>-5779</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>202684</v>
+        <v>-4657</v>
       </c>
       <c r="Q21" s="6" t="n">
-        <v>176070</v>
+        <v>-4044</v>
       </c>
       <c r="R21" s="6" t="n">
-        <v>366763</v>
+        <v>-3702</v>
       </c>
       <c r="S21" s="6" t="n">
-        <v>560116</v>
+        <v>-5767</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Deposits from customers</t>
+          <t>Depreciation of plant and equipment</t>
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>1304816</v>
+        <v>-1870</v>
       </c>
       <c r="C22" s="6" t="n">
-        <v>1355529</v>
+        <v>-1540</v>
       </c>
       <c r="D22" s="6" t="n">
-        <v>1223068</v>
+        <v>-1572</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>1291150</v>
+        <v>-1462</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>1333523</v>
+        <v>-1802</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>1215647</v>
+        <v>-2342</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>1132193</v>
+        <v>-2498</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>1107439</v>
+        <v>-691</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>1019007</v>
+        <v>-794</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>982361</v>
+        <v>-918</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>737724</v>
+        <v>-965</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>765899</v>
+        <v>-859</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>537699</v>
+        <v>-831</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>398239</v>
+        <v>-589</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>352176</v>
+        <v>-507</v>
       </c>
       <c r="Q22" s="6" t="n">
-        <v>296289</v>
+        <v>-516</v>
       </c>
       <c r="R22" s="6" t="n">
-        <v>378219</v>
+        <v>-496</v>
       </c>
       <c r="S22" s="6" t="n">
-        <v>290289</v>
+        <v>-292</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>Derivative financial instruments</t>
+          <t>Amortisation of intangible assets</t>
         </is>
       </c>
       <c r="B23" s="6" t="n">
-        <v>289</v>
+        <v>-161</v>
       </c>
       <c r="C23" s="6" t="n">
-        <v>2</v>
+        <v>-104</v>
       </c>
       <c r="D23" s="6" t="n">
-        <v>3</v>
+        <v>-52</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>13</v>
+        <v>-271</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>5280</v>
+        <v>-237</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>56924</v>
+        <v>-256</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>8771</v>
+        <v>-100</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>1977</v>
+        <v>-53</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>257</v>
+        <v>-45</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>4150</v>
+        <v>-144</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>11505</v>
+        <v>-146</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>21499</v>
+        <v>-129</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>42505</v>
+        <v>-47</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>3435</v>
+        <v>-105</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>4416</v>
+        <v>-160</v>
       </c>
       <c r="Q23" s="6" t="n">
-        <v>5956</v>
+        <v>-161</v>
       </c>
       <c r="R23" s="6" t="n">
-        <v>5766</v>
+        <v>-106</v>
       </c>
       <c r="S23" s="6" t="n">
-        <v>5390</v>
+        <v>-84</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>Other liabilities</t>
-        </is>
-      </c>
-      <c r="B24" s="6" t="n">
-        <v>39574</v>
-      </c>
-      <c r="C24" s="6" t="n">
-        <v>37473</v>
-      </c>
-      <c r="D24" s="6" t="n">
-        <v>38352</v>
-      </c>
-      <c r="E24" s="6" t="n">
-        <v>50379</v>
-      </c>
-      <c r="F24" s="6" t="n">
-        <v>43571</v>
-      </c>
-      <c r="G24" s="6" t="n">
-        <v>36086</v>
-      </c>
-      <c r="H24" s="6" t="n">
-        <v>43609</v>
-      </c>
-      <c r="I24" s="6" t="n">
-        <v>21359</v>
-      </c>
-      <c r="J24" s="6" t="n">
-        <v>20158</v>
-      </c>
-      <c r="K24" s="6" t="n">
-        <v>13620</v>
-      </c>
-      <c r="L24" s="6" t="n">
-        <v>17145</v>
-      </c>
-      <c r="M24" s="6" t="n">
-        <v>18089</v>
-      </c>
-      <c r="N24" s="6" t="n">
-        <v>23787</v>
-      </c>
-      <c r="O24" s="6" t="n">
-        <v>19123</v>
-      </c>
-      <c r="P24" s="6" t="n">
-        <v>15290</v>
-      </c>
-      <c r="Q24" s="6" t="n">
-        <v>14205</v>
-      </c>
-      <c r="R24" s="6" t="n">
-        <v>13404</v>
-      </c>
-      <c r="S24" s="6" t="n">
-        <v>10601</v>
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Total operating expenses (sum of Staff costs + Other expenses + Depreciation + Amortisation - excludes credit loss provisions and subsidiary items per standard cost-to-income convention, not itself a printed AR subtotal)</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>-98139</v>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>-83573</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>-79225</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>-70759</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>-61117</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>-69021</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>-72925</v>
+      </c>
+      <c r="I24" s="5" t="n">
+        <v>-50469</v>
+      </c>
+      <c r="J24" s="5" t="n">
+        <v>-50074</v>
+      </c>
+      <c r="K24" s="5" t="n">
+        <v>-40797</v>
+      </c>
+      <c r="L24" s="5" t="n">
+        <v>-37155</v>
+      </c>
+      <c r="M24" s="5" t="n">
+        <v>-37568</v>
+      </c>
+      <c r="N24" s="5" t="n">
+        <v>-30354</v>
+      </c>
+      <c r="O24" s="5" t="n">
+        <v>-25700</v>
+      </c>
+      <c r="P24" s="5" t="n">
+        <v>-21527</v>
+      </c>
+      <c r="Q24" s="5" t="n">
+        <v>-18480</v>
+      </c>
+      <c r="R24" s="5" t="n">
+        <v>-16065</v>
+      </c>
+      <c r="S24" s="5" t="n">
+        <v>-17772</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>Accruals and deferred income</t>
+          <t>Credit/(provision) for expected credit losses</t>
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>18650</v>
+        <v>217</v>
       </c>
       <c r="C25" s="6" t="n">
-        <v>23257</v>
+        <v>3953</v>
       </c>
       <c r="D25" s="6" t="n">
-        <v>15017</v>
+        <v>11235</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>7720</v>
+        <v>11526</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>5657</v>
+        <v>-23665</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>5705</v>
+        <v>-3172</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>6390</v>
+        <v>-377</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>6207</v>
+        <v>458</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>4176</v>
+        <v>187</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>5874</v>
+        <v>-527</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>4512</v>
+        <v>155</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>4016</v>
+        <v>-722</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>3729</v>
+        <v>-60</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>4828</v>
+        <v>-4455</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>3602</v>
+        <v>-8272</v>
       </c>
       <c r="Q25" s="6" t="n">
-        <v>3137</v>
+        <v>-35</v>
       </c>
       <c r="R25" s="6" t="n">
-        <v>2166</v>
+        <v>-1827</v>
       </c>
       <c r="S25" s="6" t="n">
-        <v>4099</v>
+        <v>-9386</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>Current tax liabilities</t>
+          <t>Impairment of investment in subsidiary</t>
         </is>
       </c>
       <c r="B26" s="6" t="n"/>
@@ -8144,48 +10091,28 @@
       <c r="D26" s="6" t="n"/>
       <c r="E26" s="6" t="n"/>
       <c r="F26" s="6" t="n"/>
-      <c r="G26" s="6" t="n">
-        <v>4891</v>
-      </c>
-      <c r="H26" s="6" t="n">
-        <v>675</v>
-      </c>
-      <c r="I26" s="6" t="n">
-        <v>4908</v>
-      </c>
-      <c r="J26" s="6" t="n">
-        <v>5447</v>
-      </c>
-      <c r="K26" s="6" t="n">
-        <v>8680</v>
-      </c>
-      <c r="L26" s="6" t="n">
-        <v>3520</v>
-      </c>
-      <c r="M26" s="6" t="n">
-        <v>3873</v>
-      </c>
-      <c r="N26" s="6" t="n">
-        <v>2521</v>
-      </c>
-      <c r="O26" s="6" t="n">
-        <v>3715</v>
-      </c>
-      <c r="P26" s="6" t="n"/>
+      <c r="G26" s="6" t="n"/>
+      <c r="H26" s="6" t="n"/>
+      <c r="I26" s="6" t="n"/>
+      <c r="J26" s="6" t="n"/>
+      <c r="K26" s="6" t="n"/>
+      <c r="L26" s="6" t="n"/>
+      <c r="M26" s="6" t="n"/>
+      <c r="N26" s="6" t="n"/>
+      <c r="O26" s="6" t="n"/>
+      <c r="P26" s="6" t="n">
+        <v>-31432</v>
+      </c>
       <c r="Q26" s="6" t="n">
-        <v>14184</v>
-      </c>
-      <c r="R26" s="6" t="n">
-        <v>4106</v>
-      </c>
-      <c r="S26" s="6" t="n">
-        <v>195</v>
-      </c>
+        <v>-8432</v>
+      </c>
+      <c r="R26" s="6" t="n"/>
+      <c r="S26" s="6" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>Deferred tax liabilities</t>
+          <t>Gain/(loss) on disposal of subsidiary</t>
         </is>
       </c>
       <c r="B27" s="6" t="n"/>
@@ -8198,178 +10125,208 @@
       <c r="I27" s="6" t="n"/>
       <c r="J27" s="6" t="n"/>
       <c r="K27" s="6" t="n"/>
-      <c r="L27" s="6" t="n"/>
+      <c r="L27" s="6" t="n">
+        <v>-1707</v>
+      </c>
       <c r="M27" s="6" t="n"/>
       <c r="N27" s="6" t="n">
-        <v>28</v>
-      </c>
-      <c r="O27" s="6" t="n"/>
+        <v>1632</v>
+      </c>
+      <c r="O27" s="6" t="n">
+        <v>-1074</v>
+      </c>
       <c r="P27" s="6" t="n"/>
       <c r="Q27" s="6" t="n"/>
       <c r="R27" s="6" t="n"/>
-      <c r="S27" s="6" t="n">
-        <v>14</v>
-      </c>
+      <c r="S27" s="6" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t>Impairment provision on off balance sheet products</t>
-        </is>
-      </c>
-      <c r="B28" s="6" t="n">
-        <v>138</v>
-      </c>
-      <c r="C28" s="6" t="n">
-        <v>58</v>
-      </c>
-      <c r="D28" s="6" t="n">
-        <v>54</v>
-      </c>
-      <c r="E28" s="6" t="n">
-        <v>51</v>
-      </c>
-      <c r="F28" s="6" t="n">
-        <v>119</v>
-      </c>
-      <c r="G28" s="6" t="n">
-        <v>310</v>
-      </c>
-      <c r="H28" s="6" t="n">
-        <v>102</v>
-      </c>
-      <c r="I28" s="6" t="n">
-        <v>97</v>
-      </c>
-      <c r="J28" s="6" t="n"/>
-      <c r="K28" s="6" t="n"/>
-      <c r="L28" s="6" t="n"/>
-      <c r="M28" s="6" t="n"/>
-      <c r="N28" s="6" t="n"/>
-      <c r="O28" s="6" t="n"/>
-      <c r="P28" s="6" t="n"/>
-      <c r="Q28" s="6" t="n"/>
-      <c r="R28" s="6" t="n"/>
-      <c r="S28" s="6" t="n"/>
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Profit before income tax</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>90368</v>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>107643</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>138195</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>91147</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>39266</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>47910</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>41935</v>
+      </c>
+      <c r="I28" s="5" t="n">
+        <v>64550</v>
+      </c>
+      <c r="J28" s="5" t="n">
+        <v>44596</v>
+      </c>
+      <c r="K28" s="5" t="n">
+        <v>49858</v>
+      </c>
+      <c r="L28" s="5" t="n">
+        <v>56214</v>
+      </c>
+      <c r="M28" s="5" t="n">
+        <v>33331</v>
+      </c>
+      <c r="N28" s="5" t="n">
+        <v>41617</v>
+      </c>
+      <c r="O28" s="5" t="n">
+        <v>32708</v>
+      </c>
+      <c r="P28" s="5" t="n">
+        <v>-23864</v>
+      </c>
+      <c r="Q28" s="5" t="n">
+        <v>19615</v>
+      </c>
+      <c r="R28" s="5" t="n">
+        <v>16631</v>
+      </c>
+      <c r="S28" s="5" t="n">
+        <v>4574</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>Subordinated liabilities</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="n"/>
-      <c r="C29" s="6" t="n"/>
-      <c r="D29" s="6" t="n"/>
-      <c r="E29" s="6" t="n"/>
+          <t>Income tax expense</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n">
+        <v>-21437</v>
+      </c>
+      <c r="C29" s="6" t="n">
+        <v>-23726</v>
+      </c>
+      <c r="D29" s="6" t="n">
+        <v>-34982</v>
+      </c>
+      <c r="E29" s="6" t="n">
+        <v>-22583</v>
+      </c>
       <c r="F29" s="6" t="n">
-        <v>60000</v>
+        <v>-7788</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>60000</v>
+        <v>-12745</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>60000</v>
+        <v>-9830</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>60000</v>
+        <v>-13427</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>60000</v>
+        <v>-12532</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>60000</v>
+        <v>-14168</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>60000</v>
+        <v>-10764</v>
       </c>
       <c r="M29" s="6" t="n">
-        <v>60000</v>
+        <v>-7376</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>60000</v>
+        <v>-9744</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>60000</v>
+        <v>-8278</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>60000</v>
+        <v>-2206</v>
       </c>
       <c r="Q29" s="6" t="n">
-        <v>60000</v>
+        <v>-8836</v>
       </c>
       <c r="R29" s="6" t="n">
-        <v>60000</v>
+        <v>-4071</v>
       </c>
       <c r="S29" s="6" t="n">
-        <v>60000</v>
+        <v>-1562</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>Total liabilities</t>
+          <t>Profit/(loss) for the year</t>
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>1875428</v>
+        <v>68931</v>
       </c>
       <c r="C30" s="5" t="n">
-        <v>1909575</v>
+        <v>83917</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>1646084</v>
+        <v>103213</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>1888700</v>
+        <v>68564</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>1844404</v>
+        <v>31478</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>1598941</v>
+        <v>35165</v>
       </c>
       <c r="H30" s="5" t="n">
-        <v>1380330</v>
+        <v>32105</v>
       </c>
       <c r="I30" s="5" t="n">
-        <v>1304906</v>
+        <v>51123</v>
       </c>
       <c r="J30" s="5" t="n">
-        <v>1232167</v>
+        <v>32064</v>
       </c>
       <c r="K30" s="5" t="n">
-        <v>1239534</v>
+        <v>35690</v>
       </c>
       <c r="L30" s="5" t="n">
-        <v>971142</v>
+        <v>45450</v>
       </c>
       <c r="M30" s="5" t="n">
-        <v>913636</v>
+        <v>25955</v>
       </c>
       <c r="N30" s="5" t="n">
-        <v>742401</v>
+        <v>31873</v>
       </c>
       <c r="O30" s="5" t="n">
-        <v>551724</v>
+        <v>24430</v>
       </c>
       <c r="P30" s="5" t="n">
-        <v>638168</v>
+        <v>-26070</v>
       </c>
       <c r="Q30" s="5" t="n">
-        <v>569841</v>
+        <v>10779</v>
       </c>
       <c r="R30" s="5" t="n">
-        <v>830424</v>
+        <v>12560</v>
       </c>
       <c r="S30" s="5" t="n">
-        <v>930704</v>
+        <v>3012</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>Equity</t>
+          <t>Other comprehensive income</t>
         </is>
       </c>
       <c r="B31" s="6" t="n"/>
@@ -8394,1951 +10351,6 @@
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>Authorised and called up share capital</t>
-        </is>
-      </c>
-      <c r="B32" s="6" t="n">
-        <v>250000</v>
-      </c>
-      <c r="C32" s="6" t="n">
-        <v>250000</v>
-      </c>
-      <c r="D32" s="6" t="n">
-        <v>250000</v>
-      </c>
-      <c r="E32" s="6" t="n">
-        <v>250000</v>
-      </c>
-      <c r="F32" s="6" t="n">
-        <v>250000</v>
-      </c>
-      <c r="G32" s="6" t="n">
-        <v>250000</v>
-      </c>
-      <c r="H32" s="6" t="n">
-        <v>250000</v>
-      </c>
-      <c r="I32" s="6" t="n">
-        <v>250000</v>
-      </c>
-      <c r="J32" s="6" t="n">
-        <v>250000</v>
-      </c>
-      <c r="K32" s="6" t="n">
-        <v>250000</v>
-      </c>
-      <c r="L32" s="6" t="n">
-        <v>250000</v>
-      </c>
-      <c r="M32" s="6" t="n">
-        <v>250000</v>
-      </c>
-      <c r="N32" s="6" t="n">
-        <v>250000</v>
-      </c>
-      <c r="O32" s="6" t="n">
-        <v>250000</v>
-      </c>
-      <c r="P32" s="6" t="n">
-        <v>140000</v>
-      </c>
-      <c r="Q32" s="6" t="n">
-        <v>140000</v>
-      </c>
-      <c r="R32" s="6" t="n">
-        <v>140000</v>
-      </c>
-      <c r="S32" s="6" t="n">
-        <v>140000</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="6" t="inlineStr">
-        <is>
-          <t>Other equity instruments (Additional Tier 1)</t>
-        </is>
-      </c>
-      <c r="B33" s="6" t="n">
-        <v>60000</v>
-      </c>
-      <c r="C33" s="6" t="n">
-        <v>60000</v>
-      </c>
-      <c r="D33" s="6" t="n">
-        <v>60000</v>
-      </c>
-      <c r="E33" s="6" t="n">
-        <v>60000</v>
-      </c>
-      <c r="F33" s="6" t="n"/>
-      <c r="G33" s="6" t="n"/>
-      <c r="H33" s="6" t="n"/>
-      <c r="I33" s="6" t="n"/>
-      <c r="J33" s="6" t="n"/>
-      <c r="K33" s="6" t="n"/>
-      <c r="L33" s="6" t="n"/>
-      <c r="M33" s="6" t="n"/>
-      <c r="N33" s="6" t="n"/>
-      <c r="O33" s="6" t="n"/>
-      <c r="P33" s="6" t="n"/>
-      <c r="Q33" s="6" t="n"/>
-      <c r="R33" s="6" t="n"/>
-      <c r="S33" s="6" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="6" t="inlineStr">
-        <is>
-          <t>Retained earnings</t>
-        </is>
-      </c>
-      <c r="B34" s="6" t="n">
-        <v>89013</v>
-      </c>
-      <c r="C34" s="6" t="n">
-        <v>103744</v>
-      </c>
-      <c r="D34" s="6" t="n">
-        <v>123289</v>
-      </c>
-      <c r="E34" s="6" t="n">
-        <v>91893</v>
-      </c>
-      <c r="F34" s="6" t="n">
-        <v>56776</v>
-      </c>
-      <c r="G34" s="6" t="n">
-        <v>92164</v>
-      </c>
-      <c r="H34" s="6" t="n">
-        <v>57058</v>
-      </c>
-      <c r="I34" s="6" t="n">
-        <v>76076</v>
-      </c>
-      <c r="J34" s="6" t="n">
-        <v>57022</v>
-      </c>
-      <c r="K34" s="6" t="n">
-        <v>60648</v>
-      </c>
-      <c r="L34" s="6" t="n">
-        <v>70408</v>
-      </c>
-      <c r="M34" s="6" t="n">
-        <v>50913</v>
-      </c>
-      <c r="N34" s="6" t="n">
-        <v>56831</v>
-      </c>
-      <c r="O34" s="6" t="n">
-        <v>24958</v>
-      </c>
-      <c r="P34" s="6" t="n">
-        <v>528</v>
-      </c>
-      <c r="Q34" s="6" t="n">
-        <v>26598</v>
-      </c>
-      <c r="R34" s="6" t="n">
-        <v>15819</v>
-      </c>
-      <c r="S34" s="6" t="n">
-        <v>3259</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="6" t="inlineStr">
-        <is>
-          <t>Available for sale reserve</t>
-        </is>
-      </c>
-      <c r="B35" s="6" t="n"/>
-      <c r="C35" s="6" t="n"/>
-      <c r="D35" s="6" t="n"/>
-      <c r="E35" s="6" t="n"/>
-      <c r="F35" s="6" t="n"/>
-      <c r="G35" s="6" t="n"/>
-      <c r="H35" s="6" t="n"/>
-      <c r="I35" s="6" t="n"/>
-      <c r="J35" s="6" t="n">
-        <v>32</v>
-      </c>
-      <c r="K35" s="6" t="n">
-        <v>-284</v>
-      </c>
-      <c r="L35" s="6" t="n">
-        <v>-140</v>
-      </c>
-      <c r="M35" s="6" t="n">
-        <v>567</v>
-      </c>
-      <c r="N35" s="6" t="n">
-        <v>843</v>
-      </c>
-      <c r="O35" s="6" t="n">
-        <v>845</v>
-      </c>
-      <c r="P35" s="6" t="n">
-        <v>-971</v>
-      </c>
-      <c r="Q35" s="6" t="n">
-        <v>-945</v>
-      </c>
-      <c r="R35" s="6" t="n">
-        <v>-4170</v>
-      </c>
-      <c r="S35" s="6" t="n">
-        <v>-18154</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>Total shareholders' equity</t>
-        </is>
-      </c>
-      <c r="B36" s="5" t="n">
-        <v>399013</v>
-      </c>
-      <c r="C36" s="5" t="n">
-        <v>413744</v>
-      </c>
-      <c r="D36" s="5" t="n">
-        <v>433289</v>
-      </c>
-      <c r="E36" s="5" t="n">
-        <v>401893</v>
-      </c>
-      <c r="F36" s="5" t="n">
-        <v>306776</v>
-      </c>
-      <c r="G36" s="5" t="n">
-        <v>342164</v>
-      </c>
-      <c r="H36" s="5" t="n">
-        <v>307058</v>
-      </c>
-      <c r="I36" s="5" t="n">
-        <v>326076</v>
-      </c>
-      <c r="J36" s="5" t="n">
-        <v>307054</v>
-      </c>
-      <c r="K36" s="5" t="n">
-        <v>310364</v>
-      </c>
-      <c r="L36" s="5" t="n">
-        <v>320268</v>
-      </c>
-      <c r="M36" s="5" t="n">
-        <v>301480</v>
-      </c>
-      <c r="N36" s="5" t="n">
-        <v>307674</v>
-      </c>
-      <c r="O36" s="5" t="n">
-        <v>275803</v>
-      </c>
-      <c r="P36" s="5" t="n">
-        <v>139557</v>
-      </c>
-      <c r="Q36" s="5" t="n">
-        <v>165653</v>
-      </c>
-      <c r="R36" s="5" t="n">
-        <v>151649</v>
-      </c>
-      <c r="S36" s="5" t="n">
-        <v>125105</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>Total liabilities and equity</t>
-        </is>
-      </c>
-      <c r="B37" s="5" t="n">
-        <v>2274441</v>
-      </c>
-      <c r="C37" s="5" t="n">
-        <v>2323319</v>
-      </c>
-      <c r="D37" s="5" t="n">
-        <v>2079373</v>
-      </c>
-      <c r="E37" s="5" t="n">
-        <v>2290593</v>
-      </c>
-      <c r="F37" s="5" t="n">
-        <v>2151180</v>
-      </c>
-      <c r="G37" s="5" t="n">
-        <v>1941105</v>
-      </c>
-      <c r="H37" s="5" t="n">
-        <v>1687388</v>
-      </c>
-      <c r="I37" s="5" t="n">
-        <v>1630982</v>
-      </c>
-      <c r="J37" s="5" t="n">
-        <v>1539221</v>
-      </c>
-      <c r="K37" s="5" t="n">
-        <v>1549898</v>
-      </c>
-      <c r="L37" s="5" t="n">
-        <v>1291410</v>
-      </c>
-      <c r="M37" s="5" t="n">
-        <v>1215116</v>
-      </c>
-      <c r="N37" s="5" t="n">
-        <v>1050075</v>
-      </c>
-      <c r="O37" s="5" t="n">
-        <v>827527</v>
-      </c>
-      <c r="P37" s="5" t="n">
-        <v>777725</v>
-      </c>
-      <c r="Q37" s="5" t="n">
-        <v>735494</v>
-      </c>
-      <c r="R37" s="5" t="n">
-        <v>982073</v>
-      </c>
-      <c r="S37" s="5" t="n">
-        <v>1055809</v>
-      </c>
-    </row>
-    <row r="39" ht="200" customHeight="1">
-      <c r="A39" s="8" t="inlineStr">
-        <is>
-          <t>Sources - Bank of China (UK) Limited's own Statement of Financial Position (Bank/solo basis - no group accounts prepared, Companies Act 2006 s.401 exemption), £'000, each year's own originally-published report:
-FY2025: Annual Report 2025, p.49 - https://pic.bankofchina.com/bocappd/uk/202605/P020260506389809417235.pdf
-FY2024: Annual Report 2024, p.49 - https://pic.bankofchina.com/bocappd/uk/202507/P020250718380377744220.pdf (FY2024's own primary source is its own report (AR2024_URL), not AR2025's comparative column - both are identical figures (verified), no restatement.)
-FY2023: Annual Report 2023, p.50 - https://pic.bankofchina.com/bocappd/uk/202405/P020240508355110735895.pdf
-FY2022: Financial Statements 2022, p.38 - https://pic.bankofchina.com/bocappd/uk/202403/P020240315379765805794.pdf
-FY2021: Financial Statements 2021, p.35 - https://pic.bankofchina.com/bocappd/uk/202303/P020230331590070165221.pdf
-FY2020: Financial Statements 2020, p.33 - https://pic.bankofchina.com/bocappd/uk/202109/P020210902654360894172.pdf
-FY2019: Financial Statements 2019, p.32 - https://pic.bankofchina.com/bocappd/uk/202007/P020200727323473194461.pdf
-FY2018: Financial Statements 2018, p.27 - https://pic.bankofchina.com/bocappd/uk/201904/P020190410506087628158.pdf
-FY2017: Financial Statements 2017, p.25 - https://pic.bankofchina.com/bocappd/uk/201805/P020180517534275167127.pdf
-FY2016: Financial Statements 2016, p.20 - https://pic.bankofchina.com/bocappd/uk/201706/P020170627373089457851.pdf
-FY2015: Financial Statements 2015, p.19 - https://pic.bankofchina.com/bocappd/uk/201606/P020160620504225340480.pdf
-FY2014: Financial Statements 2015's own FY2014 comparative column, p.19 - https://pic.bankofchina.com/bocappd/uk/201606/P020160620504225340480.pdf (AR2014_URL note: the Bank's own FY2014 Annual Report PDF is a scanned/photocopied document (Canon iR-ADV C5045 scanner output) with no extractable text layer - pdftotext and qpdf both confirm zero recoverable text after a repair pass. FY2014 figures on every sheet are therefore taken from the FY2015 Annual Report's own FY2014 comparative column instead (a real, live, text-searchable document), the same each-year's-own-report methodology used everywhere else in this workbook, just one year removed since FY2014's own PDF cannot be read as text.)
-FY2013: Annual Report and Financial Statements 2013, p.17 - https://pic.bankofchina.com/bocappd/uk/201505/P020150504339499661074.pdf (AR2013_URL note: the Bank's own FY2013 Annual Report PDF is a scanned/photocopied document (Xerox WorkCentre 5665 scanner output) with no extractable text layer, the same pattern HD-046 found on FY2014's own PDF. Unlike FY2014 (where a later year's clean comparative column exists), FY2014's own PDF is itself unreadable, so no clean comparative source exists for FY2013 either - FY2013 figures here were instead OCR'd directly off this scanned PDF (ocrmypdf --force-ocr + tesseract), then cross-checked two ways: (1) the resulting FY2013 closing equity/balance-sheet/cash-flow figures tie out internally (assets = liabilities + equity; operating + investing + financing cash flows = the disclosed net movement; opening + net movement = closing cash) and (2) the OCR'd FY2013 closing Statement of Changes in Equity figures match this workbook's own pre-existing FY2014 opening balance exactly (250,000 / 56,831 / 843 / 307,674), which was itself sourced independently via AR2015's FY2014 comparative column under HD-046. Several individual OCR digit errors were caught and corrected via these tie-outs (e.g. 'Interest income from financial investments' misread as 4,294 instead of 1,294, 'Total assets' misread as 4,050,075 instead of 1,050,075 - a recurring 1-to-4 OCR confusion in this particular scan).)
-FY2012: Annual Report 2012, p.24 - https://pic.bankofchina.com/bocappd/uk/201312/P020131213310466908739.pdf
-FY2011: Annual Report 2011, p.24 - https://pic.bankofchina.com/bocappd/uk/201301/P020130110394685934112.pdf
-FY2010: Annual Report 2011's own FY2010 comparative column, p.24 - https://pic.bankofchina.com/bocappd/uk/201301/P020130110394685934112.pdf (AR2010_URL note: the Bank's own FY2010 Annual Report PDF is a scanned/photocopied document (Canon iR-ADV C5045 scanner output, the same scanner/pattern as FY2014's own PDF) with no extractable text layer. FY2010 figures on every sheet are therefore taken from the FY2011 Annual Report's own FY2010 comparative column instead (a real, live, text-searchable document), the same each-year's-own-report-one-year-removed methodology used for FY2014 via AR2015.)
-FY2009: 2009 Report and Financial Statements, p.31 - https://pic.bankofchina.com/bocappd/uk/201109/P020110901339600023124.pdf
-FY2008: 2009 Report's own FY2008 comparative column, p.31 - https://pic.bankofchina.com/bocappd/uk/201109/P020110901339600023124.pdf, cross-checked against the Bank's own 2008 Report and Financial Statements (Balance Sheet, p.29) - https://pic.bankofchina.com/bocappd/uk/201109/P020110901339400504145.pdf (figures identical). FY2008 period note: Bank of China (UK) Limited's first accounting period ran 1 April 2007 - 30 September 2007 (a 6-month stub, outside this workbook's scope), and its second and only 'FY2008' statutory period is genuinely a 15-month period from 1 October 2007 to 31 December 2008 (the year-end was moved to December during this period) - not a standard 12-month year. Both the Bank's own FY2008 Report and Financial Statements (AR2008_URL) and the FY2009 Report's own FY2008 comparative column (AR2009_URL) show this identical 15-month figure set, cross-checked and tying exactly. Shown here as 'FY2008' per this workbook's year-labelling convention, but flagged as non-comparable in length to every other year in this workbook - growth trends spanning the FY2008/FY2009 boundary should be read with that caveat.
-HD-075 extension presentation notes (FY2008-FY2013): 'Investment in subsidiary/group companies' is its own row for these 6 years only (a real, non-nil balance - the subsidiary was disposed of during FY2012, hence nil/omitted from FY2014 onward). 'Deferred tax liabilities' is its own row for FY2008 (£14k) and FY2013 (£28k) only - nil/not disclosed as a separate line in every other year shown. 'Authorised and called up share capital' rose from £140,000k to £250,000k during FY2012 via a £110,000k ordinary share issue (see the Statement of Changes in Equity sheet). FY2013's Balance Sheet total assets/liabilities were affected by two OCR digit corrections cross-checked against the statement's own subtotals - see AR2013_SCAN_NOTE.
-Presentation notes: 'Government bonds' only appears as its own line from FY2022 onward. 'Subordinated liabilities' (£60,000k every year FY2014-FY2021) was repaid and replaced by an equal £60,000k Additional Tier 1 instrument in June 2022 - both nil/blank in the years they don't apply. 'Investment in subsidiary companies' is nil every year and omitted as a row. 'Available for sale financial investments' and its matching equity 'Available for sale reserve' existed under IAS 39 through FY2017 and were replaced by 'Financial assets at fair value through profit and loss' / 'Debt instruments at amortised cost' at the 1 January 2018 IFRS 9 transition (a £495k opening-equity charge that year, see the Statement of Changes in Equity sheet) - both pairs of rows are blank/zero in the years they don't apply, not force-matched. FY2021's own report's Statement of Changes in Equity states closing retained earnings as £56,706k, £70k less than the Balance Sheet's own £56,776k for the same date - the Balance Sheet's single 'Retained earnings' line appears to combine the SOCE's separate retained-earnings and FX-translation-reserve columns (£56,706k + £70k = £56,776k); the same pattern recurs one year earlier at FY2020 (SOCE retained earnings £92,228k + FX reserve -£64k = Balance Sheet's own £92,164k); total equity ties out exactly either way in both years. FY2014 cash resolved (HD-081, 2026-09-07): FY2015's own filing originally appeared to show two different FY2014 cash figures - £199,954k on the Balance Sheet's comparative column vs. £199,854k on the Cash Flow Statement's own comparative closing balance. Re-summing FY2014's own 9 asset line items as originally transcribed (199,954 + 207,026 + 722,307 + 16,173 + 27,820 + 37,469 + 751 + 3,390 + 326) gives £1,215,216k, £100k more than the Balance Sheet's own stated 'Total assets' of £1,215,116k for that column; substituting £199,854k for the cash line instead sums to exactly £1,215,116k. The Balance Sheet's own internal subtotal therefore only ties out with £199,854k, confirming £199,954k was a single-digit transcription/OCR misread of the FY2015 filing's FY2014 comparative column (a 9 misread for an 8 in the thousands place) and that £199,854k, matching the Cash Flow Statement, is the correct figure. Corrected here to £199,854k; FY2014's own primary report remains unreadable as text (see AR2014_SCAN_NOTE), so this arithmetic cross-check within FY2015's own filing is the resolving evidence.
-Entity note: Bank of China (UK) Limited (company 06193060, FRN 467410) is a wholly-owned UK subsidiary of Bank of China Limited (state-owned). It does not take the FRS 101/102 cash-flow-statement exemption - a full Statement of Cash Flows is published every year. All figures are the Bank's own solo entity basis throughout.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A39:S39"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:S37"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="68" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="15" customWidth="1" min="12" max="12"/>
-    <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="15" customWidth="1" min="14" max="14"/>
-    <col width="15" customWidth="1" min="15" max="15"/>
-    <col width="15" customWidth="1" min="16" max="16"/>
-    <col width="15" customWidth="1" min="17" max="17"/>
-    <col width="15" customWidth="1" min="18" max="18"/>
-    <col width="15" customWidth="1" min="19" max="19"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Bank of China (UK) Limited — Income Statement and Statement of Comprehensive Income</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Bank of China (UK) Limited (solo entity basis), £'000</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Line item</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025 (£'000)</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024 (£'000)</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023 (£'000)</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022 (£'000)</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021 (£'000)</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>FY2020 (£'000)</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>FY2019 (£'000)</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>FY2018 (£'000)</t>
-        </is>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>FY2017 (£'000)</t>
-        </is>
-      </c>
-      <c r="K3" s="4" t="inlineStr">
-        <is>
-          <t>FY2016 (£'000)</t>
-        </is>
-      </c>
-      <c r="L3" s="4" t="inlineStr">
-        <is>
-          <t>FY2015 (£'000)</t>
-        </is>
-      </c>
-      <c r="M3" s="4" t="inlineStr">
-        <is>
-          <t>FY2014 (£'000)</t>
-        </is>
-      </c>
-      <c r="N3" s="4" t="inlineStr">
-        <is>
-          <t>FY2013 (£'000)</t>
-        </is>
-      </c>
-      <c r="O3" s="4" t="inlineStr">
-        <is>
-          <t>FY2012 (£'000)</t>
-        </is>
-      </c>
-      <c r="P3" s="4" t="inlineStr">
-        <is>
-          <t>FY2011 (£'000)</t>
-        </is>
-      </c>
-      <c r="Q3" s="4" t="inlineStr">
-        <is>
-          <t>FY2010 (£'000)</t>
-        </is>
-      </c>
-      <c r="R3" s="4" t="inlineStr">
-        <is>
-          <t>FY2009 (£'000)</t>
-        </is>
-      </c>
-      <c r="S3" s="4" t="inlineStr">
-        <is>
-          <t>FY2008 (£'000)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>Income</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n"/>
-      <c r="C4" s="6" t="n"/>
-      <c r="D4" s="6" t="n"/>
-      <c r="E4" s="6" t="n"/>
-      <c r="F4" s="6" t="n"/>
-      <c r="G4" s="6" t="n"/>
-      <c r="H4" s="6" t="n"/>
-      <c r="I4" s="6" t="n"/>
-      <c r="J4" s="6" t="n"/>
-      <c r="K4" s="6" t="n"/>
-      <c r="L4" s="6" t="n"/>
-      <c r="M4" s="6" t="n"/>
-      <c r="N4" s="6" t="n"/>
-      <c r="O4" s="6" t="n"/>
-      <c r="P4" s="6" t="n"/>
-      <c r="Q4" s="6" t="n"/>
-      <c r="R4" s="6" t="n"/>
-      <c r="S4" s="6" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>Interest income</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="n">
-        <v>110123</v>
-      </c>
-      <c r="C5" s="6" t="n">
-        <v>128817</v>
-      </c>
-      <c r="D5" s="6" t="n">
-        <v>121217</v>
-      </c>
-      <c r="E5" s="6" t="n">
-        <v>62661</v>
-      </c>
-      <c r="F5" s="6" t="n">
-        <v>36936</v>
-      </c>
-      <c r="G5" s="6" t="n">
-        <v>40327</v>
-      </c>
-      <c r="H5" s="6" t="n">
-        <v>45693</v>
-      </c>
-      <c r="I5" s="6" t="n">
-        <v>40759</v>
-      </c>
-      <c r="J5" s="6" t="n">
-        <v>38234</v>
-      </c>
-      <c r="K5" s="6" t="n">
-        <v>34591</v>
-      </c>
-      <c r="L5" s="6" t="n">
-        <v>25645</v>
-      </c>
-      <c r="M5" s="6" t="n">
-        <v>26082</v>
-      </c>
-      <c r="N5" s="6" t="n">
-        <v>18724</v>
-      </c>
-      <c r="O5" s="6" t="n">
-        <v>14523</v>
-      </c>
-      <c r="P5" s="6" t="n">
-        <v>12956</v>
-      </c>
-      <c r="Q5" s="6" t="n">
-        <v>16182</v>
-      </c>
-      <c r="R5" s="6" t="n">
-        <v>20622</v>
-      </c>
-      <c r="S5" s="6" t="n">
-        <v>54071</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>Interest expense</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="n">
-        <v>-53024</v>
-      </c>
-      <c r="C6" s="6" t="n">
-        <v>-57415</v>
-      </c>
-      <c r="D6" s="6" t="n">
-        <v>-40422</v>
-      </c>
-      <c r="E6" s="6" t="n">
-        <v>-13239</v>
-      </c>
-      <c r="F6" s="6" t="n">
-        <v>-3650</v>
-      </c>
-      <c r="G6" s="6" t="n">
-        <v>-6276</v>
-      </c>
-      <c r="H6" s="6" t="n">
-        <v>-9313</v>
-      </c>
-      <c r="I6" s="6" t="n">
-        <v>-6553</v>
-      </c>
-      <c r="J6" s="6" t="n">
-        <v>-5788</v>
-      </c>
-      <c r="K6" s="6" t="n">
-        <v>-4629</v>
-      </c>
-      <c r="L6" s="6" t="n">
-        <v>-3095</v>
-      </c>
-      <c r="M6" s="6" t="n">
-        <v>-3635</v>
-      </c>
-      <c r="N6" s="6" t="n">
-        <v>-2800</v>
-      </c>
-      <c r="O6" s="6" t="n">
-        <v>-2828</v>
-      </c>
-      <c r="P6" s="6" t="n">
-        <v>-2828</v>
-      </c>
-      <c r="Q6" s="6" t="n">
-        <v>-3858</v>
-      </c>
-      <c r="R6" s="6" t="n">
-        <v>-7677</v>
-      </c>
-      <c r="S6" s="6" t="n">
-        <v>-35584</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>Net interest income</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="n">
-        <v>57099</v>
-      </c>
-      <c r="C7" s="5" t="n">
-        <v>71402</v>
-      </c>
-      <c r="D7" s="5" t="n">
-        <v>80795</v>
-      </c>
-      <c r="E7" s="5" t="n">
-        <v>49422</v>
-      </c>
-      <c r="F7" s="5" t="n">
-        <v>33286</v>
-      </c>
-      <c r="G7" s="5" t="n">
-        <v>34051</v>
-      </c>
-      <c r="H7" s="5" t="n">
-        <v>36380</v>
-      </c>
-      <c r="I7" s="5" t="n">
-        <v>34206</v>
-      </c>
-      <c r="J7" s="5" t="n">
-        <v>32446</v>
-      </c>
-      <c r="K7" s="5" t="n">
-        <v>29962</v>
-      </c>
-      <c r="L7" s="5" t="n">
-        <v>22550</v>
-      </c>
-      <c r="M7" s="5" t="n">
-        <v>22447</v>
-      </c>
-      <c r="N7" s="5" t="n">
-        <v>15924</v>
-      </c>
-      <c r="O7" s="5" t="n">
-        <v>11695</v>
-      </c>
-      <c r="P7" s="5" t="n">
-        <v>10128</v>
-      </c>
-      <c r="Q7" s="5" t="n">
-        <v>12324</v>
-      </c>
-      <c r="R7" s="5" t="n">
-        <v>12945</v>
-      </c>
-      <c r="S7" s="5" t="n">
-        <v>18487</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>Fee and commission income</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="n">
-        <v>3399</v>
-      </c>
-      <c r="C8" s="6" t="n">
-        <v>3228</v>
-      </c>
-      <c r="D8" s="6" t="n">
-        <v>3378</v>
-      </c>
-      <c r="E8" s="6" t="n">
-        <v>3955</v>
-      </c>
-      <c r="F8" s="6" t="n">
-        <v>4294</v>
-      </c>
-      <c r="G8" s="6" t="n">
-        <v>3627</v>
-      </c>
-      <c r="H8" s="6" t="n">
-        <v>4674</v>
-      </c>
-      <c r="I8" s="6" t="n">
-        <v>4850</v>
-      </c>
-      <c r="J8" s="6" t="n">
-        <v>5502</v>
-      </c>
-      <c r="K8" s="6" t="n">
-        <v>4029</v>
-      </c>
-      <c r="L8" s="6" t="n">
-        <v>8906</v>
-      </c>
-      <c r="M8" s="6" t="n">
-        <v>7109</v>
-      </c>
-      <c r="N8" s="6" t="n">
-        <v>9445</v>
-      </c>
-      <c r="O8" s="6" t="n">
-        <v>7448</v>
-      </c>
-      <c r="P8" s="6" t="n">
-        <v>6353</v>
-      </c>
-      <c r="Q8" s="6" t="n">
-        <v>6317</v>
-      </c>
-      <c r="R8" s="6" t="n">
-        <v>3689</v>
-      </c>
-      <c r="S8" s="6" t="n">
-        <v>3886</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>Fee and commission expense</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="n">
-        <v>-1462</v>
-      </c>
-      <c r="C9" s="6" t="n">
-        <v>-1481</v>
-      </c>
-      <c r="D9" s="6" t="n">
-        <v>-1692</v>
-      </c>
-      <c r="E9" s="6" t="n">
-        <v>-1694</v>
-      </c>
-      <c r="F9" s="6" t="n">
-        <v>-1319</v>
-      </c>
-      <c r="G9" s="6" t="n">
-        <v>-1549</v>
-      </c>
-      <c r="H9" s="6" t="n">
-        <v>-1170</v>
-      </c>
-      <c r="I9" s="6" t="n">
-        <v>-886</v>
-      </c>
-      <c r="J9" s="6" t="n">
-        <v>-813</v>
-      </c>
-      <c r="K9" s="6" t="n">
-        <v>-776</v>
-      </c>
-      <c r="L9" s="6" t="n">
-        <v>-582</v>
-      </c>
-      <c r="M9" s="6" t="n">
-        <v>-1022</v>
-      </c>
-      <c r="N9" s="6" t="n">
-        <v>-580</v>
-      </c>
-      <c r="O9" s="6" t="n">
-        <v>-783</v>
-      </c>
-      <c r="P9" s="6" t="n">
-        <v>-507</v>
-      </c>
-      <c r="Q9" s="6" t="n">
-        <v>-170</v>
-      </c>
-      <c r="R9" s="6" t="n">
-        <v>-135</v>
-      </c>
-      <c r="S9" s="6" t="n">
-        <v>-238</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>Net fee and commission income</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="n">
-        <v>1937</v>
-      </c>
-      <c r="C10" s="5" t="n">
-        <v>1747</v>
-      </c>
-      <c r="D10" s="5" t="n">
-        <v>1686</v>
-      </c>
-      <c r="E10" s="5" t="n">
-        <v>2261</v>
-      </c>
-      <c r="F10" s="5" t="n">
-        <v>2975</v>
-      </c>
-      <c r="G10" s="5" t="n">
-        <v>2078</v>
-      </c>
-      <c r="H10" s="5" t="n">
-        <v>3504</v>
-      </c>
-      <c r="I10" s="5" t="n">
-        <v>3964</v>
-      </c>
-      <c r="J10" s="5" t="n">
-        <v>4689</v>
-      </c>
-      <c r="K10" s="5" t="n">
-        <v>3253</v>
-      </c>
-      <c r="L10" s="5" t="n">
-        <v>8324</v>
-      </c>
-      <c r="M10" s="5" t="n">
-        <v>6087</v>
-      </c>
-      <c r="N10" s="5" t="n">
-        <v>8865</v>
-      </c>
-      <c r="O10" s="5" t="n">
-        <v>6665</v>
-      </c>
-      <c r="P10" s="5" t="n">
-        <v>5846</v>
-      </c>
-      <c r="Q10" s="5" t="n">
-        <v>6147</v>
-      </c>
-      <c r="R10" s="5" t="n">
-        <v>3554</v>
-      </c>
-      <c r="S10" s="5" t="n">
-        <v>3648</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>Net fair value gain/(loss) on financial instruments</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="n">
-        <v>3431</v>
-      </c>
-      <c r="C11" s="6" t="n">
-        <v>4711</v>
-      </c>
-      <c r="D11" s="6" t="n">
-        <v>9119</v>
-      </c>
-      <c r="E11" s="6" t="n">
-        <v>148</v>
-      </c>
-      <c r="F11" s="6" t="n">
-        <v>1923</v>
-      </c>
-      <c r="G11" s="6" t="n">
-        <v>-3151</v>
-      </c>
-      <c r="H11" s="6" t="n">
-        <v>-1165</v>
-      </c>
-      <c r="I11" s="6" t="n">
-        <v>-331</v>
-      </c>
-      <c r="J11" s="6" t="n">
-        <v>51</v>
-      </c>
-      <c r="K11" s="6" t="n">
-        <v>241</v>
-      </c>
-      <c r="L11" s="6" t="n">
-        <v>511</v>
-      </c>
-      <c r="M11" s="6" t="n">
-        <v>-1413</v>
-      </c>
-      <c r="N11" s="6" t="n">
-        <v>826</v>
-      </c>
-      <c r="O11" s="6" t="n"/>
-      <c r="P11" s="6" t="n"/>
-      <c r="Q11" s="6" t="n"/>
-      <c r="R11" s="6" t="n"/>
-      <c r="S11" s="6" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>Net gain/(loss) on derivative financial instruments (FY2008-FY2012 presentation)</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="n"/>
-      <c r="C12" s="6" t="n"/>
-      <c r="D12" s="6" t="n"/>
-      <c r="E12" s="6" t="n"/>
-      <c r="F12" s="6" t="n"/>
-      <c r="G12" s="6" t="n"/>
-      <c r="H12" s="6" t="n"/>
-      <c r="I12" s="6" t="n"/>
-      <c r="J12" s="6" t="n"/>
-      <c r="K12" s="6" t="n"/>
-      <c r="L12" s="6" t="n"/>
-      <c r="M12" s="6" t="n"/>
-      <c r="N12" s="6" t="n"/>
-      <c r="O12" s="6" t="n">
-        <v>-1478</v>
-      </c>
-      <c r="P12" s="6" t="n">
-        <v>-927</v>
-      </c>
-      <c r="Q12" s="6" t="n">
-        <v>-2312</v>
-      </c>
-      <c r="R12" s="6" t="n">
-        <v>-2181</v>
-      </c>
-      <c r="S12" s="6" t="n">
-        <v>-3314</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>Foreign exchange gain</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="n">
-        <v>2388</v>
-      </c>
-      <c r="C13" s="6" t="n">
-        <v>2295</v>
-      </c>
-      <c r="D13" s="6" t="n">
-        <v>386</v>
-      </c>
-      <c r="E13" s="6" t="n">
-        <v>4916</v>
-      </c>
-      <c r="F13" s="6" t="n">
-        <v>2590</v>
-      </c>
-      <c r="G13" s="6" t="n">
-        <v>1489</v>
-      </c>
-      <c r="H13" s="6" t="n">
-        <v>4767</v>
-      </c>
-      <c r="I13" s="6" t="n">
-        <v>3167</v>
-      </c>
-      <c r="J13" s="6" t="n">
-        <v>2593</v>
-      </c>
-      <c r="K13" s="6" t="n">
-        <v>2827</v>
-      </c>
-      <c r="L13" s="6" t="n">
-        <v>2492</v>
-      </c>
-      <c r="M13" s="6" t="n">
-        <v>2100</v>
-      </c>
-      <c r="N13" s="6" t="n">
-        <v>554</v>
-      </c>
-      <c r="O13" s="6" t="n">
-        <v>1688</v>
-      </c>
-      <c r="P13" s="6" t="n">
-        <v>-2080</v>
-      </c>
-      <c r="Q13" s="6" t="n">
-        <v>262</v>
-      </c>
-      <c r="R13" s="6" t="n">
-        <v>303</v>
-      </c>
-      <c r="S13" s="6" t="n">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>Net other operating income</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="n">
-        <v>123435</v>
-      </c>
-      <c r="C14" s="6" t="n">
-        <v>107108</v>
-      </c>
-      <c r="D14" s="6" t="n">
-        <v>114199</v>
-      </c>
-      <c r="E14" s="6" t="n">
-        <v>93633</v>
-      </c>
-      <c r="F14" s="6" t="n">
-        <v>83274</v>
-      </c>
-      <c r="G14" s="6" t="n">
-        <v>85636</v>
-      </c>
-      <c r="H14" s="6" t="n">
-        <v>71751</v>
-      </c>
-      <c r="I14" s="6" t="n">
-        <v>73555</v>
-      </c>
-      <c r="J14" s="6" t="n">
-        <v>54704</v>
-      </c>
-      <c r="K14" s="6" t="n">
-        <v>54899</v>
-      </c>
-      <c r="L14" s="6" t="n">
-        <v>61054</v>
-      </c>
-      <c r="M14" s="6" t="n">
-        <v>42403</v>
-      </c>
-      <c r="N14" s="6" t="n">
-        <v>42508</v>
-      </c>
-      <c r="O14" s="6" t="n">
-        <v>45390</v>
-      </c>
-      <c r="P14" s="6" t="n">
-        <v>25698</v>
-      </c>
-      <c r="Q14" s="6" t="n">
-        <v>30331</v>
-      </c>
-      <c r="R14" s="6" t="n">
-        <v>19368</v>
-      </c>
-      <c r="S14" s="6" t="n">
-        <v>9501</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>Gain/(loss) on sale of debt securities</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="n"/>
-      <c r="C15" s="6" t="n"/>
-      <c r="D15" s="6" t="n"/>
-      <c r="E15" s="6" t="n"/>
-      <c r="F15" s="6" t="n"/>
-      <c r="G15" s="6" t="n"/>
-      <c r="H15" s="6" t="n"/>
-      <c r="I15" s="6" t="n"/>
-      <c r="J15" s="6" t="n"/>
-      <c r="K15" s="6" t="n"/>
-      <c r="L15" s="6" t="n"/>
-      <c r="M15" s="6" t="n">
-        <v>-3</v>
-      </c>
-      <c r="N15" s="6" t="n">
-        <v>-436</v>
-      </c>
-      <c r="O15" s="6" t="n">
-        <v>-23</v>
-      </c>
-      <c r="P15" s="6" t="n">
-        <v>-1298</v>
-      </c>
-      <c r="Q15" s="6" t="n">
-        <v>-190</v>
-      </c>
-      <c r="R15" s="6" t="n">
-        <v>534</v>
-      </c>
-      <c r="S15" s="6" t="n">
-        <v>2495</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>Profit on sale of impaired loan</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="n"/>
-      <c r="C16" s="6" t="n"/>
-      <c r="D16" s="6" t="n"/>
-      <c r="E16" s="6" t="n"/>
-      <c r="F16" s="6" t="n"/>
-      <c r="G16" s="6" t="n"/>
-      <c r="H16" s="6" t="n"/>
-      <c r="I16" s="6" t="n"/>
-      <c r="J16" s="6" t="n"/>
-      <c r="K16" s="6" t="n"/>
-      <c r="L16" s="6" t="n"/>
-      <c r="M16" s="6" t="n"/>
-      <c r="N16" s="6" t="n">
-        <v>2158</v>
-      </c>
-      <c r="O16" s="6" t="n"/>
-      <c r="P16" s="6" t="n"/>
-      <c r="Q16" s="6" t="n"/>
-      <c r="R16" s="6" t="n"/>
-      <c r="S16" s="6" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>Non-interest income</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="n">
-        <v>129254</v>
-      </c>
-      <c r="C17" s="5" t="n">
-        <v>114114</v>
-      </c>
-      <c r="D17" s="5" t="n">
-        <v>123704</v>
-      </c>
-      <c r="E17" s="5" t="n">
-        <v>98697</v>
-      </c>
-      <c r="F17" s="5" t="n">
-        <v>87787</v>
-      </c>
-      <c r="G17" s="5" t="n">
-        <v>83974</v>
-      </c>
-      <c r="H17" s="5" t="n">
-        <v>75353</v>
-      </c>
-      <c r="I17" s="5" t="n">
-        <v>76391</v>
-      </c>
-      <c r="J17" s="5" t="n">
-        <v>57348</v>
-      </c>
-      <c r="K17" s="5" t="n">
-        <v>57967</v>
-      </c>
-      <c r="L17" s="5" t="n">
-        <v>64047</v>
-      </c>
-      <c r="M17" s="5" t="n">
-        <v>43087</v>
-      </c>
-      <c r="N17" s="5" t="n">
-        <v>45610</v>
-      </c>
-      <c r="O17" s="5" t="n">
-        <v>45577</v>
-      </c>
-      <c r="P17" s="5" t="n">
-        <v>21393</v>
-      </c>
-      <c r="Q17" s="5" t="n">
-        <v>28091</v>
-      </c>
-      <c r="R17" s="5" t="n">
-        <v>18024</v>
-      </c>
-      <c r="S17" s="5" t="n">
-        <v>9597</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>Total income</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="n">
-        <v>188290</v>
-      </c>
-      <c r="C18" s="5" t="n">
-        <v>187263</v>
-      </c>
-      <c r="D18" s="5" t="n">
-        <v>206185</v>
-      </c>
-      <c r="E18" s="5" t="n">
-        <v>150380</v>
-      </c>
-      <c r="F18" s="5" t="n">
-        <v>124048</v>
-      </c>
-      <c r="G18" s="5" t="n">
-        <v>120103</v>
-      </c>
-      <c r="H18" s="5" t="n">
-        <v>115237</v>
-      </c>
-      <c r="I18" s="5" t="n">
-        <v>114561</v>
-      </c>
-      <c r="J18" s="5" t="n">
-        <v>94483</v>
-      </c>
-      <c r="K18" s="5" t="n">
-        <v>91182</v>
-      </c>
-      <c r="L18" s="5" t="n">
-        <v>94921</v>
-      </c>
-      <c r="M18" s="5" t="n">
-        <v>71621</v>
-      </c>
-      <c r="N18" s="5" t="n">
-        <v>70399</v>
-      </c>
-      <c r="O18" s="5" t="n">
-        <v>63937</v>
-      </c>
-      <c r="P18" s="5" t="n">
-        <v>37367</v>
-      </c>
-      <c r="Q18" s="5" t="n">
-        <v>46562</v>
-      </c>
-      <c r="R18" s="5" t="n">
-        <v>34523</v>
-      </c>
-      <c r="S18" s="5" t="n">
-        <v>31732</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="n"/>
-      <c r="C19" s="6" t="n"/>
-      <c r="D19" s="6" t="n"/>
-      <c r="E19" s="6" t="n"/>
-      <c r="F19" s="6" t="n"/>
-      <c r="G19" s="6" t="n"/>
-      <c r="H19" s="6" t="n"/>
-      <c r="I19" s="6" t="n"/>
-      <c r="J19" s="6" t="n"/>
-      <c r="K19" s="6" t="n"/>
-      <c r="L19" s="6" t="n"/>
-      <c r="M19" s="6" t="n"/>
-      <c r="N19" s="6" t="n"/>
-      <c r="O19" s="6" t="n"/>
-      <c r="P19" s="6" t="n"/>
-      <c r="Q19" s="6" t="n"/>
-      <c r="R19" s="6" t="n"/>
-      <c r="S19" s="6" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>Staff costs</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="n">
-        <v>-86079</v>
-      </c>
-      <c r="C20" s="6" t="n">
-        <v>-72194</v>
-      </c>
-      <c r="D20" s="6" t="n">
-        <v>-68058</v>
-      </c>
-      <c r="E20" s="6" t="n">
-        <v>-59208</v>
-      </c>
-      <c r="F20" s="6" t="n">
-        <v>-50154</v>
-      </c>
-      <c r="G20" s="6" t="n">
-        <v>-47607</v>
-      </c>
-      <c r="H20" s="6" t="n">
-        <v>-47279</v>
-      </c>
-      <c r="I20" s="6" t="n">
-        <v>-41868</v>
-      </c>
-      <c r="J20" s="6" t="n">
-        <v>-41365</v>
-      </c>
-      <c r="K20" s="6" t="n">
-        <v>-32821</v>
-      </c>
-      <c r="L20" s="6" t="n">
-        <v>-29500</v>
-      </c>
-      <c r="M20" s="6" t="n">
-        <v>-30178</v>
-      </c>
-      <c r="N20" s="6" t="n">
-        <v>-24489</v>
-      </c>
-      <c r="O20" s="6" t="n">
-        <v>-19227</v>
-      </c>
-      <c r="P20" s="6" t="n">
-        <v>-16203</v>
-      </c>
-      <c r="Q20" s="6" t="n">
-        <v>-13759</v>
-      </c>
-      <c r="R20" s="6" t="n">
-        <v>-11761</v>
-      </c>
-      <c r="S20" s="6" t="n">
-        <v>-11629</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>Other expenses</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="n">
-        <v>-10029</v>
-      </c>
-      <c r="C21" s="6" t="n">
-        <v>-9735</v>
-      </c>
-      <c r="D21" s="6" t="n">
-        <v>-9543</v>
-      </c>
-      <c r="E21" s="6" t="n">
-        <v>-9818</v>
-      </c>
-      <c r="F21" s="6" t="n">
-        <v>-8924</v>
-      </c>
-      <c r="G21" s="6" t="n">
-        <v>-18816</v>
-      </c>
-      <c r="H21" s="6" t="n">
-        <v>-23048</v>
-      </c>
-      <c r="I21" s="6" t="n">
-        <v>-7857</v>
-      </c>
-      <c r="J21" s="6" t="n">
-        <v>-7870</v>
-      </c>
-      <c r="K21" s="6" t="n">
-        <v>-6914</v>
-      </c>
-      <c r="L21" s="6" t="n">
-        <v>-6544</v>
-      </c>
-      <c r="M21" s="6" t="n">
-        <v>-6402</v>
-      </c>
-      <c r="N21" s="6" t="n">
-        <v>-4987</v>
-      </c>
-      <c r="O21" s="6" t="n">
-        <v>-5779</v>
-      </c>
-      <c r="P21" s="6" t="n">
-        <v>-4657</v>
-      </c>
-      <c r="Q21" s="6" t="n">
-        <v>-4044</v>
-      </c>
-      <c r="R21" s="6" t="n">
-        <v>-3702</v>
-      </c>
-      <c r="S21" s="6" t="n">
-        <v>-5767</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>Depreciation of plant and equipment</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="n">
-        <v>-1870</v>
-      </c>
-      <c r="C22" s="6" t="n">
-        <v>-1540</v>
-      </c>
-      <c r="D22" s="6" t="n">
-        <v>-1572</v>
-      </c>
-      <c r="E22" s="6" t="n">
-        <v>-1462</v>
-      </c>
-      <c r="F22" s="6" t="n">
-        <v>-1802</v>
-      </c>
-      <c r="G22" s="6" t="n">
-        <v>-2342</v>
-      </c>
-      <c r="H22" s="6" t="n">
-        <v>-2498</v>
-      </c>
-      <c r="I22" s="6" t="n">
-        <v>-691</v>
-      </c>
-      <c r="J22" s="6" t="n">
-        <v>-794</v>
-      </c>
-      <c r="K22" s="6" t="n">
-        <v>-918</v>
-      </c>
-      <c r="L22" s="6" t="n">
-        <v>-965</v>
-      </c>
-      <c r="M22" s="6" t="n">
-        <v>-859</v>
-      </c>
-      <c r="N22" s="6" t="n">
-        <v>-831</v>
-      </c>
-      <c r="O22" s="6" t="n">
-        <v>-589</v>
-      </c>
-      <c r="P22" s="6" t="n">
-        <v>-507</v>
-      </c>
-      <c r="Q22" s="6" t="n">
-        <v>-516</v>
-      </c>
-      <c r="R22" s="6" t="n">
-        <v>-496</v>
-      </c>
-      <c r="S22" s="6" t="n">
-        <v>-292</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>Amortisation of intangible assets</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="n">
-        <v>-161</v>
-      </c>
-      <c r="C23" s="6" t="n">
-        <v>-104</v>
-      </c>
-      <c r="D23" s="6" t="n">
-        <v>-52</v>
-      </c>
-      <c r="E23" s="6" t="n">
-        <v>-271</v>
-      </c>
-      <c r="F23" s="6" t="n">
-        <v>-237</v>
-      </c>
-      <c r="G23" s="6" t="n">
-        <v>-256</v>
-      </c>
-      <c r="H23" s="6" t="n">
-        <v>-100</v>
-      </c>
-      <c r="I23" s="6" t="n">
-        <v>-53</v>
-      </c>
-      <c r="J23" s="6" t="n">
-        <v>-45</v>
-      </c>
-      <c r="K23" s="6" t="n">
-        <v>-144</v>
-      </c>
-      <c r="L23" s="6" t="n">
-        <v>-146</v>
-      </c>
-      <c r="M23" s="6" t="n">
-        <v>-129</v>
-      </c>
-      <c r="N23" s="6" t="n">
-        <v>-47</v>
-      </c>
-      <c r="O23" s="6" t="n">
-        <v>-105</v>
-      </c>
-      <c r="P23" s="6" t="n">
-        <v>-160</v>
-      </c>
-      <c r="Q23" s="6" t="n">
-        <v>-161</v>
-      </c>
-      <c r="R23" s="6" t="n">
-        <v>-106</v>
-      </c>
-      <c r="S23" s="6" t="n">
-        <v>-84</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>Total operating expenses (sum of Staff costs + Other expenses + Depreciation + Amortisation - excludes credit loss provisions and subsidiary items per standard cost-to-income convention, not itself a printed AR subtotal)</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="n">
-        <v>-98139</v>
-      </c>
-      <c r="C24" s="5" t="n">
-        <v>-83573</v>
-      </c>
-      <c r="D24" s="5" t="n">
-        <v>-79225</v>
-      </c>
-      <c r="E24" s="5" t="n">
-        <v>-70759</v>
-      </c>
-      <c r="F24" s="5" t="n">
-        <v>-61117</v>
-      </c>
-      <c r="G24" s="5" t="n">
-        <v>-69021</v>
-      </c>
-      <c r="H24" s="5" t="n">
-        <v>-72925</v>
-      </c>
-      <c r="I24" s="5" t="n">
-        <v>-50469</v>
-      </c>
-      <c r="J24" s="5" t="n">
-        <v>-50074</v>
-      </c>
-      <c r="K24" s="5" t="n">
-        <v>-40797</v>
-      </c>
-      <c r="L24" s="5" t="n">
-        <v>-37155</v>
-      </c>
-      <c r="M24" s="5" t="n">
-        <v>-37568</v>
-      </c>
-      <c r="N24" s="5" t="n">
-        <v>-30354</v>
-      </c>
-      <c r="O24" s="5" t="n">
-        <v>-25700</v>
-      </c>
-      <c r="P24" s="5" t="n">
-        <v>-21527</v>
-      </c>
-      <c r="Q24" s="5" t="n">
-        <v>-18480</v>
-      </c>
-      <c r="R24" s="5" t="n">
-        <v>-16065</v>
-      </c>
-      <c r="S24" s="5" t="n">
-        <v>-17772</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t>Credit/(provision) for expected credit losses</t>
-        </is>
-      </c>
-      <c r="B25" s="6" t="n">
-        <v>217</v>
-      </c>
-      <c r="C25" s="6" t="n">
-        <v>3953</v>
-      </c>
-      <c r="D25" s="6" t="n">
-        <v>11235</v>
-      </c>
-      <c r="E25" s="6" t="n">
-        <v>11526</v>
-      </c>
-      <c r="F25" s="6" t="n">
-        <v>-23665</v>
-      </c>
-      <c r="G25" s="6" t="n">
-        <v>-3172</v>
-      </c>
-      <c r="H25" s="6" t="n">
-        <v>-377</v>
-      </c>
-      <c r="I25" s="6" t="n">
-        <v>458</v>
-      </c>
-      <c r="J25" s="6" t="n">
-        <v>187</v>
-      </c>
-      <c r="K25" s="6" t="n">
-        <v>-527</v>
-      </c>
-      <c r="L25" s="6" t="n">
-        <v>155</v>
-      </c>
-      <c r="M25" s="6" t="n">
-        <v>-722</v>
-      </c>
-      <c r="N25" s="6" t="n">
-        <v>-60</v>
-      </c>
-      <c r="O25" s="6" t="n">
-        <v>-4455</v>
-      </c>
-      <c r="P25" s="6" t="n">
-        <v>-8272</v>
-      </c>
-      <c r="Q25" s="6" t="n">
-        <v>-35</v>
-      </c>
-      <c r="R25" s="6" t="n">
-        <v>-1827</v>
-      </c>
-      <c r="S25" s="6" t="n">
-        <v>-9386</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t>Impairment of investment in subsidiary</t>
-        </is>
-      </c>
-      <c r="B26" s="6" t="n"/>
-      <c r="C26" s="6" t="n"/>
-      <c r="D26" s="6" t="n"/>
-      <c r="E26" s="6" t="n"/>
-      <c r="F26" s="6" t="n"/>
-      <c r="G26" s="6" t="n"/>
-      <c r="H26" s="6" t="n"/>
-      <c r="I26" s="6" t="n"/>
-      <c r="J26" s="6" t="n"/>
-      <c r="K26" s="6" t="n"/>
-      <c r="L26" s="6" t="n"/>
-      <c r="M26" s="6" t="n"/>
-      <c r="N26" s="6" t="n"/>
-      <c r="O26" s="6" t="n"/>
-      <c r="P26" s="6" t="n">
-        <v>-31432</v>
-      </c>
-      <c r="Q26" s="6" t="n">
-        <v>-8432</v>
-      </c>
-      <c r="R26" s="6" t="n"/>
-      <c r="S26" s="6" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>Gain/(loss) on disposal of subsidiary</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="n"/>
-      <c r="C27" s="6" t="n"/>
-      <c r="D27" s="6" t="n"/>
-      <c r="E27" s="6" t="n"/>
-      <c r="F27" s="6" t="n"/>
-      <c r="G27" s="6" t="n"/>
-      <c r="H27" s="6" t="n"/>
-      <c r="I27" s="6" t="n"/>
-      <c r="J27" s="6" t="n"/>
-      <c r="K27" s="6" t="n"/>
-      <c r="L27" s="6" t="n">
-        <v>-1707</v>
-      </c>
-      <c r="M27" s="6" t="n"/>
-      <c r="N27" s="6" t="n">
-        <v>1632</v>
-      </c>
-      <c r="O27" s="6" t="n">
-        <v>-1074</v>
-      </c>
-      <c r="P27" s="6" t="n"/>
-      <c r="Q27" s="6" t="n"/>
-      <c r="R27" s="6" t="n"/>
-      <c r="S27" s="6" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>Profit before income tax</t>
-        </is>
-      </c>
-      <c r="B28" s="5" t="n">
-        <v>90368</v>
-      </c>
-      <c r="C28" s="5" t="n">
-        <v>107643</v>
-      </c>
-      <c r="D28" s="5" t="n">
-        <v>138195</v>
-      </c>
-      <c r="E28" s="5" t="n">
-        <v>91147</v>
-      </c>
-      <c r="F28" s="5" t="n">
-        <v>39266</v>
-      </c>
-      <c r="G28" s="5" t="n">
-        <v>47910</v>
-      </c>
-      <c r="H28" s="5" t="n">
-        <v>41935</v>
-      </c>
-      <c r="I28" s="5" t="n">
-        <v>64550</v>
-      </c>
-      <c r="J28" s="5" t="n">
-        <v>44596</v>
-      </c>
-      <c r="K28" s="5" t="n">
-        <v>49858</v>
-      </c>
-      <c r="L28" s="5" t="n">
-        <v>56214</v>
-      </c>
-      <c r="M28" s="5" t="n">
-        <v>33331</v>
-      </c>
-      <c r="N28" s="5" t="n">
-        <v>41617</v>
-      </c>
-      <c r="O28" s="5" t="n">
-        <v>32708</v>
-      </c>
-      <c r="P28" s="5" t="n">
-        <v>-23864</v>
-      </c>
-      <c r="Q28" s="5" t="n">
-        <v>19615</v>
-      </c>
-      <c r="R28" s="5" t="n">
-        <v>16631</v>
-      </c>
-      <c r="S28" s="5" t="n">
-        <v>4574</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>Income tax expense</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="n">
-        <v>-21437</v>
-      </c>
-      <c r="C29" s="6" t="n">
-        <v>-23726</v>
-      </c>
-      <c r="D29" s="6" t="n">
-        <v>-34982</v>
-      </c>
-      <c r="E29" s="6" t="n">
-        <v>-22583</v>
-      </c>
-      <c r="F29" s="6" t="n">
-        <v>-7788</v>
-      </c>
-      <c r="G29" s="6" t="n">
-        <v>-12745</v>
-      </c>
-      <c r="H29" s="6" t="n">
-        <v>-9830</v>
-      </c>
-      <c r="I29" s="6" t="n">
-        <v>-13427</v>
-      </c>
-      <c r="J29" s="6" t="n">
-        <v>-12532</v>
-      </c>
-      <c r="K29" s="6" t="n">
-        <v>-14168</v>
-      </c>
-      <c r="L29" s="6" t="n">
-        <v>-10764</v>
-      </c>
-      <c r="M29" s="6" t="n">
-        <v>-7376</v>
-      </c>
-      <c r="N29" s="6" t="n">
-        <v>-9744</v>
-      </c>
-      <c r="O29" s="6" t="n">
-        <v>-8278</v>
-      </c>
-      <c r="P29" s="6" t="n">
-        <v>-2206</v>
-      </c>
-      <c r="Q29" s="6" t="n">
-        <v>-8836</v>
-      </c>
-      <c r="R29" s="6" t="n">
-        <v>-4071</v>
-      </c>
-      <c r="S29" s="6" t="n">
-        <v>-1562</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>Profit/(loss) for the year</t>
-        </is>
-      </c>
-      <c r="B30" s="5" t="n">
-        <v>68931</v>
-      </c>
-      <c r="C30" s="5" t="n">
-        <v>83917</v>
-      </c>
-      <c r="D30" s="5" t="n">
-        <v>103213</v>
-      </c>
-      <c r="E30" s="5" t="n">
-        <v>68564</v>
-      </c>
-      <c r="F30" s="5" t="n">
-        <v>31478</v>
-      </c>
-      <c r="G30" s="5" t="n">
-        <v>35165</v>
-      </c>
-      <c r="H30" s="5" t="n">
-        <v>32105</v>
-      </c>
-      <c r="I30" s="5" t="n">
-        <v>51123</v>
-      </c>
-      <c r="J30" s="5" t="n">
-        <v>32064</v>
-      </c>
-      <c r="K30" s="5" t="n">
-        <v>35690</v>
-      </c>
-      <c r="L30" s="5" t="n">
-        <v>45450</v>
-      </c>
-      <c r="M30" s="5" t="n">
-        <v>25955</v>
-      </c>
-      <c r="N30" s="5" t="n">
-        <v>31873</v>
-      </c>
-      <c r="O30" s="5" t="n">
-        <v>24430</v>
-      </c>
-      <c r="P30" s="5" t="n">
-        <v>-26070</v>
-      </c>
-      <c r="Q30" s="5" t="n">
-        <v>10779</v>
-      </c>
-      <c r="R30" s="5" t="n">
-        <v>12560</v>
-      </c>
-      <c r="S30" s="5" t="n">
-        <v>3012</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>Other comprehensive income</t>
-        </is>
-      </c>
-      <c r="B31" s="6" t="n"/>
-      <c r="C31" s="6" t="n"/>
-      <c r="D31" s="6" t="n"/>
-      <c r="E31" s="6" t="n"/>
-      <c r="F31" s="6" t="n"/>
-      <c r="G31" s="6" t="n"/>
-      <c r="H31" s="6" t="n"/>
-      <c r="I31" s="6" t="n"/>
-      <c r="J31" s="6" t="n"/>
-      <c r="K31" s="6" t="n"/>
-      <c r="L31" s="6" t="n"/>
-      <c r="M31" s="6" t="n"/>
-      <c r="N31" s="6" t="n"/>
-      <c r="O31" s="6" t="n"/>
-      <c r="P31" s="6" t="n"/>
-      <c r="Q31" s="6" t="n"/>
-      <c r="R31" s="6" t="n"/>
-      <c r="S31" s="6" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
           <t>Foreign currency translation</t>
         </is>
       </c>
@@ -10538,7 +10550,7 @@
         <v>-15142</v>
       </c>
     </row>
-    <row r="37" ht="180" customHeight="1">
+    <row r="37" ht="377" customHeight="1">
       <c r="A37" s="8" t="inlineStr">
         <is>
           <t>Sources - Bank of China (UK) Limited's own Income Statement / Statement of Comprehensive Income (Bank/solo basis), £'000, each year's own originally-published report:
@@ -10560,15 +10572,23 @@
 FY2010: Annual Report 2011's own FY2010 comparative column, p.22-23 - https://pic.bankofchina.com/bocappd/uk/201301/P020130110394685934112.pdf (AR2010_URL note: the Bank's own FY2010 Annual Report PDF is a scanned/photocopied document (Canon iR-ADV C5045 scanner output, the same scanner/pattern as FY2014's own PDF) with no extractable text layer. FY2010 figures on every sheet are therefore taken from the FY2011 Annual Report's own FY2010 comparative column instead (a real, live, text-searchable document), the same each-year's-own-report-one-year-removed methodology used for FY2014 via AR2015.)
 FY2009: 2009 Report and Financial Statements, p.28-29 - https://pic.bankofchina.com/bocappd/uk/201109/P020110901339600023124.pdf
 FY2008: 2009 Report's own FY2008 comparative column, p.28-29 - https://pic.bankofchina.com/bocappd/uk/201109/P020110901339600023124.pdf, cross-checked against the Bank's own 2008 Report and Financial Statements (Income Statement, p.28) - https://pic.bankofchina.com/bocappd/uk/201109/P020110901339400504145.pdf (figures identical). FY2008 period note: Bank of China (UK) Limited's first accounting period ran 1 April 2007 - 30 September 2007 (a 6-month stub, outside this workbook's scope), and its second and only 'FY2008' statutory period is genuinely a 15-month period from 1 October 2007 to 31 December 2008 (the year-end was moved to December during this period) - not a standard 12-month year. Both the Bank's own FY2008 Report and Financial Statements (AR2008_URL) and the FY2009 Report's own FY2008 comparative column (AR2009_URL) show this identical 15-month figure set, cross-checked and tying exactly. Shown here as 'FY2008' per this workbook's year-labelling convention, but flagged as non-comparable in length to every other year in this workbook - growth trends spanning the FY2008/FY2009 boundary should be read with that caveat.
-HD-075 extension presentation notes (FY2008-FY2013): FY2008-FY2012 present a single 'Net gain/(loss) on derivative financial instruments' line (its own row here) instead of the 'Net fair value gain/(loss) on financial instruments' concept first used from FY2013 onward - both blank in the years the other applies, not force-mapped together. FY2013's own P&amp;L shows one-off 'Loss on sale of debt securities' (-£436k) and 'Profit on sale of impaired loan' (+£2,158k) as separate lines; FY2012's 'Loss on disposal of subsidiary' (-£1,074k) reverses to a one-off '+£1,632k' gain in FY2013 (own row, renamed 'Gain/(loss) on disposal of subsidiary' to accommodate both signs across the years it appears). FY2010-FY2011 show a one-off 'Impairment of investment in subsidiary' expense (£8,432k / £31,432k respectively, its own row) relating to the same UK subsidiary later disposed of in FY2012. FY2009-FY2008's 'Other expenses' row is labelled 'Administration and general expenses' in both years' own reports (same concept, folded into this row for consistency with FY2010 onward). Every FY2008-FY2013 year's Other Comprehensive Income is a single combined available-for-sale fair-value movement (net of tax), consistent with the existing FY2014-FY2017 row.
+HD-075 extension presentation notes (FY2008-FY2013): FY2008-FY2012 present a single 'Net gain/(loss) on derivative financial instruments' line (its own row here) instead of the 'Net fair value gain/(loss) on financial instruments' concept first used from FY2013 onward - both blank in the years the other applies, not force-mapped together. FY2013's own P&amp;L shows one-off 'Loss on sale of debt securities' (-£436k) and 'Profit on sale of impaired loan' (+£2,158k) as separate lines; FY2012's 'Loss on disposal of subsidiary' (-£1,074k) reverses to a one-off '+£1,632k' gain in FY2013 (own row, renamed 'Gain/(loss) on disposal of subsidiary' to accommodate both signs across the years it appears). FY2010-FY2011 show a one-off 'Impairment of investment in subsidiary' expense (£8,432k / £31,432k respectively, its own row) relating to the same UK subsidiary later disposed of in FY2012. FY2009-FY2008's 'Other expenses' row is labelled 'Administration and general expenses' in both years' own reports (same concept, folded into this row for consistency with FY2010 onward). Every FY2008-FY2013 year's Other Comprehensive Income is a single combined available-for-sale fair-value movement (net of tax), consistent with the existing FY2014-FY2017 row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="180" customHeight="1">
+      <c r="A39" s="8" t="inlineStr">
+        <is>
+          <t>(continued)
 Profit before income tax ties exactly to the Cash Flow Statement's own 'Profit before income tax' row for every year, cross-checked as a reconciliation. Presentation notes: FY2014's Income Statement splits 'Interest income' into 'Interest income from financial investments' + 'Other interest income' sub-lines through FY2020 (summed into the single 'Interest income' row here to match FY2021 onward's presentation - e.g. FY2014's £654k + £25,428k = £26,082k). FY2014's own P&amp;L shows a one-off £3k 'Loss on sale of debt securities' (its own row here, income section); FY2015's own P&amp;L shows a separate one-off £1,707k 'Loss on disposal of subsidiary' (its own row here, expenses section, immediately before Profit before income tax) - neither recurs in any other year. Other comprehensive income was governed by IAS 39's 'available for sale financial assets' fair-value reserve through FY2017 (its own row here) before the 1 January 2018 IFRS 9 transition removed the AFS category entirely (FY2018/FY2019 OCI is genuinely nil); the 'Foreign currency translation' OCI item used FY2021 onward first appears at FY2020 (a different, unrelated OCI component, not a renamed AFS reserve) - both rows are blank in the years the other applies, not force-matched.
 Entity note: Bank of China (UK) Limited (company 06193060, FRN 467410) is a wholly-owned UK subsidiary of Bank of China Limited (state-owned). It does not take the FRS 101/102 cash-flow-statement exemption - a full Statement of Cash Flows is published every year. All figures are the Bank's own solo entity basis throughout.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A37:S37"/>
+    <mergeCell ref="A39:S39"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10580,7 +10600,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G92"/>
+  <dimension ref="A1:G94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -12624,7 +12644,7 @@
         <v>399013</v>
       </c>
     </row>
-    <row r="92" ht="190" customHeight="1">
+    <row r="92" ht="390" customHeight="1">
       <c r="A92" s="8" t="inlineStr">
         <is>
           <t>Sources - Bank of China (UK) Limited's own Statement of Changes in Equity (Bank/solo basis), £'000, chronological roll-forward reconstructed from each year's own originally-published report:
@@ -12634,7 +12654,14 @@
 2011 movements: Annual Report 2011, p.25 - https://pic.bankofchina.com/bocappd/uk/201301/P020130110394685934112.pdf
 2012 movements: Annual Report 2012, p.25 (includes the £110,000k ordinary share issue that took share capital from £140,000k to £250,000k) - https://pic.bankofchina.com/bocappd/uk/201312/P020131213310466908739.pdf
 2013 movements: Annual Report and Financial Statements 2013, p.18 - https://pic.bankofchina.com/bocappd/uk/201505/P020150504339499661074.pdf (AR2013_URL note: the Bank's own FY2013 Annual Report PDF is a scanned/photocopied document (Xerox WorkCentre 5665 scanner output) with no extractable text layer, the same pattern HD-046 found on FY2014's own PDF. Unlike FY2014 (where a later year's clean comparative column exists), FY2014's own PDF is itself unreadable, so no clean comparative source exists for FY2013 either - FY2013 figures here were instead OCR'd directly off this scanned PDF (ocrmypdf --force-ocr + tesseract), then cross-checked two ways: (1) the resulting FY2013 closing equity/balance-sheet/cash-flow figures tie out internally (assets = liabilities + equity; operating + investing + financing cash flows = the disclosed net movement; opening + net movement = closing cash) and (2) the OCR'd FY2013 closing Statement of Changes in Equity figures match this workbook's own pre-existing FY2014 opening balance exactly (250,000 / 56,831 / 843 / 307,674), which was itself sourced independently via AR2015's FY2014 comparative column under HD-046. Several individual OCR digit errors were caught and corrected via these tie-outs (e.g. 'Interest income from financial investments' misread as 4,294 instead of 1,294, 'Total assets' misread as 4,050,075 instead of 1,050,075 - a recurring 1-to-4 OCR confusion in this particular scan).)
-2014 movements: Financial Statements 2015's own FY2014 comparative, p.17 - https://pic.bankofchina.com/bocappd/uk/201606/P020160620504225340480.pdf (AR2014_URL note: the Bank's own FY2014 Annual Report PDF is a scanned/photocopied document (Canon iR-ADV C5045 scanner output) with no extractable text layer - pdftotext and qpdf both confirm zero recoverable text after a repair pass. FY2014 figures on every sheet are therefore taken from the FY2015 Annual Report's own FY2014 comparative column instead (a real, live, text-searchable document), the same each-year's-own-report methodology used everywhere else in this workbook, just one year removed since FY2014's own PDF cannot be read as text.)
+2014 movements: Financial Statements 2015's own FY2014 comparative, p.17 - https://pic.bankofchina.com/bocappd/uk/201606/P020160620504225340480.pdf (AR2014_URL note: the Bank's own FY2014 Annual Report PDF is a scanned/photocopied document (Canon iR-ADV C5045 scanner output) with no extractable text layer - pdftotext and qpdf both confirm zero recoverable text after a repair pass. FY2014 figures on every sheet are therefore taken from the FY2015 Annual Report's own FY2014 comparative column instead (a real, live, text-searchable document), the same each-year's-own-report methodology used everywhere else in this workbook, just one year removed since FY2014's own PDF cannot be read as text.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="325" customHeight="1">
+      <c r="A94" s="8" t="inlineStr">
+        <is>
+          <t>(continued)
 2015 movements: Financial Statements 2015, p.17 - https://pic.bankofchina.com/bocappd/uk/201606/P020160620504225340480.pdf
 2016 movements: Financial Statements 2016, p.20 - https://pic.bankofchina.com/bocappd/uk/201706/P020170627373089457851.pdf
 2017 movements: Financial Statements 2017, p.25 - https://pic.bankofchina.com/bocappd/uk/201805/P020180517534275167127.pdf
@@ -12652,8 +12679,9 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A92:G92"/>
+    <mergeCell ref="A94:G94"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12665,7 +12693,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S70"/>
+  <dimension ref="A1:S72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="72" customWidth="1" min="1" max="1"/>
@@ -15483,7 +15511,7 @@
         <v>40069</v>
       </c>
     </row>
-    <row r="70" ht="210" customHeight="1">
+    <row r="70" ht="377" customHeight="1">
       <c r="A70" s="8" t="inlineStr">
         <is>
           <t>Sources - all figures are Bank of China (UK) Limited's own Statement of Cash Flows, £'000, as published on the Bank's own site (each year's own originally-published report, not a later restated comparative):
@@ -15505,7 +15533,14 @@
 FY2010: Annual Report 2011's own FY2010 comparative column, p.26 - https://pic.bankofchina.com/bocappd/uk/201301/P020130110394685934112.pdf (AR2010_URL note: the Bank's own FY2010 Annual Report PDF is a scanned/photocopied document (Canon iR-ADV C5045 scanner output, the same scanner/pattern as FY2014's own PDF) with no extractable text layer. FY2010 figures on every sheet are therefore taken from the FY2011 Annual Report's own FY2010 comparative column instead (a real, live, text-searchable document), the same each-year's-own-report-one-year-removed methodology used for FY2014 via AR2015.)
 FY2009: 2009 Report and Financial Statements, p.33 - https://pic.bankofchina.com/bocappd/uk/201109/P020110901339600023124.pdf
 FY2008: 2009 Report's own FY2008 comparative column, p.33 - https://pic.bankofchina.com/bocappd/uk/201109/P020110901339600023124.pdf, cross-checked against the Bank's own 2008 Report and Financial Statements (Statement of Cash Flows, p.31) - https://pic.bankofchina.com/bocappd/uk/201109/P020110901339400504145.pdf (figures identical). FY2008 period note: Bank of China (UK) Limited's first accounting period ran 1 April 2007 - 30 September 2007 (a 6-month stub, outside this workbook's scope), and its second and only 'FY2008' statutory period is genuinely a 15-month period from 1 October 2007 to 31 December 2008 (the year-end was moved to December during this period) - not a standard 12-month year. Both the Bank's own FY2008 Report and Financial Statements (AR2008_URL) and the FY2009 Report's own FY2008 comparative column (AR2009_URL) show this identical 15-month figure set, cross-checked and tying exactly. Shown here as 'FY2008' per this workbook's year-labelling convention, but flagged as non-comparable in length to every other year in this workbook - growth trends spanning the FY2008/FY2009 boundary should be read with that caveat.
-FY2008-FY2020 presentation note: through FY2020's own report, 'Dividend paid' and 'Interest paid' sit inside the operating-activities 'Adjustment for cash items' subsection (own rows here, labelled '...FY2008-FY2020 presentation' to distinguish them from the FY2021-onward financing-section rows of the same name, which are left blank for FY2008-FY2020 rather than merged into a single row spanning two different statement sections); 'Cash flows from financing activities' is genuinely nil every year FY2008-FY2019 and, in FY2020's own report, contains only the new lease-liability repayment line. FY2014's cash flow figure (£199,854k) was confirmed against the Balance Sheet's own internal subtotal arithmetic (see the Balance Sheet sheet's own source note, HD-081 2026-09-07) - the Balance Sheet's originally-transcribed £199,954k was a single-digit misread that broke its own 'Total assets' subtotal by £100k; every year's cash-flow closing balance ties exactly to that year's own Balance Sheet cash figure. Individual reconciling items were independently verified by summing each year's disclosed components back to that year's own reported 'Net cash generated from operating activities' total (all matched exactly), used as a correction check against several PDFs' garbled OCR text (e.g. FY2014's 'Acquisition of intangible assets' printed without its minus sign was resolved to -£426k this way).
+FY2008-FY2020 presentation note: through FY2020's own report, 'Dividend paid' and 'Interest paid' sit inside the operating-activities 'Adjustment for cash items' subsection (own rows here, labelled '...FY2008-FY2020 presentation' to distinguish them from the FY2021-onward financing-section rows of the same name, which are left blank for FY2008-FY2020 rather than merged into a single row spanning two different statement sections); 'Cash flows from financing activities' is genuinely nil every year FY2008-FY2019 and, in FY2020's own report, contains only the new lease-liability repayment line. FY2014's cash flow figure (£199,854k) was confirmed against the Balance Sheet's own internal subtotal arithmetic (see the Balance Sheet sheet's own source note, HD-081 2026-09-07) - the Balance Sheet's originally-transcribed £199,954k was a single-digit misread that broke its own 'Total assets' subtotal by £100k; every year's cash-flow closing balance ties exactly to that year's own Balance Sheet cash figure. Individual reconciling items were independently verified by summing each year's disclosed components back to that year's own reported 'Net cash generated from operating activities' total (all matched exactly), used as a correction check against several PDFs' garbled OCR text (e.g. FY2014's 'Acquisition of intangible assets' printed without its minus sign was resolved to -£426k this way).</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="210" customHeight="1">
+      <c r="A72" s="8" t="inlineStr">
+        <is>
+          <t>(continued)
 HD-075 extension presentation notes (FY2008-FY2013): FY2008-FY2009's own statements separately disclose 'Change in derivative assets/liabilities held for risk management' (folded into the FY2014+ 'Change in derivative financial instruments assets/liabilities' rows here); FY2010-FY2012 combine both into a single 'Change in derivatives held for risk management' line instead (its own row, not force-split). FY2012's own statement presents 'Proceeds from the issue of ordinary shares' (£110,000k, the same capital raise recorded on the Statement of Changes in Equity sheet) and 'Investment in subsidiaries' (£62,210k, the same-year subsidiary disposal) both under investing activities rather than financing (own rows, noting this year's presentation); FY2013's own restated FY2012 comparative instead splits the ordinary-share proceeds into financing activities - this workbook uses each year's own originally-published presentation throughout, per project convention, so FY2012's own figures stay under investing here. FY2013's own statement has no corresponding 'Loss/(gain) on disposal of subsidiary' cash-flow addback despite the Income Statement's one-off £1,632k gain that year - confirmed absent by full-text reading of the OCR'd document and by the fact that FY2013's own operating/investing/financing subtotals already tie exactly to its own disclosed opening/closing cash balances without one (see AR2013_SCAN_NOTE). FY2009's own statement includes a standalone 'Effects of exchange-rate changes on cash and cash equivalents' line (-£2,477k) between the net movement and closing balance, not present in any other year (own row). Every FY2008-FY2013 year's cash-flow closing balance ties exactly to that year's own Balance Sheet cash figure, and every operating/investing/financing subtotal for these 6 years was independently verified by full-component summation against each year's own disclosed net-movement and opening/closing balances (all matched exactly, including through the FY2013 OCR reconstruction).
 Restatement note: FY2023's own report marks its FY2022 comparative column 'Restated' and shows different figures (e.g. operating activities -£17,138k, closing cash £687,013k) to FY2022's own originally-published report (operating activities +£22,570k, closing cash £657,656k). This workbook uses each year's own originally-published figures as the primary column (project convention), which creates a genuine, disclosed £29,357k gap between FY2022's own closing balance and FY2023's own opening balance - flagged here rather than silently blended or force-reconciled. The underlying cause of the restatement is not explained in either source.
 Presentation notes: FY2021-FY2023 include small 'Exchange rate movements on plant and equipment/on equity' lines not present in FY2024/FY2025's statements. FY2022 alone shows a one-off Tier 2-to-AT1 capital replacement (subordinated debt of £60,000k repaid, an equal Additional Tier 1 instrument issued, both under financing activities). FY2025's own report split 'Change in financial assets at amortised cost/fair value' into two lines (the government-bond component shown separately) and separated lease-liability cash flows into principal and interest portions for the first time - both are FY2025-only presentational changes with no net impact on any section total. FY2025's own supplementary 'cash and cash equivalents comprise' note totals £1,073,245k (£157k less than the statement's own £1,073,402k closing balance), a gap matching the same page's separately-shown expected-credit-loss allowance of £157k - the statement's own total is used as the primary closing-balance figure here. FY2022's own report does not break out a separate 'Interest paid on Additional Tier 1 instrument' line (the AT1 instrument was only issued in June 2022); FY2023's restated FY2022 comparative does show one (£1,759k), consistent with the broader FY2022 restatement noted above - not included here since it wasn't part of FY2022's own originally-published statement.
@@ -15514,8 +15549,9 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A70:S70"/>
+    <mergeCell ref="A72:S72"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -16723,7 +16759,7 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="430" customHeight="1">
+    <row r="42" ht="409" customHeight="1">
       <c r="A42" s="8" t="inlineStr">
         <is>
           <t>Sources - Note 6(a) 'Analysis of risk concentration in the financial position' (Global/Europe/US/UK/UK Retail x Stage 1/2/3 geographic table), Bank/solo basis, £'000. By-product figures here are summed from that table's 'Loans and advances to customers' product rows (Wholesale/Housing/Syndicated/Factoring/Overdraft/Credit Cards/Mortgage/Financing Order) across all geography columns:
@@ -16761,7 +16797,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="72" customWidth="1" min="1" max="1"/>
@@ -17452,7 +17488,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="300" customHeight="1">
+    <row r="32" ht="390" customHeight="1">
       <c r="A32" s="8" t="inlineStr">
         <is>
           <t>Sources - Bank of China (UK) Limited Pillar 3 disclosures (UK KM1 Key Metrics template from FY2022 onward; FY2021's own document is narrative/ratio-only and predates the KM1 template; FY2014-FY2020 use the pre-KM1 CRD IV 'Table 1: Total capital resources and risk asset ratios' / 'Table 2: Leverage ratio' narrative-table format), £'000 unless stated:
@@ -17472,7 +17508,14 @@
 FY2014-FY2017 note: 'Tier 1 capital' equals 'CET1 capital' every year (£274,958k throughout - the Bank issued no AT1 instruments until far later) and 'Total capital' equals CET1 capital plus the £60,000k Tier 2 subordinated debt facility, both stated directly in each year's own Table 1. LCR and NSFR are genuinely undisclosed for FY2014-FY2016 (no LCR/HQLA/NSFR concept appears anywhere in those 3 documents, confirmed by reading each in full); FY2017's LCR ratio (167%) is not in FY2017's own document at all (confirmed absent) but appears as the FY2018 Pillar 3 document's own FY2017 comparative column, the earliest point any LCR figure for this bank exists - shown here with no £-breakdown since none is given for that comparative year. RWA breakdown by risk category (credit/market/operational/CVA) is genuinely undisclosed for FY2014-FY2018 (only the single aggregate RWA figure appears in each Table 1); the FY2020 Pillar 3 document introduces a full 'Table 9: Overview of risk weighted assets' (its own year plus its own FY2019 comparative column), the first and only such breakdown found across all 12 years covered.
 Entity note: Bank of China (UK) Limited (company 06193060, FRN 467410) is a wholly-owned UK subsidiary of Bank of China Limited (state-owned). It does not take the FRS 101/102 cash-flow-statement exemption - a full Statement of Cash Flows is published every year. All figures are the Bank's own solo entity basis throughout.
 KM1 presentation notes:
-• LATEST-EDITION CHECK 2026-09-16: the Bank's own disclosure index at https://www.bankofchina.com/uk/aboutus/ab5/ lists 'Pillar 3 Disclosure 31 December 2025' as its newest document, which is the one cited above. Checked, none newer.
+• LATEST-EDITION CHECK 2026-09-16: the Bank's own disclosure index at https://www.bankofchina.com/uk/aboutus/ab5/ lists 'Pillar 3 Disclosure 31 December 2025' as its newest document, which is the one cited above. Checked, none newer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="300" customHeight="1">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>(continued)
 • A BASEL ROW SET UNDER A UK KM1 HEADING. The table is headed 'UK KM1 - Key Metrics' (FY2022's edition: 'UK KM1 - Key metrics template'), but rows 8-11 are the BCBS buffer block and rows 13-14 are captioned 'Basel III leverage ratio exposure measure' / 'Basel III leverage ratio'. The PRA template's UK 7a-7d, UK 8a, UK 9a, UK 10a, UK 11a and UK 16a/16b rows appear in no edition. This sheet reproduces the Bank's row set and does not add the PRA rows back as blanks, because the Bank's table does not contain them.
 • ROW 16 IS PRINTED AS '6'. '6 Total net cash outflow' sits between rows 15 and 17 in the FY2022, FY2023, FY2024 and FY2025 documents alike. It is a persistent typo in the Bank's own template, checked in all four editions, and is reproduced rather than corrected.
 • ROW 12 CHANGED BASIS AND CAPTION IN FY2025, from 'CET1 available after meeting the bank's minimum Cap Req (%)' to 'CET1 available after meeting the total SREP own funds requirements (%)'. The FY2025 edition restates FY2024 as 19.5% on the new basis; the FY2024 edition printed 20.3% on the old one. The cell here carries 20.3%, that year's own edition, per this project's rule that each year comes from its own edition rather than a later comparative. Both figures are the Bank's; they are not reconciled. Every other row agrees exactly across overlapping editions.
@@ -17483,7 +17526,8 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
+    <mergeCell ref="A34:F34"/>
     <mergeCell ref="A32:F32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -17638,7 +17682,7 @@
         <v>274958</v>
       </c>
     </row>
-    <row r="6" ht="170" customHeight="1">
+    <row r="6" ht="299" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Sources - Bank of China (UK) Limited Pillar 3 disclosures (UK KM1 Key Metrics template from FY2022 onward; FY2021's own document is narrative/ratio-only and predates the KM1 template; FY2014-FY2020 use the pre-KM1 CRD IV 'Table 1: Total capital resources and risk asset ratios' / 'Table 2: Leverage ratio' narrative-table format), £'000 unless stated:
@@ -17840,7 +17884,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="170" customHeight="1">
+    <row r="6" ht="299" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Sources - Bank of China (UK) Limited Pillar 3 disclosures (UK KM1 Key Metrics template from FY2022 onward; FY2021's own document is narrative/ratio-only and predates the KM1 template; FY2014-FY2020 use the pre-KM1 CRD IV 'Table 1: Total capital resources and risk asset ratios' / 'Table 2: Leverage ratio' narrative-table format), £'000 unless stated:

--- a/banks/BANK OF CHINA UK FINANCIALS.xlsx
+++ b/banks/BANK OF CHINA UK FINANCIALS.xlsx
@@ -13,19 +13,20 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Statement of Changes in Equity" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flow Statement" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Asset Quality" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KM1 Key Metrics" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Capital" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Ratio" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Capital" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Ratio" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital Ratio" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total RWAs" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RWA Breakdown" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leverage Ratio" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LCR" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NSFR" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MREL Ratio" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Profitability" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KM1 Key Metrics" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Capital" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Ratio" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Capital" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Ratio" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital Ratio" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total RWAs" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RWA Breakdown" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leverage Ratio" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LCR" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NSFR" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MREL Ratio" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4326,7 +4327,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -4347,14 +4348,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Bank of China (UK) Limited — Tier 1 Capital</t>
+          <t>Bank of China (UK) Limited — CET1 Ratio</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>£'000</t>
+          <t>% of RWA</t>
         </is>
       </c>
     </row>
@@ -4428,55 +4429,72 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Tier 1 capital</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>334521</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>334294</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>335056</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>335000</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>275164</v>
-      </c>
-      <c r="G4" s="6" t="n">
-        <v>307058</v>
-      </c>
-      <c r="H4" s="6" t="n">
-        <v>274958</v>
-      </c>
-      <c r="I4" s="6" t="n">
-        <v>274958</v>
-      </c>
-      <c r="J4" s="6" t="n">
-        <v>274958</v>
-      </c>
-      <c r="K4" s="6" t="n">
-        <v>274958</v>
-      </c>
-      <c r="L4" s="6" t="n">
-        <v>274958</v>
-      </c>
-      <c r="M4" s="6" t="n">
-        <v>274958</v>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Note: Equal to CET1 capital every year FY2014-FY2021 (no AT1 instruments in issue until June 2022). A £60m Additional Tier 1 instrument was issued in June 2022, replacing an equal amount of Tier 2 subordinated debt.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="299" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
+          <t>Common Equity Tier 1 ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>27.2%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>24.8%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>26.8%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>23.4%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>24.6%</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>26.7%</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>27.8%</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>29.2%</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="K4" s="6" t="inlineStr">
+        <is>
+          <t>27%</t>
+        </is>
+      </c>
+      <c r="L4" s="6" t="inlineStr">
+        <is>
+          <t>31%</t>
+        </is>
+      </c>
+      <c r="M4" s="6" t="inlineStr">
+        <is>
+          <t>34%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="299" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Sources - Bank of China (UK) Limited Pillar 3 disclosures (UK KM1 Key Metrics template from FY2022 onward; FY2021's own document is narrative/ratio-only and predates the KM1 template; FY2014-FY2020 use the pre-KM1 CRD IV 'Table 1: Total capital resources and risk asset ratios' / 'Table 2: Leverage ratio' narrative-table format), £'000 unless stated:
 FY2025 &amp; FY2024 comparative: Pillar 3 Disclosure 31 December 2025, p.15 (UK KM1) - https://pic.bankofchina.com/bocappd/uk/202607/P020260716391457618567.pdf
@@ -4498,9 +4516,8 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A5:M5"/>
-    <mergeCell ref="A7:M7"/>
+  <mergeCells count="1">
+    <mergeCell ref="A6:M6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4533,14 +4550,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Bank of China (UK) Limited — Tier 1 Ratio</t>
+          <t>Bank of China (UK) Limited — Tier 1 Capital</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>% of RWA</t>
+          <t>£'000</t>
         </is>
       </c>
     </row>
@@ -4614,74 +4631,50 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Tier 1 ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>33.2%</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>30.2%</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>32.7%</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>28.5%</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>24.6%</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>26.7%</t>
-        </is>
-      </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>27.8%</t>
-        </is>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>29.2%</t>
-        </is>
-      </c>
-      <c r="J4" s="6" t="inlineStr">
-        <is>
-          <t>30%</t>
-        </is>
-      </c>
-      <c r="K4" s="6" t="inlineStr">
-        <is>
-          <t>27%</t>
-        </is>
-      </c>
-      <c r="L4" s="6" t="inlineStr">
-        <is>
-          <t>31%</t>
-        </is>
-      </c>
-      <c r="M4" s="6" t="inlineStr">
-        <is>
-          <t>34%</t>
-        </is>
+          <t>Tier 1 capital</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>334521</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>334294</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>335056</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>335000</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>275164</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>307058</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>274958</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>274958</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>274958</v>
+      </c>
+      <c r="K4" s="6" t="n">
+        <v>274958</v>
+      </c>
+      <c r="L4" s="6" t="n">
+        <v>274958</v>
+      </c>
+      <c r="M4" s="6" t="n">
+        <v>274958</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Note: Numerically equal to the CET1 ratio every year FY2014-FY2021 since Tier 1 capital equalled CET1 capital exactly (no AT1 in issue until June 2022); each year's own Table 1/KM1 document states this explicitly as its own 'Tier 1 capital ratio' line, not just inferred.</t>
+          <t>Note: Equal to CET1 capital every year FY2014-FY2021 (no AT1 instruments in issue until June 2022). A £60m Additional Tier 1 instrument was issued in June 2022, replacing an equal amount of Tier 2 subordinated debt.</t>
         </is>
       </c>
     </row>
@@ -4722,7 +4715,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -4743,14 +4736,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Bank of China (UK) Limited — Total Capital</t>
+          <t>Bank of China (UK) Limited — Tier 1 Ratio</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>£'000</t>
+          <t>% of RWA</t>
         </is>
       </c>
     </row>
@@ -4824,48 +4817,79 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total regulatory capital</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>334521</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>334294</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>335056</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>335000</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>335164</v>
-      </c>
-      <c r="G4" s="6" t="n">
-        <v>367058</v>
-      </c>
-      <c r="H4" s="6" t="n">
-        <v>334958</v>
-      </c>
-      <c r="I4" s="6" t="n">
-        <v>334958</v>
-      </c>
-      <c r="J4" s="6" t="n">
-        <v>334958</v>
-      </c>
-      <c r="K4" s="6" t="n">
-        <v>334958</v>
-      </c>
-      <c r="L4" s="6" t="n">
-        <v>334958</v>
-      </c>
-      <c r="M4" s="6" t="n">
-        <v>334958</v>
-      </c>
-    </row>
-    <row r="6" ht="299" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
+          <t>Tier 1 ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>33.2%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>30.2%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>32.7%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>28.5%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>24.6%</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>26.7%</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>27.8%</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>29.2%</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="K4" s="6" t="inlineStr">
+        <is>
+          <t>27%</t>
+        </is>
+      </c>
+      <c r="L4" s="6" t="inlineStr">
+        <is>
+          <t>31%</t>
+        </is>
+      </c>
+      <c r="M4" s="6" t="inlineStr">
+        <is>
+          <t>34%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Note: Numerically equal to the CET1 ratio every year FY2014-FY2021 since Tier 1 capital equalled CET1 capital exactly (no AT1 in issue until June 2022); each year's own Table 1/KM1 document states this explicitly as its own 'Tier 1 capital ratio' line, not just inferred.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="299" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Sources - Bank of China (UK) Limited Pillar 3 disclosures (UK KM1 Key Metrics template from FY2022 onward; FY2021's own document is narrative/ratio-only and predates the KM1 template; FY2014-FY2020 use the pre-KM1 CRD IV 'Table 1: Total capital resources and risk asset ratios' / 'Table 2: Leverage ratio' narrative-table format), £'000 unless stated:
 FY2025 &amp; FY2024 comparative: Pillar 3 Disclosure 31 December 2025, p.15 (UK KM1) - https://pic.bankofchina.com/bocappd/uk/202607/P020260716391457618567.pdf
@@ -4887,8 +4911,9 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A6:M6"/>
+  <mergeCells count="2">
+    <mergeCell ref="A5:M5"/>
+    <mergeCell ref="A7:M7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4921,14 +4946,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Bank of China (UK) Limited — Total Capital Ratio</t>
+          <t>Bank of China (UK) Limited — Total Capital</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>% of RWA</t>
+          <t>£'000</t>
         </is>
       </c>
     </row>
@@ -5002,68 +5027,44 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total capital ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>33.2%</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>30.2%</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>32.7%</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>28.5%</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>29.9%</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>31.9%</t>
-        </is>
-      </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>33.9%</t>
-        </is>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>35.6%</t>
-        </is>
-      </c>
-      <c r="J4" s="6" t="inlineStr">
-        <is>
-          <t>36%</t>
-        </is>
-      </c>
-      <c r="K4" s="6" t="inlineStr">
-        <is>
-          <t>33%</t>
-        </is>
-      </c>
-      <c r="L4" s="6" t="inlineStr">
-        <is>
-          <t>37%</t>
-        </is>
-      </c>
-      <c r="M4" s="6" t="inlineStr">
-        <is>
-          <t>42%</t>
-        </is>
+          <t>Total regulatory capital</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>334521</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>334294</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>335056</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>335000</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>335164</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>367058</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>334958</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>334958</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>334958</v>
+      </c>
+      <c r="K4" s="6" t="n">
+        <v>334958</v>
+      </c>
+      <c r="L4" s="6" t="n">
+        <v>334958</v>
+      </c>
+      <c r="M4" s="6" t="n">
+        <v>334958</v>
       </c>
     </row>
     <row r="6" ht="299" customHeight="1">
@@ -5097,6 +5098,208 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Bank of China (UK) Limited — Total Capital Ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>% of RWA</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>FY2017</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>FY2016</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>FY2015</t>
+        </is>
+      </c>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>FY2014</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Total capital ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>33.2%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>30.2%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>32.7%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>28.5%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>29.9%</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>31.9%</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>33.9%</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>35.6%</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>36%</t>
+        </is>
+      </c>
+      <c r="K4" s="6" t="inlineStr">
+        <is>
+          <t>33%</t>
+        </is>
+      </c>
+      <c r="L4" s="6" t="inlineStr">
+        <is>
+          <t>37%</t>
+        </is>
+      </c>
+      <c r="M4" s="6" t="inlineStr">
+        <is>
+          <t>42%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="299" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Sources - Bank of China (UK) Limited Pillar 3 disclosures (UK KM1 Key Metrics template from FY2022 onward; FY2021's own document is narrative/ratio-only and predates the KM1 template; FY2014-FY2020 use the pre-KM1 CRD IV 'Table 1: Total capital resources and risk asset ratios' / 'Table 2: Leverage ratio' narrative-table format), £'000 unless stated:
+FY2025 &amp; FY2024 comparative: Pillar 3 Disclosure 31 December 2025, p.15 (UK KM1) - https://pic.bankofchina.com/bocappd/uk/202607/P020260716391457618567.pdf
+FY2024 (own year) &amp; FY2023 comparative: Pillar 3 Disclosures 31 December 2024, p.16 (UK KM1) - https://www.bankofchina.com/uk/aboutus/ab5/202507/P020250718380587744231.pdf
+FY2023 (own year) &amp; FY2022 comparative: Pillar 3 disclosures 31 December 2023, p.14 (UK KM1) - https://www.bankofchina.com/uk/aboutus/ab5/202410/P020241008402737321677.pdf
+FY2022 (own year) &amp; FY2021 comparative: Pillar 3 Disclosures 2022, p.14 (UK KM1) - https://www.bankofchina.com/uk/aboutus/ab5/202310/P020231026347190320350.pdf
+FY2021 (own year, narrative/ratio-only - no KM1 template yet): Pillar 3 Disclosures 2021, p.12-14, 24 - https://www.bankofchina.com/uk/aboutus/ab5/202303/P020230315381669571541.pdf
+FY2021 note: the Bank's own FY2021 Pillar 3 document states CET1/Total Capital as rounded £275m/£335m and gives no £-breakdown for leverage exposure, LCR HQLA/outflow, or NSFR (NSFR was not yet a formal disclosure). The precise FY2021 figures used on those sheets (CET1/Tier 1 £275,164k, Total Capital £335,164k, leverage exposure £2,431,869k, LCR HQLA £527,697k/outflow £294,774k, NSFR £1,438,026k/£950,742k) are taken from the FY2022 Pillar 3 document's FY2021 comparative column instead, since it is the more complete disclosure - all overlapping ratios (CET1 24.6%, Total Capital 29.9%, Leverage 11.3%, LCR 179.0%) match the FY2021 document's own narrative figures exactly.
+FY2020 (own year) &amp; FY2019 comparative: Pillar 3 Disclosures 31 December 2020, Table 9 'Overview of risk weighted assets', p.20-22, Table 31 'Liquidity coverage ratio' - https://pic.bankofchina.com/bocappd/uk/202110/P020211027537761891740.pdf
+FY2019 (own year) &amp; FY2018 comparative: Pillar 3 Disclosures 31 December 2019, p.16-19, 33 - https://pic.bankofchina.com/bocappd/uk/202009/P020200909535865685853.pdf
+FY2018 (own year) &amp; FY2017 comparative: Pillar 3 Disclosures 31 December 2018, p.15-18, 31 - https://pic.bankofchina.com/bocappd/uk/201904/P020190410408108385209.pdf
+FY2017 (own year) &amp; FY2016 comparative: Pillar 3 Disclosures 2017, Table 1/Table 2, p.9-10 - https://pic.bankofchina.com/bocappd/uk/201803/P020180328577372288229.pdf
+FY2016 (own year) &amp; FY2015 comparative: Pillar 3 Disclosures 2016, Table 1/Table 2, p.10-11 - https://pic.bankofchina.com/bocappd/uk/201706/P020170627381103226068.pdf
+FY2015 (own year) &amp; FY2014 comparative: Pillar III Disclosures 2015, Table 1/Table 2, p.9-10 - https://pic.bankofchina.com/bocappd/uk/201606/P020160620504436264971.pdf
+FY2014 (own year) &amp; FY2013 comparative: Pillar III Disclosure 2014, Table 1/Table 2, p.8-9 - https://pic.bankofchina.com/bocappd/uk/201509/P020150910375228515274.pdf
+FY2014-FY2017 note: 'Tier 1 capital' equals 'CET1 capital' every year (£274,958k throughout - the Bank issued no AT1 instruments until far later) and 'Total capital' equals CET1 capital plus the £60,000k Tier 2 subordinated debt facility, both stated directly in each year's own Table 1. LCR and NSFR are genuinely undisclosed for FY2014-FY2016 (no LCR/HQLA/NSFR concept appears anywhere in those 3 documents, confirmed by reading each in full); FY2017's LCR ratio (167%) is not in FY2017's own document at all (confirmed absent) but appears as the FY2018 Pillar 3 document's own FY2017 comparative column, the earliest point any LCR figure for this bank exists - shown here with no £-breakdown since none is given for that comparative year. RWA breakdown by risk category (credit/market/operational/CVA) is genuinely undisclosed for FY2014-FY2018 (only the single aggregate RWA figure appears in each Table 1); the FY2020 Pillar 3 document introduces a full 'Table 9: Overview of risk weighted assets' (its own year plus its own FY2019 comparative column), the first and only such breakdown found across all 12 years covered.
+Entity note: Bank of China (UK) Limited (company 06193060, FRN 467410) is a wholly-owned UK subsidiary of Bank of China Limited (state-owned). It does not take the FRS 101/102 cash-flow-statement exemption - a full Statement of Cash Flows is published every year. All figures are the Bank's own solo entity basis throughout.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A6:M6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5282,7 +5485,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5942,7 +6145,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6199,7 +6402,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6440,7 +6643,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6663,212 +6866,6 @@
   <mergeCells count="2">
     <mergeCell ref="A7:I7"/>
     <mergeCell ref="A9:I9"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:M7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="15" customWidth="1" min="12" max="12"/>
-    <col width="15" customWidth="1" min="13" max="13"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Bank of China (UK) Limited — MREL Ratio</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>FY2020</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>FY2019</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>FY2018</t>
-        </is>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>FY2017</t>
-        </is>
-      </c>
-      <c r="K3" s="4" t="inlineStr">
-        <is>
-          <t>FY2016</t>
-        </is>
-      </c>
-      <c r="L3" s="4" t="inlineStr">
-        <is>
-          <t>FY2015</t>
-        </is>
-      </c>
-      <c r="M3" s="4" t="inlineStr">
-        <is>
-          <t>FY2014</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>MREL ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>Not published – BoC (UK) FY2025 Pillar 3 has no MREL figure, KM2 or eligible-liabilities disclosure (text probe 0 hits, 2026-09-19)</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>Not published – BoC (UK) FY2024 Pillar 3 has no MREL figure, KM2 or eligible-liabilities disclosure (text probe 0 hits, 2026-09-19)</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>Not published – BoC (UK) FY2023 Pillar 3 has no MREL figure, KM2 or eligible-liabilities disclosure (text probe 0 hits, 2026-09-19)</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>Not published – BoC (UK) FY2022 Pillar 3 has no MREL figure, KM2 or eligible-liabilities disclosure (text probe 0 hits, 2026-09-19)</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>Not published – BoC (UK) FY2021 Pillar 3 has no MREL figure, KM2 or eligible-liabilities disclosure (text probe 0 hits, 2026-09-19)</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>Not published – BoC (UK) FY2020 Pillar 3 has no MREL figure, KM2 or eligible-liabilities disclosure (text probe 0 hits, 2026-09-19)</t>
-        </is>
-      </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>Not published – BoC (UK) FY2019 Pillar 3 has no MREL figure, KM2 or eligible-liabilities disclosure (text probe 0 hits, 2026-09-19)</t>
-        </is>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>Not published – BoC (UK) FY2018 Pillar 3 has no MREL figure, KM2 or eligible-liabilities disclosure (text probe 0 hits, 2026-09-19)</t>
-        </is>
-      </c>
-      <c r="J4" s="6" t="inlineStr">
-        <is>
-          <t>Not published – BoC (UK) FY2017 Pillar 3 has no MREL figure, KM2 or eligible-liabilities disclosure (text probe 0 hits, 2026-09-19)</t>
-        </is>
-      </c>
-      <c r="K4" s="6" t="inlineStr">
-        <is>
-          <t>Not published – BoC (UK) FY2016 Pillar 3 has no MREL figure, KM2 or eligible-liabilities disclosure (text probe 0 hits, 2026-09-19)</t>
-        </is>
-      </c>
-      <c r="L4" s="6" t="inlineStr">
-        <is>
-          <t>Not published – BoC (UK) FY2015 Pillar 3 has no MREL figure, KM2 or eligible-liabilities disclosure (text probe 0 hits, 2026-09-19)</t>
-        </is>
-      </c>
-      <c r="M4" s="6" t="inlineStr">
-        <is>
-          <t>Not published – BoC (UK) FY2014 Pillar 3 has no MREL figure, KM2 or eligible-liabilities disclosure (text probe 0 hits, 2026-09-19)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Note: No MREL disclosure found in any of the 12 available Pillar 3 documents (FY2014-FY2025) - each was read in full (table of contents plus a full-text search for 'MREL') and none contains one. Re-checked 2026-09-19 (GA-020): all 12 editions re-downloaded (%PDF, text-native); 0 hits for 'MREL', 'KM2' and 'eligible liabilities' in each, against 93-223 'capital' hits; the only 'loss-absorbing' hits are the generic countercyclical-buffer description.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="299" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>Sources - Bank of China (UK) Limited Pillar 3 disclosures (UK KM1 Key Metrics template from FY2022 onward; FY2021's own document is narrative/ratio-only and predates the KM1 template; FY2014-FY2020 use the pre-KM1 CRD IV 'Table 1: Total capital resources and risk asset ratios' / 'Table 2: Leverage ratio' narrative-table format), £'000 unless stated:
-FY2025 &amp; FY2024 comparative: Pillar 3 Disclosure 31 December 2025, p.15 (UK KM1) - https://pic.bankofchina.com/bocappd/uk/202607/P020260716391457618567.pdf
-FY2024 (own year) &amp; FY2023 comparative: Pillar 3 Disclosures 31 December 2024, p.16 (UK KM1) - https://www.bankofchina.com/uk/aboutus/ab5/202507/P020250718380587744231.pdf
-FY2023 (own year) &amp; FY2022 comparative: Pillar 3 disclosures 31 December 2023, p.14 (UK KM1) - https://www.bankofchina.com/uk/aboutus/ab5/202410/P020241008402737321677.pdf
-FY2022 (own year) &amp; FY2021 comparative: Pillar 3 Disclosures 2022, p.14 (UK KM1) - https://www.bankofchina.com/uk/aboutus/ab5/202310/P020231026347190320350.pdf
-FY2021 (own year, narrative/ratio-only - no KM1 template yet): Pillar 3 Disclosures 2021, p.12-14, 24 - https://www.bankofchina.com/uk/aboutus/ab5/202303/P020230315381669571541.pdf
-FY2021 note: the Bank's own FY2021 Pillar 3 document states CET1/Total Capital as rounded £275m/£335m and gives no £-breakdown for leverage exposure, LCR HQLA/outflow, or NSFR (NSFR was not yet a formal disclosure). The precise FY2021 figures used on those sheets (CET1/Tier 1 £275,164k, Total Capital £335,164k, leverage exposure £2,431,869k, LCR HQLA £527,697k/outflow £294,774k, NSFR £1,438,026k/£950,742k) are taken from the FY2022 Pillar 3 document's FY2021 comparative column instead, since it is the more complete disclosure - all overlapping ratios (CET1 24.6%, Total Capital 29.9%, Leverage 11.3%, LCR 179.0%) match the FY2021 document's own narrative figures exactly.
-FY2020 (own year) &amp; FY2019 comparative: Pillar 3 Disclosures 31 December 2020, Table 9 'Overview of risk weighted assets', p.20-22, Table 31 'Liquidity coverage ratio' - https://pic.bankofchina.com/bocappd/uk/202110/P020211027537761891740.pdf
-FY2019 (own year) &amp; FY2018 comparative: Pillar 3 Disclosures 31 December 2019, p.16-19, 33 - https://pic.bankofchina.com/bocappd/uk/202009/P020200909535865685853.pdf
-FY2018 (own year) &amp; FY2017 comparative: Pillar 3 Disclosures 31 December 2018, p.15-18, 31 - https://pic.bankofchina.com/bocappd/uk/201904/P020190410408108385209.pdf
-FY2017 (own year) &amp; FY2016 comparative: Pillar 3 Disclosures 2017, Table 1/Table 2, p.9-10 - https://pic.bankofchina.com/bocappd/uk/201803/P020180328577372288229.pdf
-FY2016 (own year) &amp; FY2015 comparative: Pillar 3 Disclosures 2016, Table 1/Table 2, p.10-11 - https://pic.bankofchina.com/bocappd/uk/201706/P020170627381103226068.pdf
-FY2015 (own year) &amp; FY2014 comparative: Pillar III Disclosures 2015, Table 1/Table 2, p.9-10 - https://pic.bankofchina.com/bocappd/uk/201606/P020160620504436264971.pdf
-FY2014 (own year) &amp; FY2013 comparative: Pillar III Disclosure 2014, Table 1/Table 2, p.8-9 - https://pic.bankofchina.com/bocappd/uk/201509/P020150910375228515274.pdf
-FY2014-FY2017 note: 'Tier 1 capital' equals 'CET1 capital' every year (£274,958k throughout - the Bank issued no AT1 instruments until far later) and 'Total capital' equals CET1 capital plus the £60,000k Tier 2 subordinated debt facility, both stated directly in each year's own Table 1. LCR and NSFR are genuinely undisclosed for FY2014-FY2016 (no LCR/HQLA/NSFR concept appears anywhere in those 3 documents, confirmed by reading each in full); FY2017's LCR ratio (167%) is not in FY2017's own document at all (confirmed absent) but appears as the FY2018 Pillar 3 document's own FY2017 comparative column, the earliest point any LCR figure for this bank exists - shown here with no £-breakdown since none is given for that comparative year. RWA breakdown by risk category (credit/market/operational/CVA) is genuinely undisclosed for FY2014-FY2018 (only the single aggregate RWA figure appears in each Table 1); the FY2020 Pillar 3 document introduces a full 'Table 9: Overview of risk weighted assets' (its own year plus its own FY2019 comparative column), the first and only such breakdown found across all 12 years covered.
-Entity note: Bank of China (UK) Limited (company 06193060, FRN 467410) is a wholly-owned UK subsidiary of Bank of China Limited (state-owned). It does not take the FRS 101/102 cash-flow-statement exemption - a full Statement of Cash Flows is published every year. All figures are the Bank's own solo entity basis throughout.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A5:M5"/>
-    <mergeCell ref="A7:M7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8756,6 +8753,212 @@
   <mergeCells count="2">
     <mergeCell ref="A41:S41"/>
     <mergeCell ref="A39:S39"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Bank of China (UK) Limited — MREL Ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>FY2017</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>FY2016</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>FY2015</t>
+        </is>
+      </c>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>FY2014</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>MREL ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Not published – BoC (UK) FY2025 Pillar 3 has no MREL figure, KM2 or eligible-liabilities disclosure (text probe 0 hits, 2026-09-19)</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Not published – BoC (UK) FY2024 Pillar 3 has no MREL figure, KM2 or eligible-liabilities disclosure (text probe 0 hits, 2026-09-19)</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Not published – BoC (UK) FY2023 Pillar 3 has no MREL figure, KM2 or eligible-liabilities disclosure (text probe 0 hits, 2026-09-19)</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>Not published – BoC (UK) FY2022 Pillar 3 has no MREL figure, KM2 or eligible-liabilities disclosure (text probe 0 hits, 2026-09-19)</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Not published – BoC (UK) FY2021 Pillar 3 has no MREL figure, KM2 or eligible-liabilities disclosure (text probe 0 hits, 2026-09-19)</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>Not published – BoC (UK) FY2020 Pillar 3 has no MREL figure, KM2 or eligible-liabilities disclosure (text probe 0 hits, 2026-09-19)</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>Not published – BoC (UK) FY2019 Pillar 3 has no MREL figure, KM2 or eligible-liabilities disclosure (text probe 0 hits, 2026-09-19)</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>Not published – BoC (UK) FY2018 Pillar 3 has no MREL figure, KM2 or eligible-liabilities disclosure (text probe 0 hits, 2026-09-19)</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>Not published – BoC (UK) FY2017 Pillar 3 has no MREL figure, KM2 or eligible-liabilities disclosure (text probe 0 hits, 2026-09-19)</t>
+        </is>
+      </c>
+      <c r="K4" s="6" t="inlineStr">
+        <is>
+          <t>Not published – BoC (UK) FY2016 Pillar 3 has no MREL figure, KM2 or eligible-liabilities disclosure (text probe 0 hits, 2026-09-19)</t>
+        </is>
+      </c>
+      <c r="L4" s="6" t="inlineStr">
+        <is>
+          <t>Not published – BoC (UK) FY2015 Pillar 3 has no MREL figure, KM2 or eligible-liabilities disclosure (text probe 0 hits, 2026-09-19)</t>
+        </is>
+      </c>
+      <c r="M4" s="6" t="inlineStr">
+        <is>
+          <t>Not published – BoC (UK) FY2014 Pillar 3 has no MREL figure, KM2 or eligible-liabilities disclosure (text probe 0 hits, 2026-09-19)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Note: No MREL disclosure found in any of the 12 available Pillar 3 documents (FY2014-FY2025) - each was read in full (table of contents plus a full-text search for 'MREL') and none contains one. Re-checked 2026-09-19 (GA-020): all 12 editions re-downloaded (%PDF, text-native); 0 hits for 'MREL', 'KM2' and 'eligible liabilities' in each, against 93-223 'capital' hits; the only 'loss-absorbing' hits are the generic countercyclical-buffer description.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="299" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>Sources - Bank of China (UK) Limited Pillar 3 disclosures (UK KM1 Key Metrics template from FY2022 onward; FY2021's own document is narrative/ratio-only and predates the KM1 template; FY2014-FY2020 use the pre-KM1 CRD IV 'Table 1: Total capital resources and risk asset ratios' / 'Table 2: Leverage ratio' narrative-table format), £'000 unless stated:
+FY2025 &amp; FY2024 comparative: Pillar 3 Disclosure 31 December 2025, p.15 (UK KM1) - https://pic.bankofchina.com/bocappd/uk/202607/P020260716391457618567.pdf
+FY2024 (own year) &amp; FY2023 comparative: Pillar 3 Disclosures 31 December 2024, p.16 (UK KM1) - https://www.bankofchina.com/uk/aboutus/ab5/202507/P020250718380587744231.pdf
+FY2023 (own year) &amp; FY2022 comparative: Pillar 3 disclosures 31 December 2023, p.14 (UK KM1) - https://www.bankofchina.com/uk/aboutus/ab5/202410/P020241008402737321677.pdf
+FY2022 (own year) &amp; FY2021 comparative: Pillar 3 Disclosures 2022, p.14 (UK KM1) - https://www.bankofchina.com/uk/aboutus/ab5/202310/P020231026347190320350.pdf
+FY2021 (own year, narrative/ratio-only - no KM1 template yet): Pillar 3 Disclosures 2021, p.12-14, 24 - https://www.bankofchina.com/uk/aboutus/ab5/202303/P020230315381669571541.pdf
+FY2021 note: the Bank's own FY2021 Pillar 3 document states CET1/Total Capital as rounded £275m/£335m and gives no £-breakdown for leverage exposure, LCR HQLA/outflow, or NSFR (NSFR was not yet a formal disclosure). The precise FY2021 figures used on those sheets (CET1/Tier 1 £275,164k, Total Capital £335,164k, leverage exposure £2,431,869k, LCR HQLA £527,697k/outflow £294,774k, NSFR £1,438,026k/£950,742k) are taken from the FY2022 Pillar 3 document's FY2021 comparative column instead, since it is the more complete disclosure - all overlapping ratios (CET1 24.6%, Total Capital 29.9%, Leverage 11.3%, LCR 179.0%) match the FY2021 document's own narrative figures exactly.
+FY2020 (own year) &amp; FY2019 comparative: Pillar 3 Disclosures 31 December 2020, Table 9 'Overview of risk weighted assets', p.20-22, Table 31 'Liquidity coverage ratio' - https://pic.bankofchina.com/bocappd/uk/202110/P020211027537761891740.pdf
+FY2019 (own year) &amp; FY2018 comparative: Pillar 3 Disclosures 31 December 2019, p.16-19, 33 - https://pic.bankofchina.com/bocappd/uk/202009/P020200909535865685853.pdf
+FY2018 (own year) &amp; FY2017 comparative: Pillar 3 Disclosures 31 December 2018, p.15-18, 31 - https://pic.bankofchina.com/bocappd/uk/201904/P020190410408108385209.pdf
+FY2017 (own year) &amp; FY2016 comparative: Pillar 3 Disclosures 2017, Table 1/Table 2, p.9-10 - https://pic.bankofchina.com/bocappd/uk/201803/P020180328577372288229.pdf
+FY2016 (own year) &amp; FY2015 comparative: Pillar 3 Disclosures 2016, Table 1/Table 2, p.10-11 - https://pic.bankofchina.com/bocappd/uk/201706/P020170627381103226068.pdf
+FY2015 (own year) &amp; FY2014 comparative: Pillar III Disclosures 2015, Table 1/Table 2, p.9-10 - https://pic.bankofchina.com/bocappd/uk/201606/P020160620504436264971.pdf
+FY2014 (own year) &amp; FY2013 comparative: Pillar III Disclosure 2014, Table 1/Table 2, p.8-9 - https://pic.bankofchina.com/bocappd/uk/201509/P020150910375228515274.pdf
+FY2014-FY2017 note: 'Tier 1 capital' equals 'CET1 capital' every year (£274,958k throughout - the Bank issued no AT1 instruments until far later) and 'Total capital' equals CET1 capital plus the £60,000k Tier 2 subordinated debt facility, both stated directly in each year's own Table 1. LCR and NSFR are genuinely undisclosed for FY2014-FY2016 (no LCR/HQLA/NSFR concept appears anywhere in those 3 documents, confirmed by reading each in full); FY2017's LCR ratio (167%) is not in FY2017's own document at all (confirmed absent) but appears as the FY2018 Pillar 3 document's own FY2017 comparative column, the earliest point any LCR figure for this bank exists - shown here with no £-breakdown since none is given for that comparative year. RWA breakdown by risk category (credit/market/operational/CVA) is genuinely undisclosed for FY2014-FY2018 (only the single aggregate RWA figure appears in each Table 1); the FY2020 Pillar 3 document introduces a full 'Table 9: Overview of risk weighted assets' (its own year plus its own FY2019 comparative column), the first and only such breakdown found across all 12 years covered.
+Entity note: Bank of China (UK) Limited (company 06193060, FRN 467410) is a wholly-owned UK subsidiary of Bank of China Limited (state-owned). It does not take the FRS 101/102 cash-flow-statement exemption - a full Statement of Cash Flows is published every year. All figures are the Bank's own solo entity basis throughout.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A5:M5"/>
+    <mergeCell ref="A7:M7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -16797,6 +17000,464 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:M11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="51" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Bank of China (UK) Limited — Profitability</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Return on equity and return on assets in per cent, computed from this workbook's own Balance Sheet and Profit &amp; Loss sheets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>FY2020</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>FY2019</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>FY2018</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>FY2017</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>FY2016</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>FY2015</t>
+        </is>
+      </c>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>FY2014</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Return on equity - average equity basis</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>16.96%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>19.81%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>24.72%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>19.35%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>9.70%</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>10.83%</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>10.14%</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>16.15%</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>10.39%</t>
+        </is>
+      </c>
+      <c r="K4" s="6" t="inlineStr">
+        <is>
+          <t>11.32%</t>
+        </is>
+      </c>
+      <c r="L4" s="6" t="inlineStr">
+        <is>
+          <t>14.62%</t>
+        </is>
+      </c>
+      <c r="M4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Return on equity - year-end equity basis</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>17.28%</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>20.28%</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>23.82%</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>17.06%</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>10.26%</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>10.28%</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>10.46%</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>15.68%</t>
+        </is>
+      </c>
+      <c r="J5" s="6" t="inlineStr">
+        <is>
+          <t>10.44%</t>
+        </is>
+      </c>
+      <c r="K5" s="6" t="inlineStr">
+        <is>
+          <t>11.50%</t>
+        </is>
+      </c>
+      <c r="L5" s="6" t="inlineStr">
+        <is>
+          <t>14.19%</t>
+        </is>
+      </c>
+      <c r="M5" s="6" t="inlineStr">
+        <is>
+          <t>8.61%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Return on assets - average assets basis</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>3.00%</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>3.81%</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>4.72%</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>3.09%</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>1.54%</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>1.94%</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>1.93%</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>3.23%</t>
+        </is>
+      </c>
+      <c r="J6" s="6" t="inlineStr">
+        <is>
+          <t>2.08%</t>
+        </is>
+      </c>
+      <c r="K6" s="6" t="inlineStr">
+        <is>
+          <t>2.51%</t>
+        </is>
+      </c>
+      <c r="L6" s="6" t="inlineStr">
+        <is>
+          <t>3.63%</t>
+        </is>
+      </c>
+      <c r="M6" s="6" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Return on assets - year-end assets basis</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>3.03%</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>3.61%</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>4.96%</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>2.99%</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>1.46%</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>1.81%</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>1.90%</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>3.13%</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>2.08%</t>
+        </is>
+      </c>
+      <c r="K7" s="6" t="inlineStr">
+        <is>
+          <t>2.30%</t>
+        </is>
+      </c>
+      <c r="L7" s="6" t="inlineStr">
+        <is>
+          <t>3.52%</t>
+        </is>
+      </c>
+      <c r="M7" s="6" t="inlineStr">
+        <is>
+          <t>2.14%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Bank of China (UK) Limited's own published return</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="K8" s="6" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="L8" s="6" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="M8" s="6" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="117" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>Note: COMPUTED, NOT PUBLISHED. The bank's official 122-page FY2024 own-entity annual report publishes total assets, total operating income, profit before tax and profit after tax in its CEO statement and Strategic Business Review, but no ROE, ROA or RoTE. Whole-document searches for return-on-equity/assets variants found no relevant profitability-return measure, and both principal financial-performance pages were rendered and visually read at 300 dpi. Every percentage above is therefore this project's own arithmetic on the figures printed on this workbook's statement sheets, and is labelled as such. That the bank publishes none is a POSITIVE FINDING, recorded in research/profitability/published_returns.jsonl, and not a failed search: for this bank the computed figure is the only figure there is.
+WHY TWO BASES ARE PRINTED FOR EACH RATIO, AND NEITHER IS PREFERRED. The average basis divides by the mean of the opening and closing balance and is the fairer measure of a year in which the balance sheet moved a long way; the year-end basis divides by the closing balance alone and is what most outside sources quote. Both are shown so the reader can see which question a figure answers. They are not averaged and neither is 'the' return. The two diverge most in FY2022, where return on equity is 19.35% on an average basis and 17.06% on a year-end basis.
+FY2014 HAS NO AVERAGE-BASIS RATIO, AND THAT IS CORRECT. An average denominator needs an opening balance, and FY2014 is the oldest column this workbook carries, so there is no prior year to open from. The blank is structural, not a missing figure. The year-end basis is shown for FY2014 because it needs only the closing balance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="170" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>Computed by this workbook's own build script from the Profit &amp; Loss and Balance Sheet sheets of this same workbook - the Profit &amp; Loss row “profit/(loss) for the year” and the Balance Sheet rows “total shareholders' equity” and “total assets”, resolved BY LABEL at build time through the shared resolver scripts/profitability_rows.py, so this sheet cannot drift from the statements it summarises. Those rows are themselves transcribed from Bank of China (UK) Limited's Annual Report and Accounts for each year; see the source cells on the Balance Sheet and Profit &amp; Loss sheets for the exact document, page and table behind every input to every percentage above.
+The finding that Bank of China (UK) Limited publishes no return of its own is recorded in research/profitability/published_returns.jsonl under ‘BANK OF CHINA UK’, verified against the bank's own annual report rendered at 300 dpi.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A11:M11"/>
+    <mergeCell ref="A9:M9"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -17529,184 +18190,6 @@
   <mergeCells count="2">
     <mergeCell ref="A34:F34"/>
     <mergeCell ref="A32:F32"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="15" customWidth="1" min="12" max="12"/>
-    <col width="15" customWidth="1" min="13" max="13"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Bank of China (UK) Limited — CET1 Capital</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>£'000</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>FY2020</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>FY2019</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>FY2018</t>
-        </is>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>FY2017</t>
-        </is>
-      </c>
-      <c r="K3" s="4" t="inlineStr">
-        <is>
-          <t>FY2016</t>
-        </is>
-      </c>
-      <c r="L3" s="4" t="inlineStr">
-        <is>
-          <t>FY2015</t>
-        </is>
-      </c>
-      <c r="M3" s="4" t="inlineStr">
-        <is>
-          <t>FY2014</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Common Equity Tier 1 (CET1) capital</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>274521</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>274294</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>275056</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>275000</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>275164</v>
-      </c>
-      <c r="G4" s="6" t="n">
-        <v>307058</v>
-      </c>
-      <c r="H4" s="6" t="n">
-        <v>274958</v>
-      </c>
-      <c r="I4" s="6" t="n">
-        <v>274958</v>
-      </c>
-      <c r="J4" s="6" t="n">
-        <v>274958</v>
-      </c>
-      <c r="K4" s="6" t="n">
-        <v>274958</v>
-      </c>
-      <c r="L4" s="6" t="n">
-        <v>274958</v>
-      </c>
-      <c r="M4" s="6" t="n">
-        <v>274958</v>
-      </c>
-    </row>
-    <row r="6" ht="299" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>Sources - Bank of China (UK) Limited Pillar 3 disclosures (UK KM1 Key Metrics template from FY2022 onward; FY2021's own document is narrative/ratio-only and predates the KM1 template; FY2014-FY2020 use the pre-KM1 CRD IV 'Table 1: Total capital resources and risk asset ratios' / 'Table 2: Leverage ratio' narrative-table format), £'000 unless stated:
-FY2025 &amp; FY2024 comparative: Pillar 3 Disclosure 31 December 2025, p.15 (UK KM1) - https://pic.bankofchina.com/bocappd/uk/202607/P020260716391457618567.pdf
-FY2024 (own year) &amp; FY2023 comparative: Pillar 3 Disclosures 31 December 2024, p.16 (UK KM1) - https://www.bankofchina.com/uk/aboutus/ab5/202507/P020250718380587744231.pdf
-FY2023 (own year) &amp; FY2022 comparative: Pillar 3 disclosures 31 December 2023, p.14 (UK KM1) - https://www.bankofchina.com/uk/aboutus/ab5/202410/P020241008402737321677.pdf
-FY2022 (own year) &amp; FY2021 comparative: Pillar 3 Disclosures 2022, p.14 (UK KM1) - https://www.bankofchina.com/uk/aboutus/ab5/202310/P020231026347190320350.pdf
-FY2021 (own year, narrative/ratio-only - no KM1 template yet): Pillar 3 Disclosures 2021, p.12-14, 24 - https://www.bankofchina.com/uk/aboutus/ab5/202303/P020230315381669571541.pdf
-FY2021 note: the Bank's own FY2021 Pillar 3 document states CET1/Total Capital as rounded £275m/£335m and gives no £-breakdown for leverage exposure, LCR HQLA/outflow, or NSFR (NSFR was not yet a formal disclosure). The precise FY2021 figures used on those sheets (CET1/Tier 1 £275,164k, Total Capital £335,164k, leverage exposure £2,431,869k, LCR HQLA £527,697k/outflow £294,774k, NSFR £1,438,026k/£950,742k) are taken from the FY2022 Pillar 3 document's FY2021 comparative column instead, since it is the more complete disclosure - all overlapping ratios (CET1 24.6%, Total Capital 29.9%, Leverage 11.3%, LCR 179.0%) match the FY2021 document's own narrative figures exactly.
-FY2020 (own year) &amp; FY2019 comparative: Pillar 3 Disclosures 31 December 2020, Table 9 'Overview of risk weighted assets', p.20-22, Table 31 'Liquidity coverage ratio' - https://pic.bankofchina.com/bocappd/uk/202110/P020211027537761891740.pdf
-FY2019 (own year) &amp; FY2018 comparative: Pillar 3 Disclosures 31 December 2019, p.16-19, 33 - https://pic.bankofchina.com/bocappd/uk/202009/P020200909535865685853.pdf
-FY2018 (own year) &amp; FY2017 comparative: Pillar 3 Disclosures 31 December 2018, p.15-18, 31 - https://pic.bankofchina.com/bocappd/uk/201904/P020190410408108385209.pdf
-FY2017 (own year) &amp; FY2016 comparative: Pillar 3 Disclosures 2017, Table 1/Table 2, p.9-10 - https://pic.bankofchina.com/bocappd/uk/201803/P020180328577372288229.pdf
-FY2016 (own year) &amp; FY2015 comparative: Pillar 3 Disclosures 2016, Table 1/Table 2, p.10-11 - https://pic.bankofchina.com/bocappd/uk/201706/P020170627381103226068.pdf
-FY2015 (own year) &amp; FY2014 comparative: Pillar III Disclosures 2015, Table 1/Table 2, p.9-10 - https://pic.bankofchina.com/bocappd/uk/201606/P020160620504436264971.pdf
-FY2014 (own year) &amp; FY2013 comparative: Pillar III Disclosure 2014, Table 1/Table 2, p.8-9 - https://pic.bankofchina.com/bocappd/uk/201509/P020150910375228515274.pdf
-FY2014-FY2017 note: 'Tier 1 capital' equals 'CET1 capital' every year (£274,958k throughout - the Bank issued no AT1 instruments until far later) and 'Total capital' equals CET1 capital plus the £60,000k Tier 2 subordinated debt facility, both stated directly in each year's own Table 1. LCR and NSFR are genuinely undisclosed for FY2014-FY2016 (no LCR/HQLA/NSFR concept appears anywhere in those 3 documents, confirmed by reading each in full); FY2017's LCR ratio (167%) is not in FY2017's own document at all (confirmed absent) but appears as the FY2018 Pillar 3 document's own FY2017 comparative column, the earliest point any LCR figure for this bank exists - shown here with no £-breakdown since none is given for that comparative year. RWA breakdown by risk category (credit/market/operational/CVA) is genuinely undisclosed for FY2014-FY2018 (only the single aggregate RWA figure appears in each Table 1); the FY2020 Pillar 3 document introduces a full 'Table 9: Overview of risk weighted assets' (its own year plus its own FY2019 comparative column), the first and only such breakdown found across all 12 years covered.
-Entity note: Bank of China (UK) Limited (company 06193060, FRN 467410) is a wholly-owned UK subsidiary of Bank of China Limited (state-owned). It does not take the FRS 101/102 cash-flow-statement exemption - a full Statement of Cash Flows is published every year. All figures are the Bank's own solo entity basis throughout.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A6:M6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -17739,14 +18222,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Bank of China (UK) Limited — CET1 Ratio</t>
+          <t>Bank of China (UK) Limited — CET1 Capital</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>% of RWA</t>
+          <t>£'000</t>
         </is>
       </c>
     </row>
@@ -17820,68 +18303,44 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Common Equity Tier 1 ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>27.2%</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>24.8%</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>26.8%</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>23.4%</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>24.6%</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>26.7%</t>
-        </is>
-      </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>27.8%</t>
-        </is>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>29.2%</t>
-        </is>
-      </c>
-      <c r="J4" s="6" t="inlineStr">
-        <is>
-          <t>30%</t>
-        </is>
-      </c>
-      <c r="K4" s="6" t="inlineStr">
-        <is>
-          <t>27%</t>
-        </is>
-      </c>
-      <c r="L4" s="6" t="inlineStr">
-        <is>
-          <t>31%</t>
-        </is>
-      </c>
-      <c r="M4" s="6" t="inlineStr">
-        <is>
-          <t>34%</t>
-        </is>
+          <t>Common Equity Tier 1 (CET1) capital</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>274521</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>274294</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>275056</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>275000</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>275164</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>307058</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>274958</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>274958</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>274958</v>
+      </c>
+      <c r="K4" s="6" t="n">
+        <v>274958</v>
+      </c>
+      <c r="L4" s="6" t="n">
+        <v>274958</v>
+      </c>
+      <c r="M4" s="6" t="n">
+        <v>274958</v>
       </c>
     </row>
     <row r="6" ht="299" customHeight="1">
